--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123699068</v>
+        <v>123699047</v>
       </c>
       <c r="B2" t="n">
-        <v>78775</v>
+        <v>79766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>855190</v>
+        <v>854770</v>
       </c>
       <c r="R2" t="n">
-        <v>7477967</v>
+        <v>7477947</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123699063</v>
+        <v>123699074</v>
       </c>
       <c r="B3" t="n">
-        <v>90984</v>
+        <v>82568</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>855109</v>
+        <v>855205</v>
       </c>
       <c r="R3" t="n">
-        <v>7478143</v>
+        <v>7477980</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123699071</v>
+        <v>123699086</v>
       </c>
       <c r="B4" t="n">
-        <v>82562</v>
+        <v>79797</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6457</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>855073</v>
+        <v>854738</v>
       </c>
       <c r="R4" t="n">
-        <v>7478043</v>
+        <v>7477969</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123699041</v>
+        <v>123699069</v>
       </c>
       <c r="B5" t="n">
-        <v>56683</v>
+        <v>78781</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>854968</v>
+        <v>855047</v>
       </c>
       <c r="R5" t="n">
-        <v>7478151</v>
+        <v>7478172</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1057,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123699058</v>
+        <v>123699059</v>
       </c>
       <c r="B6" t="n">
-        <v>56683</v>
+        <v>90979</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>855091</v>
+        <v>855112</v>
       </c>
       <c r="R6" t="n">
-        <v>7478072</v>
+        <v>7478087</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1164,11 +1159,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123699050</v>
+        <v>123699058</v>
       </c>
       <c r="B7" t="n">
-        <v>79892</v>
+        <v>56689</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>855140</v>
+        <v>855091</v>
       </c>
       <c r="R7" t="n">
-        <v>7478022</v>
+        <v>7478072</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1271,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123699046</v>
+        <v>123699042</v>
       </c>
       <c r="B8" t="n">
-        <v>79760</v>
+        <v>79863</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>855119</v>
+        <v>855063</v>
       </c>
       <c r="R8" t="n">
-        <v>7478027</v>
+        <v>7478073</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1399,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123699059</v>
+        <v>123699082</v>
       </c>
       <c r="B9" t="n">
-        <v>90962</v>
+        <v>79797</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6457</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>855112</v>
+        <v>855140</v>
       </c>
       <c r="R9" t="n">
-        <v>7478087</v>
+        <v>7478068</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1501,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123699072</v>
+        <v>123699077</v>
       </c>
       <c r="B10" t="n">
-        <v>82562</v>
+        <v>82568</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>855123</v>
+        <v>855121</v>
       </c>
       <c r="R10" t="n">
-        <v>7478116</v>
+        <v>7478158</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1603,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123699048</v>
+        <v>123699070</v>
       </c>
       <c r="B11" t="n">
-        <v>79892</v>
+        <v>82568</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>855062</v>
+        <v>855114</v>
       </c>
       <c r="R11" t="n">
-        <v>7478067</v>
+        <v>7478219</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1705,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123699070</v>
+        <v>123699071</v>
       </c>
       <c r="B12" t="n">
-        <v>82562</v>
+        <v>82568</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1745,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>855114</v>
+        <v>855073</v>
       </c>
       <c r="R12" t="n">
-        <v>7478219</v>
+        <v>7478043</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1807,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123699082</v>
+        <v>123699051</v>
       </c>
       <c r="B13" t="n">
-        <v>79791</v>
+        <v>79898</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6457</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>855140</v>
+        <v>854961</v>
       </c>
       <c r="R13" t="n">
-        <v>7478068</v>
+        <v>7478150</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1909,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123699083</v>
+        <v>123699045</v>
       </c>
       <c r="B14" t="n">
-        <v>79791</v>
+        <v>79766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6457</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>855119</v>
+        <v>855058</v>
       </c>
       <c r="R14" t="n">
-        <v>7478027</v>
+        <v>7478025</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2011,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123699045</v>
+        <v>123699090</v>
       </c>
       <c r="B15" t="n">
-        <v>79760</v>
+        <v>79897</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>855058</v>
+        <v>854901</v>
       </c>
       <c r="R15" t="n">
-        <v>7478025</v>
+        <v>7478143</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2113,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123699086</v>
+        <v>123699050</v>
       </c>
       <c r="B16" t="n">
-        <v>79791</v>
+        <v>79898</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6457</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>854738</v>
+        <v>855140</v>
       </c>
       <c r="R16" t="n">
-        <v>7477969</v>
+        <v>7478022</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2215,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123699060</v>
+        <v>123699064</v>
       </c>
       <c r="B17" t="n">
-        <v>90962</v>
+        <v>91001</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>855099</v>
+        <v>855084</v>
       </c>
       <c r="R17" t="n">
-        <v>7478014</v>
+        <v>7478212</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2317,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123699074</v>
+        <v>123699046</v>
       </c>
       <c r="B18" t="n">
-        <v>82562</v>
+        <v>79766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2329,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>855205</v>
+        <v>855119</v>
       </c>
       <c r="R18" t="n">
-        <v>7477980</v>
+        <v>7478027</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2419,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123699073</v>
+        <v>123699044</v>
       </c>
       <c r="B19" t="n">
-        <v>82562</v>
+        <v>79766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2431,25 +2426,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>855119</v>
+        <v>854836</v>
       </c>
       <c r="R19" t="n">
-        <v>7477995</v>
+        <v>7478088</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2497,12 +2492,18 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På  grov asp, 180 cm i omkrets.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2521,10 +2522,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123699065</v>
+        <v>123699067</v>
       </c>
       <c r="B20" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2561,10 +2562,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>855061</v>
+        <v>855198</v>
       </c>
       <c r="R20" t="n">
-        <v>7478034</v>
+        <v>7477984</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2623,10 +2624,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123699049</v>
+        <v>123699084</v>
       </c>
       <c r="B21" t="n">
-        <v>79892</v>
+        <v>79797</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2639,21 +2640,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>6457</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2664,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>855147</v>
+        <v>855181</v>
       </c>
       <c r="R21" t="n">
-        <v>7477980</v>
+        <v>7478022</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2725,10 +2726,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123699066</v>
+        <v>123699089</v>
       </c>
       <c r="B22" t="n">
-        <v>78775</v>
+        <v>79897</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2737,20 +2738,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2765,10 +2766,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>855081</v>
+        <v>855063</v>
       </c>
       <c r="R22" t="n">
-        <v>7478053</v>
+        <v>7478073</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2827,10 +2828,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123699064</v>
+        <v>123699083</v>
       </c>
       <c r="B23" t="n">
-        <v>90984</v>
+        <v>79797</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2839,25 +2840,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6457</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2868,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>855084</v>
+        <v>855119</v>
       </c>
       <c r="R23" t="n">
-        <v>7478212</v>
+        <v>7478027</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2929,10 +2930,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123699090</v>
+        <v>123699041</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>56689</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2941,25 +2942,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>102612</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2969,10 +2970,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>854901</v>
+        <v>854968</v>
       </c>
       <c r="R24" t="n">
-        <v>7478143</v>
+        <v>7478151</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3005,6 +3006,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3031,10 +3037,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123699044</v>
+        <v>123699060</v>
       </c>
       <c r="B25" t="n">
-        <v>79760</v>
+        <v>90979</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3043,25 +3049,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3077,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>854836</v>
+        <v>855099</v>
       </c>
       <c r="R25" t="n">
-        <v>7478088</v>
+        <v>7478014</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3109,18 +3115,12 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På  grov asp, 180 cm i omkrets.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123699084</v>
+        <v>123699066</v>
       </c>
       <c r="B26" t="n">
-        <v>79791</v>
+        <v>78781</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3151,25 +3151,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>855181</v>
+        <v>855081</v>
       </c>
       <c r="R26" t="n">
-        <v>7478022</v>
+        <v>7478053</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3241,10 +3241,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123699069</v>
+        <v>123699087</v>
       </c>
       <c r="B27" t="n">
-        <v>78775</v>
+        <v>79797</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3253,25 +3253,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>855047</v>
+        <v>854993</v>
       </c>
       <c r="R27" t="n">
-        <v>7478172</v>
+        <v>7478183</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3343,10 +3343,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123699077</v>
+        <v>123699049</v>
       </c>
       <c r="B28" t="n">
-        <v>82562</v>
+        <v>79898</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3355,25 +3355,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>855121</v>
+        <v>855147</v>
       </c>
       <c r="R28" t="n">
-        <v>7478158</v>
+        <v>7477980</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3445,10 +3445,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123699089</v>
+        <v>123699073</v>
       </c>
       <c r="B29" t="n">
-        <v>79891</v>
+        <v>82568</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3457,25 +3457,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>855063</v>
+        <v>855119</v>
       </c>
       <c r="R29" t="n">
-        <v>7478073</v>
+        <v>7477995</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3547,10 +3547,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123699047</v>
+        <v>123699063</v>
       </c>
       <c r="B30" t="n">
-        <v>79760</v>
+        <v>91001</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3559,25 +3559,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>854770</v>
+        <v>855109</v>
       </c>
       <c r="R30" t="n">
-        <v>7477947</v>
+        <v>7478143</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3649,10 +3649,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123699067</v>
+        <v>123699065</v>
       </c>
       <c r="B31" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>855198</v>
+        <v>855061</v>
       </c>
       <c r="R31" t="n">
-        <v>7477984</v>
+        <v>7478034</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3751,10 +3751,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123699040</v>
+        <v>123699048</v>
       </c>
       <c r="B32" t="n">
-        <v>90966</v>
+        <v>79898</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3763,25 +3763,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>855106</v>
+        <v>855062</v>
       </c>
       <c r="R32" t="n">
-        <v>7478141</v>
+        <v>7478067</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3853,10 +3853,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123699042</v>
+        <v>123699068</v>
       </c>
       <c r="B33" t="n">
-        <v>79857</v>
+        <v>78781</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3869,21 +3869,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>855063</v>
+        <v>855190</v>
       </c>
       <c r="R33" t="n">
-        <v>7478073</v>
+        <v>7477967</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3955,10 +3955,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123699087</v>
+        <v>123699072</v>
       </c>
       <c r="B34" t="n">
-        <v>79791</v>
+        <v>82568</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3967,25 +3967,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6457</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>854993</v>
+        <v>855123</v>
       </c>
       <c r="R34" t="n">
-        <v>7478183</v>
+        <v>7478116</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4057,10 +4057,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123699051</v>
+        <v>123699040</v>
       </c>
       <c r="B35" t="n">
-        <v>79892</v>
+        <v>90983</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4069,25 +4069,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4097,10 +4097,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>854961</v>
+        <v>855106</v>
       </c>
       <c r="R35" t="n">
-        <v>7478150</v>
+        <v>7478141</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123699047</v>
+        <v>123699074</v>
       </c>
       <c r="B2" t="n">
-        <v>79766</v>
+        <v>82568</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>854770</v>
+        <v>855205</v>
       </c>
       <c r="R2" t="n">
-        <v>7477947</v>
+        <v>7477980</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123699074</v>
+        <v>123699047</v>
       </c>
       <c r="B3" t="n">
-        <v>82568</v>
+        <v>79766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>855205</v>
+        <v>854770</v>
       </c>
       <c r="R3" t="n">
-        <v>7477980</v>
+        <v>7477947</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123699064</v>
+        <v>123699046</v>
       </c>
       <c r="B17" t="n">
-        <v>91001</v>
+        <v>79766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,25 +2222,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>855084</v>
+        <v>855119</v>
       </c>
       <c r="R17" t="n">
-        <v>7478212</v>
+        <v>7478027</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,7 +2312,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123699046</v>
+        <v>123699044</v>
       </c>
       <c r="B18" t="n">
         <v>79766</v>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>855119</v>
+        <v>854836</v>
       </c>
       <c r="R18" t="n">
-        <v>7478027</v>
+        <v>7478088</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2390,12 +2390,18 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På  grov asp, 180 cm i omkrets.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2414,10 +2420,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123699044</v>
+        <v>123699064</v>
       </c>
       <c r="B19" t="n">
-        <v>79766</v>
+        <v>91001</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2426,25 +2432,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2460,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>854836</v>
+        <v>855084</v>
       </c>
       <c r="R19" t="n">
-        <v>7478088</v>
+        <v>7478212</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2492,18 +2498,12 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På  grov asp, 180 cm i omkrets.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3037,10 +3037,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123699060</v>
+        <v>123699087</v>
       </c>
       <c r="B25" t="n">
-        <v>90979</v>
+        <v>79797</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3049,25 +3049,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>6457</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>855099</v>
+        <v>854993</v>
       </c>
       <c r="R25" t="n">
-        <v>7478014</v>
+        <v>7478183</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3241,10 +3241,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123699087</v>
+        <v>123699060</v>
       </c>
       <c r="B27" t="n">
-        <v>79797</v>
+        <v>90979</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3253,25 +3253,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6457</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>854993</v>
+        <v>855099</v>
       </c>
       <c r="R27" t="n">
-        <v>7478183</v>
+        <v>7478014</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123699074</v>
+        <v>123699047</v>
       </c>
       <c r="B2" t="n">
-        <v>82568</v>
+        <v>79766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>855205</v>
+        <v>854770</v>
       </c>
       <c r="R2" t="n">
-        <v>7477980</v>
+        <v>7477947</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123699047</v>
+        <v>123699074</v>
       </c>
       <c r="B3" t="n">
-        <v>79766</v>
+        <v>82568</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>854770</v>
+        <v>855205</v>
       </c>
       <c r="R3" t="n">
-        <v>7477947</v>
+        <v>7477980</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123699046</v>
+        <v>123699064</v>
       </c>
       <c r="B17" t="n">
-        <v>79766</v>
+        <v>91001</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,25 +2222,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>855119</v>
+        <v>855084</v>
       </c>
       <c r="R17" t="n">
-        <v>7478027</v>
+        <v>7478212</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,7 +2312,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123699044</v>
+        <v>123699046</v>
       </c>
       <c r="B18" t="n">
         <v>79766</v>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>854836</v>
+        <v>855119</v>
       </c>
       <c r="R18" t="n">
-        <v>7478088</v>
+        <v>7478027</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2390,18 +2390,12 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På  grov asp, 180 cm i omkrets.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2420,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123699064</v>
+        <v>123699044</v>
       </c>
       <c r="B19" t="n">
-        <v>91001</v>
+        <v>79766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2432,25 +2426,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2460,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>855084</v>
+        <v>854836</v>
       </c>
       <c r="R19" t="n">
-        <v>7478212</v>
+        <v>7478088</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2498,12 +2492,18 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På  grov asp, 180 cm i omkrets.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3037,10 +3037,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123699087</v>
+        <v>123699060</v>
       </c>
       <c r="B25" t="n">
-        <v>79797</v>
+        <v>90979</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3049,25 +3049,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6457</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>854993</v>
+        <v>855099</v>
       </c>
       <c r="R25" t="n">
-        <v>7478183</v>
+        <v>7478014</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3241,10 +3241,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123699060</v>
+        <v>123699087</v>
       </c>
       <c r="B27" t="n">
-        <v>90979</v>
+        <v>79797</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3253,25 +3253,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>6457</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>855099</v>
+        <v>854993</v>
       </c>
       <c r="R27" t="n">
-        <v>7478014</v>
+        <v>7478183</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123699047</v>
+        <v>123699074</v>
       </c>
       <c r="B2" t="n">
-        <v>79766</v>
+        <v>82568</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>854770</v>
+        <v>855205</v>
       </c>
       <c r="R2" t="n">
-        <v>7477947</v>
+        <v>7477980</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123699074</v>
+        <v>123699047</v>
       </c>
       <c r="B3" t="n">
-        <v>82568</v>
+        <v>79766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>855205</v>
+        <v>854770</v>
       </c>
       <c r="R3" t="n">
-        <v>7477980</v>
+        <v>7477947</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -3037,10 +3037,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123699060</v>
+        <v>123699066</v>
       </c>
       <c r="B25" t="n">
-        <v>90979</v>
+        <v>78781</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3053,21 +3053,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>855099</v>
+        <v>855081</v>
       </c>
       <c r="R25" t="n">
-        <v>7478014</v>
+        <v>7478053</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123699066</v>
+        <v>123699060</v>
       </c>
       <c r="B26" t="n">
-        <v>78781</v>
+        <v>90979</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>855081</v>
+        <v>855099</v>
       </c>
       <c r="R26" t="n">
-        <v>7478053</v>
+        <v>7478014</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123699074</v>
+        <v>123699071</v>
       </c>
       <c r="B2" t="n">
-        <v>82568</v>
+        <v>82573</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>855205</v>
+        <v>855073</v>
       </c>
       <c r="R2" t="n">
-        <v>7477980</v>
+        <v>7478043</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123699047</v>
+        <v>123699072</v>
       </c>
       <c r="B3" t="n">
-        <v>79766</v>
+        <v>82573</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>854770</v>
+        <v>855123</v>
       </c>
       <c r="R3" t="n">
-        <v>7477947</v>
+        <v>7478116</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123699086</v>
+        <v>123699090</v>
       </c>
       <c r="B4" t="n">
-        <v>79797</v>
+        <v>79902</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6457</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>854738</v>
+        <v>854901</v>
       </c>
       <c r="R4" t="n">
-        <v>7477969</v>
+        <v>7478143</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123699069</v>
+        <v>123699050</v>
       </c>
       <c r="B5" t="n">
-        <v>78781</v>
+        <v>79903</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>855047</v>
+        <v>855140</v>
       </c>
       <c r="R5" t="n">
-        <v>7478172</v>
+        <v>7478022</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123699059</v>
+        <v>123699069</v>
       </c>
       <c r="B6" t="n">
-        <v>90979</v>
+        <v>78786</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>855112</v>
+        <v>855047</v>
       </c>
       <c r="R6" t="n">
-        <v>7478087</v>
+        <v>7478172</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123699058</v>
+        <v>123699040</v>
       </c>
       <c r="B7" t="n">
-        <v>56689</v>
+        <v>90988</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>855091</v>
+        <v>855106</v>
       </c>
       <c r="R7" t="n">
-        <v>7478072</v>
+        <v>7478141</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1261,11 +1261,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123699042</v>
+        <v>123699066</v>
       </c>
       <c r="B8" t="n">
-        <v>79863</v>
+        <v>78786</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>855063</v>
+        <v>855081</v>
       </c>
       <c r="R8" t="n">
-        <v>7478073</v>
+        <v>7478053</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1394,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123699082</v>
+        <v>123699089</v>
       </c>
       <c r="B9" t="n">
-        <v>79797</v>
+        <v>79902</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6457</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>855140</v>
+        <v>855063</v>
       </c>
       <c r="R9" t="n">
-        <v>7478068</v>
+        <v>7478073</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123699077</v>
+        <v>123699047</v>
       </c>
       <c r="B10" t="n">
-        <v>82568</v>
+        <v>79771</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>855121</v>
+        <v>854770</v>
       </c>
       <c r="R10" t="n">
-        <v>7478158</v>
+        <v>7477947</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123699070</v>
+        <v>123699068</v>
       </c>
       <c r="B11" t="n">
-        <v>82568</v>
+        <v>78786</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>855114</v>
+        <v>855190</v>
       </c>
       <c r="R11" t="n">
-        <v>7478219</v>
+        <v>7477967</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1700,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123699071</v>
+        <v>123699087</v>
       </c>
       <c r="B12" t="n">
-        <v>82568</v>
+        <v>79802</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6457</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>855073</v>
+        <v>854993</v>
       </c>
       <c r="R12" t="n">
-        <v>7478043</v>
+        <v>7478183</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1802,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123699051</v>
+        <v>123699049</v>
       </c>
       <c r="B13" t="n">
-        <v>79898</v>
+        <v>79903</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1842,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>854961</v>
+        <v>855147</v>
       </c>
       <c r="R13" t="n">
-        <v>7478150</v>
+        <v>7477980</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1904,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123699045</v>
+        <v>123699077</v>
       </c>
       <c r="B14" t="n">
-        <v>79766</v>
+        <v>82573</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>855058</v>
+        <v>855121</v>
       </c>
       <c r="R14" t="n">
-        <v>7478025</v>
+        <v>7478158</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2006,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123699090</v>
+        <v>123699051</v>
       </c>
       <c r="B15" t="n">
-        <v>79897</v>
+        <v>79903</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>854901</v>
+        <v>854961</v>
       </c>
       <c r="R15" t="n">
-        <v>7478143</v>
+        <v>7478150</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2108,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123699050</v>
+        <v>123699084</v>
       </c>
       <c r="B16" t="n">
-        <v>79898</v>
+        <v>79802</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6457</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,7 +2143,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>855140</v>
+        <v>855181</v>
       </c>
       <c r="R16" t="n">
         <v>7478022</v>
@@ -2210,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123699064</v>
+        <v>123699082</v>
       </c>
       <c r="B17" t="n">
-        <v>91001</v>
+        <v>79802</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6457</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>855084</v>
+        <v>855140</v>
       </c>
       <c r="R17" t="n">
-        <v>7478212</v>
+        <v>7478068</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123699046</v>
+        <v>123699048</v>
       </c>
       <c r="B18" t="n">
-        <v>79766</v>
+        <v>79903</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>855119</v>
+        <v>855062</v>
       </c>
       <c r="R18" t="n">
-        <v>7478027</v>
+        <v>7478067</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2414,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123699044</v>
+        <v>123699083</v>
       </c>
       <c r="B19" t="n">
-        <v>79766</v>
+        <v>79802</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,21 +2425,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>854836</v>
+        <v>855119</v>
       </c>
       <c r="R19" t="n">
-        <v>7478088</v>
+        <v>7478027</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2492,18 +2487,12 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På  grov asp, 180 cm i omkrets.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2522,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123699067</v>
+        <v>123699086</v>
       </c>
       <c r="B20" t="n">
-        <v>78781</v>
+        <v>79802</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2534,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2562,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>855198</v>
+        <v>854738</v>
       </c>
       <c r="R20" t="n">
-        <v>7477984</v>
+        <v>7477969</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2624,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123699084</v>
+        <v>123699074</v>
       </c>
       <c r="B21" t="n">
-        <v>79797</v>
+        <v>82573</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2636,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6457</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2664,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>855181</v>
+        <v>855205</v>
       </c>
       <c r="R21" t="n">
-        <v>7478022</v>
+        <v>7477980</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2726,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123699089</v>
+        <v>123699058</v>
       </c>
       <c r="B22" t="n">
-        <v>79897</v>
+        <v>56692</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2738,25 +2727,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2766,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>855063</v>
+        <v>855091</v>
       </c>
       <c r="R22" t="n">
-        <v>7478073</v>
+        <v>7478072</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2802,6 +2791,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2828,10 +2822,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123699083</v>
+        <v>123699073</v>
       </c>
       <c r="B23" t="n">
-        <v>79797</v>
+        <v>82573</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2840,25 +2834,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6457</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2871,7 +2865,7 @@
         <v>855119</v>
       </c>
       <c r="R23" t="n">
-        <v>7478027</v>
+        <v>7477995</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2930,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123699041</v>
+        <v>123699063</v>
       </c>
       <c r="B24" t="n">
-        <v>56689</v>
+        <v>91006</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2946,21 +2940,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2970,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>854968</v>
+        <v>855109</v>
       </c>
       <c r="R24" t="n">
-        <v>7478151</v>
+        <v>7478143</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3006,11 +3000,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3037,10 +3026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123699066</v>
+        <v>123699042</v>
       </c>
       <c r="B25" t="n">
-        <v>78781</v>
+        <v>79868</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3053,21 +3042,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3077,10 +3066,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>855081</v>
+        <v>855063</v>
       </c>
       <c r="R25" t="n">
-        <v>7478053</v>
+        <v>7478073</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3139,10 +3128,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123699060</v>
+        <v>123699059</v>
       </c>
       <c r="B26" t="n">
-        <v>90979</v>
+        <v>90984</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3179,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>855099</v>
+        <v>855112</v>
       </c>
       <c r="R26" t="n">
-        <v>7478014</v>
+        <v>7478087</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3241,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123699087</v>
+        <v>123699065</v>
       </c>
       <c r="B27" t="n">
-        <v>79797</v>
+        <v>78786</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3253,25 +3242,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3281,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>854993</v>
+        <v>855061</v>
       </c>
       <c r="R27" t="n">
-        <v>7478183</v>
+        <v>7478034</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3343,10 +3332,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123699049</v>
+        <v>123699044</v>
       </c>
       <c r="B28" t="n">
-        <v>79898</v>
+        <v>79771</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3359,21 +3348,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3383,10 +3372,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>855147</v>
+        <v>854836</v>
       </c>
       <c r="R28" t="n">
-        <v>7477980</v>
+        <v>7478088</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3421,12 +3410,18 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På  grov asp, 180 cm i omkrets.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3445,10 +3440,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123699073</v>
+        <v>123699070</v>
       </c>
       <c r="B29" t="n">
-        <v>82568</v>
+        <v>82573</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3485,10 +3480,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>855119</v>
+        <v>855114</v>
       </c>
       <c r="R29" t="n">
-        <v>7477995</v>
+        <v>7478219</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3547,10 +3542,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123699063</v>
+        <v>123699045</v>
       </c>
       <c r="B30" t="n">
-        <v>91001</v>
+        <v>79771</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3559,25 +3554,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3587,10 +3582,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>855109</v>
+        <v>855058</v>
       </c>
       <c r="R30" t="n">
-        <v>7478143</v>
+        <v>7478025</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3649,10 +3644,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123699065</v>
+        <v>123699046</v>
       </c>
       <c r="B31" t="n">
-        <v>78781</v>
+        <v>79771</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3661,25 +3656,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3689,10 +3684,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>855061</v>
+        <v>855119</v>
       </c>
       <c r="R31" t="n">
-        <v>7478034</v>
+        <v>7478027</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3751,10 +3746,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123699048</v>
+        <v>123699067</v>
       </c>
       <c r="B32" t="n">
-        <v>79898</v>
+        <v>78786</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3763,25 +3758,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3791,10 +3786,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>855062</v>
+        <v>855198</v>
       </c>
       <c r="R32" t="n">
-        <v>7478067</v>
+        <v>7477984</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3853,10 +3848,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123699068</v>
+        <v>123699041</v>
       </c>
       <c r="B33" t="n">
-        <v>78781</v>
+        <v>56692</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3869,21 +3864,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3893,10 +3888,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>855190</v>
+        <v>854968</v>
       </c>
       <c r="R33" t="n">
-        <v>7477967</v>
+        <v>7478151</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3929,6 +3924,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3955,10 +3955,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123699072</v>
+        <v>123699060</v>
       </c>
       <c r="B34" t="n">
-        <v>82568</v>
+        <v>90984</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3971,21 +3971,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>855123</v>
+        <v>855099</v>
       </c>
       <c r="R34" t="n">
-        <v>7478116</v>
+        <v>7478014</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4057,10 +4057,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123699040</v>
+        <v>123699064</v>
       </c>
       <c r="B35" t="n">
-        <v>90983</v>
+        <v>91006</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4073,21 +4073,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4097,10 +4097,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>855106</v>
+        <v>855084</v>
       </c>
       <c r="R35" t="n">
-        <v>7478141</v>
+        <v>7478212</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123699071</v>
+        <v>123699069</v>
       </c>
       <c r="B2" t="n">
-        <v>82573</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>855073</v>
+        <v>855047</v>
       </c>
       <c r="R2" t="n">
-        <v>7478043</v>
+        <v>7478172</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123699072</v>
+        <v>123699044</v>
       </c>
       <c r="B3" t="n">
-        <v>82573</v>
+        <v>79773</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>855123</v>
+        <v>854836</v>
       </c>
       <c r="R3" t="n">
-        <v>7478116</v>
+        <v>7478088</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -855,12 +855,18 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På  grov asp, 180 cm i omkrets.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123699090</v>
+        <v>123699041</v>
       </c>
       <c r="B4" t="n">
-        <v>79902</v>
+        <v>56692</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +897,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>854901</v>
+        <v>854968</v>
       </c>
       <c r="R4" t="n">
-        <v>7478143</v>
+        <v>7478151</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -955,6 +961,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123699050</v>
+        <v>123699073</v>
       </c>
       <c r="B5" t="n">
-        <v>79903</v>
+        <v>82575</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +1004,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>855140</v>
+        <v>855119</v>
       </c>
       <c r="R5" t="n">
-        <v>7478022</v>
+        <v>7477995</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123699069</v>
+        <v>123699071</v>
       </c>
       <c r="B6" t="n">
-        <v>78786</v>
+        <v>82575</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>855047</v>
+        <v>855073</v>
       </c>
       <c r="R6" t="n">
-        <v>7478172</v>
+        <v>7478043</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1196,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123699040</v>
+        <v>123699059</v>
       </c>
       <c r="B7" t="n">
-        <v>90988</v>
+        <v>90986</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1212,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1236,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>855106</v>
+        <v>855112</v>
       </c>
       <c r="R7" t="n">
-        <v>7478141</v>
+        <v>7478087</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1298,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123699066</v>
+        <v>123699065</v>
       </c>
       <c r="B8" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>855081</v>
+        <v>855061</v>
       </c>
       <c r="R8" t="n">
-        <v>7478053</v>
+        <v>7478034</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1400,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123699089</v>
+        <v>123699074</v>
       </c>
       <c r="B9" t="n">
-        <v>79902</v>
+        <v>82575</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1412,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1440,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>855063</v>
+        <v>855205</v>
       </c>
       <c r="R9" t="n">
-        <v>7478073</v>
+        <v>7477980</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1502,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123699047</v>
+        <v>123699051</v>
       </c>
       <c r="B10" t="n">
-        <v>79771</v>
+        <v>79905</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1518,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>854770</v>
+        <v>854961</v>
       </c>
       <c r="R10" t="n">
-        <v>7477947</v>
+        <v>7478150</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,10 +1604,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123699068</v>
+        <v>123699089</v>
       </c>
       <c r="B11" t="n">
-        <v>78786</v>
+        <v>79904</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,20 +1616,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1633,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>855190</v>
+        <v>855063</v>
       </c>
       <c r="R11" t="n">
-        <v>7477967</v>
+        <v>7478073</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1695,10 +1706,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123699087</v>
+        <v>123699067</v>
       </c>
       <c r="B12" t="n">
-        <v>79802</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1718,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1746,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>854993</v>
+        <v>855198</v>
       </c>
       <c r="R12" t="n">
-        <v>7478183</v>
+        <v>7477984</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1797,10 +1808,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123699049</v>
+        <v>123699058</v>
       </c>
       <c r="B13" t="n">
-        <v>79903</v>
+        <v>56692</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1820,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1848,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>855147</v>
+        <v>855091</v>
       </c>
       <c r="R13" t="n">
-        <v>7477980</v>
+        <v>7478072</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1873,6 +1884,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123699077</v>
+        <v>123699042</v>
       </c>
       <c r="B14" t="n">
-        <v>82573</v>
+        <v>79870</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1931,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1955,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>855121</v>
+        <v>855063</v>
       </c>
       <c r="R14" t="n">
-        <v>7478158</v>
+        <v>7478073</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2001,10 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123699051</v>
+        <v>123699047</v>
       </c>
       <c r="B15" t="n">
-        <v>79903</v>
+        <v>79773</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2033,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2057,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>854961</v>
+        <v>854770</v>
       </c>
       <c r="R15" t="n">
-        <v>7478150</v>
+        <v>7477947</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2103,10 +2119,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123699084</v>
+        <v>123699040</v>
       </c>
       <c r="B16" t="n">
-        <v>79802</v>
+        <v>90990</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2131,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6457</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>855181</v>
+        <v>855106</v>
       </c>
       <c r="R16" t="n">
-        <v>7478022</v>
+        <v>7478141</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2205,10 +2221,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123699082</v>
+        <v>123699049</v>
       </c>
       <c r="B17" t="n">
-        <v>79802</v>
+        <v>79905</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2237,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6457</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2261,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>855140</v>
+        <v>855147</v>
       </c>
       <c r="R17" t="n">
-        <v>7478068</v>
+        <v>7477980</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2307,10 +2323,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123699048</v>
+        <v>123699086</v>
       </c>
       <c r="B18" t="n">
-        <v>79903</v>
+        <v>79804</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2339,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>6457</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2363,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>855062</v>
+        <v>854738</v>
       </c>
       <c r="R18" t="n">
-        <v>7478067</v>
+        <v>7477969</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2409,10 +2425,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123699083</v>
+        <v>123699068</v>
       </c>
       <c r="B19" t="n">
-        <v>79802</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,25 +2437,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2465,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>855119</v>
+        <v>855190</v>
       </c>
       <c r="R19" t="n">
-        <v>7478027</v>
+        <v>7477967</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2511,10 +2527,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123699086</v>
+        <v>123699060</v>
       </c>
       <c r="B20" t="n">
-        <v>79802</v>
+        <v>90986</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,25 +2539,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6457</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2567,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>854738</v>
+        <v>855099</v>
       </c>
       <c r="R20" t="n">
-        <v>7477969</v>
+        <v>7478014</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2613,10 +2629,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123699074</v>
+        <v>123699082</v>
       </c>
       <c r="B21" t="n">
-        <v>82573</v>
+        <v>79804</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2641,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6457</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2669,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>855205</v>
+        <v>855140</v>
       </c>
       <c r="R21" t="n">
-        <v>7477980</v>
+        <v>7478068</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2715,10 +2731,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123699058</v>
+        <v>123699084</v>
       </c>
       <c r="B22" t="n">
-        <v>56692</v>
+        <v>79804</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2727,25 +2743,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>6457</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2771,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>855091</v>
+        <v>855181</v>
       </c>
       <c r="R22" t="n">
-        <v>7478072</v>
+        <v>7478022</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2791,11 +2807,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2822,10 +2833,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123699073</v>
+        <v>123699077</v>
       </c>
       <c r="B23" t="n">
-        <v>82573</v>
+        <v>82575</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2862,10 +2873,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>855119</v>
+        <v>855121</v>
       </c>
       <c r="R23" t="n">
-        <v>7477995</v>
+        <v>7478158</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2924,10 +2935,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123699063</v>
+        <v>123699066</v>
       </c>
       <c r="B24" t="n">
-        <v>91006</v>
+        <v>78788</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,21 +2951,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2975,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>855109</v>
+        <v>855081</v>
       </c>
       <c r="R24" t="n">
-        <v>7478143</v>
+        <v>7478053</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3026,10 +3037,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123699042</v>
+        <v>123699048</v>
       </c>
       <c r="B25" t="n">
-        <v>79868</v>
+        <v>79905</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,25 +3049,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3066,10 +3077,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>855063</v>
+        <v>855062</v>
       </c>
       <c r="R25" t="n">
-        <v>7478073</v>
+        <v>7478067</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3128,10 +3139,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123699059</v>
+        <v>123699070</v>
       </c>
       <c r="B26" t="n">
-        <v>90984</v>
+        <v>82575</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,21 +3155,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3179,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>855112</v>
+        <v>855114</v>
       </c>
       <c r="R26" t="n">
-        <v>7478087</v>
+        <v>7478219</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3230,10 +3241,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123699065</v>
+        <v>123699046</v>
       </c>
       <c r="B27" t="n">
-        <v>78786</v>
+        <v>79773</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3242,25 +3253,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3270,10 +3281,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>855061</v>
+        <v>855119</v>
       </c>
       <c r="R27" t="n">
-        <v>7478034</v>
+        <v>7478027</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3332,10 +3343,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123699044</v>
+        <v>123699072</v>
       </c>
       <c r="B28" t="n">
-        <v>79771</v>
+        <v>82575</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3344,25 +3355,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3372,10 +3383,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>854836</v>
+        <v>855123</v>
       </c>
       <c r="R28" t="n">
-        <v>7478088</v>
+        <v>7478116</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3410,18 +3421,12 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På  grov asp, 180 cm i omkrets.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3440,10 +3445,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123699070</v>
+        <v>123699064</v>
       </c>
       <c r="B29" t="n">
-        <v>82573</v>
+        <v>91008</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3456,21 +3461,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3480,10 +3485,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>855114</v>
+        <v>855084</v>
       </c>
       <c r="R29" t="n">
-        <v>7478219</v>
+        <v>7478212</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3545,7 +3550,7 @@
         <v>123699045</v>
       </c>
       <c r="B30" t="n">
-        <v>79771</v>
+        <v>79773</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3644,10 +3649,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123699046</v>
+        <v>123699050</v>
       </c>
       <c r="B31" t="n">
-        <v>79771</v>
+        <v>79905</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3660,21 +3665,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3684,10 +3689,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>855119</v>
+        <v>855140</v>
       </c>
       <c r="R31" t="n">
-        <v>7478027</v>
+        <v>7478022</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3746,10 +3751,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123699067</v>
+        <v>123699087</v>
       </c>
       <c r="B32" t="n">
-        <v>78786</v>
+        <v>79804</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3758,25 +3763,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3786,10 +3791,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>855198</v>
+        <v>854993</v>
       </c>
       <c r="R32" t="n">
-        <v>7477984</v>
+        <v>7478183</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3848,10 +3853,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123699041</v>
+        <v>123699083</v>
       </c>
       <c r="B33" t="n">
-        <v>56692</v>
+        <v>79804</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3860,25 +3865,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>6457</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3888,10 +3893,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>854968</v>
+        <v>855119</v>
       </c>
       <c r="R33" t="n">
-        <v>7478151</v>
+        <v>7478027</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3924,11 +3929,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3955,10 +3955,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123699060</v>
+        <v>123699063</v>
       </c>
       <c r="B34" t="n">
-        <v>90984</v>
+        <v>91008</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3971,21 +3971,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>855099</v>
+        <v>855109</v>
       </c>
       <c r="R34" t="n">
-        <v>7478014</v>
+        <v>7478143</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4057,10 +4057,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123699064</v>
+        <v>123699090</v>
       </c>
       <c r="B35" t="n">
-        <v>91006</v>
+        <v>79904</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4069,25 +4069,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4097,10 +4097,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>855084</v>
+        <v>854901</v>
       </c>
       <c r="R35" t="n">
-        <v>7478212</v>
+        <v>7478143</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123699069</v>
+        <v>123699044</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>79773</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>855047</v>
+        <v>854836</v>
       </c>
       <c r="R2" t="n">
-        <v>7478172</v>
+        <v>7478088</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -753,12 +753,18 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På  grov asp, 180 cm i omkrets.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123699044</v>
+        <v>123699069</v>
       </c>
       <c r="B3" t="n">
-        <v>79773</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +795,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>854836</v>
+        <v>855047</v>
       </c>
       <c r="R3" t="n">
-        <v>7478088</v>
+        <v>7478172</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -855,18 +861,12 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På  grov asp, 180 cm i omkrets.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1400,10 +1400,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123699074</v>
+        <v>123699051</v>
       </c>
       <c r="B9" t="n">
-        <v>82575</v>
+        <v>79905</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1412,25 +1412,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>855205</v>
+        <v>854961</v>
       </c>
       <c r="R9" t="n">
-        <v>7477980</v>
+        <v>7478150</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1502,10 +1502,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123699051</v>
+        <v>123699074</v>
       </c>
       <c r="B10" t="n">
-        <v>79905</v>
+        <v>82575</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1514,25 +1514,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1542,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>854961</v>
+        <v>855205</v>
       </c>
       <c r="R10" t="n">
-        <v>7478150</v>
+        <v>7477980</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123699058</v>
+        <v>123699047</v>
       </c>
       <c r="B13" t="n">
-        <v>56692</v>
+        <v>79773</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1820,25 +1820,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1848,10 +1848,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>855091</v>
+        <v>854770</v>
       </c>
       <c r="R13" t="n">
-        <v>7478072</v>
+        <v>7477947</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1884,11 +1884,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1915,10 +1910,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123699042</v>
+        <v>123699058</v>
       </c>
       <c r="B14" t="n">
-        <v>79870</v>
+        <v>56692</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1931,21 +1926,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1955,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>855063</v>
+        <v>855091</v>
       </c>
       <c r="R14" t="n">
-        <v>7478073</v>
+        <v>7478072</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1991,6 +1986,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2017,10 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123699047</v>
+        <v>123699042</v>
       </c>
       <c r="B15" t="n">
-        <v>79773</v>
+        <v>79870</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2029,25 +2029,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>854770</v>
+        <v>855063</v>
       </c>
       <c r="R15" t="n">
-        <v>7477947</v>
+        <v>7478073</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2425,10 +2425,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123699068</v>
+        <v>123699060</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>90986</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>855190</v>
+        <v>855099</v>
       </c>
       <c r="R19" t="n">
-        <v>7477967</v>
+        <v>7478014</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2527,10 +2527,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123699060</v>
+        <v>123699068</v>
       </c>
       <c r="B20" t="n">
-        <v>90986</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2543,21 +2543,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>855099</v>
+        <v>855190</v>
       </c>
       <c r="R20" t="n">
-        <v>7478014</v>
+        <v>7477967</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -3955,10 +3955,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123699063</v>
+        <v>123699090</v>
       </c>
       <c r="B34" t="n">
-        <v>91008</v>
+        <v>79904</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3967,25 +3967,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>855109</v>
+        <v>854901</v>
       </c>
       <c r="R34" t="n">
         <v>7478143</v>
@@ -4057,10 +4057,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123699090</v>
+        <v>123699063</v>
       </c>
       <c r="B35" t="n">
-        <v>79904</v>
+        <v>91008</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4069,25 +4069,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>854901</v>
+        <v>855109</v>
       </c>
       <c r="R35" t="n">
         <v>7478143</v>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -2425,10 +2425,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123699060</v>
+        <v>123699068</v>
       </c>
       <c r="B19" t="n">
-        <v>90986</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>855099</v>
+        <v>855190</v>
       </c>
       <c r="R19" t="n">
-        <v>7478014</v>
+        <v>7477967</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2527,10 +2527,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123699068</v>
+        <v>123699060</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>90986</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2543,21 +2543,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>855190</v>
+        <v>855099</v>
       </c>
       <c r="R20" t="n">
-        <v>7477967</v>
+        <v>7478014</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -783,10 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123699069</v>
+        <v>123699040</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,21 +799,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>855047</v>
+        <v>855106</v>
       </c>
       <c r="R3" t="n">
-        <v>7478172</v>
+        <v>7478141</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123699041</v>
+        <v>123699065</v>
       </c>
       <c r="B4" t="n">
-        <v>56692</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,21 +901,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>854968</v>
+        <v>855061</v>
       </c>
       <c r="R4" t="n">
-        <v>7478151</v>
+        <v>7478034</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -961,11 +961,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,10 +987,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123699073</v>
+        <v>123699064</v>
       </c>
       <c r="B5" t="n">
-        <v>82575</v>
+        <v>91008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,21 +1003,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1032,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>855119</v>
+        <v>855084</v>
       </c>
       <c r="R5" t="n">
-        <v>7477995</v>
+        <v>7478212</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1094,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123699071</v>
+        <v>123699059</v>
       </c>
       <c r="B6" t="n">
-        <v>82575</v>
+        <v>90986</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,21 +1105,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>855073</v>
+        <v>855112</v>
       </c>
       <c r="R6" t="n">
-        <v>7478043</v>
+        <v>7478087</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1196,10 +1191,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123699059</v>
+        <v>123699082</v>
       </c>
       <c r="B7" t="n">
-        <v>90986</v>
+        <v>79804</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1208,25 +1203,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>6457</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1236,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>855112</v>
+        <v>855140</v>
       </c>
       <c r="R7" t="n">
-        <v>7478087</v>
+        <v>7478068</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1298,10 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123699065</v>
+        <v>123699047</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>79773</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1310,25 +1305,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1338,10 +1333,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>855061</v>
+        <v>854770</v>
       </c>
       <c r="R8" t="n">
-        <v>7478034</v>
+        <v>7477947</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1502,10 +1497,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123699074</v>
+        <v>123699087</v>
       </c>
       <c r="B10" t="n">
-        <v>82575</v>
+        <v>79804</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1514,25 +1509,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6457</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1542,10 +1537,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>855205</v>
+        <v>854993</v>
       </c>
       <c r="R10" t="n">
-        <v>7477980</v>
+        <v>7478183</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1604,10 +1599,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123699089</v>
+        <v>123699046</v>
       </c>
       <c r="B11" t="n">
-        <v>79904</v>
+        <v>79773</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,21 +1615,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1644,10 +1639,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>855063</v>
+        <v>855119</v>
       </c>
       <c r="R11" t="n">
-        <v>7478073</v>
+        <v>7478027</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1808,7 +1803,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123699047</v>
+        <v>123699045</v>
       </c>
       <c r="B13" t="n">
         <v>79773</v>
@@ -1848,10 +1843,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>854770</v>
+        <v>855058</v>
       </c>
       <c r="R13" t="n">
-        <v>7477947</v>
+        <v>7478025</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1910,7 +1905,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123699058</v>
+        <v>123699041</v>
       </c>
       <c r="B14" t="n">
         <v>56692</v>
@@ -1950,10 +1945,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>855091</v>
+        <v>854968</v>
       </c>
       <c r="R14" t="n">
-        <v>7478072</v>
+        <v>7478151</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1990,7 +1985,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Adult 1</t>
+          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2017,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123699042</v>
+        <v>123699058</v>
       </c>
       <c r="B15" t="n">
-        <v>79870</v>
+        <v>56692</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,21 +2028,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2057,10 +2052,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>855063</v>
+        <v>855091</v>
       </c>
       <c r="R15" t="n">
-        <v>7478073</v>
+        <v>7478072</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2093,6 +2088,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2119,10 +2119,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123699040</v>
+        <v>123699060</v>
       </c>
       <c r="B16" t="n">
-        <v>90990</v>
+        <v>90986</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,21 +2135,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>855106</v>
+        <v>855099</v>
       </c>
       <c r="R16" t="n">
-        <v>7478141</v>
+        <v>7478014</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2221,10 +2221,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123699049</v>
+        <v>123699074</v>
       </c>
       <c r="B17" t="n">
-        <v>79905</v>
+        <v>82575</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2233,25 +2233,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>855147</v>
+        <v>855205</v>
       </c>
       <c r="R17" t="n">
         <v>7477980</v>
@@ -2425,10 +2425,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123699068</v>
+        <v>123699089</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>79904</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2437,20 +2437,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>855190</v>
+        <v>855063</v>
       </c>
       <c r="R19" t="n">
-        <v>7477967</v>
+        <v>7478073</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2527,10 +2527,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123699060</v>
+        <v>123699084</v>
       </c>
       <c r="B20" t="n">
-        <v>90986</v>
+        <v>79804</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2539,25 +2539,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6457</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>855099</v>
+        <v>855181</v>
       </c>
       <c r="R20" t="n">
-        <v>7478014</v>
+        <v>7478022</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123699082</v>
+        <v>123699073</v>
       </c>
       <c r="B21" t="n">
-        <v>79804</v>
+        <v>82575</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2641,25 +2641,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6457</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>855140</v>
+        <v>855119</v>
       </c>
       <c r="R21" t="n">
-        <v>7478068</v>
+        <v>7477995</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123699084</v>
+        <v>123699066</v>
       </c>
       <c r="B22" t="n">
-        <v>79804</v>
+        <v>78788</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2743,25 +2743,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>855181</v>
+        <v>855081</v>
       </c>
       <c r="R22" t="n">
-        <v>7478022</v>
+        <v>7478053</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2833,10 +2833,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123699077</v>
+        <v>123699042</v>
       </c>
       <c r="B23" t="n">
-        <v>82575</v>
+        <v>79870</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2849,21 +2849,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>855121</v>
+        <v>855063</v>
       </c>
       <c r="R23" t="n">
-        <v>7478158</v>
+        <v>7478073</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2935,10 +2935,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123699066</v>
+        <v>123699090</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>79904</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2947,20 +2947,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2975,10 +2975,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>855081</v>
+        <v>854901</v>
       </c>
       <c r="R24" t="n">
-        <v>7478053</v>
+        <v>7478143</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3037,10 +3037,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123699048</v>
+        <v>123699072</v>
       </c>
       <c r="B25" t="n">
-        <v>79905</v>
+        <v>82575</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3049,25 +3049,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>855062</v>
+        <v>855123</v>
       </c>
       <c r="R25" t="n">
-        <v>7478067</v>
+        <v>7478116</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123699070</v>
+        <v>123699048</v>
       </c>
       <c r="B26" t="n">
-        <v>82575</v>
+        <v>79905</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3151,25 +3151,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>855114</v>
+        <v>855062</v>
       </c>
       <c r="R26" t="n">
-        <v>7478219</v>
+        <v>7478067</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3241,10 +3241,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123699046</v>
+        <v>123699069</v>
       </c>
       <c r="B27" t="n">
-        <v>79773</v>
+        <v>78788</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3253,25 +3253,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>855119</v>
+        <v>855047</v>
       </c>
       <c r="R27" t="n">
-        <v>7478027</v>
+        <v>7478172</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3343,10 +3343,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123699072</v>
+        <v>123699049</v>
       </c>
       <c r="B28" t="n">
-        <v>82575</v>
+        <v>79905</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3355,25 +3355,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>855123</v>
+        <v>855147</v>
       </c>
       <c r="R28" t="n">
-        <v>7478116</v>
+        <v>7477980</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3445,10 +3445,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123699064</v>
+        <v>123699050</v>
       </c>
       <c r="B29" t="n">
-        <v>91008</v>
+        <v>79905</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3457,25 +3457,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>855084</v>
+        <v>855140</v>
       </c>
       <c r="R29" t="n">
-        <v>7478212</v>
+        <v>7478022</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3547,10 +3547,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123699045</v>
+        <v>123699077</v>
       </c>
       <c r="B30" t="n">
-        <v>79773</v>
+        <v>82575</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3559,25 +3559,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>855058</v>
+        <v>855121</v>
       </c>
       <c r="R30" t="n">
-        <v>7478025</v>
+        <v>7478158</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3649,10 +3649,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123699050</v>
+        <v>123699083</v>
       </c>
       <c r="B31" t="n">
-        <v>79905</v>
+        <v>79804</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3665,21 +3665,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>6457</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>855140</v>
+        <v>855119</v>
       </c>
       <c r="R31" t="n">
-        <v>7478022</v>
+        <v>7478027</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3751,10 +3751,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123699087</v>
+        <v>123699068</v>
       </c>
       <c r="B32" t="n">
-        <v>79804</v>
+        <v>78788</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3763,25 +3763,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>854993</v>
+        <v>855190</v>
       </c>
       <c r="R32" t="n">
-        <v>7478183</v>
+        <v>7477967</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3853,10 +3853,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123699083</v>
+        <v>123699070</v>
       </c>
       <c r="B33" t="n">
-        <v>79804</v>
+        <v>82575</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3865,25 +3865,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6457</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>855119</v>
+        <v>855114</v>
       </c>
       <c r="R33" t="n">
-        <v>7478027</v>
+        <v>7478219</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3955,10 +3955,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123699090</v>
+        <v>123699071</v>
       </c>
       <c r="B34" t="n">
-        <v>79904</v>
+        <v>82575</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3967,25 +3967,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>854901</v>
+        <v>855073</v>
       </c>
       <c r="R34" t="n">
-        <v>7478143</v>
+        <v>7478043</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123699059</v>
+        <v>123699082</v>
       </c>
       <c r="B6" t="n">
-        <v>90986</v>
+        <v>79804</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1101,25 +1101,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6457</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>855112</v>
+        <v>855140</v>
       </c>
       <c r="R6" t="n">
-        <v>7478087</v>
+        <v>7478068</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1191,10 +1191,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123699082</v>
+        <v>123699059</v>
       </c>
       <c r="B7" t="n">
-        <v>79804</v>
+        <v>90986</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1203,25 +1203,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6457</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>855140</v>
+        <v>855112</v>
       </c>
       <c r="R7" t="n">
-        <v>7478068</v>
+        <v>7478087</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1803,10 +1803,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123699045</v>
+        <v>123699060</v>
       </c>
       <c r="B13" t="n">
-        <v>79773</v>
+        <v>90986</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1815,25 +1815,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>855058</v>
+        <v>855099</v>
       </c>
       <c r="R13" t="n">
-        <v>7478025</v>
+        <v>7478014</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1905,10 +1905,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123699041</v>
+        <v>123699045</v>
       </c>
       <c r="B14" t="n">
-        <v>56692</v>
+        <v>79773</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1917,25 +1917,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1945,10 +1945,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>854968</v>
+        <v>855058</v>
       </c>
       <c r="R14" t="n">
-        <v>7478151</v>
+        <v>7478025</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1981,11 +1981,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2012,7 +2007,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123699058</v>
+        <v>123699041</v>
       </c>
       <c r="B15" t="n">
         <v>56692</v>
@@ -2052,10 +2047,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>855091</v>
+        <v>854968</v>
       </c>
       <c r="R15" t="n">
-        <v>7478072</v>
+        <v>7478151</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2092,7 +2087,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Adult 1</t>
+          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2119,10 +2114,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123699060</v>
+        <v>123699058</v>
       </c>
       <c r="B16" t="n">
-        <v>90986</v>
+        <v>56692</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,21 +2130,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2159,10 +2154,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>855099</v>
+        <v>855091</v>
       </c>
       <c r="R16" t="n">
-        <v>7478014</v>
+        <v>7478072</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2195,6 +2190,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2527,10 +2527,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123699084</v>
+        <v>123699073</v>
       </c>
       <c r="B20" t="n">
-        <v>79804</v>
+        <v>82575</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2539,25 +2539,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6457</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>855181</v>
+        <v>855119</v>
       </c>
       <c r="R20" t="n">
-        <v>7478022</v>
+        <v>7477995</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123699073</v>
+        <v>123699084</v>
       </c>
       <c r="B21" t="n">
-        <v>82575</v>
+        <v>79804</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2641,25 +2641,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6457</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2669,10 +2669,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>855119</v>
+        <v>855181</v>
       </c>
       <c r="R21" t="n">
-        <v>7477995</v>
+        <v>7478022</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123699048</v>
+        <v>123699069</v>
       </c>
       <c r="B26" t="n">
-        <v>79905</v>
+        <v>78788</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3151,25 +3151,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>855062</v>
+        <v>855047</v>
       </c>
       <c r="R26" t="n">
-        <v>7478067</v>
+        <v>7478172</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3241,10 +3241,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123699069</v>
+        <v>123699048</v>
       </c>
       <c r="B27" t="n">
-        <v>78788</v>
+        <v>79905</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3253,25 +3253,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>855047</v>
+        <v>855062</v>
       </c>
       <c r="R27" t="n">
-        <v>7478172</v>
+        <v>7478067</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3649,10 +3649,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123699083</v>
+        <v>123699068</v>
       </c>
       <c r="B31" t="n">
-        <v>79804</v>
+        <v>78788</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3661,25 +3661,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>855119</v>
+        <v>855190</v>
       </c>
       <c r="R31" t="n">
-        <v>7478027</v>
+        <v>7477967</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3751,10 +3751,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123699068</v>
+        <v>123699083</v>
       </c>
       <c r="B32" t="n">
-        <v>78788</v>
+        <v>79804</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3763,25 +3763,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>855190</v>
+        <v>855119</v>
       </c>
       <c r="R32" t="n">
-        <v>7477967</v>
+        <v>7478027</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123699044</v>
+        <v>123699087</v>
       </c>
       <c r="B2" t="n">
-        <v>79773</v>
+        <v>79804</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>854836</v>
+        <v>854993</v>
       </c>
       <c r="R2" t="n">
-        <v>7478088</v>
+        <v>7478183</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -753,18 +753,12 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På  grov asp, 180 cm i omkrets.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -783,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123699040</v>
+        <v>123699058</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>56692</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>855106</v>
+        <v>855091</v>
       </c>
       <c r="R3" t="n">
-        <v>7478141</v>
+        <v>7478072</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -859,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123699065</v>
+        <v>123699045</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>79773</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -897,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>855061</v>
+        <v>855058</v>
       </c>
       <c r="R4" t="n">
-        <v>7478034</v>
+        <v>7478025</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -987,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123699064</v>
+        <v>123699090</v>
       </c>
       <c r="B5" t="n">
-        <v>91008</v>
+        <v>79904</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -999,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1027,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>855084</v>
+        <v>854901</v>
       </c>
       <c r="R5" t="n">
-        <v>7478212</v>
+        <v>7478143</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1089,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123699082</v>
+        <v>123699042</v>
       </c>
       <c r="B6" t="n">
-        <v>79804</v>
+        <v>79870</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1101,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6457</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1129,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>855140</v>
+        <v>855063</v>
       </c>
       <c r="R6" t="n">
-        <v>7478068</v>
+        <v>7478073</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1191,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123699059</v>
+        <v>123699069</v>
       </c>
       <c r="B7" t="n">
-        <v>90986</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1231,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>855112</v>
+        <v>855047</v>
       </c>
       <c r="R7" t="n">
-        <v>7478087</v>
+        <v>7478172</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1293,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123699047</v>
+        <v>123699065</v>
       </c>
       <c r="B8" t="n">
-        <v>79773</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1305,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1333,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>854770</v>
+        <v>855061</v>
       </c>
       <c r="R8" t="n">
-        <v>7477947</v>
+        <v>7478034</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1395,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123699051</v>
+        <v>123699050</v>
       </c>
       <c r="B9" t="n">
         <v>79905</v>
@@ -1435,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>854961</v>
+        <v>855140</v>
       </c>
       <c r="R9" t="n">
-        <v>7478150</v>
+        <v>7478022</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1497,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123699087</v>
+        <v>123699086</v>
       </c>
       <c r="B10" t="n">
         <v>79804</v>
@@ -1537,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>854993</v>
+        <v>854738</v>
       </c>
       <c r="R10" t="n">
-        <v>7478183</v>
+        <v>7477969</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1599,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123699046</v>
+        <v>123699049</v>
       </c>
       <c r="B11" t="n">
-        <v>79773</v>
+        <v>79905</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1639,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>855119</v>
+        <v>855147</v>
       </c>
       <c r="R11" t="n">
-        <v>7478027</v>
+        <v>7477980</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1701,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123699067</v>
+        <v>123699070</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>82575</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1741,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>855198</v>
+        <v>855114</v>
       </c>
       <c r="R12" t="n">
-        <v>7477984</v>
+        <v>7478219</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1803,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123699060</v>
+        <v>123699048</v>
       </c>
       <c r="B13" t="n">
-        <v>90986</v>
+        <v>79905</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1815,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1843,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>855099</v>
+        <v>855062</v>
       </c>
       <c r="R13" t="n">
-        <v>7478014</v>
+        <v>7478067</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1905,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123699045</v>
+        <v>123699051</v>
       </c>
       <c r="B14" t="n">
-        <v>79773</v>
+        <v>79905</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1945,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>855058</v>
+        <v>854961</v>
       </c>
       <c r="R14" t="n">
-        <v>7478025</v>
+        <v>7478150</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2007,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123699041</v>
+        <v>123699089</v>
       </c>
       <c r="B15" t="n">
-        <v>56692</v>
+        <v>79904</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2019,25 +2018,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2047,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>854968</v>
+        <v>855063</v>
       </c>
       <c r="R15" t="n">
-        <v>7478151</v>
+        <v>7478073</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2083,11 +2082,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2114,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123699058</v>
+        <v>123699083</v>
       </c>
       <c r="B16" t="n">
-        <v>56692</v>
+        <v>79804</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2126,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>6457</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2154,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>855091</v>
+        <v>855119</v>
       </c>
       <c r="R16" t="n">
-        <v>7478072</v>
+        <v>7478027</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2190,11 +2184,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2221,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123699074</v>
+        <v>123699064</v>
       </c>
       <c r="B17" t="n">
-        <v>82575</v>
+        <v>91008</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2237,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2261,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>855205</v>
+        <v>855084</v>
       </c>
       <c r="R17" t="n">
-        <v>7477980</v>
+        <v>7478212</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2323,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123699086</v>
+        <v>123699044</v>
       </c>
       <c r="B18" t="n">
-        <v>79804</v>
+        <v>79773</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2339,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6457</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2363,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>854738</v>
+        <v>854836</v>
       </c>
       <c r="R18" t="n">
-        <v>7477969</v>
+        <v>7478088</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2401,12 +2390,18 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På  grov asp, 180 cm i omkrets.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2425,10 +2420,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123699089</v>
+        <v>123699084</v>
       </c>
       <c r="B19" t="n">
-        <v>79904</v>
+        <v>79804</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2441,21 +2436,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>6457</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2465,10 +2460,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>855063</v>
+        <v>855181</v>
       </c>
       <c r="R19" t="n">
-        <v>7478073</v>
+        <v>7478022</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2527,10 +2522,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123699073</v>
+        <v>123699040</v>
       </c>
       <c r="B20" t="n">
-        <v>82575</v>
+        <v>90990</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2543,21 +2538,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2567,10 +2562,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>855119</v>
+        <v>855106</v>
       </c>
       <c r="R20" t="n">
-        <v>7477995</v>
+        <v>7478141</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2629,10 +2624,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123699084</v>
+        <v>123699072</v>
       </c>
       <c r="B21" t="n">
-        <v>79804</v>
+        <v>82575</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2641,25 +2636,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6457</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2669,10 +2664,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>855181</v>
+        <v>855123</v>
       </c>
       <c r="R21" t="n">
-        <v>7478022</v>
+        <v>7478116</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2731,10 +2726,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123699066</v>
+        <v>123699073</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
+        <v>82575</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2747,21 +2742,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2771,10 +2766,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>855081</v>
+        <v>855119</v>
       </c>
       <c r="R22" t="n">
-        <v>7478053</v>
+        <v>7477995</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2833,10 +2828,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123699042</v>
+        <v>123699046</v>
       </c>
       <c r="B23" t="n">
-        <v>79870</v>
+        <v>79773</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2845,25 +2840,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2873,10 +2868,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>855063</v>
+        <v>855119</v>
       </c>
       <c r="R23" t="n">
-        <v>7478073</v>
+        <v>7478027</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2935,10 +2930,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123699090</v>
+        <v>123699063</v>
       </c>
       <c r="B24" t="n">
-        <v>79904</v>
+        <v>91008</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2947,25 +2942,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2975,7 +2970,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>854901</v>
+        <v>855109</v>
       </c>
       <c r="R24" t="n">
         <v>7478143</v>
@@ -3037,7 +3032,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123699072</v>
+        <v>123699077</v>
       </c>
       <c r="B25" t="n">
         <v>82575</v>
@@ -3077,10 +3072,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>855123</v>
+        <v>855121</v>
       </c>
       <c r="R25" t="n">
-        <v>7478116</v>
+        <v>7478158</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3139,10 +3134,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123699069</v>
+        <v>123699074</v>
       </c>
       <c r="B26" t="n">
-        <v>78788</v>
+        <v>82575</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3155,21 +3150,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3179,10 +3174,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>855047</v>
+        <v>855205</v>
       </c>
       <c r="R26" t="n">
-        <v>7478172</v>
+        <v>7477980</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3241,10 +3236,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123699048</v>
+        <v>123699047</v>
       </c>
       <c r="B27" t="n">
-        <v>79905</v>
+        <v>79773</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3257,21 +3252,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3281,10 +3276,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>855062</v>
+        <v>854770</v>
       </c>
       <c r="R27" t="n">
-        <v>7478067</v>
+        <v>7477947</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3343,10 +3338,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123699049</v>
+        <v>123699067</v>
       </c>
       <c r="B28" t="n">
-        <v>79905</v>
+        <v>78788</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3355,25 +3350,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3383,10 +3378,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>855147</v>
+        <v>855198</v>
       </c>
       <c r="R28" t="n">
-        <v>7477980</v>
+        <v>7477984</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3445,10 +3440,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123699050</v>
+        <v>123699059</v>
       </c>
       <c r="B29" t="n">
-        <v>79905</v>
+        <v>90986</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3457,25 +3452,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3485,10 +3480,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>855140</v>
+        <v>855112</v>
       </c>
       <c r="R29" t="n">
-        <v>7478022</v>
+        <v>7478087</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3547,10 +3542,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123699077</v>
+        <v>123699041</v>
       </c>
       <c r="B30" t="n">
-        <v>82575</v>
+        <v>56692</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3563,21 +3558,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3587,10 +3582,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>855121</v>
+        <v>854968</v>
       </c>
       <c r="R30" t="n">
-        <v>7478158</v>
+        <v>7478151</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3623,6 +3618,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3649,10 +3649,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123699068</v>
+        <v>123699071</v>
       </c>
       <c r="B31" t="n">
-        <v>78788</v>
+        <v>82575</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3665,21 +3665,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>855190</v>
+        <v>855073</v>
       </c>
       <c r="R31" t="n">
-        <v>7477967</v>
+        <v>7478043</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3751,10 +3751,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123699083</v>
+        <v>123699060</v>
       </c>
       <c r="B32" t="n">
-        <v>79804</v>
+        <v>90986</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3763,25 +3763,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6457</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>855119</v>
+        <v>855099</v>
       </c>
       <c r="R32" t="n">
-        <v>7478027</v>
+        <v>7478014</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3853,10 +3853,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123699070</v>
+        <v>123699066</v>
       </c>
       <c r="B33" t="n">
-        <v>82575</v>
+        <v>78788</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3869,21 +3869,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>855114</v>
+        <v>855081</v>
       </c>
       <c r="R33" t="n">
-        <v>7478219</v>
+        <v>7478053</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3955,10 +3955,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123699071</v>
+        <v>123699068</v>
       </c>
       <c r="B34" t="n">
-        <v>82575</v>
+        <v>78788</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3971,21 +3971,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>855073</v>
+        <v>855190</v>
       </c>
       <c r="R34" t="n">
-        <v>7478043</v>
+        <v>7477967</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4057,10 +4057,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123699063</v>
+        <v>123699082</v>
       </c>
       <c r="B35" t="n">
-        <v>91008</v>
+        <v>79804</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4069,25 +4069,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6457</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4097,10 +4097,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>855109</v>
+        <v>855140</v>
       </c>
       <c r="R35" t="n">
-        <v>7478143</v>
+        <v>7478068</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123699087</v>
+        <v>123699059</v>
       </c>
       <c r="B2" t="n">
-        <v>79804</v>
+        <v>90986</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6457</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>854993</v>
+        <v>855112</v>
       </c>
       <c r="R2" t="n">
-        <v>7478183</v>
+        <v>7478087</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123699058</v>
+        <v>123699048</v>
       </c>
       <c r="B3" t="n">
-        <v>56692</v>
+        <v>79905</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>855091</v>
+        <v>855062</v>
       </c>
       <c r="R3" t="n">
-        <v>7478072</v>
+        <v>7478067</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123699045</v>
+        <v>123699064</v>
       </c>
       <c r="B4" t="n">
-        <v>79773</v>
+        <v>91008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>855058</v>
+        <v>855084</v>
       </c>
       <c r="R4" t="n">
-        <v>7478025</v>
+        <v>7478212</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123699090</v>
+        <v>123699077</v>
       </c>
       <c r="B5" t="n">
-        <v>79904</v>
+        <v>82575</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>854901</v>
+        <v>855121</v>
       </c>
       <c r="R5" t="n">
-        <v>7478143</v>
+        <v>7478158</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123699042</v>
+        <v>123699084</v>
       </c>
       <c r="B6" t="n">
-        <v>79870</v>
+        <v>79804</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6457</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>855063</v>
+        <v>855181</v>
       </c>
       <c r="R6" t="n">
-        <v>7478073</v>
+        <v>7478022</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123699069</v>
+        <v>123699072</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>82575</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>855047</v>
+        <v>855123</v>
       </c>
       <c r="R7" t="n">
-        <v>7478172</v>
+        <v>7478116</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123699065</v>
+        <v>123699070</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>82575</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>855061</v>
+        <v>855114</v>
       </c>
       <c r="R8" t="n">
-        <v>7478034</v>
+        <v>7478219</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1394,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123699050</v>
+        <v>123699090</v>
       </c>
       <c r="B9" t="n">
-        <v>79905</v>
+        <v>79904</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>855140</v>
+        <v>854901</v>
       </c>
       <c r="R9" t="n">
-        <v>7478022</v>
+        <v>7478143</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123699086</v>
+        <v>123699046</v>
       </c>
       <c r="B10" t="n">
-        <v>79804</v>
+        <v>79773</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6457</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>854738</v>
+        <v>855119</v>
       </c>
       <c r="R10" t="n">
-        <v>7477969</v>
+        <v>7478027</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123699049</v>
+        <v>123699041</v>
       </c>
       <c r="B11" t="n">
-        <v>79905</v>
+        <v>56692</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>855147</v>
+        <v>854968</v>
       </c>
       <c r="R11" t="n">
-        <v>7477980</v>
+        <v>7478151</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1674,6 +1669,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123699070</v>
+        <v>123699040</v>
       </c>
       <c r="B12" t="n">
-        <v>82575</v>
+        <v>90990</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>855114</v>
+        <v>855106</v>
       </c>
       <c r="R12" t="n">
-        <v>7478219</v>
+        <v>7478141</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123699048</v>
+        <v>123699058</v>
       </c>
       <c r="B13" t="n">
-        <v>79905</v>
+        <v>56692</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>855062</v>
+        <v>855091</v>
       </c>
       <c r="R13" t="n">
-        <v>7478067</v>
+        <v>7478072</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1878,6 +1878,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1904,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123699051</v>
+        <v>123699063</v>
       </c>
       <c r="B14" t="n">
-        <v>79905</v>
+        <v>91008</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,25 +1921,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>854961</v>
+        <v>855109</v>
       </c>
       <c r="R14" t="n">
-        <v>7478150</v>
+        <v>7478143</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2006,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123699089</v>
+        <v>123699049</v>
       </c>
       <c r="B15" t="n">
-        <v>79904</v>
+        <v>79905</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2027,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>855063</v>
+        <v>855147</v>
       </c>
       <c r="R15" t="n">
-        <v>7478073</v>
+        <v>7477980</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2108,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123699083</v>
+        <v>123699050</v>
       </c>
       <c r="B16" t="n">
-        <v>79804</v>
+        <v>79905</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6457</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>855119</v>
+        <v>855140</v>
       </c>
       <c r="R16" t="n">
-        <v>7478027</v>
+        <v>7478022</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2210,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123699064</v>
+        <v>123699069</v>
       </c>
       <c r="B17" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>855084</v>
+        <v>855047</v>
       </c>
       <c r="R17" t="n">
-        <v>7478212</v>
+        <v>7478172</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123699044</v>
+        <v>123699089</v>
       </c>
       <c r="B18" t="n">
-        <v>79773</v>
+        <v>79904</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>854836</v>
+        <v>855063</v>
       </c>
       <c r="R18" t="n">
-        <v>7478088</v>
+        <v>7478073</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2390,18 +2395,12 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På  grov asp, 180 cm i omkrets.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2420,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123699084</v>
+        <v>123699074</v>
       </c>
       <c r="B19" t="n">
-        <v>79804</v>
+        <v>82575</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2432,25 +2431,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6457</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2460,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>855181</v>
+        <v>855205</v>
       </c>
       <c r="R19" t="n">
-        <v>7478022</v>
+        <v>7477980</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2522,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123699040</v>
+        <v>123699066</v>
       </c>
       <c r="B20" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2538,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2562,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>855106</v>
+        <v>855081</v>
       </c>
       <c r="R20" t="n">
-        <v>7478141</v>
+        <v>7478053</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2624,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123699072</v>
+        <v>123699047</v>
       </c>
       <c r="B21" t="n">
-        <v>82575</v>
+        <v>79773</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2636,25 +2635,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2664,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>855123</v>
+        <v>854770</v>
       </c>
       <c r="R21" t="n">
-        <v>7478116</v>
+        <v>7477947</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2726,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123699073</v>
+        <v>123699068</v>
       </c>
       <c r="B22" t="n">
-        <v>82575</v>
+        <v>78788</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2742,21 +2741,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2766,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>855119</v>
+        <v>855190</v>
       </c>
       <c r="R22" t="n">
-        <v>7477995</v>
+        <v>7477967</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2828,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123699046</v>
+        <v>123699086</v>
       </c>
       <c r="B23" t="n">
-        <v>79773</v>
+        <v>79804</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2844,21 +2843,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2868,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>855119</v>
+        <v>854738</v>
       </c>
       <c r="R23" t="n">
-        <v>7478027</v>
+        <v>7477969</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2930,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123699063</v>
+        <v>123699073</v>
       </c>
       <c r="B24" t="n">
-        <v>91008</v>
+        <v>82575</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2946,21 +2945,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2970,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>855109</v>
+        <v>855119</v>
       </c>
       <c r="R24" t="n">
-        <v>7478143</v>
+        <v>7477995</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3032,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123699077</v>
+        <v>123699051</v>
       </c>
       <c r="B25" t="n">
-        <v>82575</v>
+        <v>79905</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3044,25 +3043,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3072,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>855121</v>
+        <v>854961</v>
       </c>
       <c r="R25" t="n">
-        <v>7478158</v>
+        <v>7478150</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3134,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123699074</v>
+        <v>123699045</v>
       </c>
       <c r="B26" t="n">
-        <v>82575</v>
+        <v>79773</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3146,25 +3145,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3174,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>855205</v>
+        <v>855058</v>
       </c>
       <c r="R26" t="n">
-        <v>7477980</v>
+        <v>7478025</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3236,7 +3235,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123699047</v>
+        <v>123699044</v>
       </c>
       <c r="B27" t="n">
         <v>79773</v>
@@ -3276,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>854770</v>
+        <v>854836</v>
       </c>
       <c r="R27" t="n">
-        <v>7477947</v>
+        <v>7478088</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3314,12 +3313,18 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På  grov asp, 180 cm i omkrets.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3338,10 +3343,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123699067</v>
+        <v>123699060</v>
       </c>
       <c r="B28" t="n">
-        <v>78788</v>
+        <v>90986</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3354,21 +3359,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3378,10 +3383,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>855198</v>
+        <v>855099</v>
       </c>
       <c r="R28" t="n">
-        <v>7477984</v>
+        <v>7478014</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3440,10 +3445,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123699059</v>
+        <v>123699087</v>
       </c>
       <c r="B29" t="n">
-        <v>90986</v>
+        <v>79804</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3452,25 +3457,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>6457</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3480,10 +3485,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>855112</v>
+        <v>854993</v>
       </c>
       <c r="R29" t="n">
-        <v>7478087</v>
+        <v>7478183</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3542,10 +3547,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123699041</v>
+        <v>123699071</v>
       </c>
       <c r="B30" t="n">
-        <v>56692</v>
+        <v>82575</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3558,21 +3563,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102612</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3582,10 +3587,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>854968</v>
+        <v>855073</v>
       </c>
       <c r="R30" t="n">
-        <v>7478151</v>
+        <v>7478043</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3618,11 +3623,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3649,10 +3649,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123699071</v>
+        <v>123699065</v>
       </c>
       <c r="B31" t="n">
-        <v>82575</v>
+        <v>78788</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3665,21 +3665,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>855073</v>
+        <v>855061</v>
       </c>
       <c r="R31" t="n">
-        <v>7478043</v>
+        <v>7478034</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3751,10 +3751,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123699060</v>
+        <v>123699042</v>
       </c>
       <c r="B32" t="n">
-        <v>90986</v>
+        <v>79870</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3767,21 +3767,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>855099</v>
+        <v>855063</v>
       </c>
       <c r="R32" t="n">
-        <v>7478014</v>
+        <v>7478073</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3853,10 +3853,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123699066</v>
+        <v>123699082</v>
       </c>
       <c r="B33" t="n">
-        <v>78788</v>
+        <v>79804</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3865,25 +3865,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>855081</v>
+        <v>855140</v>
       </c>
       <c r="R33" t="n">
-        <v>7478053</v>
+        <v>7478068</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3955,7 +3955,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123699068</v>
+        <v>123699067</v>
       </c>
       <c r="B34" t="n">
         <v>78788</v>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>855190</v>
+        <v>855198</v>
       </c>
       <c r="R34" t="n">
-        <v>7477967</v>
+        <v>7477984</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4057,7 +4057,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123699082</v>
+        <v>123699083</v>
       </c>
       <c r="B35" t="n">
         <v>79804</v>
@@ -4097,10 +4097,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>855140</v>
+        <v>855119</v>
       </c>
       <c r="R35" t="n">
-        <v>7478068</v>
+        <v>7478027</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123699059</v>
+        <v>123699077</v>
       </c>
       <c r="B2" t="n">
-        <v>90986</v>
+        <v>82575</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>855112</v>
+        <v>855121</v>
       </c>
       <c r="R2" t="n">
-        <v>7478087</v>
+        <v>7478158</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123699048</v>
+        <v>123699040</v>
       </c>
       <c r="B3" t="n">
-        <v>79905</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>855062</v>
+        <v>855106</v>
       </c>
       <c r="R3" t="n">
-        <v>7478067</v>
+        <v>7478141</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123699064</v>
+        <v>123699059</v>
       </c>
       <c r="B4" t="n">
-        <v>91008</v>
+        <v>90986</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>855084</v>
+        <v>855112</v>
       </c>
       <c r="R4" t="n">
-        <v>7478212</v>
+        <v>7478087</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123699077</v>
+        <v>123699086</v>
       </c>
       <c r="B5" t="n">
-        <v>82575</v>
+        <v>79804</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6457</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>855121</v>
+        <v>854738</v>
       </c>
       <c r="R5" t="n">
-        <v>7478158</v>
+        <v>7477969</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123699084</v>
+        <v>123699041</v>
       </c>
       <c r="B6" t="n">
-        <v>79804</v>
+        <v>56692</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6457</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>855181</v>
+        <v>854968</v>
       </c>
       <c r="R6" t="n">
-        <v>7478022</v>
+        <v>7478151</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1159,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123699072</v>
+        <v>123699071</v>
       </c>
       <c r="B7" t="n">
         <v>82575</v>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>855123</v>
+        <v>855073</v>
       </c>
       <c r="R7" t="n">
-        <v>7478116</v>
+        <v>7478043</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123699070</v>
+        <v>123699064</v>
       </c>
       <c r="B8" t="n">
-        <v>82575</v>
+        <v>91008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>855114</v>
+        <v>855084</v>
       </c>
       <c r="R8" t="n">
-        <v>7478219</v>
+        <v>7478212</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123699090</v>
+        <v>123699073</v>
       </c>
       <c r="B9" t="n">
-        <v>79904</v>
+        <v>82575</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>854901</v>
+        <v>855119</v>
       </c>
       <c r="R9" t="n">
-        <v>7478143</v>
+        <v>7477995</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123699046</v>
+        <v>123699049</v>
       </c>
       <c r="B10" t="n">
-        <v>79773</v>
+        <v>79905</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>855119</v>
+        <v>855147</v>
       </c>
       <c r="R10" t="n">
-        <v>7478027</v>
+        <v>7477980</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123699041</v>
+        <v>123699087</v>
       </c>
       <c r="B11" t="n">
-        <v>56692</v>
+        <v>79804</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>6457</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>854968</v>
+        <v>854993</v>
       </c>
       <c r="R11" t="n">
-        <v>7478151</v>
+        <v>7478183</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1669,11 +1674,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123699040</v>
+        <v>123699070</v>
       </c>
       <c r="B12" t="n">
-        <v>90990</v>
+        <v>82575</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>855106</v>
+        <v>855114</v>
       </c>
       <c r="R12" t="n">
-        <v>7478141</v>
+        <v>7478219</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123699058</v>
+        <v>123699060</v>
       </c>
       <c r="B13" t="n">
-        <v>56692</v>
+        <v>90986</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>855091</v>
+        <v>855099</v>
       </c>
       <c r="R13" t="n">
-        <v>7478072</v>
+        <v>7478014</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1878,11 +1878,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2011,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123699049</v>
+        <v>123699067</v>
       </c>
       <c r="B15" t="n">
-        <v>79905</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2023,25 +2018,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>855147</v>
+        <v>855198</v>
       </c>
       <c r="R15" t="n">
-        <v>7477980</v>
+        <v>7477984</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2113,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123699050</v>
+        <v>123699069</v>
       </c>
       <c r="B16" t="n">
-        <v>79905</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2125,25 +2120,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>855140</v>
+        <v>855047</v>
       </c>
       <c r="R16" t="n">
-        <v>7478022</v>
+        <v>7478172</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2215,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123699069</v>
+        <v>123699045</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>79773</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2227,25 +2222,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>855047</v>
+        <v>855058</v>
       </c>
       <c r="R17" t="n">
-        <v>7478172</v>
+        <v>7478025</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2317,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123699089</v>
+        <v>123699072</v>
       </c>
       <c r="B18" t="n">
-        <v>79904</v>
+        <v>82575</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2329,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>855063</v>
+        <v>855123</v>
       </c>
       <c r="R18" t="n">
-        <v>7478073</v>
+        <v>7478116</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2419,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123699074</v>
+        <v>123699084</v>
       </c>
       <c r="B19" t="n">
-        <v>82575</v>
+        <v>79804</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2431,25 +2426,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6457</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>855205</v>
+        <v>855181</v>
       </c>
       <c r="R19" t="n">
-        <v>7477980</v>
+        <v>7478022</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2521,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123699066</v>
+        <v>123699044</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>79773</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2533,25 +2528,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2556,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>855081</v>
+        <v>854836</v>
       </c>
       <c r="R20" t="n">
-        <v>7478053</v>
+        <v>7478088</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2599,12 +2594,18 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På  grov asp, 180 cm i omkrets.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2623,10 +2624,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123699047</v>
+        <v>123699066</v>
       </c>
       <c r="B21" t="n">
-        <v>79773</v>
+        <v>78788</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2635,25 +2636,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2664,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>854770</v>
+        <v>855081</v>
       </c>
       <c r="R21" t="n">
-        <v>7477947</v>
+        <v>7478053</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2725,10 +2726,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123699068</v>
+        <v>123699083</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
+        <v>79804</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2737,25 +2738,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2766,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>855190</v>
+        <v>855119</v>
       </c>
       <c r="R22" t="n">
-        <v>7477967</v>
+        <v>7478027</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2827,10 +2828,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123699086</v>
+        <v>123699048</v>
       </c>
       <c r="B23" t="n">
-        <v>79804</v>
+        <v>79905</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2843,21 +2844,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6457</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2868,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>854738</v>
+        <v>855062</v>
       </c>
       <c r="R23" t="n">
-        <v>7477969</v>
+        <v>7478067</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2929,10 +2930,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123699073</v>
+        <v>123699090</v>
       </c>
       <c r="B24" t="n">
-        <v>82575</v>
+        <v>79904</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2941,25 +2942,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2969,10 +2970,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>855119</v>
+        <v>854901</v>
       </c>
       <c r="R24" t="n">
-        <v>7477995</v>
+        <v>7478143</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3031,10 +3032,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123699051</v>
+        <v>123699042</v>
       </c>
       <c r="B25" t="n">
-        <v>79905</v>
+        <v>79870</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3043,25 +3044,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3071,10 +3072,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>854961</v>
+        <v>855063</v>
       </c>
       <c r="R25" t="n">
-        <v>7478150</v>
+        <v>7478073</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3133,10 +3134,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123699045</v>
+        <v>123699058</v>
       </c>
       <c r="B26" t="n">
-        <v>79773</v>
+        <v>56692</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3145,25 +3146,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,10 +3174,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>855058</v>
+        <v>855091</v>
       </c>
       <c r="R26" t="n">
-        <v>7478025</v>
+        <v>7478072</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3209,6 +3210,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3235,10 +3241,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123699044</v>
+        <v>123699074</v>
       </c>
       <c r="B27" t="n">
-        <v>79773</v>
+        <v>82575</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3247,25 +3253,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3281,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>854836</v>
+        <v>855205</v>
       </c>
       <c r="R27" t="n">
-        <v>7478088</v>
+        <v>7477980</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3313,18 +3319,12 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På  grov asp, 180 cm i omkrets.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3343,10 +3343,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123699060</v>
+        <v>123699082</v>
       </c>
       <c r="B28" t="n">
-        <v>90986</v>
+        <v>79804</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3355,25 +3355,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>6457</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>855099</v>
+        <v>855140</v>
       </c>
       <c r="R28" t="n">
-        <v>7478014</v>
+        <v>7478068</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3445,10 +3445,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123699087</v>
+        <v>123699046</v>
       </c>
       <c r="B29" t="n">
-        <v>79804</v>
+        <v>79773</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3461,21 +3461,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6457</v>
+        <v>6456</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>854993</v>
+        <v>855119</v>
       </c>
       <c r="R29" t="n">
-        <v>7478183</v>
+        <v>7478027</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3547,10 +3547,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123699071</v>
+        <v>123699068</v>
       </c>
       <c r="B30" t="n">
-        <v>82575</v>
+        <v>78788</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3563,21 +3563,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>855073</v>
+        <v>855190</v>
       </c>
       <c r="R30" t="n">
-        <v>7478043</v>
+        <v>7477967</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3649,10 +3649,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123699065</v>
+        <v>123699051</v>
       </c>
       <c r="B31" t="n">
-        <v>78788</v>
+        <v>79905</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3661,25 +3661,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>855061</v>
+        <v>854961</v>
       </c>
       <c r="R31" t="n">
-        <v>7478034</v>
+        <v>7478150</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3751,10 +3751,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123699042</v>
+        <v>123699089</v>
       </c>
       <c r="B32" t="n">
-        <v>79870</v>
+        <v>79904</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3763,25 +3763,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3853,10 +3853,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123699082</v>
+        <v>123699047</v>
       </c>
       <c r="B33" t="n">
-        <v>79804</v>
+        <v>79773</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3869,21 +3869,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6457</v>
+        <v>6456</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>855140</v>
+        <v>854770</v>
       </c>
       <c r="R33" t="n">
-        <v>7478068</v>
+        <v>7477947</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3955,7 +3955,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123699067</v>
+        <v>123699065</v>
       </c>
       <c r="B34" t="n">
         <v>78788</v>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>855198</v>
+        <v>855061</v>
       </c>
       <c r="R34" t="n">
-        <v>7477984</v>
+        <v>7478034</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4057,10 +4057,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123699083</v>
+        <v>123699050</v>
       </c>
       <c r="B35" t="n">
-        <v>79804</v>
+        <v>79905</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4073,21 +4073,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6457</v>
+        <v>6464</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4097,10 +4097,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>855119</v>
+        <v>855140</v>
       </c>
       <c r="R35" t="n">
-        <v>7478027</v>
+        <v>7478022</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123699041</v>
+        <v>123699064</v>
       </c>
       <c r="B6" t="n">
-        <v>56692</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>854968</v>
+        <v>855084</v>
       </c>
       <c r="R6" t="n">
-        <v>7478151</v>
+        <v>7478212</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1159,11 +1159,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123699071</v>
+        <v>123699041</v>
       </c>
       <c r="B7" t="n">
-        <v>82575</v>
+        <v>56692</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>855073</v>
+        <v>854968</v>
       </c>
       <c r="R7" t="n">
-        <v>7478043</v>
+        <v>7478151</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1266,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123699064</v>
+        <v>123699071</v>
       </c>
       <c r="B8" t="n">
-        <v>91008</v>
+        <v>82575</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>855084</v>
+        <v>855073</v>
       </c>
       <c r="R8" t="n">
-        <v>7478212</v>
+        <v>7478043</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123699069</v>
+        <v>123699072</v>
       </c>
       <c r="B16" t="n">
-        <v>78788</v>
+        <v>82575</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>855047</v>
+        <v>855123</v>
       </c>
       <c r="R16" t="n">
-        <v>7478172</v>
+        <v>7478116</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123699045</v>
+        <v>123699069</v>
       </c>
       <c r="B17" t="n">
-        <v>79773</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,25 +2222,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>855058</v>
+        <v>855047</v>
       </c>
       <c r="R17" t="n">
-        <v>7478025</v>
+        <v>7478172</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123699072</v>
+        <v>123699045</v>
       </c>
       <c r="B18" t="n">
-        <v>82575</v>
+        <v>79773</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,25 +2324,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>855123</v>
+        <v>855058</v>
       </c>
       <c r="R18" t="n">
-        <v>7478116</v>
+        <v>7478025</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2828,10 +2828,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123699048</v>
+        <v>123699042</v>
       </c>
       <c r="B23" t="n">
-        <v>79905</v>
+        <v>79870</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2840,25 +2840,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>855062</v>
+        <v>855063</v>
       </c>
       <c r="R23" t="n">
-        <v>7478067</v>
+        <v>7478073</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2930,10 +2930,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123699090</v>
+        <v>123699058</v>
       </c>
       <c r="B24" t="n">
-        <v>79904</v>
+        <v>56692</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2942,25 +2942,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>102612</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>854901</v>
+        <v>855091</v>
       </c>
       <c r="R24" t="n">
-        <v>7478143</v>
+        <v>7478072</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3006,6 +3006,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3032,10 +3037,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123699042</v>
+        <v>123699048</v>
       </c>
       <c r="B25" t="n">
-        <v>79870</v>
+        <v>79905</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3044,25 +3049,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3072,10 +3077,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>855063</v>
+        <v>855062</v>
       </c>
       <c r="R25" t="n">
-        <v>7478073</v>
+        <v>7478067</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3134,10 +3139,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123699058</v>
+        <v>123699090</v>
       </c>
       <c r="B26" t="n">
-        <v>56692</v>
+        <v>79904</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3146,25 +3151,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3174,10 +3179,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>855091</v>
+        <v>854901</v>
       </c>
       <c r="R26" t="n">
-        <v>7478072</v>
+        <v>7478143</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3210,11 +3215,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123699077</v>
+        <v>123699090</v>
       </c>
       <c r="B2" t="n">
-        <v>82575</v>
+        <v>79904</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>855121</v>
+        <v>854901</v>
       </c>
       <c r="R2" t="n">
-        <v>7478158</v>
+        <v>7478143</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123699040</v>
+        <v>123699042</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>79870</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>855106</v>
+        <v>855063</v>
       </c>
       <c r="R3" t="n">
-        <v>7478141</v>
+        <v>7478073</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123699059</v>
+        <v>123699073</v>
       </c>
       <c r="B4" t="n">
-        <v>90986</v>
+        <v>82575</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>855112</v>
+        <v>855119</v>
       </c>
       <c r="R4" t="n">
-        <v>7478087</v>
+        <v>7477995</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123699086</v>
+        <v>123699084</v>
       </c>
       <c r="B5" t="n">
         <v>79804</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>854738</v>
+        <v>855181</v>
       </c>
       <c r="R5" t="n">
-        <v>7477969</v>
+        <v>7478022</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123699064</v>
+        <v>123699086</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>79804</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6457</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>855084</v>
+        <v>854738</v>
       </c>
       <c r="R6" t="n">
-        <v>7478212</v>
+        <v>7477969</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123699041</v>
+        <v>123699063</v>
       </c>
       <c r="B7" t="n">
-        <v>56692</v>
+        <v>91008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>854968</v>
+        <v>855109</v>
       </c>
       <c r="R7" t="n">
-        <v>7478151</v>
+        <v>7478143</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1261,11 +1261,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123699071</v>
+        <v>123699064</v>
       </c>
       <c r="B8" t="n">
-        <v>82575</v>
+        <v>91008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>855073</v>
+        <v>855084</v>
       </c>
       <c r="R8" t="n">
-        <v>7478043</v>
+        <v>7478212</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1394,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123699073</v>
+        <v>123699049</v>
       </c>
       <c r="B9" t="n">
-        <v>82575</v>
+        <v>79905</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>855119</v>
+        <v>855147</v>
       </c>
       <c r="R9" t="n">
-        <v>7477995</v>
+        <v>7477980</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123699049</v>
+        <v>123699066</v>
       </c>
       <c r="B10" t="n">
-        <v>79905</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>855147</v>
+        <v>855081</v>
       </c>
       <c r="R10" t="n">
-        <v>7477980</v>
+        <v>7478053</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123699087</v>
+        <v>123699058</v>
       </c>
       <c r="B11" t="n">
-        <v>79804</v>
+        <v>56692</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6457</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>854993</v>
+        <v>855091</v>
       </c>
       <c r="R11" t="n">
-        <v>7478183</v>
+        <v>7478072</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1674,6 +1669,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123699070</v>
+        <v>123699051</v>
       </c>
       <c r="B12" t="n">
-        <v>82575</v>
+        <v>79905</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>855114</v>
+        <v>854961</v>
       </c>
       <c r="R12" t="n">
-        <v>7478219</v>
+        <v>7478150</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123699060</v>
+        <v>123699087</v>
       </c>
       <c r="B13" t="n">
-        <v>90986</v>
+        <v>79804</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>6457</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>855099</v>
+        <v>854993</v>
       </c>
       <c r="R13" t="n">
-        <v>7478014</v>
+        <v>7478183</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123699063</v>
+        <v>123699050</v>
       </c>
       <c r="B14" t="n">
-        <v>91008</v>
+        <v>79905</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,25 +1916,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>855109</v>
+        <v>855140</v>
       </c>
       <c r="R14" t="n">
-        <v>7478143</v>
+        <v>7478022</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123699067</v>
+        <v>123699041</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>56692</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>855198</v>
+        <v>854968</v>
       </c>
       <c r="R15" t="n">
-        <v>7477984</v>
+        <v>7478151</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2082,6 +2082,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2108,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123699072</v>
+        <v>123699067</v>
       </c>
       <c r="B16" t="n">
-        <v>82575</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>855123</v>
+        <v>855198</v>
       </c>
       <c r="R16" t="n">
-        <v>7478116</v>
+        <v>7477984</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2210,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123699069</v>
+        <v>123699047</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>79773</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,25 +2227,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>855047</v>
+        <v>854770</v>
       </c>
       <c r="R17" t="n">
-        <v>7478172</v>
+        <v>7477947</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2312,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123699045</v>
+        <v>123699048</v>
       </c>
       <c r="B18" t="n">
-        <v>79773</v>
+        <v>79905</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>855058</v>
+        <v>855062</v>
       </c>
       <c r="R18" t="n">
-        <v>7478025</v>
+        <v>7478067</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2414,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123699084</v>
+        <v>123699074</v>
       </c>
       <c r="B19" t="n">
-        <v>79804</v>
+        <v>82575</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2426,25 +2431,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6457</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>855181</v>
+        <v>855205</v>
       </c>
       <c r="R19" t="n">
-        <v>7478022</v>
+        <v>7477980</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2516,10 +2521,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123699044</v>
+        <v>123699068</v>
       </c>
       <c r="B20" t="n">
-        <v>79773</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2528,25 +2533,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2556,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>854836</v>
+        <v>855190</v>
       </c>
       <c r="R20" t="n">
-        <v>7478088</v>
+        <v>7477967</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2594,18 +2599,12 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På  grov asp, 180 cm i omkrets.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2624,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123699066</v>
+        <v>123699040</v>
       </c>
       <c r="B21" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2640,21 +2639,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2664,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>855081</v>
+        <v>855106</v>
       </c>
       <c r="R21" t="n">
-        <v>7478053</v>
+        <v>7478141</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2726,10 +2725,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123699083</v>
+        <v>123699071</v>
       </c>
       <c r="B22" t="n">
-        <v>79804</v>
+        <v>82575</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2738,25 +2737,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6457</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2766,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>855119</v>
+        <v>855073</v>
       </c>
       <c r="R22" t="n">
-        <v>7478027</v>
+        <v>7478043</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2828,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123699042</v>
+        <v>123699069</v>
       </c>
       <c r="B23" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2844,21 +2843,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2868,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>855063</v>
+        <v>855047</v>
       </c>
       <c r="R23" t="n">
-        <v>7478073</v>
+        <v>7478172</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2930,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123699058</v>
+        <v>123699089</v>
       </c>
       <c r="B24" t="n">
-        <v>56692</v>
+        <v>79904</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2942,25 +2941,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102612</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2970,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>855091</v>
+        <v>855063</v>
       </c>
       <c r="R24" t="n">
-        <v>7478072</v>
+        <v>7478073</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3006,11 +3005,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3037,10 +3031,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123699048</v>
+        <v>123699083</v>
       </c>
       <c r="B25" t="n">
-        <v>79905</v>
+        <v>79804</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3053,21 +3047,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>6457</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3077,10 +3071,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>855062</v>
+        <v>855119</v>
       </c>
       <c r="R25" t="n">
-        <v>7478067</v>
+        <v>7478027</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3139,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123699090</v>
+        <v>123699072</v>
       </c>
       <c r="B26" t="n">
-        <v>79904</v>
+        <v>82575</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3151,25 +3145,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3179,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>854901</v>
+        <v>855123</v>
       </c>
       <c r="R26" t="n">
-        <v>7478143</v>
+        <v>7478116</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3241,7 +3235,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123699074</v>
+        <v>123699070</v>
       </c>
       <c r="B27" t="n">
         <v>82575</v>
@@ -3281,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>855205</v>
+        <v>855114</v>
       </c>
       <c r="R27" t="n">
-        <v>7477980</v>
+        <v>7478219</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3343,10 +3337,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123699082</v>
+        <v>123699045</v>
       </c>
       <c r="B28" t="n">
-        <v>79804</v>
+        <v>79773</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3359,21 +3353,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6457</v>
+        <v>6456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3383,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>855140</v>
+        <v>855058</v>
       </c>
       <c r="R28" t="n">
-        <v>7478068</v>
+        <v>7478025</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3445,10 +3439,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123699046</v>
+        <v>123699082</v>
       </c>
       <c r="B29" t="n">
-        <v>79773</v>
+        <v>79804</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3461,21 +3455,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3485,10 +3479,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>855119</v>
+        <v>855140</v>
       </c>
       <c r="R29" t="n">
-        <v>7478027</v>
+        <v>7478068</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3547,7 +3541,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123699068</v>
+        <v>123699065</v>
       </c>
       <c r="B30" t="n">
         <v>78788</v>
@@ -3587,10 +3581,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>855190</v>
+        <v>855061</v>
       </c>
       <c r="R30" t="n">
-        <v>7477967</v>
+        <v>7478034</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3649,10 +3643,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123699051</v>
+        <v>123699077</v>
       </c>
       <c r="B31" t="n">
-        <v>79905</v>
+        <v>82575</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3661,25 +3655,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3689,10 +3683,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>854961</v>
+        <v>855121</v>
       </c>
       <c r="R31" t="n">
-        <v>7478150</v>
+        <v>7478158</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3751,10 +3745,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123699089</v>
+        <v>123699060</v>
       </c>
       <c r="B32" t="n">
-        <v>79904</v>
+        <v>90986</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3763,25 +3757,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3791,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>855063</v>
+        <v>855099</v>
       </c>
       <c r="R32" t="n">
-        <v>7478073</v>
+        <v>7478014</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3853,7 +3847,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123699047</v>
+        <v>123699046</v>
       </c>
       <c r="B33" t="n">
         <v>79773</v>
@@ -3893,10 +3887,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>854770</v>
+        <v>855119</v>
       </c>
       <c r="R33" t="n">
-        <v>7477947</v>
+        <v>7478027</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3955,10 +3949,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123699065</v>
+        <v>123699044</v>
       </c>
       <c r="B34" t="n">
-        <v>78788</v>
+        <v>79773</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3967,25 +3961,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3995,10 +3989,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>855061</v>
+        <v>854836</v>
       </c>
       <c r="R34" t="n">
-        <v>7478034</v>
+        <v>7478088</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4033,12 +4027,18 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På  grov asp, 180 cm i omkrets.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4057,10 +4057,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123699050</v>
+        <v>123699059</v>
       </c>
       <c r="B35" t="n">
-        <v>79905</v>
+        <v>90986</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4069,25 +4069,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4097,10 +4097,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>855140</v>
+        <v>855112</v>
       </c>
       <c r="R35" t="n">
-        <v>7478022</v>
+        <v>7478087</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4157,6 +4157,2417 @@
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>124427351</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>855056</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7478165</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>124427369</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57666</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>854943</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7478362</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>124427401</v>
+      </c>
+      <c r="B38" t="n">
+        <v>82597</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>855011</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7478352</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>124427402</v>
+      </c>
+      <c r="B39" t="n">
+        <v>82597</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>854960</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7478309</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>124427365</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79428</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>854939</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7478324</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>124427400</v>
+      </c>
+      <c r="B41" t="n">
+        <v>82597</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>855012</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7478269</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>124427391</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>855091</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7478207</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>124427356</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79926</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>854977</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7478167</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>124427388</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>855074</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7478164</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>124427386</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>855066</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7478180</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>124427352</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>855059</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7478173</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>124427375</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79927</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>854922</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7478323</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>124427345</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79927</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>854967</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7478177</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>124427389</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>855110</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7478072</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>124427347</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79927</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>855063</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7478044</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>124427346</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79927</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>855044</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7478074</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>124427354</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>855018</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7478119</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>124427403</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79826</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6457</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Scytinium teretiusculum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>854946</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7478367</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>124427393</v>
+      </c>
+      <c r="B54" t="n">
+        <v>56714</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>854990</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7478363</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>124427387</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>855102</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7478191</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>124427398</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>855100</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7478058</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>124427406</v>
+      </c>
+      <c r="B57" t="n">
+        <v>91579</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>760</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>855096</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7478199</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>124427399</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>855007</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7478357</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -4159,7 +4159,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427351</v>
+        <v>124427391</v>
       </c>
       <c r="B36" t="n">
         <v>98101</v>
@@ -4194,19 +4194,19 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>855056</v>
+        <v>855091</v>
       </c>
       <c r="R36" t="n">
-        <v>7478165</v>
+        <v>7478207</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4266,10 +4266,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427369</v>
+        <v>124427403</v>
       </c>
       <c r="B37" t="n">
-        <v>57666</v>
+        <v>79826</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4278,25 +4278,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6457</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>854943</v>
+        <v>854946</v>
       </c>
       <c r="R37" t="n">
-        <v>7478362</v>
+        <v>7478367</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4350,6 +4350,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4368,10 +4369,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427401</v>
+        <v>124427347</v>
       </c>
       <c r="B38" t="n">
-        <v>82597</v>
+        <v>79927</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4380,38 +4381,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>855011</v>
+        <v>855063</v>
       </c>
       <c r="R38" t="n">
-        <v>7478352</v>
+        <v>7478044</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4470,10 +4471,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427402</v>
+        <v>124427352</v>
       </c>
       <c r="B39" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4482,38 +4483,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>854960</v>
+        <v>855059</v>
       </c>
       <c r="R39" t="n">
-        <v>7478309</v>
+        <v>7478173</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4554,6 +4559,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4572,10 +4578,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427365</v>
+        <v>124427389</v>
       </c>
       <c r="B40" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4584,38 +4590,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>854939</v>
+        <v>855110</v>
       </c>
       <c r="R40" t="n">
-        <v>7478324</v>
+        <v>7478072</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4656,6 +4666,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4674,10 +4685,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427400</v>
+        <v>124427387</v>
       </c>
       <c r="B41" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4686,38 +4697,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>855012</v>
+        <v>855102</v>
       </c>
       <c r="R41" t="n">
-        <v>7478269</v>
+        <v>7478191</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4758,6 +4773,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4776,10 +4792,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427391</v>
+        <v>124427406</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>91579</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4792,38 +4808,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>855091</v>
+        <v>855096</v>
       </c>
       <c r="R42" t="n">
-        <v>7478207</v>
+        <v>7478199</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4856,6 +4875,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4883,10 +4907,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427356</v>
+        <v>124427345</v>
       </c>
       <c r="B43" t="n">
-        <v>79926</v>
+        <v>79927</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4899,21 +4923,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4923,10 +4947,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>854977</v>
+        <v>854967</v>
       </c>
       <c r="R43" t="n">
-        <v>7478167</v>
+        <v>7478177</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5092,10 +5116,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427386</v>
+        <v>124427399</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5104,42 +5128,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>855066</v>
+        <v>855007</v>
       </c>
       <c r="R45" t="n">
-        <v>7478180</v>
+        <v>7478357</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5180,7 +5200,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5199,10 +5218,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427352</v>
+        <v>124427354</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5211,42 +5230,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>855059</v>
+        <v>855018</v>
       </c>
       <c r="R46" t="n">
-        <v>7478173</v>
+        <v>7478119</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5287,7 +5302,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5306,10 +5320,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427375</v>
+        <v>124427351</v>
       </c>
       <c r="B47" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5318,38 +5332,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>854922</v>
+        <v>855056</v>
       </c>
       <c r="R47" t="n">
-        <v>7478323</v>
+        <v>7478165</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5393,21 +5411,6 @@
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5424,10 +5427,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427345</v>
+        <v>124427365</v>
       </c>
       <c r="B48" t="n">
-        <v>79927</v>
+        <v>79428</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5436,38 +5439,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>854967</v>
+        <v>854939</v>
       </c>
       <c r="R48" t="n">
-        <v>7478177</v>
+        <v>7478324</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5526,10 +5529,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427389</v>
+        <v>124427369</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5538,42 +5541,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>855110</v>
+        <v>854943</v>
       </c>
       <c r="R49" t="n">
-        <v>7478072</v>
+        <v>7478362</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5614,7 +5613,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5633,10 +5631,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427347</v>
+        <v>124427400</v>
       </c>
       <c r="B50" t="n">
-        <v>79927</v>
+        <v>82597</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5645,38 +5643,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>855063</v>
+        <v>855012</v>
       </c>
       <c r="R50" t="n">
-        <v>7478044</v>
+        <v>7478269</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5735,10 +5733,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427346</v>
+        <v>124427386</v>
       </c>
       <c r="B51" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5747,38 +5745,42 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>855044</v>
+        <v>855066</v>
       </c>
       <c r="R51" t="n">
-        <v>7478074</v>
+        <v>7478180</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5819,6 +5821,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5837,10 +5840,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427354</v>
+        <v>124427393</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5853,34 +5856,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>855018</v>
+        <v>854990</v>
       </c>
       <c r="R52" t="n">
-        <v>7478119</v>
+        <v>7478363</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5939,10 +5942,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427403</v>
+        <v>124427398</v>
       </c>
       <c r="B53" t="n">
-        <v>79826</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5951,25 +5954,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5979,10 +5982,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>854946</v>
+        <v>855100</v>
       </c>
       <c r="R53" t="n">
-        <v>7478367</v>
+        <v>7478058</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6023,7 +6026,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6042,10 +6044,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427393</v>
+        <v>124427401</v>
       </c>
       <c r="B54" t="n">
-        <v>56714</v>
+        <v>82597</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6058,21 +6060,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>102612</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6082,10 +6084,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>854990</v>
+        <v>855011</v>
       </c>
       <c r="R54" t="n">
-        <v>7478363</v>
+        <v>7478352</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6144,10 +6146,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427387</v>
+        <v>124427346</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6156,42 +6158,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>855102</v>
+        <v>855044</v>
       </c>
       <c r="R55" t="n">
-        <v>7478191</v>
+        <v>7478074</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6232,7 +6230,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6251,10 +6248,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427398</v>
+        <v>124427375</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6263,25 +6260,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6291,10 +6288,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>855100</v>
+        <v>854922</v>
       </c>
       <c r="R56" t="n">
-        <v>7478058</v>
+        <v>7478323</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6335,8 +6332,24 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6353,10 +6366,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124427406</v>
+        <v>124427356</v>
       </c>
       <c r="B57" t="n">
-        <v>91579</v>
+        <v>79926</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6365,45 +6378,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>760</v>
+        <v>6463</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>855096</v>
+        <v>854977</v>
       </c>
       <c r="R57" t="n">
-        <v>7478199</v>
+        <v>7478167</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6438,18 +6444,12 @@
           <t>2025-04-24</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6468,10 +6468,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124427399</v>
+        <v>124427402</v>
       </c>
       <c r="B58" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6484,21 +6484,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6508,10 +6508,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>855007</v>
+        <v>854960</v>
       </c>
       <c r="R58" t="n">
-        <v>7478357</v>
+        <v>7478309</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427391</v>
+        <v>124427345</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4171,42 +4171,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>855091</v>
+        <v>854967</v>
       </c>
       <c r="R36" t="n">
-        <v>7478207</v>
+        <v>7478177</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4247,7 +4243,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4266,10 +4261,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427403</v>
+        <v>124427399</v>
       </c>
       <c r="B37" t="n">
-        <v>79826</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4278,25 +4273,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4306,10 +4301,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>854946</v>
+        <v>855007</v>
       </c>
       <c r="R37" t="n">
-        <v>7478367</v>
+        <v>7478357</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4350,7 +4345,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4369,10 +4363,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427347</v>
+        <v>124427400</v>
       </c>
       <c r="B38" t="n">
-        <v>79927</v>
+        <v>82597</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4381,38 +4375,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>855063</v>
+        <v>855012</v>
       </c>
       <c r="R38" t="n">
-        <v>7478044</v>
+        <v>7478269</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4471,10 +4465,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427352</v>
+        <v>124427403</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>79826</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4483,42 +4477,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>855059</v>
+        <v>854946</v>
       </c>
       <c r="R39" t="n">
-        <v>7478173</v>
+        <v>7478367</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4578,10 +4568,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427389</v>
+        <v>124427346</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4590,42 +4580,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>855110</v>
+        <v>855044</v>
       </c>
       <c r="R40" t="n">
-        <v>7478072</v>
+        <v>7478074</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4666,7 +4652,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4685,10 +4670,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427387</v>
+        <v>124427393</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4697,42 +4682,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>855102</v>
+        <v>854990</v>
       </c>
       <c r="R41" t="n">
-        <v>7478191</v>
+        <v>7478363</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4773,7 +4754,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4792,10 +4772,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427406</v>
+        <v>124427389</v>
       </c>
       <c r="B42" t="n">
-        <v>91579</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4808,41 +4788,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>855096</v>
+        <v>855110</v>
       </c>
       <c r="R42" t="n">
-        <v>7478199</v>
+        <v>7478072</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4875,11 +4852,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-24</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4907,10 +4879,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427345</v>
+        <v>124427369</v>
       </c>
       <c r="B43" t="n">
-        <v>79927</v>
+        <v>57666</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4919,38 +4891,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>854967</v>
+        <v>854943</v>
       </c>
       <c r="R43" t="n">
-        <v>7478177</v>
+        <v>7478362</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5009,10 +4981,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427388</v>
+        <v>124427401</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>82597</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5021,42 +4993,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>855074</v>
+        <v>855011</v>
       </c>
       <c r="R44" t="n">
-        <v>7478164</v>
+        <v>7478352</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5097,7 +5065,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5116,7 +5083,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427399</v>
+        <v>124427398</v>
       </c>
       <c r="B45" t="n">
         <v>78810</v>
@@ -5156,10 +5123,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>855007</v>
+        <v>855100</v>
       </c>
       <c r="R45" t="n">
-        <v>7478357</v>
+        <v>7478058</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5218,10 +5185,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427354</v>
+        <v>124427402</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5234,34 +5201,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>855018</v>
+        <v>854960</v>
       </c>
       <c r="R46" t="n">
-        <v>7478119</v>
+        <v>7478309</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5320,10 +5287,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427351</v>
+        <v>124427347</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5332,42 +5299,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>855056</v>
+        <v>855063</v>
       </c>
       <c r="R47" t="n">
-        <v>7478165</v>
+        <v>7478044</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5408,7 +5371,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5529,10 +5491,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427369</v>
+        <v>124427387</v>
       </c>
       <c r="B49" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5541,38 +5503,42 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>854943</v>
+        <v>855102</v>
       </c>
       <c r="R49" t="n">
-        <v>7478362</v>
+        <v>7478191</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5613,6 +5579,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5631,10 +5598,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427400</v>
+        <v>124427375</v>
       </c>
       <c r="B50" t="n">
-        <v>82597</v>
+        <v>79927</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5643,25 +5610,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5671,10 +5638,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>855012</v>
+        <v>854922</v>
       </c>
       <c r="R50" t="n">
-        <v>7478269</v>
+        <v>7478323</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5715,8 +5682,24 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5733,7 +5716,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427386</v>
+        <v>124427351</v>
       </c>
       <c r="B51" t="n">
         <v>98101</v>
@@ -5768,19 +5751,19 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>137</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>855066</v>
+        <v>855056</v>
       </c>
       <c r="R51" t="n">
-        <v>7478180</v>
+        <v>7478165</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5840,10 +5823,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427393</v>
+        <v>124427352</v>
       </c>
       <c r="B52" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5852,38 +5835,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>854990</v>
+        <v>855059</v>
       </c>
       <c r="R52" t="n">
-        <v>7478363</v>
+        <v>7478173</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5924,6 +5911,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5942,10 +5930,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427398</v>
+        <v>124427406</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>91579</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5954,38 +5942,45 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855100</v>
+        <v>855096</v>
       </c>
       <c r="R53" t="n">
-        <v>7478058</v>
+        <v>7478199</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6020,12 +6015,18 @@
           <t>2025-04-24</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6044,10 +6045,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427401</v>
+        <v>124427356</v>
       </c>
       <c r="B54" t="n">
-        <v>82597</v>
+        <v>79926</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6056,38 +6057,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>855011</v>
+        <v>854977</v>
       </c>
       <c r="R54" t="n">
-        <v>7478352</v>
+        <v>7478167</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6146,10 +6147,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427346</v>
+        <v>124427354</v>
       </c>
       <c r="B55" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6158,25 +6159,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6186,10 +6187,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>855044</v>
+        <v>855018</v>
       </c>
       <c r="R55" t="n">
-        <v>7478074</v>
+        <v>7478119</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6248,10 +6249,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427375</v>
+        <v>124427386</v>
       </c>
       <c r="B56" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6260,38 +6261,42 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>854922</v>
+        <v>855066</v>
       </c>
       <c r="R56" t="n">
-        <v>7478323</v>
+        <v>7478180</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6335,21 +6340,6 @@
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6366,10 +6356,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124427356</v>
+        <v>124427388</v>
       </c>
       <c r="B57" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6378,38 +6368,42 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>854977</v>
+        <v>855074</v>
       </c>
       <c r="R57" t="n">
-        <v>7478167</v>
+        <v>7478164</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6450,6 +6444,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6468,10 +6463,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124427402</v>
+        <v>124427391</v>
       </c>
       <c r="B58" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6480,38 +6475,42 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>854960</v>
+        <v>855091</v>
       </c>
       <c r="R58" t="n">
-        <v>7478309</v>
+        <v>7478207</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6552,6 +6551,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6568,6 +6568,5293 @@
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>124855474</v>
+      </c>
+      <c r="B59" t="n">
+        <v>56714</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>855065</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7478197</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>124855376</v>
+      </c>
+      <c r="B60" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>854741</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7477958</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>124855512</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79926</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>854911</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7478164</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>124855381</v>
+      </c>
+      <c r="B62" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>854803</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7477930</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>124855424</v>
+      </c>
+      <c r="B63" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>854780</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7477939</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>124855377</v>
+      </c>
+      <c r="B64" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>854672</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7477865</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>I utkanten av nytt hygge</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>124855483</v>
+      </c>
+      <c r="B65" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>855251</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7478036</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>124855423</v>
+      </c>
+      <c r="B66" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>854915</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7477851</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>124855389</v>
+      </c>
+      <c r="B67" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>854906</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7477891</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>124855404</v>
+      </c>
+      <c r="B68" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>854832</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7477880</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>124855366</v>
+      </c>
+      <c r="B69" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>854807</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7477926</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>124855417</v>
+      </c>
+      <c r="B70" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>855202</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7477976</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>124855232</v>
+      </c>
+      <c r="B71" t="n">
+        <v>105102</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>855094</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7477931</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>124855467</v>
+      </c>
+      <c r="B72" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>855062</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7478002</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>124855468</v>
+      </c>
+      <c r="B73" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>855069</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7477999</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>124855364</v>
+      </c>
+      <c r="B74" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>855120</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7477887</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>124855235</v>
+      </c>
+      <c r="B75" t="n">
+        <v>105102</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>854686</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7477923</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>124855316</v>
+      </c>
+      <c r="B76" t="n">
+        <v>96985</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>855019</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7477888</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>124855469</v>
+      </c>
+      <c r="B77" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>854979</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7477885</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>124855394</v>
+      </c>
+      <c r="B78" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>854897</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7477846</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>124855380</v>
+      </c>
+      <c r="B79" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>854745</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7477946</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>124855358</v>
+      </c>
+      <c r="B80" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>854772</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7477881</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>124855318</v>
+      </c>
+      <c r="B81" t="n">
+        <v>96985</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>854817</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7477931</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>124854791</v>
+      </c>
+      <c r="B82" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>854840</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7477716</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>124855420</v>
+      </c>
+      <c r="B83" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>855071</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7477912</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>124855250</v>
+      </c>
+      <c r="B84" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>854814</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7477852</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>124855482</v>
+      </c>
+      <c r="B85" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>855134</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7477890</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>124855233</v>
+      </c>
+      <c r="B86" t="n">
+        <v>105102</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>855073</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7477920</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>124854790</v>
+      </c>
+      <c r="B87" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>854766</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7478012</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>124855415</v>
+      </c>
+      <c r="B88" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>854928</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7478107</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>124855466</v>
+      </c>
+      <c r="B89" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>854921</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7478082</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>124855416</v>
+      </c>
+      <c r="B90" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>855002</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7478149</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>124855313</v>
+      </c>
+      <c r="B91" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>658</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>854814</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7477852</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>124855333</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79927</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>854924</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7478087</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>124855277</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>855068</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7478046</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>124855398</v>
+      </c>
+      <c r="B94" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>854737</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7477850</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>124855386</v>
+      </c>
+      <c r="B95" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>854810</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7477930</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>124855231</v>
+      </c>
+      <c r="B96" t="n">
+        <v>105102</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>854954</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7478125</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>124855421</v>
+      </c>
+      <c r="B97" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>854951</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7477899</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>124855275</v>
+      </c>
+      <c r="B98" t="n">
+        <v>92321</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>854889</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7477847</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>124855390</v>
+      </c>
+      <c r="B99" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>854899</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7477831</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>124855500</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79826</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6457</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Scytinium teretiusculum</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>854850</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7477915</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>124855371</v>
+      </c>
+      <c r="B101" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>854845</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7477869</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>124855359</v>
+      </c>
+      <c r="B102" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>854838</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7477840</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>124855249</v>
+      </c>
+      <c r="B103" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>854811</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7477849</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>124855524</v>
+      </c>
+      <c r="B104" t="n">
+        <v>79926</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>854793</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7477805</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>124855464</v>
+      </c>
+      <c r="B105" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>854898</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7478156</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>124855418</v>
+      </c>
+      <c r="B106" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>855131</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7477924</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>124855475</v>
+      </c>
+      <c r="B107" t="n">
+        <v>56714</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>854813</v>
+      </c>
+      <c r="R107" t="n">
+        <v>7477923</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>124855317</v>
+      </c>
+      <c r="B108" t="n">
+        <v>96985</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>854783</v>
+      </c>
+      <c r="R108" t="n">
+        <v>7477935</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>124855244</v>
+      </c>
+      <c r="B109" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>855187</v>
+      </c>
+      <c r="R109" t="n">
+        <v>7478029</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427345</v>
+        <v>124427388</v>
       </c>
       <c r="B36" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4171,38 +4171,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>854967</v>
+        <v>855074</v>
       </c>
       <c r="R36" t="n">
-        <v>7478177</v>
+        <v>7478164</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4243,6 +4247,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4261,10 +4266,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427399</v>
+        <v>124427406</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>91579</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4273,38 +4278,45 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>855007</v>
+        <v>855096</v>
       </c>
       <c r="R37" t="n">
-        <v>7478357</v>
+        <v>7478199</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4339,12 +4351,18 @@
           <t>2025-04-24</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4363,10 +4381,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427400</v>
+        <v>124427365</v>
       </c>
       <c r="B38" t="n">
-        <v>82597</v>
+        <v>79428</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4379,21 +4397,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4403,10 +4421,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>855012</v>
+        <v>854939</v>
       </c>
       <c r="R38" t="n">
-        <v>7478269</v>
+        <v>7478324</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4465,10 +4483,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427403</v>
+        <v>124427400</v>
       </c>
       <c r="B39" t="n">
-        <v>79826</v>
+        <v>82597</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4477,25 +4495,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6457</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4505,10 +4523,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>854946</v>
+        <v>855012</v>
       </c>
       <c r="R39" t="n">
-        <v>7478367</v>
+        <v>7478269</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4549,7 +4567,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4568,7 +4585,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427346</v>
+        <v>124427345</v>
       </c>
       <c r="B40" t="n">
         <v>79927</v>
@@ -4608,10 +4625,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>855044</v>
+        <v>854967</v>
       </c>
       <c r="R40" t="n">
-        <v>7478074</v>
+        <v>7478177</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4670,10 +4687,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427393</v>
+        <v>124427403</v>
       </c>
       <c r="B41" t="n">
-        <v>56714</v>
+        <v>79826</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4682,25 +4699,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102612</v>
+        <v>6457</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4710,10 +4727,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>854990</v>
+        <v>854946</v>
       </c>
       <c r="R41" t="n">
-        <v>7478363</v>
+        <v>7478367</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4754,6 +4771,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4772,10 +4790,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427389</v>
+        <v>124427347</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4784,42 +4802,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>855110</v>
+        <v>855063</v>
       </c>
       <c r="R42" t="n">
-        <v>7478072</v>
+        <v>7478044</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4860,7 +4874,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4879,10 +4892,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427369</v>
+        <v>124427398</v>
       </c>
       <c r="B43" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4895,21 +4908,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4919,10 +4932,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>854943</v>
+        <v>855100</v>
       </c>
       <c r="R43" t="n">
-        <v>7478362</v>
+        <v>7478058</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4981,10 +4994,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427401</v>
+        <v>124427391</v>
       </c>
       <c r="B44" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4993,38 +5006,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>855011</v>
+        <v>855091</v>
       </c>
       <c r="R44" t="n">
-        <v>7478352</v>
+        <v>7478207</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5065,6 +5082,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5083,10 +5101,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427398</v>
+        <v>124427352</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5095,38 +5113,42 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>855100</v>
+        <v>855059</v>
       </c>
       <c r="R45" t="n">
-        <v>7478058</v>
+        <v>7478173</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5167,6 +5189,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5185,10 +5208,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427402</v>
+        <v>124427387</v>
       </c>
       <c r="B46" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5197,38 +5220,42 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>854960</v>
+        <v>855102</v>
       </c>
       <c r="R46" t="n">
-        <v>7478309</v>
+        <v>7478191</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5269,6 +5296,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5287,10 +5315,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427347</v>
+        <v>124427393</v>
       </c>
       <c r="B47" t="n">
-        <v>79927</v>
+        <v>56714</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5299,38 +5327,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>855063</v>
+        <v>854990</v>
       </c>
       <c r="R47" t="n">
-        <v>7478044</v>
+        <v>7478363</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5389,10 +5417,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427365</v>
+        <v>124427369</v>
       </c>
       <c r="B48" t="n">
-        <v>79428</v>
+        <v>57666</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5405,21 +5433,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5429,10 +5457,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>854939</v>
+        <v>854943</v>
       </c>
       <c r="R48" t="n">
-        <v>7478324</v>
+        <v>7478362</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5491,10 +5519,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427387</v>
+        <v>124427354</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5503,42 +5531,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>855102</v>
+        <v>855018</v>
       </c>
       <c r="R49" t="n">
-        <v>7478191</v>
+        <v>7478119</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5579,7 +5603,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5598,10 +5621,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427375</v>
+        <v>124427351</v>
       </c>
       <c r="B50" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5610,38 +5633,42 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>854922</v>
+        <v>855056</v>
       </c>
       <c r="R50" t="n">
-        <v>7478323</v>
+        <v>7478165</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5685,21 +5712,6 @@
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5716,10 +5728,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427351</v>
+        <v>124427356</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5728,42 +5740,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>855056</v>
+        <v>854977</v>
       </c>
       <c r="R51" t="n">
-        <v>7478165</v>
+        <v>7478167</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5804,7 +5812,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5823,10 +5830,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427352</v>
+        <v>124427402</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>82597</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5835,42 +5842,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>855059</v>
+        <v>854960</v>
       </c>
       <c r="R52" t="n">
-        <v>7478173</v>
+        <v>7478309</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5911,7 +5914,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5930,10 +5932,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427406</v>
+        <v>124427401</v>
       </c>
       <c r="B53" t="n">
-        <v>91579</v>
+        <v>82597</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5942,45 +5944,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>760</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855096</v>
+        <v>855011</v>
       </c>
       <c r="R53" t="n">
-        <v>7478199</v>
+        <v>7478352</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6015,18 +6010,12 @@
           <t>2025-04-24</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6045,10 +6034,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427356</v>
+        <v>124427389</v>
       </c>
       <c r="B54" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6057,38 +6046,42 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>854977</v>
+        <v>855110</v>
       </c>
       <c r="R54" t="n">
-        <v>7478167</v>
+        <v>7478072</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6129,6 +6122,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6147,10 +6141,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427354</v>
+        <v>124427346</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6159,25 +6153,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6187,10 +6181,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>855018</v>
+        <v>855044</v>
       </c>
       <c r="R55" t="n">
-        <v>7478119</v>
+        <v>7478074</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6356,10 +6350,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124427388</v>
+        <v>124427375</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6368,42 +6362,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>855074</v>
+        <v>854922</v>
       </c>
       <c r="R57" t="n">
-        <v>7478164</v>
+        <v>7478323</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6447,6 +6437,21 @@
       <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -6463,10 +6468,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124427391</v>
+        <v>124427399</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6475,42 +6480,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>855091</v>
+        <v>855007</v>
       </c>
       <c r="R58" t="n">
-        <v>7478207</v>
+        <v>7478357</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6551,7 +6552,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6570,10 +6570,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855474</v>
+        <v>124855249</v>
       </c>
       <c r="B59" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6586,21 +6586,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>855065</v>
+        <v>854811</v>
       </c>
       <c r="R59" t="n">
-        <v>7478197</v>
+        <v>7477849</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6672,7 +6672,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855376</v>
+        <v>124855389</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>854741</v>
+        <v>854906</v>
       </c>
       <c r="R60" t="n">
-        <v>7477958</v>
+        <v>7477891</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6779,10 +6779,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124855512</v>
+        <v>124855423</v>
       </c>
       <c r="B61" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6791,25 +6791,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6819,10 +6819,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>854911</v>
+        <v>854915</v>
       </c>
       <c r="R61" t="n">
-        <v>7478164</v>
+        <v>7477851</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6881,7 +6881,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124855381</v>
+        <v>124855404</v>
       </c>
       <c r="B62" t="n">
         <v>98101</v>
@@ -6914,17 +6914,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>854803</v>
+        <v>854832</v>
       </c>
       <c r="R62" t="n">
-        <v>7477930</v>
+        <v>7477880</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6984,10 +6988,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124855424</v>
+        <v>124855318</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6996,25 +7000,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7024,10 +7028,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>854780</v>
+        <v>854817</v>
       </c>
       <c r="R63" t="n">
-        <v>7477939</v>
+        <v>7477931</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7086,7 +7090,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124855377</v>
+        <v>124855380</v>
       </c>
       <c r="B64" t="n">
         <v>98101</v>
@@ -7119,21 +7123,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>854672</v>
+        <v>854745</v>
       </c>
       <c r="R64" t="n">
-        <v>7477865</v>
+        <v>7477946</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7160,17 +7160,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>I utkanten av nytt hygge</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7198,10 +7193,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124855483</v>
+        <v>124854790</v>
       </c>
       <c r="B65" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7210,38 +7205,42 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>855251</v>
+        <v>854766</v>
       </c>
       <c r="R65" t="n">
-        <v>7478036</v>
+        <v>7478012</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7282,6 +7281,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7300,10 +7300,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855423</v>
+        <v>124855524</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7312,25 +7312,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7340,10 +7340,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>854915</v>
+        <v>854793</v>
       </c>
       <c r="R66" t="n">
-        <v>7477851</v>
+        <v>7477805</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7370,12 +7370,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7402,7 +7402,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855389</v>
+        <v>124855421</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -7435,21 +7435,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>854906</v>
+        <v>854951</v>
       </c>
       <c r="R67" t="n">
-        <v>7477891</v>
+        <v>7477899</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7490,7 +7486,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7509,7 +7504,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855404</v>
+        <v>124855468</v>
       </c>
       <c r="B68" t="n">
         <v>98101</v>
@@ -7542,21 +7537,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854832</v>
+        <v>855069</v>
       </c>
       <c r="R68" t="n">
-        <v>7477880</v>
+        <v>7477999</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7597,7 +7588,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7616,7 +7606,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855366</v>
+        <v>124855377</v>
       </c>
       <c r="B69" t="n">
         <v>98101</v>
@@ -7651,19 +7641,19 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>64</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>854807</v>
+        <v>854672</v>
       </c>
       <c r="R69" t="n">
-        <v>7477926</v>
+        <v>7477865</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7690,12 +7680,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>I utkanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7723,10 +7718,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855417</v>
+        <v>124855277</v>
       </c>
       <c r="B70" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7735,25 +7730,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7763,10 +7758,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>855202</v>
+        <v>855068</v>
       </c>
       <c r="R70" t="n">
-        <v>7477976</v>
+        <v>7478046</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7825,10 +7820,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855232</v>
+        <v>124855483</v>
       </c>
       <c r="B71" t="n">
-        <v>105102</v>
+        <v>78810</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7837,25 +7832,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7865,10 +7860,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>855094</v>
+        <v>855251</v>
       </c>
       <c r="R71" t="n">
-        <v>7477931</v>
+        <v>7478036</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7927,10 +7922,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855467</v>
+        <v>124855482</v>
       </c>
       <c r="B72" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7939,25 +7934,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7967,10 +7962,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>855062</v>
+        <v>855134</v>
       </c>
       <c r="R72" t="n">
-        <v>7478002</v>
+        <v>7477890</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8029,10 +8024,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855468</v>
+        <v>124855250</v>
       </c>
       <c r="B73" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8041,25 +8036,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8069,10 +8064,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>855069</v>
+        <v>854814</v>
       </c>
       <c r="R73" t="n">
-        <v>7477999</v>
+        <v>7477852</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8131,10 +8126,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855364</v>
+        <v>124855317</v>
       </c>
       <c r="B74" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8143,38 +8138,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>855120</v>
+        <v>854783</v>
       </c>
       <c r="R74" t="n">
-        <v>7477887</v>
+        <v>7477935</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8209,18 +8204,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8239,10 +8228,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855235</v>
+        <v>124855398</v>
       </c>
       <c r="B75" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8251,38 +8240,42 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854686</v>
+        <v>854737</v>
       </c>
       <c r="R75" t="n">
-        <v>7477923</v>
+        <v>7477850</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8309,12 +8302,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8323,6 +8321,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8341,10 +8340,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855316</v>
+        <v>124855366</v>
       </c>
       <c r="B76" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8353,38 +8352,42 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>855019</v>
+        <v>854807</v>
       </c>
       <c r="R76" t="n">
-        <v>7477888</v>
+        <v>7477926</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8425,6 +8428,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8443,10 +8447,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124855469</v>
+        <v>124855316</v>
       </c>
       <c r="B77" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8455,25 +8459,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8483,10 +8487,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>854979</v>
+        <v>855019</v>
       </c>
       <c r="R77" t="n">
-        <v>7477885</v>
+        <v>7477888</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8545,7 +8549,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855394</v>
+        <v>124855359</v>
       </c>
       <c r="B78" t="n">
         <v>98101</v>
@@ -8578,21 +8582,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>854897</v>
+        <v>854838</v>
       </c>
       <c r="R78" t="n">
-        <v>7477846</v>
+        <v>7477840</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8625,6 +8625,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8652,7 +8657,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855380</v>
+        <v>124855424</v>
       </c>
       <c r="B79" t="n">
         <v>98101</v>
@@ -8692,10 +8697,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>854745</v>
+        <v>854780</v>
       </c>
       <c r="R79" t="n">
-        <v>7477946</v>
+        <v>7477939</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8736,7 +8741,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8755,7 +8759,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124855358</v>
+        <v>124855417</v>
       </c>
       <c r="B80" t="n">
         <v>98101</v>
@@ -8791,14 +8795,14 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>854772</v>
+        <v>855202</v>
       </c>
       <c r="R80" t="n">
-        <v>7477881</v>
+        <v>7477976</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8833,18 +8837,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8863,10 +8861,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855318</v>
+        <v>124855244</v>
       </c>
       <c r="B81" t="n">
-        <v>96985</v>
+        <v>91012</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8875,25 +8873,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8903,10 +8901,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>854817</v>
+        <v>855187</v>
       </c>
       <c r="R81" t="n">
-        <v>7477931</v>
+        <v>7478029</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8965,10 +8963,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124854791</v>
+        <v>124855474</v>
       </c>
       <c r="B82" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8981,34 +8979,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>854840</v>
+        <v>855065</v>
       </c>
       <c r="R82" t="n">
-        <v>7477716</v>
+        <v>7478197</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9035,12 +9033,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9169,10 +9167,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855250</v>
+        <v>124855500</v>
       </c>
       <c r="B84" t="n">
-        <v>91012</v>
+        <v>79826</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9181,25 +9179,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>6457</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9209,10 +9207,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>854814</v>
+        <v>854850</v>
       </c>
       <c r="R84" t="n">
-        <v>7477852</v>
+        <v>7477915</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9271,10 +9269,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855482</v>
+        <v>124855512</v>
       </c>
       <c r="B85" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9283,20 +9281,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9311,10 +9309,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>855134</v>
+        <v>854911</v>
       </c>
       <c r="R85" t="n">
-        <v>7477890</v>
+        <v>7478164</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9373,10 +9371,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855233</v>
+        <v>124855390</v>
       </c>
       <c r="B86" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9385,38 +9383,42 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>855073</v>
+        <v>854899</v>
       </c>
       <c r="R86" t="n">
-        <v>7477920</v>
+        <v>7477831</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9457,6 +9459,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9475,7 +9478,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124854790</v>
+        <v>124855358</v>
       </c>
       <c r="B87" t="n">
         <v>98101</v>
@@ -9508,21 +9511,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>854766</v>
+        <v>854772</v>
       </c>
       <c r="R87" t="n">
-        <v>7478012</v>
+        <v>7477881</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9555,6 +9554,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9582,7 +9586,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855415</v>
+        <v>124855376</v>
       </c>
       <c r="B88" t="n">
         <v>98101</v>
@@ -9615,17 +9619,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>854928</v>
+        <v>854741</v>
       </c>
       <c r="R88" t="n">
-        <v>7478107</v>
+        <v>7477958</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9666,6 +9674,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9684,7 +9693,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855466</v>
+        <v>124855416</v>
       </c>
       <c r="B89" t="n">
         <v>98101</v>
@@ -9724,10 +9733,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>854921</v>
+        <v>855002</v>
       </c>
       <c r="R89" t="n">
-        <v>7478082</v>
+        <v>7478149</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9786,7 +9795,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124855416</v>
+        <v>124855418</v>
       </c>
       <c r="B90" t="n">
         <v>98101</v>
@@ -9826,10 +9835,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>855002</v>
+        <v>855131</v>
       </c>
       <c r="R90" t="n">
-        <v>7478149</v>
+        <v>7477924</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9888,10 +9897,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124855313</v>
+        <v>124855467</v>
       </c>
       <c r="B91" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9900,25 +9909,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9928,10 +9937,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>854814</v>
+        <v>855062</v>
       </c>
       <c r="R91" t="n">
-        <v>7477852</v>
+        <v>7478002</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9990,10 +9999,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124855333</v>
+        <v>124855364</v>
       </c>
       <c r="B92" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10002,38 +10011,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>854924</v>
+        <v>855120</v>
       </c>
       <c r="R92" t="n">
-        <v>7478087</v>
+        <v>7477887</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10068,12 +10077,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10092,10 +10107,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124855277</v>
+        <v>124855381</v>
       </c>
       <c r="B93" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10104,25 +10119,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10132,10 +10147,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>855068</v>
+        <v>854803</v>
       </c>
       <c r="R93" t="n">
-        <v>7478046</v>
+        <v>7477930</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10176,6 +10191,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10194,10 +10210,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855398</v>
+        <v>124855333</v>
       </c>
       <c r="B94" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10206,42 +10222,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>854737</v>
+        <v>854924</v>
       </c>
       <c r="R94" t="n">
-        <v>7477850</v>
+        <v>7478087</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10268,17 +10280,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10287,7 +10294,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10306,10 +10312,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855386</v>
+        <v>124855235</v>
       </c>
       <c r="B95" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10318,42 +10324,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>854810</v>
+        <v>854686</v>
       </c>
       <c r="R95" t="n">
-        <v>7477930</v>
+        <v>7477923</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10394,7 +10396,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10413,7 +10414,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855231</v>
+        <v>124855233</v>
       </c>
       <c r="B96" t="n">
         <v>105102</v>
@@ -10453,10 +10454,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>854954</v>
+        <v>855073</v>
       </c>
       <c r="R96" t="n">
-        <v>7478125</v>
+        <v>7477920</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10515,10 +10516,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124855421</v>
+        <v>124855313</v>
       </c>
       <c r="B97" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10527,25 +10528,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10555,10 +10556,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>854951</v>
+        <v>854814</v>
       </c>
       <c r="R97" t="n">
-        <v>7477899</v>
+        <v>7477852</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10617,10 +10618,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124855275</v>
+        <v>124854791</v>
       </c>
       <c r="B98" t="n">
-        <v>92321</v>
+        <v>78810</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10633,21 +10634,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10657,10 +10658,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>854889</v>
+        <v>854840</v>
       </c>
       <c r="R98" t="n">
-        <v>7477847</v>
+        <v>7477716</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10687,12 +10688,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10719,10 +10720,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124855390</v>
+        <v>124855232</v>
       </c>
       <c r="B99" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10731,42 +10732,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>854899</v>
+        <v>855094</v>
       </c>
       <c r="R99" t="n">
-        <v>7477831</v>
+        <v>7477931</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10807,7 +10804,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10826,10 +10822,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124855500</v>
+        <v>124855469</v>
       </c>
       <c r="B100" t="n">
-        <v>79826</v>
+        <v>98101</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10838,25 +10834,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6457</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10866,10 +10862,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>854850</v>
+        <v>854979</v>
       </c>
       <c r="R100" t="n">
-        <v>7477915</v>
+        <v>7477885</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10928,7 +10924,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855371</v>
+        <v>124855466</v>
       </c>
       <c r="B101" t="n">
         <v>98101</v>
@@ -10961,21 +10957,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>854845</v>
+        <v>854921</v>
       </c>
       <c r="R101" t="n">
-        <v>7477869</v>
+        <v>7478082</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11016,7 +11008,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11035,7 +11026,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124855359</v>
+        <v>124855386</v>
       </c>
       <c r="B102" t="n">
         <v>98101</v>
@@ -11068,17 +11059,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>854838</v>
+        <v>854810</v>
       </c>
       <c r="R102" t="n">
-        <v>7477840</v>
+        <v>7477930</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11111,11 +11106,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11143,10 +11133,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855249</v>
+        <v>124855475</v>
       </c>
       <c r="B103" t="n">
-        <v>91012</v>
+        <v>56714</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11159,21 +11149,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11183,10 +11173,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>854811</v>
+        <v>854813</v>
       </c>
       <c r="R103" t="n">
-        <v>7477849</v>
+        <v>7477923</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11245,10 +11235,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855524</v>
+        <v>124855415</v>
       </c>
       <c r="B104" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11257,25 +11247,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11285,10 +11275,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>854793</v>
+        <v>854928</v>
       </c>
       <c r="R104" t="n">
-        <v>7477805</v>
+        <v>7478107</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11315,12 +11305,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11347,7 +11337,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855464</v>
+        <v>124855371</v>
       </c>
       <c r="B105" t="n">
         <v>98101</v>
@@ -11380,17 +11370,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>854898</v>
+        <v>854845</v>
       </c>
       <c r="R105" t="n">
-        <v>7478156</v>
+        <v>7477869</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11431,6 +11425,7 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11449,7 +11444,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855418</v>
+        <v>124855464</v>
       </c>
       <c r="B106" t="n">
         <v>98101</v>
@@ -11489,10 +11484,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>855131</v>
+        <v>854898</v>
       </c>
       <c r="R106" t="n">
-        <v>7477924</v>
+        <v>7478156</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11551,10 +11546,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855475</v>
+        <v>124855231</v>
       </c>
       <c r="B107" t="n">
-        <v>56714</v>
+        <v>105102</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11563,25 +11558,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>102612</v>
+        <v>221725</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11591,10 +11586,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>854813</v>
+        <v>854954</v>
       </c>
       <c r="R107" t="n">
-        <v>7477923</v>
+        <v>7478125</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11653,10 +11648,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855317</v>
+        <v>124855275</v>
       </c>
       <c r="B108" t="n">
-        <v>96985</v>
+        <v>92321</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11665,38 +11660,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221941</v>
+        <v>5449</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>854783</v>
+        <v>854889</v>
       </c>
       <c r="R108" t="n">
-        <v>7477935</v>
+        <v>7477847</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11755,10 +11750,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855244</v>
+        <v>124855394</v>
       </c>
       <c r="B109" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11767,38 +11762,42 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>855187</v>
+        <v>854897</v>
       </c>
       <c r="R109" t="n">
-        <v>7478029</v>
+        <v>7477846</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11839,6 +11838,7 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427388</v>
+        <v>124427406</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>91579</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4175,38 +4175,41 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>855074</v>
+        <v>855096</v>
       </c>
       <c r="R36" t="n">
-        <v>7478164</v>
+        <v>7478199</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4239,6 +4242,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4266,10 +4274,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427406</v>
+        <v>124427365</v>
       </c>
       <c r="B37" t="n">
-        <v>91579</v>
+        <v>79428</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4278,45 +4286,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>760</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>855096</v>
+        <v>854939</v>
       </c>
       <c r="R37" t="n">
-        <v>7478199</v>
+        <v>7478324</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4351,18 +4352,12 @@
           <t>2025-04-24</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4381,10 +4376,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427365</v>
+        <v>124427388</v>
       </c>
       <c r="B38" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4393,38 +4388,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>854939</v>
+        <v>855074</v>
       </c>
       <c r="R38" t="n">
-        <v>7478324</v>
+        <v>7478164</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4465,6 +4464,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5621,10 +5621,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427351</v>
+        <v>124427356</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5633,42 +5633,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>855056</v>
+        <v>854977</v>
       </c>
       <c r="R50" t="n">
-        <v>7478165</v>
+        <v>7478167</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5709,7 +5705,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5728,10 +5723,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427356</v>
+        <v>124427351</v>
       </c>
       <c r="B51" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5740,38 +5735,42 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>854977</v>
+        <v>855056</v>
       </c>
       <c r="R51" t="n">
-        <v>7478167</v>
+        <v>7478165</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5812,6 +5811,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6570,10 +6570,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855249</v>
+        <v>124855389</v>
       </c>
       <c r="B59" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6582,38 +6582,42 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>854811</v>
+        <v>854906</v>
       </c>
       <c r="R59" t="n">
-        <v>7477849</v>
+        <v>7477891</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6654,6 +6658,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6672,10 +6677,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855389</v>
+        <v>124855249</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6684,42 +6689,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>854906</v>
+        <v>854811</v>
       </c>
       <c r="R60" t="n">
-        <v>7477891</v>
+        <v>7477849</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6760,7 +6761,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7820,10 +7820,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855483</v>
+        <v>124855250</v>
       </c>
       <c r="B71" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7836,21 +7836,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7860,10 +7860,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>855251</v>
+        <v>854814</v>
       </c>
       <c r="R71" t="n">
-        <v>7478036</v>
+        <v>7477852</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7922,10 +7922,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855482</v>
+        <v>124855317</v>
       </c>
       <c r="B72" t="n">
-        <v>78810</v>
+        <v>96985</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7934,25 +7934,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7962,10 +7962,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>855134</v>
+        <v>854783</v>
       </c>
       <c r="R72" t="n">
-        <v>7477890</v>
+        <v>7477935</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8024,10 +8024,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855250</v>
+        <v>124855398</v>
       </c>
       <c r="B73" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8036,38 +8036,42 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>854814</v>
+        <v>854737</v>
       </c>
       <c r="R73" t="n">
-        <v>7477852</v>
+        <v>7477850</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8094,12 +8098,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8108,6 +8117,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8126,10 +8136,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855317</v>
+        <v>124855366</v>
       </c>
       <c r="B74" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8138,38 +8148,42 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>854783</v>
+        <v>854807</v>
       </c>
       <c r="R74" t="n">
-        <v>7477935</v>
+        <v>7477926</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8210,6 +8224,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8228,10 +8243,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855398</v>
+        <v>124855483</v>
       </c>
       <c r="B75" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8240,42 +8255,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854737</v>
+        <v>855251</v>
       </c>
       <c r="R75" t="n">
-        <v>7477850</v>
+        <v>7478036</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8302,17 +8313,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8321,7 +8327,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8340,10 +8345,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855366</v>
+        <v>124855482</v>
       </c>
       <c r="B76" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8352,42 +8357,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>854807</v>
+        <v>855134</v>
       </c>
       <c r="R76" t="n">
-        <v>7477926</v>
+        <v>7477890</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8428,7 +8429,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -7300,10 +7300,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855524</v>
+        <v>124855468</v>
       </c>
       <c r="B66" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7312,25 +7312,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7340,10 +7340,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>854793</v>
+        <v>855069</v>
       </c>
       <c r="R66" t="n">
-        <v>7477805</v>
+        <v>7477999</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7370,12 +7370,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7402,10 +7402,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855421</v>
+        <v>124855524</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7414,25 +7414,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7442,10 +7442,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>854951</v>
+        <v>854793</v>
       </c>
       <c r="R67" t="n">
-        <v>7477899</v>
+        <v>7477805</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7472,12 +7472,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7504,7 +7504,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855468</v>
+        <v>124855421</v>
       </c>
       <c r="B68" t="n">
         <v>98101</v>
@@ -7544,10 +7544,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>855069</v>
+        <v>854951</v>
       </c>
       <c r="R68" t="n">
-        <v>7477999</v>
+        <v>7477899</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7922,10 +7922,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855317</v>
+        <v>124855483</v>
       </c>
       <c r="B72" t="n">
-        <v>96985</v>
+        <v>78810</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7934,25 +7934,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7962,10 +7962,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>854783</v>
+        <v>855251</v>
       </c>
       <c r="R72" t="n">
-        <v>7477935</v>
+        <v>7478036</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8024,10 +8024,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855398</v>
+        <v>124855482</v>
       </c>
       <c r="B73" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8036,42 +8036,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>854737</v>
+        <v>855134</v>
       </c>
       <c r="R73" t="n">
-        <v>7477850</v>
+        <v>7477890</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8098,17 +8094,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8117,7 +8108,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8136,10 +8126,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855366</v>
+        <v>124855317</v>
       </c>
       <c r="B74" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8148,42 +8138,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>854807</v>
+        <v>854783</v>
       </c>
       <c r="R74" t="n">
-        <v>7477926</v>
+        <v>7477935</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8224,7 +8210,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8243,10 +8228,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855483</v>
+        <v>124855398</v>
       </c>
       <c r="B75" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8255,38 +8240,42 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>855251</v>
+        <v>854737</v>
       </c>
       <c r="R75" t="n">
-        <v>7478036</v>
+        <v>7477850</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8313,12 +8302,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8327,6 +8321,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8345,10 +8340,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855482</v>
+        <v>124855366</v>
       </c>
       <c r="B76" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8357,38 +8352,42 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>855134</v>
+        <v>854807</v>
       </c>
       <c r="R76" t="n">
-        <v>7477890</v>
+        <v>7477926</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8429,6 +8428,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -11648,10 +11648,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855275</v>
+        <v>124855394</v>
       </c>
       <c r="B108" t="n">
-        <v>92321</v>
+        <v>98101</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11660,38 +11660,42 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>854889</v>
+        <v>854897</v>
       </c>
       <c r="R108" t="n">
-        <v>7477847</v>
+        <v>7477846</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11732,6 +11736,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11750,10 +11755,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855394</v>
+        <v>124855275</v>
       </c>
       <c r="B109" t="n">
-        <v>98101</v>
+        <v>92321</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11762,42 +11767,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>854897</v>
+        <v>854889</v>
       </c>
       <c r="R109" t="n">
-        <v>7477846</v>
+        <v>7477847</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11838,7 +11839,6 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427406</v>
+        <v>124427400</v>
       </c>
       <c r="B36" t="n">
-        <v>91579</v>
+        <v>82597</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4171,45 +4171,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>760</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>855096</v>
+        <v>855012</v>
       </c>
       <c r="R36" t="n">
-        <v>7478199</v>
+        <v>7478269</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4244,18 +4237,12 @@
           <t>2025-04-24</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4274,10 +4261,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427365</v>
+        <v>124427356</v>
       </c>
       <c r="B37" t="n">
-        <v>79428</v>
+        <v>79926</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4286,38 +4273,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>854939</v>
+        <v>854977</v>
       </c>
       <c r="R37" t="n">
-        <v>7478324</v>
+        <v>7478167</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4376,10 +4363,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427388</v>
+        <v>124427345</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4388,42 +4375,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>855074</v>
+        <v>854967</v>
       </c>
       <c r="R38" t="n">
-        <v>7478164</v>
+        <v>7478177</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4464,7 +4447,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4483,10 +4465,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427400</v>
+        <v>124427347</v>
       </c>
       <c r="B39" t="n">
-        <v>82597</v>
+        <v>79927</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4495,38 +4477,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>855012</v>
+        <v>855063</v>
       </c>
       <c r="R39" t="n">
-        <v>7478269</v>
+        <v>7478044</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4585,10 +4567,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427345</v>
+        <v>124427401</v>
       </c>
       <c r="B40" t="n">
-        <v>79927</v>
+        <v>82597</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4597,38 +4579,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>854967</v>
+        <v>855011</v>
       </c>
       <c r="R40" t="n">
-        <v>7478177</v>
+        <v>7478352</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4687,10 +4669,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427403</v>
+        <v>124427365</v>
       </c>
       <c r="B41" t="n">
-        <v>79826</v>
+        <v>79428</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4699,25 +4681,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6457</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4727,10 +4709,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>854946</v>
+        <v>854939</v>
       </c>
       <c r="R41" t="n">
-        <v>7478367</v>
+        <v>7478324</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4771,7 +4753,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4790,10 +4771,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427347</v>
+        <v>124427406</v>
       </c>
       <c r="B42" t="n">
-        <v>79927</v>
+        <v>91579</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4802,38 +4783,45 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>760</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>855063</v>
+        <v>855096</v>
       </c>
       <c r="R42" t="n">
-        <v>7478044</v>
+        <v>7478199</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4868,12 +4856,18 @@
           <t>2025-04-24</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4892,10 +4886,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427398</v>
+        <v>124427369</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4908,21 +4902,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4932,10 +4926,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>855100</v>
+        <v>854943</v>
       </c>
       <c r="R43" t="n">
-        <v>7478058</v>
+        <v>7478362</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4994,10 +4988,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427391</v>
+        <v>124427403</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>79826</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5006,42 +5000,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>855091</v>
+        <v>854946</v>
       </c>
       <c r="R44" t="n">
-        <v>7478207</v>
+        <v>7478367</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5101,10 +5091,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427352</v>
+        <v>124427399</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5113,42 +5103,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>855059</v>
+        <v>855007</v>
       </c>
       <c r="R45" t="n">
-        <v>7478173</v>
+        <v>7478357</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5189,7 +5175,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5208,7 +5193,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427387</v>
+        <v>124427389</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -5243,7 +5228,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5252,10 +5237,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>855102</v>
+        <v>855110</v>
       </c>
       <c r="R46" t="n">
-        <v>7478191</v>
+        <v>7478072</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5315,10 +5300,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427393</v>
+        <v>124427402</v>
       </c>
       <c r="B47" t="n">
-        <v>56714</v>
+        <v>82597</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5331,21 +5316,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102612</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5355,10 +5340,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>854990</v>
+        <v>854960</v>
       </c>
       <c r="R47" t="n">
-        <v>7478363</v>
+        <v>7478309</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5417,10 +5402,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427369</v>
+        <v>124427354</v>
       </c>
       <c r="B48" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5433,34 +5418,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>854943</v>
+        <v>855018</v>
       </c>
       <c r="R48" t="n">
-        <v>7478362</v>
+        <v>7478119</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5519,10 +5504,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427354</v>
+        <v>124427375</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5531,38 +5516,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>855018</v>
+        <v>854922</v>
       </c>
       <c r="R49" t="n">
-        <v>7478119</v>
+        <v>7478323</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5603,8 +5588,24 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5621,10 +5622,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427356</v>
+        <v>124427393</v>
       </c>
       <c r="B50" t="n">
-        <v>79926</v>
+        <v>56714</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5633,38 +5634,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6463</v>
+        <v>102612</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>854977</v>
+        <v>854990</v>
       </c>
       <c r="R50" t="n">
-        <v>7478167</v>
+        <v>7478363</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5723,7 +5724,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427351</v>
+        <v>124427387</v>
       </c>
       <c r="B51" t="n">
         <v>98101</v>
@@ -5758,19 +5759,19 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>855056</v>
+        <v>855102</v>
       </c>
       <c r="R51" t="n">
-        <v>7478165</v>
+        <v>7478191</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5830,10 +5831,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427402</v>
+        <v>124427351</v>
       </c>
       <c r="B52" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5842,38 +5843,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>854960</v>
+        <v>855056</v>
       </c>
       <c r="R52" t="n">
-        <v>7478309</v>
+        <v>7478165</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5914,6 +5919,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5932,10 +5938,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427401</v>
+        <v>124427352</v>
       </c>
       <c r="B53" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5944,38 +5950,42 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855011</v>
+        <v>855059</v>
       </c>
       <c r="R53" t="n">
-        <v>7478352</v>
+        <v>7478173</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6016,6 +6026,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6034,7 +6045,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427389</v>
+        <v>124427391</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -6069,7 +6080,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6078,10 +6089,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>855110</v>
+        <v>855091</v>
       </c>
       <c r="R54" t="n">
-        <v>7478072</v>
+        <v>7478207</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6141,10 +6152,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427346</v>
+        <v>124427398</v>
       </c>
       <c r="B55" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6153,38 +6164,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>855044</v>
+        <v>855100</v>
       </c>
       <c r="R55" t="n">
-        <v>7478074</v>
+        <v>7478058</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6243,10 +6254,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427386</v>
+        <v>124427346</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6255,42 +6266,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>855066</v>
+        <v>855044</v>
       </c>
       <c r="R56" t="n">
-        <v>7478180</v>
+        <v>7478074</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6331,7 +6338,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6350,10 +6356,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124427375</v>
+        <v>124427388</v>
       </c>
       <c r="B57" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6362,38 +6368,42 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>854922</v>
+        <v>855074</v>
       </c>
       <c r="R57" t="n">
-        <v>7478323</v>
+        <v>7478164</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6437,21 +6447,6 @@
       <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -6468,10 +6463,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124427399</v>
+        <v>124427386</v>
       </c>
       <c r="B58" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6480,38 +6475,42 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>855007</v>
+        <v>855066</v>
       </c>
       <c r="R58" t="n">
-        <v>7478357</v>
+        <v>7478180</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6552,6 +6551,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6570,10 +6570,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855389</v>
+        <v>124855512</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6582,42 +6582,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>854906</v>
+        <v>854911</v>
       </c>
       <c r="R59" t="n">
-        <v>7477891</v>
+        <v>7478164</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6658,7 +6654,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6677,10 +6672,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855249</v>
+        <v>124855420</v>
       </c>
       <c r="B60" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6689,25 +6684,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6717,10 +6712,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>854811</v>
+        <v>855071</v>
       </c>
       <c r="R60" t="n">
-        <v>7477849</v>
+        <v>7477912</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6779,10 +6774,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124855423</v>
+        <v>124855231</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6791,25 +6786,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6819,10 +6814,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>854915</v>
+        <v>854954</v>
       </c>
       <c r="R61" t="n">
-        <v>7477851</v>
+        <v>7478125</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6988,10 +6983,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124855318</v>
+        <v>124855313</v>
       </c>
       <c r="B63" t="n">
-        <v>96985</v>
+        <v>91299</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7000,25 +6995,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221941</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7028,10 +7023,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>854817</v>
+        <v>854814</v>
       </c>
       <c r="R63" t="n">
-        <v>7477931</v>
+        <v>7477852</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7090,10 +7085,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124855380</v>
+        <v>124855277</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7102,25 +7097,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7130,10 +7125,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>854745</v>
+        <v>855068</v>
       </c>
       <c r="R64" t="n">
-        <v>7477946</v>
+        <v>7478046</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7174,7 +7169,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7300,7 +7294,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855468</v>
+        <v>124855371</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -7333,17 +7327,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>855069</v>
+        <v>854845</v>
       </c>
       <c r="R66" t="n">
-        <v>7477999</v>
+        <v>7477869</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7384,6 +7382,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7402,10 +7401,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855524</v>
+        <v>124855358</v>
       </c>
       <c r="B67" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7414,38 +7413,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>854793</v>
+        <v>854772</v>
       </c>
       <c r="R67" t="n">
-        <v>7477805</v>
+        <v>7477881</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7472,12 +7471,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7486,6 +7490,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7504,7 +7509,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855421</v>
+        <v>124855394</v>
       </c>
       <c r="B68" t="n">
         <v>98101</v>
@@ -7537,17 +7542,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854951</v>
+        <v>854897</v>
       </c>
       <c r="R68" t="n">
-        <v>7477899</v>
+        <v>7477846</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7588,6 +7597,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7606,10 +7616,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855377</v>
+        <v>124855235</v>
       </c>
       <c r="B69" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7618,42 +7628,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>854672</v>
+        <v>854686</v>
       </c>
       <c r="R69" t="n">
-        <v>7477865</v>
+        <v>7477923</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7680,17 +7686,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>I utkanten av nytt hygge</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7699,7 +7700,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7718,10 +7718,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855277</v>
+        <v>124855366</v>
       </c>
       <c r="B70" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7730,38 +7730,42 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>855068</v>
+        <v>854807</v>
       </c>
       <c r="R70" t="n">
-        <v>7478046</v>
+        <v>7477926</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7802,6 +7806,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7820,7 +7825,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855250</v>
+        <v>124855249</v>
       </c>
       <c r="B71" t="n">
         <v>91012</v>
@@ -7860,10 +7865,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>854814</v>
+        <v>854811</v>
       </c>
       <c r="R71" t="n">
-        <v>7477852</v>
+        <v>7477849</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7922,10 +7927,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855483</v>
+        <v>124855475</v>
       </c>
       <c r="B72" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7938,21 +7943,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7962,10 +7967,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>855251</v>
+        <v>854813</v>
       </c>
       <c r="R72" t="n">
-        <v>7478036</v>
+        <v>7477923</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8024,10 +8029,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855482</v>
+        <v>124855466</v>
       </c>
       <c r="B73" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8036,25 +8041,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8064,10 +8069,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>855134</v>
+        <v>854921</v>
       </c>
       <c r="R73" t="n">
-        <v>7477890</v>
+        <v>7478082</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8126,10 +8131,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855317</v>
+        <v>124855233</v>
       </c>
       <c r="B74" t="n">
-        <v>96985</v>
+        <v>105102</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8142,21 +8147,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8166,10 +8171,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>854783</v>
+        <v>855073</v>
       </c>
       <c r="R74" t="n">
-        <v>7477935</v>
+        <v>7477920</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8228,10 +8233,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855398</v>
+        <v>124855316</v>
       </c>
       <c r="B75" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8240,42 +8245,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854737</v>
+        <v>855019</v>
       </c>
       <c r="R75" t="n">
-        <v>7477850</v>
+        <v>7477888</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8302,17 +8303,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8321,7 +8317,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8340,7 +8335,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855366</v>
+        <v>124855415</v>
       </c>
       <c r="B76" t="n">
         <v>98101</v>
@@ -8373,21 +8368,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>854807</v>
+        <v>854928</v>
       </c>
       <c r="R76" t="n">
-        <v>7477926</v>
+        <v>7478107</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8428,7 +8419,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8447,10 +8437,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124855316</v>
+        <v>124855423</v>
       </c>
       <c r="B77" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8459,25 +8449,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8487,10 +8477,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>855019</v>
+        <v>854915</v>
       </c>
       <c r="R77" t="n">
-        <v>7477888</v>
+        <v>7477851</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8549,10 +8539,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855359</v>
+        <v>124855232</v>
       </c>
       <c r="B78" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8561,38 +8551,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>854838</v>
+        <v>855094</v>
       </c>
       <c r="R78" t="n">
-        <v>7477840</v>
+        <v>7477931</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8627,18 +8617,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8657,7 +8641,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855424</v>
+        <v>124855364</v>
       </c>
       <c r="B79" t="n">
         <v>98101</v>
@@ -8693,14 +8677,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>854780</v>
+        <v>855120</v>
       </c>
       <c r="R79" t="n">
-        <v>7477939</v>
+        <v>7477887</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8735,12 +8719,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8759,7 +8749,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124855417</v>
+        <v>124855380</v>
       </c>
       <c r="B80" t="n">
         <v>98101</v>
@@ -8799,10 +8789,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>855202</v>
+        <v>854745</v>
       </c>
       <c r="R80" t="n">
-        <v>7477976</v>
+        <v>7477946</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8843,6 +8833,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8861,10 +8852,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855244</v>
+        <v>124855418</v>
       </c>
       <c r="B81" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8873,25 +8864,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8901,10 +8892,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>855187</v>
+        <v>855131</v>
       </c>
       <c r="R81" t="n">
-        <v>7478029</v>
+        <v>7477924</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8963,10 +8954,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124855474</v>
+        <v>124855398</v>
       </c>
       <c r="B82" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8975,38 +8966,42 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>855065</v>
+        <v>854737</v>
       </c>
       <c r="R82" t="n">
-        <v>7478197</v>
+        <v>7477850</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9033,12 +9028,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9047,6 +9047,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9065,10 +9066,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855420</v>
+        <v>124854791</v>
       </c>
       <c r="B83" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9077,38 +9078,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>855071</v>
+        <v>854840</v>
       </c>
       <c r="R83" t="n">
-        <v>7477912</v>
+        <v>7477716</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9135,12 +9136,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9167,10 +9168,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855500</v>
+        <v>124855381</v>
       </c>
       <c r="B84" t="n">
-        <v>79826</v>
+        <v>98101</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9179,25 +9180,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6457</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9207,10 +9208,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>854850</v>
+        <v>854803</v>
       </c>
       <c r="R84" t="n">
-        <v>7477915</v>
+        <v>7477930</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9251,6 +9252,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9269,10 +9271,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855512</v>
+        <v>124855474</v>
       </c>
       <c r="B85" t="n">
-        <v>79926</v>
+        <v>56714</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9281,25 +9283,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6463</v>
+        <v>102612</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9309,10 +9311,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>854911</v>
+        <v>855065</v>
       </c>
       <c r="R85" t="n">
-        <v>7478164</v>
+        <v>7478197</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9371,7 +9373,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855390</v>
+        <v>124855421</v>
       </c>
       <c r="B86" t="n">
         <v>98101</v>
@@ -9404,21 +9406,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>854899</v>
+        <v>854951</v>
       </c>
       <c r="R86" t="n">
-        <v>7477831</v>
+        <v>7477899</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9459,7 +9457,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9478,7 +9475,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855358</v>
+        <v>124855417</v>
       </c>
       <c r="B87" t="n">
         <v>98101</v>
@@ -9514,14 +9511,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>854772</v>
+        <v>855202</v>
       </c>
       <c r="R87" t="n">
-        <v>7477881</v>
+        <v>7477976</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9556,18 +9553,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9586,7 +9577,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855376</v>
+        <v>124855464</v>
       </c>
       <c r="B88" t="n">
         <v>98101</v>
@@ -9619,21 +9610,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>854741</v>
+        <v>854898</v>
       </c>
       <c r="R88" t="n">
-        <v>7477958</v>
+        <v>7478156</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9674,7 +9661,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9693,10 +9679,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855416</v>
+        <v>124855244</v>
       </c>
       <c r="B89" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9705,25 +9691,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9733,10 +9719,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>855002</v>
+        <v>855187</v>
       </c>
       <c r="R89" t="n">
-        <v>7478149</v>
+        <v>7478029</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9795,7 +9781,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124855418</v>
+        <v>124855416</v>
       </c>
       <c r="B90" t="n">
         <v>98101</v>
@@ -9835,10 +9821,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>855131</v>
+        <v>855002</v>
       </c>
       <c r="R90" t="n">
-        <v>7477924</v>
+        <v>7478149</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9999,10 +9985,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124855364</v>
+        <v>124855524</v>
       </c>
       <c r="B92" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10011,38 +9997,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>855120</v>
+        <v>854793</v>
       </c>
       <c r="R92" t="n">
-        <v>7477887</v>
+        <v>7477805</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10069,17 +10055,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10088,7 +10069,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10107,7 +10087,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124855381</v>
+        <v>124855386</v>
       </c>
       <c r="B93" t="n">
         <v>98101</v>
@@ -10140,14 +10120,18 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>854803</v>
+        <v>854810</v>
       </c>
       <c r="R93" t="n">
         <v>7477930</v>
@@ -10210,10 +10194,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855333</v>
+        <v>124855275</v>
       </c>
       <c r="B94" t="n">
-        <v>79927</v>
+        <v>92321</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10222,38 +10206,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6464</v>
+        <v>5449</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>854924</v>
+        <v>854889</v>
       </c>
       <c r="R94" t="n">
-        <v>7478087</v>
+        <v>7477847</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10312,10 +10296,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855235</v>
+        <v>124855250</v>
       </c>
       <c r="B95" t="n">
-        <v>105102</v>
+        <v>91012</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10324,25 +10308,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221725</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10352,10 +10336,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>854686</v>
+        <v>854814</v>
       </c>
       <c r="R95" t="n">
-        <v>7477923</v>
+        <v>7477852</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10414,10 +10398,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855233</v>
+        <v>124855377</v>
       </c>
       <c r="B96" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10426,38 +10410,42 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>855073</v>
+        <v>854672</v>
       </c>
       <c r="R96" t="n">
-        <v>7477920</v>
+        <v>7477865</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10484,12 +10472,17 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>I utkanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10498,6 +10491,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10516,10 +10510,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124855313</v>
+        <v>124855468</v>
       </c>
       <c r="B97" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10528,25 +10522,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10556,10 +10550,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>854814</v>
+        <v>855069</v>
       </c>
       <c r="R97" t="n">
-        <v>7477852</v>
+        <v>7477999</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10618,10 +10612,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124854791</v>
+        <v>124855424</v>
       </c>
       <c r="B98" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10630,38 +10624,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>854840</v>
+        <v>854780</v>
       </c>
       <c r="R98" t="n">
-        <v>7477716</v>
+        <v>7477939</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10688,12 +10682,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10720,10 +10714,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124855232</v>
+        <v>124855500</v>
       </c>
       <c r="B99" t="n">
-        <v>105102</v>
+        <v>79826</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10736,21 +10730,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221725</v>
+        <v>6457</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10760,10 +10754,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>855094</v>
+        <v>854850</v>
       </c>
       <c r="R99" t="n">
-        <v>7477931</v>
+        <v>7477915</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10822,10 +10816,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124855469</v>
+        <v>124855483</v>
       </c>
       <c r="B100" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10834,25 +10828,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10862,10 +10856,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>854979</v>
+        <v>855251</v>
       </c>
       <c r="R100" t="n">
-        <v>7477885</v>
+        <v>7478036</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10924,7 +10918,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855466</v>
+        <v>124855359</v>
       </c>
       <c r="B101" t="n">
         <v>98101</v>
@@ -10960,14 +10954,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>854921</v>
+        <v>854838</v>
       </c>
       <c r="R101" t="n">
-        <v>7478082</v>
+        <v>7477840</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11002,12 +10996,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11026,7 +11026,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124855386</v>
+        <v>124855389</v>
       </c>
       <c r="B102" t="n">
         <v>98101</v>
@@ -11061,7 +11061,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -11070,10 +11070,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>854810</v>
+        <v>854906</v>
       </c>
       <c r="R102" t="n">
-        <v>7477930</v>
+        <v>7477891</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11133,10 +11133,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855475</v>
+        <v>124855376</v>
       </c>
       <c r="B103" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11145,38 +11145,42 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>854813</v>
+        <v>854741</v>
       </c>
       <c r="R103" t="n">
-        <v>7477923</v>
+        <v>7477958</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11217,6 +11221,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11235,10 +11240,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855415</v>
+        <v>124855333</v>
       </c>
       <c r="B104" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11247,25 +11252,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11275,10 +11280,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>854928</v>
+        <v>854924</v>
       </c>
       <c r="R104" t="n">
-        <v>7478107</v>
+        <v>7478087</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11337,10 +11342,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855371</v>
+        <v>124855318</v>
       </c>
       <c r="B105" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11349,42 +11354,38 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>854845</v>
+        <v>854817</v>
       </c>
       <c r="R105" t="n">
-        <v>7477869</v>
+        <v>7477931</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11425,7 +11426,6 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11444,10 +11444,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855464</v>
+        <v>124855482</v>
       </c>
       <c r="B106" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11456,25 +11456,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11484,10 +11484,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>854898</v>
+        <v>855134</v>
       </c>
       <c r="R106" t="n">
-        <v>7478156</v>
+        <v>7477890</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11546,10 +11546,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855231</v>
+        <v>124855469</v>
       </c>
       <c r="B107" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11558,25 +11558,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11586,10 +11586,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>854954</v>
+        <v>854979</v>
       </c>
       <c r="R107" t="n">
-        <v>7478125</v>
+        <v>7477885</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11648,7 +11648,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855394</v>
+        <v>124855390</v>
       </c>
       <c r="B108" t="n">
         <v>98101</v>
@@ -11683,7 +11683,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -11692,10 +11692,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>854897</v>
+        <v>854899</v>
       </c>
       <c r="R108" t="n">
-        <v>7477846</v>
+        <v>7477831</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11755,10 +11755,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855275</v>
+        <v>124855317</v>
       </c>
       <c r="B109" t="n">
-        <v>92321</v>
+        <v>96985</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11767,38 +11767,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5449</v>
+        <v>221941</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>854889</v>
+        <v>854783</v>
       </c>
       <c r="R109" t="n">
-        <v>7477847</v>
+        <v>7477935</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -4159,7 +4159,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427400</v>
+        <v>124427402</v>
       </c>
       <c r="B36" t="n">
         <v>82597</v>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>855012</v>
+        <v>854960</v>
       </c>
       <c r="R36" t="n">
-        <v>7478269</v>
+        <v>7478309</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4261,10 +4261,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427356</v>
+        <v>124427375</v>
       </c>
       <c r="B37" t="n">
-        <v>79926</v>
+        <v>79927</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4277,34 +4277,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>854977</v>
+        <v>854922</v>
       </c>
       <c r="R37" t="n">
-        <v>7478167</v>
+        <v>7478323</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4345,8 +4345,24 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4363,10 +4379,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427345</v>
+        <v>124427351</v>
       </c>
       <c r="B38" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4375,38 +4391,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>854967</v>
+        <v>855056</v>
       </c>
       <c r="R38" t="n">
-        <v>7478177</v>
+        <v>7478165</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4447,6 +4467,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4465,10 +4486,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427347</v>
+        <v>124427389</v>
       </c>
       <c r="B39" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4477,38 +4498,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>855063</v>
+        <v>855110</v>
       </c>
       <c r="R39" t="n">
-        <v>7478044</v>
+        <v>7478072</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4549,6 +4574,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4567,10 +4593,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427401</v>
+        <v>124427391</v>
       </c>
       <c r="B40" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4579,38 +4605,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>855011</v>
+        <v>855091</v>
       </c>
       <c r="R40" t="n">
-        <v>7478352</v>
+        <v>7478207</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4651,6 +4681,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4669,10 +4700,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427365</v>
+        <v>124427401</v>
       </c>
       <c r="B41" t="n">
-        <v>79428</v>
+        <v>82597</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4685,21 +4716,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4709,10 +4740,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>854939</v>
+        <v>855011</v>
       </c>
       <c r="R41" t="n">
-        <v>7478324</v>
+        <v>7478352</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4771,10 +4802,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427406</v>
+        <v>124427386</v>
       </c>
       <c r="B42" t="n">
-        <v>91579</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4787,41 +4818,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>117</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>855096</v>
+        <v>855066</v>
       </c>
       <c r="R42" t="n">
-        <v>7478199</v>
+        <v>7478180</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4854,11 +4882,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-24</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4886,10 +4909,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427369</v>
+        <v>124427388</v>
       </c>
       <c r="B43" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4898,38 +4921,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>854943</v>
+        <v>855074</v>
       </c>
       <c r="R43" t="n">
-        <v>7478362</v>
+        <v>7478164</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4970,6 +4997,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4988,10 +5016,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427403</v>
+        <v>124427352</v>
       </c>
       <c r="B44" t="n">
-        <v>79826</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5000,38 +5028,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6457</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>854946</v>
+        <v>855059</v>
       </c>
       <c r="R44" t="n">
-        <v>7478367</v>
+        <v>7478173</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5091,10 +5123,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427399</v>
+        <v>124427387</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5103,38 +5135,42 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>855007</v>
+        <v>855102</v>
       </c>
       <c r="R45" t="n">
-        <v>7478357</v>
+        <v>7478191</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5175,6 +5211,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5193,10 +5230,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427389</v>
+        <v>124427406</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>91579</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5209,38 +5246,41 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>855110</v>
+        <v>855096</v>
       </c>
       <c r="R46" t="n">
-        <v>7478072</v>
+        <v>7478199</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5273,6 +5313,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5300,10 +5345,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427402</v>
+        <v>124427403</v>
       </c>
       <c r="B47" t="n">
-        <v>82597</v>
+        <v>79826</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5312,25 +5357,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>6457</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5340,10 +5385,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>854960</v>
+        <v>854946</v>
       </c>
       <c r="R47" t="n">
-        <v>7478309</v>
+        <v>7478367</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5384,6 +5429,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5402,7 +5448,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427354</v>
+        <v>124427398</v>
       </c>
       <c r="B48" t="n">
         <v>78810</v>
@@ -5438,14 +5484,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>855018</v>
+        <v>855100</v>
       </c>
       <c r="R48" t="n">
-        <v>7478119</v>
+        <v>7478058</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5504,10 +5550,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427375</v>
+        <v>124427354</v>
       </c>
       <c r="B49" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5516,38 +5562,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>854922</v>
+        <v>855018</v>
       </c>
       <c r="R49" t="n">
-        <v>7478323</v>
+        <v>7478119</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5588,24 +5634,8 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5724,10 +5754,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427387</v>
+        <v>124427345</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5736,42 +5766,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>855102</v>
+        <v>854967</v>
       </c>
       <c r="R51" t="n">
-        <v>7478191</v>
+        <v>7478177</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5812,7 +5838,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5831,10 +5856,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427351</v>
+        <v>124427346</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5843,42 +5868,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>855056</v>
+        <v>855044</v>
       </c>
       <c r="R52" t="n">
-        <v>7478165</v>
+        <v>7478074</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5919,7 +5940,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5938,10 +5958,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427352</v>
+        <v>124427347</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5950,42 +5970,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855059</v>
+        <v>855063</v>
       </c>
       <c r="R53" t="n">
-        <v>7478173</v>
+        <v>7478044</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6026,7 +6042,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6045,10 +6060,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427391</v>
+        <v>124427356</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6057,42 +6072,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>855091</v>
+        <v>854977</v>
       </c>
       <c r="R54" t="n">
-        <v>7478207</v>
+        <v>7478167</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6133,7 +6144,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6152,10 +6162,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427398</v>
+        <v>124427365</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6168,21 +6178,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6192,10 +6202,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>855100</v>
+        <v>854939</v>
       </c>
       <c r="R55" t="n">
-        <v>7478058</v>
+        <v>7478324</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6254,10 +6264,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427346</v>
+        <v>124427400</v>
       </c>
       <c r="B56" t="n">
-        <v>79927</v>
+        <v>82597</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6266,38 +6276,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>855044</v>
+        <v>855012</v>
       </c>
       <c r="R56" t="n">
-        <v>7478074</v>
+        <v>7478269</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6356,10 +6366,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124427388</v>
+        <v>124427369</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6368,42 +6378,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>855074</v>
+        <v>854943</v>
       </c>
       <c r="R57" t="n">
-        <v>7478164</v>
+        <v>7478362</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6444,7 +6450,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6463,10 +6468,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124427386</v>
+        <v>124427399</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6475,42 +6480,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>855066</v>
+        <v>855007</v>
       </c>
       <c r="R58" t="n">
-        <v>7478180</v>
+        <v>7478357</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6551,7 +6552,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6570,10 +6570,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855512</v>
+        <v>124855421</v>
       </c>
       <c r="B59" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6582,25 +6582,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>854911</v>
+        <v>854951</v>
       </c>
       <c r="R59" t="n">
-        <v>7478164</v>
+        <v>7477899</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6672,7 +6672,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855420</v>
+        <v>124855404</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -6705,17 +6705,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>855071</v>
+        <v>854832</v>
       </c>
       <c r="R60" t="n">
-        <v>7477912</v>
+        <v>7477880</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6756,6 +6760,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6774,10 +6779,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124855231</v>
+        <v>124855418</v>
       </c>
       <c r="B61" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6786,25 +6791,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6814,10 +6819,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>854954</v>
+        <v>855131</v>
       </c>
       <c r="R61" t="n">
-        <v>7478125</v>
+        <v>7477924</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6876,10 +6881,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124855404</v>
+        <v>124855317</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6888,42 +6893,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>854832</v>
+        <v>854783</v>
       </c>
       <c r="R62" t="n">
-        <v>7477880</v>
+        <v>7477935</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6964,7 +6965,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6983,10 +6983,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124855313</v>
+        <v>124855250</v>
       </c>
       <c r="B63" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6999,21 +6999,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7085,10 +7085,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124855277</v>
+        <v>124855475</v>
       </c>
       <c r="B64" t="n">
-        <v>79920</v>
+        <v>56714</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7097,25 +7097,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7125,10 +7125,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>855068</v>
+        <v>854813</v>
       </c>
       <c r="R64" t="n">
-        <v>7478046</v>
+        <v>7477923</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7187,7 +7187,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124854790</v>
+        <v>124855381</v>
       </c>
       <c r="B65" t="n">
         <v>98101</v>
@@ -7220,21 +7220,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>854766</v>
+        <v>854803</v>
       </c>
       <c r="R65" t="n">
-        <v>7478012</v>
+        <v>7477930</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7294,7 +7290,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855371</v>
+        <v>124855423</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -7327,21 +7323,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>854845</v>
+        <v>854915</v>
       </c>
       <c r="R66" t="n">
-        <v>7477869</v>
+        <v>7477851</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7382,7 +7374,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7401,10 +7392,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855358</v>
+        <v>124855275</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
+        <v>92321</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7413,25 +7404,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7441,10 +7432,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>854772</v>
+        <v>854889</v>
       </c>
       <c r="R67" t="n">
-        <v>7477881</v>
+        <v>7477847</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7479,18 +7470,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7509,10 +7494,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855394</v>
+        <v>124855232</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7521,42 +7506,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854897</v>
+        <v>855094</v>
       </c>
       <c r="R68" t="n">
-        <v>7477846</v>
+        <v>7477931</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7597,7 +7578,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7616,10 +7596,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855235</v>
+        <v>124855398</v>
       </c>
       <c r="B69" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7628,38 +7608,42 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>854686</v>
+        <v>854737</v>
       </c>
       <c r="R69" t="n">
-        <v>7477923</v>
+        <v>7477850</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7686,12 +7670,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7700,6 +7689,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7718,7 +7708,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855366</v>
+        <v>124855390</v>
       </c>
       <c r="B70" t="n">
         <v>98101</v>
@@ -7753,7 +7743,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>28</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -7762,10 +7752,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>854807</v>
+        <v>854899</v>
       </c>
       <c r="R70" t="n">
-        <v>7477926</v>
+        <v>7477831</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7825,10 +7815,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855249</v>
+        <v>124855358</v>
       </c>
       <c r="B71" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7837,38 +7827,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>854811</v>
+        <v>854772</v>
       </c>
       <c r="R71" t="n">
-        <v>7477849</v>
+        <v>7477881</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7903,12 +7893,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7927,10 +7923,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855475</v>
+        <v>124854791</v>
       </c>
       <c r="B72" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7943,34 +7939,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>854813</v>
+        <v>854840</v>
       </c>
       <c r="R72" t="n">
-        <v>7477923</v>
+        <v>7477716</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7997,12 +7993,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8029,7 +8025,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855466</v>
+        <v>124855464</v>
       </c>
       <c r="B73" t="n">
         <v>98101</v>
@@ -8069,10 +8065,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>854921</v>
+        <v>854898</v>
       </c>
       <c r="R73" t="n">
-        <v>7478082</v>
+        <v>7478156</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8131,10 +8127,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855233</v>
+        <v>124855377</v>
       </c>
       <c r="B74" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8143,38 +8139,42 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>855073</v>
+        <v>854672</v>
       </c>
       <c r="R74" t="n">
-        <v>7477920</v>
+        <v>7477865</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8201,12 +8201,17 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>I utkanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8215,6 +8220,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8233,10 +8239,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855316</v>
+        <v>124855389</v>
       </c>
       <c r="B75" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8245,38 +8251,42 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>855019</v>
+        <v>854906</v>
       </c>
       <c r="R75" t="n">
-        <v>7477888</v>
+        <v>7477891</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8317,6 +8327,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8335,7 +8346,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855415</v>
+        <v>124855424</v>
       </c>
       <c r="B76" t="n">
         <v>98101</v>
@@ -8375,10 +8386,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>854928</v>
+        <v>854780</v>
       </c>
       <c r="R76" t="n">
-        <v>7478107</v>
+        <v>7477939</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8437,7 +8448,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124855423</v>
+        <v>124855467</v>
       </c>
       <c r="B77" t="n">
         <v>98101</v>
@@ -8477,10 +8488,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>854915</v>
+        <v>855062</v>
       </c>
       <c r="R77" t="n">
-        <v>7477851</v>
+        <v>7478002</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8539,10 +8550,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855232</v>
+        <v>124855386</v>
       </c>
       <c r="B78" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8551,38 +8562,42 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>855094</v>
+        <v>854810</v>
       </c>
       <c r="R78" t="n">
-        <v>7477931</v>
+        <v>7477930</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8623,6 +8638,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8641,10 +8657,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855364</v>
+        <v>124855277</v>
       </c>
       <c r="B79" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8653,38 +8669,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>855120</v>
+        <v>855068</v>
       </c>
       <c r="R79" t="n">
-        <v>7477887</v>
+        <v>7478046</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8719,18 +8735,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8749,7 +8759,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124855380</v>
+        <v>124855415</v>
       </c>
       <c r="B80" t="n">
         <v>98101</v>
@@ -8789,10 +8799,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>854745</v>
+        <v>854928</v>
       </c>
       <c r="R80" t="n">
-        <v>7477946</v>
+        <v>7478107</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8833,7 +8843,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8852,7 +8861,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855418</v>
+        <v>124855394</v>
       </c>
       <c r="B81" t="n">
         <v>98101</v>
@@ -8885,17 +8894,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>855131</v>
+        <v>854897</v>
       </c>
       <c r="R81" t="n">
-        <v>7477924</v>
+        <v>7477846</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8936,6 +8949,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8954,7 +8968,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124855398</v>
+        <v>124855469</v>
       </c>
       <c r="B82" t="n">
         <v>98101</v>
@@ -8987,21 +9001,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>854737</v>
+        <v>854979</v>
       </c>
       <c r="R82" t="n">
-        <v>7477850</v>
+        <v>7477885</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9028,17 +9038,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9047,7 +9052,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9066,10 +9070,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124854791</v>
+        <v>124855468</v>
       </c>
       <c r="B83" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9078,38 +9082,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>854840</v>
+        <v>855069</v>
       </c>
       <c r="R83" t="n">
-        <v>7477716</v>
+        <v>7477999</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9136,12 +9140,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9168,7 +9172,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855381</v>
+        <v>124855420</v>
       </c>
       <c r="B84" t="n">
         <v>98101</v>
@@ -9208,10 +9212,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>854803</v>
+        <v>855071</v>
       </c>
       <c r="R84" t="n">
-        <v>7477930</v>
+        <v>7477912</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9252,7 +9256,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9271,10 +9274,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855474</v>
+        <v>124855466</v>
       </c>
       <c r="B85" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9283,25 +9286,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9311,10 +9314,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>855065</v>
+        <v>854921</v>
       </c>
       <c r="R85" t="n">
-        <v>7478197</v>
+        <v>7478082</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9373,7 +9376,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855421</v>
+        <v>124855359</v>
       </c>
       <c r="B86" t="n">
         <v>98101</v>
@@ -9409,14 +9412,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>854951</v>
+        <v>854838</v>
       </c>
       <c r="R86" t="n">
-        <v>7477899</v>
+        <v>7477840</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9451,12 +9454,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9475,10 +9484,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855417</v>
+        <v>124855483</v>
       </c>
       <c r="B87" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9487,25 +9496,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9515,10 +9524,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>855202</v>
+        <v>855251</v>
       </c>
       <c r="R87" t="n">
-        <v>7477976</v>
+        <v>7478036</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9577,7 +9586,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855464</v>
+        <v>124855366</v>
       </c>
       <c r="B88" t="n">
         <v>98101</v>
@@ -9610,17 +9619,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>854898</v>
+        <v>854807</v>
       </c>
       <c r="R88" t="n">
-        <v>7478156</v>
+        <v>7477926</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9661,6 +9674,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9679,10 +9693,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855244</v>
+        <v>124855376</v>
       </c>
       <c r="B89" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9691,38 +9705,42 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>855187</v>
+        <v>854741</v>
       </c>
       <c r="R89" t="n">
-        <v>7478029</v>
+        <v>7477958</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9763,6 +9781,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9781,10 +9800,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124855416</v>
+        <v>124855316</v>
       </c>
       <c r="B90" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9793,25 +9812,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9821,10 +9840,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>855002</v>
+        <v>855019</v>
       </c>
       <c r="R90" t="n">
-        <v>7478149</v>
+        <v>7477888</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9883,10 +9902,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124855467</v>
+        <v>124855318</v>
       </c>
       <c r="B91" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9895,25 +9914,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9923,10 +9942,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>855062</v>
+        <v>854817</v>
       </c>
       <c r="R91" t="n">
-        <v>7478002</v>
+        <v>7477931</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9985,10 +10004,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124855524</v>
+        <v>124855371</v>
       </c>
       <c r="B92" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9997,38 +10016,42 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>854793</v>
+        <v>854845</v>
       </c>
       <c r="R92" t="n">
-        <v>7477805</v>
+        <v>7477869</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10055,12 +10078,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10069,6 +10092,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10087,10 +10111,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124855386</v>
+        <v>124855233</v>
       </c>
       <c r="B93" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10099,42 +10123,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>854810</v>
+        <v>855073</v>
       </c>
       <c r="R93" t="n">
-        <v>7477930</v>
+        <v>7477920</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10175,7 +10195,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10194,10 +10213,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855275</v>
+        <v>124855313</v>
       </c>
       <c r="B94" t="n">
-        <v>92321</v>
+        <v>91299</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10210,34 +10229,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5449</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>854889</v>
+        <v>854814</v>
       </c>
       <c r="R94" t="n">
-        <v>7477847</v>
+        <v>7477852</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10296,10 +10315,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855250</v>
+        <v>124855512</v>
       </c>
       <c r="B95" t="n">
-        <v>91012</v>
+        <v>79926</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10308,25 +10327,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10336,10 +10355,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>854814</v>
+        <v>854911</v>
       </c>
       <c r="R95" t="n">
-        <v>7477852</v>
+        <v>7478164</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10398,10 +10417,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855377</v>
+        <v>124855474</v>
       </c>
       <c r="B96" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10410,42 +10429,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>854672</v>
+        <v>855065</v>
       </c>
       <c r="R96" t="n">
-        <v>7477865</v>
+        <v>7478197</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10472,17 +10487,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>I utkanten av nytt hygge</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10491,7 +10501,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10510,10 +10519,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124855468</v>
+        <v>124855231</v>
       </c>
       <c r="B97" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10522,25 +10531,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10550,10 +10559,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>855069</v>
+        <v>854954</v>
       </c>
       <c r="R97" t="n">
-        <v>7477999</v>
+        <v>7478125</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10612,10 +10621,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124855424</v>
+        <v>124855500</v>
       </c>
       <c r="B98" t="n">
-        <v>98101</v>
+        <v>79826</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10624,25 +10633,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10652,10 +10661,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>854780</v>
+        <v>854850</v>
       </c>
       <c r="R98" t="n">
-        <v>7477939</v>
+        <v>7477915</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10714,10 +10723,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124855500</v>
+        <v>124855482</v>
       </c>
       <c r="B99" t="n">
-        <v>79826</v>
+        <v>78810</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10726,25 +10735,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10754,10 +10763,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>854850</v>
+        <v>855134</v>
       </c>
       <c r="R99" t="n">
-        <v>7477915</v>
+        <v>7477890</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10816,10 +10825,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124855483</v>
+        <v>124854790</v>
       </c>
       <c r="B100" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10828,38 +10837,42 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>855251</v>
+        <v>854766</v>
       </c>
       <c r="R100" t="n">
-        <v>7478036</v>
+        <v>7478012</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10900,6 +10913,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10918,10 +10932,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855359</v>
+        <v>124855244</v>
       </c>
       <c r="B101" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10930,38 +10944,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>854838</v>
+        <v>855187</v>
       </c>
       <c r="R101" t="n">
-        <v>7477840</v>
+        <v>7478029</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10996,18 +11010,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11026,10 +11034,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124855389</v>
+        <v>124855524</v>
       </c>
       <c r="B102" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11038,42 +11046,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>854906</v>
+        <v>854793</v>
       </c>
       <c r="R102" t="n">
-        <v>7477891</v>
+        <v>7477805</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11100,12 +11104,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11114,7 +11118,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11133,7 +11136,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855376</v>
+        <v>124855417</v>
       </c>
       <c r="B103" t="n">
         <v>98101</v>
@@ -11166,21 +11169,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>854741</v>
+        <v>855202</v>
       </c>
       <c r="R103" t="n">
-        <v>7477958</v>
+        <v>7477976</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11221,7 +11220,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11240,10 +11238,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855333</v>
+        <v>124855380</v>
       </c>
       <c r="B104" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11252,25 +11250,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11280,10 +11278,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>854924</v>
+        <v>854745</v>
       </c>
       <c r="R104" t="n">
-        <v>7478087</v>
+        <v>7477946</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11324,6 +11322,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11342,10 +11341,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855318</v>
+        <v>124855333</v>
       </c>
       <c r="B105" t="n">
-        <v>96985</v>
+        <v>79927</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11358,21 +11357,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221941</v>
+        <v>6464</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11382,10 +11381,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>854817</v>
+        <v>854924</v>
       </c>
       <c r="R105" t="n">
-        <v>7477931</v>
+        <v>7478087</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11444,10 +11443,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855482</v>
+        <v>124855364</v>
       </c>
       <c r="B106" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11456,38 +11455,38 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>855134</v>
+        <v>855120</v>
       </c>
       <c r="R106" t="n">
-        <v>7477890</v>
+        <v>7477887</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11522,12 +11521,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11546,7 +11551,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855469</v>
+        <v>124855416</v>
       </c>
       <c r="B107" t="n">
         <v>98101</v>
@@ -11586,10 +11591,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>854979</v>
+        <v>855002</v>
       </c>
       <c r="R107" t="n">
-        <v>7477885</v>
+        <v>7478149</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11648,10 +11653,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855390</v>
+        <v>124855235</v>
       </c>
       <c r="B108" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11660,42 +11665,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>854899</v>
+        <v>854686</v>
       </c>
       <c r="R108" t="n">
-        <v>7477831</v>
+        <v>7477923</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11736,7 +11737,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11755,10 +11755,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855317</v>
+        <v>124855249</v>
       </c>
       <c r="B109" t="n">
-        <v>96985</v>
+        <v>91012</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11767,25 +11767,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11795,10 +11795,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>854783</v>
+        <v>854811</v>
       </c>
       <c r="R109" t="n">
-        <v>7477935</v>
+        <v>7477849</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -4486,7 +4486,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427389</v>
+        <v>124427391</v>
       </c>
       <c r="B39" t="n">
         <v>98101</v>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>855110</v>
+        <v>855091</v>
       </c>
       <c r="R39" t="n">
-        <v>7478072</v>
+        <v>7478207</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4593,7 +4593,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427391</v>
+        <v>124427389</v>
       </c>
       <c r="B40" t="n">
         <v>98101</v>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>855091</v>
+        <v>855110</v>
       </c>
       <c r="R40" t="n">
-        <v>7478207</v>
+        <v>7478072</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -7290,10 +7290,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855423</v>
+        <v>124855232</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7302,25 +7302,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>854915</v>
+        <v>855094</v>
       </c>
       <c r="R66" t="n">
-        <v>7477851</v>
+        <v>7477931</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7392,10 +7392,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855275</v>
+        <v>124855390</v>
       </c>
       <c r="B67" t="n">
-        <v>92321</v>
+        <v>98101</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7404,38 +7404,42 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>854889</v>
+        <v>854899</v>
       </c>
       <c r="R67" t="n">
-        <v>7477847</v>
+        <v>7477831</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7476,6 +7480,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7494,10 +7499,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855232</v>
+        <v>124855358</v>
       </c>
       <c r="B68" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7506,38 +7511,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>855094</v>
+        <v>854772</v>
       </c>
       <c r="R68" t="n">
-        <v>7477931</v>
+        <v>7477881</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7572,12 +7577,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7596,10 +7607,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855398</v>
+        <v>124854791</v>
       </c>
       <c r="B69" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7608,42 +7619,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>854737</v>
+        <v>854840</v>
       </c>
       <c r="R69" t="n">
-        <v>7477850</v>
+        <v>7477716</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7678,18 +7685,12 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7708,7 +7709,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855390</v>
+        <v>124855423</v>
       </c>
       <c r="B70" t="n">
         <v>98101</v>
@@ -7741,21 +7742,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>854899</v>
+        <v>854915</v>
       </c>
       <c r="R70" t="n">
-        <v>7477831</v>
+        <v>7477851</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7796,7 +7793,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7815,10 +7811,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855358</v>
+        <v>124855275</v>
       </c>
       <c r="B71" t="n">
-        <v>98101</v>
+        <v>92321</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7827,25 +7823,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7855,10 +7851,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>854772</v>
+        <v>854889</v>
       </c>
       <c r="R71" t="n">
-        <v>7477881</v>
+        <v>7477847</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7893,18 +7889,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7923,10 +7913,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124854791</v>
+        <v>124855398</v>
       </c>
       <c r="B72" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7935,38 +7925,42 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>854840</v>
+        <v>854737</v>
       </c>
       <c r="R72" t="n">
-        <v>7477716</v>
+        <v>7477850</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8001,12 +7995,18 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8025,7 +8025,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855464</v>
+        <v>124855377</v>
       </c>
       <c r="B73" t="n">
         <v>98101</v>
@@ -8058,17 +8058,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>854898</v>
+        <v>854672</v>
       </c>
       <c r="R73" t="n">
-        <v>7478156</v>
+        <v>7477865</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8095,12 +8099,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>I utkanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8109,6 +8118,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8127,7 +8137,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855377</v>
+        <v>124855389</v>
       </c>
       <c r="B74" t="n">
         <v>98101</v>
@@ -8162,19 +8172,19 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>854672</v>
+        <v>854906</v>
       </c>
       <c r="R74" t="n">
-        <v>7477865</v>
+        <v>7477891</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8201,17 +8211,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>I utkanten av nytt hygge</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8239,7 +8244,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855389</v>
+        <v>124855424</v>
       </c>
       <c r="B75" t="n">
         <v>98101</v>
@@ -8272,21 +8277,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854906</v>
+        <v>854780</v>
       </c>
       <c r="R75" t="n">
-        <v>7477891</v>
+        <v>7477939</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8327,7 +8328,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8346,7 +8346,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855424</v>
+        <v>124855464</v>
       </c>
       <c r="B76" t="n">
         <v>98101</v>
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>854780</v>
+        <v>854898</v>
       </c>
       <c r="R76" t="n">
-        <v>7477939</v>
+        <v>7478156</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9484,10 +9484,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855483</v>
+        <v>124855366</v>
       </c>
       <c r="B87" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9496,38 +9496,42 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>855251</v>
+        <v>854807</v>
       </c>
       <c r="R87" t="n">
-        <v>7478036</v>
+        <v>7477926</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9568,6 +9572,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9586,10 +9591,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855366</v>
+        <v>124855483</v>
       </c>
       <c r="B88" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9598,42 +9603,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>854807</v>
+        <v>855251</v>
       </c>
       <c r="R88" t="n">
-        <v>7477926</v>
+        <v>7478036</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9674,7 +9675,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427402</v>
+        <v>124427351</v>
       </c>
       <c r="B36" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4171,38 +4171,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>854960</v>
+        <v>855056</v>
       </c>
       <c r="R36" t="n">
-        <v>7478309</v>
+        <v>7478165</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4243,6 +4247,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4261,10 +4266,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427375</v>
+        <v>124427365</v>
       </c>
       <c r="B37" t="n">
-        <v>79927</v>
+        <v>79428</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4273,25 +4278,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4301,10 +4306,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>854922</v>
+        <v>854939</v>
       </c>
       <c r="R37" t="n">
-        <v>7478323</v>
+        <v>7478324</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4345,24 +4350,8 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4379,10 +4368,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427351</v>
+        <v>124427401</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>82597</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4391,42 +4380,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>855056</v>
+        <v>855011</v>
       </c>
       <c r="R38" t="n">
-        <v>7478165</v>
+        <v>7478352</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4467,7 +4452,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4486,10 +4470,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427391</v>
+        <v>124427369</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4498,42 +4482,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>855091</v>
+        <v>854943</v>
       </c>
       <c r="R39" t="n">
-        <v>7478207</v>
+        <v>7478362</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4574,7 +4554,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4593,7 +4572,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427389</v>
+        <v>124427386</v>
       </c>
       <c r="B40" t="n">
         <v>98101</v>
@@ -4628,7 +4607,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>117</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4637,10 +4616,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>855110</v>
+        <v>855066</v>
       </c>
       <c r="R40" t="n">
-        <v>7478072</v>
+        <v>7478180</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4700,10 +4679,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427401</v>
+        <v>124427356</v>
       </c>
       <c r="B41" t="n">
-        <v>82597</v>
+        <v>79926</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4712,38 +4691,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>855011</v>
+        <v>854977</v>
       </c>
       <c r="R41" t="n">
-        <v>7478352</v>
+        <v>7478167</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4802,10 +4781,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427386</v>
+        <v>124427399</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4814,42 +4793,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>855066</v>
+        <v>855007</v>
       </c>
       <c r="R42" t="n">
-        <v>7478180</v>
+        <v>7478357</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4890,7 +4865,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4909,7 +4883,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427388</v>
+        <v>124427389</v>
       </c>
       <c r="B43" t="n">
         <v>98101</v>
@@ -4944,7 +4918,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4953,10 +4927,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>855074</v>
+        <v>855110</v>
       </c>
       <c r="R43" t="n">
-        <v>7478164</v>
+        <v>7478072</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5016,10 +4990,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427352</v>
+        <v>124427345</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5028,42 +5002,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>855059</v>
+        <v>854967</v>
       </c>
       <c r="R44" t="n">
-        <v>7478173</v>
+        <v>7478177</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5104,7 +5074,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5123,7 +5092,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427387</v>
+        <v>124427388</v>
       </c>
       <c r="B45" t="n">
         <v>98101</v>
@@ -5158,7 +5127,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>73</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5167,10 +5136,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>855102</v>
+        <v>855074</v>
       </c>
       <c r="R45" t="n">
-        <v>7478191</v>
+        <v>7478164</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5230,10 +5199,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427406</v>
+        <v>124427398</v>
       </c>
       <c r="B46" t="n">
-        <v>91579</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5242,45 +5211,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>855096</v>
+        <v>855100</v>
       </c>
       <c r="R46" t="n">
-        <v>7478199</v>
+        <v>7478058</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5315,18 +5277,12 @@
           <t>2025-04-24</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5345,10 +5301,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427403</v>
+        <v>124427352</v>
       </c>
       <c r="B47" t="n">
-        <v>79826</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5357,38 +5313,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6457</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>854946</v>
+        <v>855059</v>
       </c>
       <c r="R47" t="n">
-        <v>7478367</v>
+        <v>7478173</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5448,10 +5408,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427398</v>
+        <v>124427387</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5460,38 +5420,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>855100</v>
+        <v>855102</v>
       </c>
       <c r="R48" t="n">
-        <v>7478058</v>
+        <v>7478191</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5532,6 +5496,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5652,10 +5617,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427393</v>
+        <v>124427346</v>
       </c>
       <c r="B50" t="n">
-        <v>56714</v>
+        <v>79927</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5664,38 +5629,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>854990</v>
+        <v>855044</v>
       </c>
       <c r="R50" t="n">
-        <v>7478363</v>
+        <v>7478074</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5754,10 +5719,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427345</v>
+        <v>124427406</v>
       </c>
       <c r="B51" t="n">
-        <v>79927</v>
+        <v>91579</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5766,38 +5731,45 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>760</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>854967</v>
+        <v>855096</v>
       </c>
       <c r="R51" t="n">
-        <v>7478177</v>
+        <v>7478199</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5832,12 +5804,18 @@
           <t>2025-04-24</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5856,10 +5834,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427346</v>
+        <v>124427391</v>
       </c>
       <c r="B52" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5868,38 +5846,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>855044</v>
+        <v>855091</v>
       </c>
       <c r="R52" t="n">
-        <v>7478074</v>
+        <v>7478207</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5940,6 +5922,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5958,10 +5941,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427347</v>
+        <v>124427400</v>
       </c>
       <c r="B53" t="n">
-        <v>79927</v>
+        <v>82597</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5970,38 +5953,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855063</v>
+        <v>855012</v>
       </c>
       <c r="R53" t="n">
-        <v>7478044</v>
+        <v>7478269</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6060,10 +6043,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427356</v>
+        <v>124427375</v>
       </c>
       <c r="B54" t="n">
-        <v>79926</v>
+        <v>79927</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6076,34 +6059,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>854977</v>
+        <v>854922</v>
       </c>
       <c r="R54" t="n">
-        <v>7478167</v>
+        <v>7478323</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6144,8 +6127,24 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6162,10 +6161,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427365</v>
+        <v>124427347</v>
       </c>
       <c r="B55" t="n">
-        <v>79428</v>
+        <v>79927</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6174,38 +6173,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>854939</v>
+        <v>855063</v>
       </c>
       <c r="R55" t="n">
-        <v>7478324</v>
+        <v>7478044</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6264,10 +6263,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427400</v>
+        <v>124427393</v>
       </c>
       <c r="B56" t="n">
-        <v>82597</v>
+        <v>56714</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6280,21 +6279,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6304,10 +6303,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>855012</v>
+        <v>854990</v>
       </c>
       <c r="R56" t="n">
-        <v>7478269</v>
+        <v>7478363</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6366,10 +6365,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124427369</v>
+        <v>124427402</v>
       </c>
       <c r="B57" t="n">
-        <v>57666</v>
+        <v>82597</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6382,21 +6381,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6406,10 +6405,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>854943</v>
+        <v>854960</v>
       </c>
       <c r="R57" t="n">
-        <v>7478362</v>
+        <v>7478309</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6468,10 +6467,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124427399</v>
+        <v>124427403</v>
       </c>
       <c r="B58" t="n">
-        <v>78810</v>
+        <v>79826</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6480,25 +6479,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6508,10 +6507,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>855007</v>
+        <v>854946</v>
       </c>
       <c r="R58" t="n">
-        <v>7478357</v>
+        <v>7478367</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6552,6 +6551,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6570,10 +6570,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855421</v>
+        <v>124855475</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6582,25 +6582,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>854951</v>
+        <v>854813</v>
       </c>
       <c r="R59" t="n">
-        <v>7477899</v>
+        <v>7477923</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6672,7 +6672,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855404</v>
+        <v>124855417</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -6705,21 +6705,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>854832</v>
+        <v>855202</v>
       </c>
       <c r="R60" t="n">
-        <v>7477880</v>
+        <v>7477976</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6760,7 +6756,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6779,7 +6774,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124855418</v>
+        <v>124855376</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -6812,17 +6807,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>855131</v>
+        <v>854741</v>
       </c>
       <c r="R61" t="n">
-        <v>7477924</v>
+        <v>7477958</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6863,6 +6862,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6881,10 +6881,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124855317</v>
+        <v>124855244</v>
       </c>
       <c r="B62" t="n">
-        <v>96985</v>
+        <v>91012</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6893,25 +6893,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>854783</v>
+        <v>855187</v>
       </c>
       <c r="R62" t="n">
-        <v>7477935</v>
+        <v>7478029</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6983,10 +6983,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124855250</v>
+        <v>124855358</v>
       </c>
       <c r="B63" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6995,38 +6995,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>854814</v>
+        <v>854772</v>
       </c>
       <c r="R63" t="n">
-        <v>7477852</v>
+        <v>7477881</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7061,12 +7061,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7085,10 +7091,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124855475</v>
+        <v>124854791</v>
       </c>
       <c r="B64" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7101,34 +7107,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>854813</v>
+        <v>854840</v>
       </c>
       <c r="R64" t="n">
-        <v>7477923</v>
+        <v>7477716</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7155,12 +7161,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7187,7 +7193,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124855381</v>
+        <v>124855421</v>
       </c>
       <c r="B65" t="n">
         <v>98101</v>
@@ -7227,10 +7233,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>854803</v>
+        <v>854951</v>
       </c>
       <c r="R65" t="n">
-        <v>7477930</v>
+        <v>7477899</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7271,7 +7277,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7290,10 +7295,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855232</v>
+        <v>124855389</v>
       </c>
       <c r="B66" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7302,38 +7307,42 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>855094</v>
+        <v>854906</v>
       </c>
       <c r="R66" t="n">
-        <v>7477931</v>
+        <v>7477891</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7374,6 +7383,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7392,7 +7402,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855390</v>
+        <v>124855359</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -7425,21 +7435,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>854899</v>
+        <v>854838</v>
       </c>
       <c r="R67" t="n">
-        <v>7477831</v>
+        <v>7477840</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7472,6 +7478,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7499,10 +7510,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855358</v>
+        <v>124855277</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7511,38 +7522,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854772</v>
+        <v>855068</v>
       </c>
       <c r="R68" t="n">
-        <v>7477881</v>
+        <v>7478046</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7577,18 +7588,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7607,10 +7612,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124854791</v>
+        <v>124855512</v>
       </c>
       <c r="B69" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7619,20 +7624,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7643,14 +7648,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>854840</v>
+        <v>854911</v>
       </c>
       <c r="R69" t="n">
-        <v>7477716</v>
+        <v>7478164</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7677,12 +7682,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7709,7 +7714,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855423</v>
+        <v>124855394</v>
       </c>
       <c r="B70" t="n">
         <v>98101</v>
@@ -7742,17 +7747,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>854915</v>
+        <v>854897</v>
       </c>
       <c r="R70" t="n">
-        <v>7477851</v>
+        <v>7477846</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7793,6 +7802,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7811,10 +7821,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855275</v>
+        <v>124855423</v>
       </c>
       <c r="B71" t="n">
-        <v>92321</v>
+        <v>98101</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7823,38 +7833,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>854889</v>
+        <v>854915</v>
       </c>
       <c r="R71" t="n">
-        <v>7477847</v>
+        <v>7477851</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7913,7 +7923,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855398</v>
+        <v>124855377</v>
       </c>
       <c r="B72" t="n">
         <v>98101</v>
@@ -7948,7 +7958,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>64</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -7957,10 +7967,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>854737</v>
+        <v>854672</v>
       </c>
       <c r="R72" t="n">
-        <v>7477850</v>
+        <v>7477865</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7997,7 +8007,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>I kanten av nytt hygge</t>
+          <t>I utkanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8025,7 +8035,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855377</v>
+        <v>124855424</v>
       </c>
       <c r="B73" t="n">
         <v>98101</v>
@@ -8058,21 +8068,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>854672</v>
+        <v>854780</v>
       </c>
       <c r="R73" t="n">
-        <v>7477865</v>
+        <v>7477939</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8099,17 +8105,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>I utkanten av nytt hygge</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8118,7 +8119,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8137,7 +8137,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855389</v>
+        <v>124855468</v>
       </c>
       <c r="B74" t="n">
         <v>98101</v>
@@ -8170,21 +8170,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>854906</v>
+        <v>855069</v>
       </c>
       <c r="R74" t="n">
-        <v>7477891</v>
+        <v>7477999</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8225,7 +8221,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8244,10 +8239,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855424</v>
+        <v>124855500</v>
       </c>
       <c r="B75" t="n">
-        <v>98101</v>
+        <v>79826</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8256,25 +8251,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8284,10 +8279,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854780</v>
+        <v>854850</v>
       </c>
       <c r="R75" t="n">
-        <v>7477939</v>
+        <v>7477915</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8346,7 +8341,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855464</v>
+        <v>124855466</v>
       </c>
       <c r="B76" t="n">
         <v>98101</v>
@@ -8386,10 +8381,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>854898</v>
+        <v>854921</v>
       </c>
       <c r="R76" t="n">
-        <v>7478156</v>
+        <v>7478082</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8448,7 +8443,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124855467</v>
+        <v>124855380</v>
       </c>
       <c r="B77" t="n">
         <v>98101</v>
@@ -8488,10 +8483,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>855062</v>
+        <v>854745</v>
       </c>
       <c r="R77" t="n">
-        <v>7478002</v>
+        <v>7477946</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8532,6 +8527,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8550,10 +8546,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855386</v>
+        <v>124855483</v>
       </c>
       <c r="B78" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8562,42 +8558,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>854810</v>
+        <v>855251</v>
       </c>
       <c r="R78" t="n">
-        <v>7477930</v>
+        <v>7478036</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8638,7 +8630,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8657,10 +8648,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855277</v>
+        <v>124855333</v>
       </c>
       <c r="B79" t="n">
-        <v>79920</v>
+        <v>79927</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8673,21 +8664,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8697,10 +8688,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>855068</v>
+        <v>854924</v>
       </c>
       <c r="R79" t="n">
-        <v>7478046</v>
+        <v>7478087</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8861,7 +8852,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855394</v>
+        <v>124855398</v>
       </c>
       <c r="B81" t="n">
         <v>98101</v>
@@ -8896,19 +8887,19 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>854897</v>
+        <v>854737</v>
       </c>
       <c r="R81" t="n">
-        <v>7477846</v>
+        <v>7477850</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8935,12 +8926,17 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8968,10 +8964,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124855469</v>
+        <v>124855250</v>
       </c>
       <c r="B82" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8980,25 +8976,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9008,10 +9004,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>854979</v>
+        <v>854814</v>
       </c>
       <c r="R82" t="n">
-        <v>7477885</v>
+        <v>7477852</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9070,10 +9066,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855468</v>
+        <v>124855313</v>
       </c>
       <c r="B83" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9082,25 +9078,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9110,10 +9106,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>855069</v>
+        <v>854814</v>
       </c>
       <c r="R83" t="n">
-        <v>7477999</v>
+        <v>7477852</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9172,10 +9168,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855420</v>
+        <v>124855231</v>
       </c>
       <c r="B84" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9184,25 +9180,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9212,10 +9208,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>855071</v>
+        <v>854954</v>
       </c>
       <c r="R84" t="n">
-        <v>7477912</v>
+        <v>7478125</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9274,7 +9270,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855466</v>
+        <v>124855366</v>
       </c>
       <c r="B85" t="n">
         <v>98101</v>
@@ -9307,17 +9303,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>854921</v>
+        <v>854807</v>
       </c>
       <c r="R85" t="n">
-        <v>7478082</v>
+        <v>7477926</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9358,6 +9358,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9376,10 +9377,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855359</v>
+        <v>124855524</v>
       </c>
       <c r="B86" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9388,38 +9389,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>854838</v>
+        <v>854793</v>
       </c>
       <c r="R86" t="n">
-        <v>7477840</v>
+        <v>7477805</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9446,17 +9447,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9465,7 +9461,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9484,7 +9479,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855366</v>
+        <v>124855420</v>
       </c>
       <c r="B87" t="n">
         <v>98101</v>
@@ -9517,21 +9512,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>854807</v>
+        <v>855071</v>
       </c>
       <c r="R87" t="n">
-        <v>7477926</v>
+        <v>7477912</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9572,7 +9563,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9591,10 +9581,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855483</v>
+        <v>124855469</v>
       </c>
       <c r="B88" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9603,25 +9593,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9631,10 +9621,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>855251</v>
+        <v>854979</v>
       </c>
       <c r="R88" t="n">
-        <v>7478036</v>
+        <v>7477885</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9693,7 +9683,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855376</v>
+        <v>124855364</v>
       </c>
       <c r="B89" t="n">
         <v>98101</v>
@@ -9726,21 +9716,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>854741</v>
+        <v>855120</v>
       </c>
       <c r="R89" t="n">
-        <v>7477958</v>
+        <v>7477887</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9773,6 +9759,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9800,10 +9791,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124855316</v>
+        <v>124855404</v>
       </c>
       <c r="B90" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9812,38 +9803,42 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>855019</v>
+        <v>854832</v>
       </c>
       <c r="R90" t="n">
-        <v>7477888</v>
+        <v>7477880</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9884,6 +9879,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9902,10 +9898,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124855318</v>
+        <v>124855233</v>
       </c>
       <c r="B91" t="n">
-        <v>96985</v>
+        <v>105102</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9918,21 +9914,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9942,10 +9938,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>854817</v>
+        <v>855073</v>
       </c>
       <c r="R91" t="n">
-        <v>7477931</v>
+        <v>7477920</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10004,7 +10000,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124855371</v>
+        <v>124855390</v>
       </c>
       <c r="B92" t="n">
         <v>98101</v>
@@ -10039,7 +10035,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>28</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -10048,10 +10044,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>854845</v>
+        <v>854899</v>
       </c>
       <c r="R92" t="n">
-        <v>7477869</v>
+        <v>7477831</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10111,10 +10107,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124855233</v>
+        <v>124855318</v>
       </c>
       <c r="B93" t="n">
-        <v>105102</v>
+        <v>96985</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10127,21 +10123,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221725</v>
+        <v>221941</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10151,10 +10147,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>855073</v>
+        <v>854817</v>
       </c>
       <c r="R93" t="n">
-        <v>7477920</v>
+        <v>7477931</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10213,10 +10209,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855313</v>
+        <v>124855275</v>
       </c>
       <c r="B94" t="n">
-        <v>91299</v>
+        <v>92321</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10229,34 +10225,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>5449</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>854814</v>
+        <v>854889</v>
       </c>
       <c r="R94" t="n">
-        <v>7477852</v>
+        <v>7477847</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10315,10 +10311,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855512</v>
+        <v>124854790</v>
       </c>
       <c r="B95" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10327,38 +10323,42 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>854911</v>
+        <v>854766</v>
       </c>
       <c r="R95" t="n">
-        <v>7478164</v>
+        <v>7478012</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10399,6 +10399,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10417,10 +10418,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855474</v>
+        <v>124855371</v>
       </c>
       <c r="B96" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10429,38 +10430,42 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>855065</v>
+        <v>854845</v>
       </c>
       <c r="R96" t="n">
-        <v>7478197</v>
+        <v>7477869</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10501,6 +10506,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10519,10 +10525,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124855231</v>
+        <v>124855249</v>
       </c>
       <c r="B97" t="n">
-        <v>105102</v>
+        <v>91012</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10531,25 +10537,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221725</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10559,10 +10565,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>854954</v>
+        <v>854811</v>
       </c>
       <c r="R97" t="n">
-        <v>7478125</v>
+        <v>7477849</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10621,10 +10627,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124855500</v>
+        <v>124855474</v>
       </c>
       <c r="B98" t="n">
-        <v>79826</v>
+        <v>56714</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10633,25 +10639,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6457</v>
+        <v>102612</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10661,10 +10667,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>854850</v>
+        <v>855065</v>
       </c>
       <c r="R98" t="n">
-        <v>7477915</v>
+        <v>7478197</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10723,10 +10729,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124855482</v>
+        <v>124855386</v>
       </c>
       <c r="B99" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10735,38 +10741,42 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>855134</v>
+        <v>854810</v>
       </c>
       <c r="R99" t="n">
-        <v>7477890</v>
+        <v>7477930</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10807,6 +10817,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10825,7 +10836,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124854790</v>
+        <v>124855381</v>
       </c>
       <c r="B100" t="n">
         <v>98101</v>
@@ -10858,21 +10869,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>854766</v>
+        <v>854803</v>
       </c>
       <c r="R100" t="n">
-        <v>7478012</v>
+        <v>7477930</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10932,10 +10939,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855244</v>
+        <v>124855316</v>
       </c>
       <c r="B101" t="n">
-        <v>91012</v>
+        <v>96985</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10944,25 +10951,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10972,10 +10979,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>855187</v>
+        <v>855019</v>
       </c>
       <c r="R101" t="n">
-        <v>7478029</v>
+        <v>7477888</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11034,10 +11041,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124855524</v>
+        <v>124855482</v>
       </c>
       <c r="B102" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11046,20 +11053,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -11074,10 +11081,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>854793</v>
+        <v>855134</v>
       </c>
       <c r="R102" t="n">
-        <v>7477805</v>
+        <v>7477890</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11104,12 +11111,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11136,10 +11143,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855417</v>
+        <v>124855232</v>
       </c>
       <c r="B103" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11148,25 +11155,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11176,10 +11183,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>855202</v>
+        <v>855094</v>
       </c>
       <c r="R103" t="n">
-        <v>7477976</v>
+        <v>7477931</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11238,7 +11245,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855380</v>
+        <v>124855464</v>
       </c>
       <c r="B104" t="n">
         <v>98101</v>
@@ -11278,10 +11285,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>854745</v>
+        <v>854898</v>
       </c>
       <c r="R104" t="n">
-        <v>7477946</v>
+        <v>7478156</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11322,7 +11329,6 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11341,10 +11347,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855333</v>
+        <v>124855418</v>
       </c>
       <c r="B105" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11353,25 +11359,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11381,10 +11387,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>854924</v>
+        <v>855131</v>
       </c>
       <c r="R105" t="n">
-        <v>7478087</v>
+        <v>7477924</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11443,7 +11449,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855364</v>
+        <v>124855416</v>
       </c>
       <c r="B106" t="n">
         <v>98101</v>
@@ -11479,14 +11485,14 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>855120</v>
+        <v>855002</v>
       </c>
       <c r="R106" t="n">
-        <v>7477887</v>
+        <v>7478149</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11521,18 +11527,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11551,10 +11551,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855416</v>
+        <v>124855317</v>
       </c>
       <c r="B107" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11563,25 +11563,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11591,10 +11591,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>855002</v>
+        <v>854783</v>
       </c>
       <c r="R107" t="n">
-        <v>7478149</v>
+        <v>7477935</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11755,10 +11755,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855249</v>
+        <v>124855467</v>
       </c>
       <c r="B109" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11767,25 +11767,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11795,10 +11795,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>854811</v>
+        <v>855062</v>
       </c>
       <c r="R109" t="n">
-        <v>7477849</v>
+        <v>7478002</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -6881,10 +6881,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124855244</v>
+        <v>124855358</v>
       </c>
       <c r="B62" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6893,38 +6893,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>855187</v>
+        <v>854772</v>
       </c>
       <c r="R62" t="n">
-        <v>7478029</v>
+        <v>7477881</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6959,12 +6959,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6983,10 +6989,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124855358</v>
+        <v>124855244</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6995,38 +7001,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>854772</v>
+        <v>855187</v>
       </c>
       <c r="R63" t="n">
-        <v>7477881</v>
+        <v>7478029</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7061,18 +7067,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -10525,10 +10525,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124855249</v>
+        <v>124855474</v>
       </c>
       <c r="B97" t="n">
-        <v>91012</v>
+        <v>56714</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10541,21 +10541,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10565,10 +10565,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>854811</v>
+        <v>855065</v>
       </c>
       <c r="R97" t="n">
-        <v>7477849</v>
+        <v>7478197</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10627,10 +10627,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124855474</v>
+        <v>124855386</v>
       </c>
       <c r="B98" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10639,38 +10639,42 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>855065</v>
+        <v>854810</v>
       </c>
       <c r="R98" t="n">
-        <v>7478197</v>
+        <v>7477930</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10711,6 +10715,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10729,10 +10734,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124855386</v>
+        <v>124855249</v>
       </c>
       <c r="B99" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10741,42 +10746,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>854810</v>
+        <v>854811</v>
       </c>
       <c r="R99" t="n">
-        <v>7477930</v>
+        <v>7477849</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10817,7 +10818,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427351</v>
+        <v>124427402</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>82597</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4171,42 +4171,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>855056</v>
+        <v>854960</v>
       </c>
       <c r="R36" t="n">
-        <v>7478165</v>
+        <v>7478309</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4247,7 +4243,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4266,10 +4261,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427365</v>
+        <v>124427345</v>
       </c>
       <c r="B37" t="n">
-        <v>79428</v>
+        <v>79927</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4278,38 +4273,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>854939</v>
+        <v>854967</v>
       </c>
       <c r="R37" t="n">
-        <v>7478324</v>
+        <v>7478177</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4368,10 +4363,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427401</v>
+        <v>124427375</v>
       </c>
       <c r="B38" t="n">
-        <v>82597</v>
+        <v>79927</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4380,25 +4375,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4408,10 +4403,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>855011</v>
+        <v>854922</v>
       </c>
       <c r="R38" t="n">
-        <v>7478352</v>
+        <v>7478323</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4452,8 +4447,24 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4470,10 +4481,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427369</v>
+        <v>124427406</v>
       </c>
       <c r="B39" t="n">
-        <v>57666</v>
+        <v>91579</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4482,38 +4493,45 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>760</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>854943</v>
+        <v>855096</v>
       </c>
       <c r="R39" t="n">
-        <v>7478362</v>
+        <v>7478199</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4548,12 +4566,18 @@
           <t>2025-04-24</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4572,10 +4596,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427386</v>
+        <v>124427365</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>79428</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4584,42 +4608,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>855066</v>
+        <v>854939</v>
       </c>
       <c r="R40" t="n">
-        <v>7478180</v>
+        <v>7478324</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4660,7 +4680,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4679,10 +4698,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427356</v>
+        <v>124427388</v>
       </c>
       <c r="B41" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4691,38 +4710,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>854977</v>
+        <v>855074</v>
       </c>
       <c r="R41" t="n">
-        <v>7478167</v>
+        <v>7478164</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4763,6 +4786,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4781,10 +4805,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427399</v>
+        <v>124427347</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4793,38 +4817,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>855007</v>
+        <v>855063</v>
       </c>
       <c r="R42" t="n">
-        <v>7478357</v>
+        <v>7478044</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4883,7 +4907,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427389</v>
+        <v>124427391</v>
       </c>
       <c r="B43" t="n">
         <v>98101</v>
@@ -4918,7 +4942,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4927,10 +4951,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>855110</v>
+        <v>855091</v>
       </c>
       <c r="R43" t="n">
-        <v>7478072</v>
+        <v>7478207</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4990,10 +5014,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427345</v>
+        <v>124427399</v>
       </c>
       <c r="B44" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5002,38 +5026,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>854967</v>
+        <v>855007</v>
       </c>
       <c r="R44" t="n">
-        <v>7478177</v>
+        <v>7478357</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5092,10 +5116,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427388</v>
+        <v>124427346</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5104,42 +5128,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>855074</v>
+        <v>855044</v>
       </c>
       <c r="R45" t="n">
-        <v>7478164</v>
+        <v>7478074</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5180,7 +5200,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5199,10 +5218,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427398</v>
+        <v>124427401</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5215,21 +5234,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5239,10 +5258,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>855100</v>
+        <v>855011</v>
       </c>
       <c r="R46" t="n">
-        <v>7478058</v>
+        <v>7478352</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5301,7 +5320,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427352</v>
+        <v>124427386</v>
       </c>
       <c r="B47" t="n">
         <v>98101</v>
@@ -5336,19 +5355,19 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>117</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>855059</v>
+        <v>855066</v>
       </c>
       <c r="R47" t="n">
-        <v>7478173</v>
+        <v>7478180</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5408,10 +5427,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427387</v>
+        <v>124427356</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5420,42 +5439,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>855102</v>
+        <v>854977</v>
       </c>
       <c r="R48" t="n">
-        <v>7478191</v>
+        <v>7478167</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5496,7 +5511,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5515,10 +5529,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427354</v>
+        <v>124427369</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5531,34 +5545,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>855018</v>
+        <v>854943</v>
       </c>
       <c r="R49" t="n">
-        <v>7478119</v>
+        <v>7478362</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5617,10 +5631,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427346</v>
+        <v>124427351</v>
       </c>
       <c r="B50" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5629,38 +5643,42 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>855044</v>
+        <v>855056</v>
       </c>
       <c r="R50" t="n">
-        <v>7478074</v>
+        <v>7478165</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5701,6 +5719,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5719,10 +5738,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427406</v>
+        <v>124427389</v>
       </c>
       <c r="B51" t="n">
-        <v>91579</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5735,41 +5754,38 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>855096</v>
+        <v>855110</v>
       </c>
       <c r="R51" t="n">
-        <v>7478199</v>
+        <v>7478072</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5802,11 +5818,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-24</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5834,10 +5845,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427391</v>
+        <v>124427393</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5846,42 +5857,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>855091</v>
+        <v>854990</v>
       </c>
       <c r="R52" t="n">
-        <v>7478207</v>
+        <v>7478363</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5922,7 +5929,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5941,10 +5947,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427400</v>
+        <v>124427387</v>
       </c>
       <c r="B53" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5953,38 +5959,42 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855012</v>
+        <v>855102</v>
       </c>
       <c r="R53" t="n">
-        <v>7478269</v>
+        <v>7478191</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6025,6 +6035,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6043,10 +6054,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427375</v>
+        <v>124427352</v>
       </c>
       <c r="B54" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6055,38 +6066,42 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>854922</v>
+        <v>855059</v>
       </c>
       <c r="R54" t="n">
-        <v>7478323</v>
+        <v>7478173</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6130,21 +6145,6 @@
       <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6161,10 +6161,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427347</v>
+        <v>124427354</v>
       </c>
       <c r="B55" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6173,25 +6173,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>855063</v>
+        <v>855018</v>
       </c>
       <c r="R55" t="n">
-        <v>7478044</v>
+        <v>7478119</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6263,10 +6263,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427393</v>
+        <v>124427398</v>
       </c>
       <c r="B56" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6279,21 +6279,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>854990</v>
+        <v>855100</v>
       </c>
       <c r="R56" t="n">
-        <v>7478363</v>
+        <v>7478058</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6365,7 +6365,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124427402</v>
+        <v>124427400</v>
       </c>
       <c r="B57" t="n">
         <v>82597</v>
@@ -6405,10 +6405,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>854960</v>
+        <v>855012</v>
       </c>
       <c r="R57" t="n">
-        <v>7478309</v>
+        <v>7478269</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6570,10 +6570,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855475</v>
+        <v>124855469</v>
       </c>
       <c r="B59" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6582,25 +6582,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>854813</v>
+        <v>854979</v>
       </c>
       <c r="R59" t="n">
-        <v>7477923</v>
+        <v>7477885</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6672,7 +6672,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855417</v>
+        <v>124855466</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -6712,10 +6712,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>855202</v>
+        <v>854921</v>
       </c>
       <c r="R60" t="n">
-        <v>7477976</v>
+        <v>7478082</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6774,7 +6774,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124855376</v>
+        <v>124855404</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>854741</v>
+        <v>854832</v>
       </c>
       <c r="R61" t="n">
-        <v>7477958</v>
+        <v>7477880</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6881,10 +6881,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124855358</v>
+        <v>124855244</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6893,38 +6893,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>854772</v>
+        <v>855187</v>
       </c>
       <c r="R62" t="n">
-        <v>7477881</v>
+        <v>7478029</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6959,18 +6959,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6989,10 +6983,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124855244</v>
+        <v>124855371</v>
       </c>
       <c r="B63" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7001,38 +6995,42 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>855187</v>
+        <v>854845</v>
       </c>
       <c r="R63" t="n">
-        <v>7478029</v>
+        <v>7477869</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7073,6 +7071,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7091,10 +7090,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124854791</v>
+        <v>124855467</v>
       </c>
       <c r="B64" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7103,38 +7102,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>854840</v>
+        <v>855062</v>
       </c>
       <c r="R64" t="n">
-        <v>7477716</v>
+        <v>7478002</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7161,12 +7160,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7193,10 +7192,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124855421</v>
+        <v>124855500</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
+        <v>79826</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7205,25 +7204,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7233,10 +7232,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>854951</v>
+        <v>854850</v>
       </c>
       <c r="R65" t="n">
-        <v>7477899</v>
+        <v>7477915</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7295,7 +7294,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855389</v>
+        <v>124855398</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -7330,19 +7329,19 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>854906</v>
+        <v>854737</v>
       </c>
       <c r="R66" t="n">
-        <v>7477891</v>
+        <v>7477850</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7369,12 +7368,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7402,10 +7406,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855359</v>
+        <v>124855317</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7414,38 +7418,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>854838</v>
+        <v>854783</v>
       </c>
       <c r="R67" t="n">
-        <v>7477840</v>
+        <v>7477935</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7480,18 +7484,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7510,10 +7508,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855277</v>
+        <v>124855232</v>
       </c>
       <c r="B68" t="n">
-        <v>79920</v>
+        <v>105102</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7526,21 +7524,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7550,10 +7548,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>855068</v>
+        <v>855094</v>
       </c>
       <c r="R68" t="n">
-        <v>7478046</v>
+        <v>7477931</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7612,10 +7610,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855512</v>
+        <v>124855482</v>
       </c>
       <c r="B69" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7624,20 +7622,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7652,10 +7650,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>854911</v>
+        <v>855134</v>
       </c>
       <c r="R69" t="n">
-        <v>7478164</v>
+        <v>7477890</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7714,10 +7712,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855394</v>
+        <v>124855474</v>
       </c>
       <c r="B70" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7726,42 +7724,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>854897</v>
+        <v>855065</v>
       </c>
       <c r="R70" t="n">
-        <v>7477846</v>
+        <v>7478197</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7802,7 +7796,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7821,10 +7814,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855423</v>
+        <v>124855231</v>
       </c>
       <c r="B71" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7833,25 +7826,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7861,10 +7854,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>854915</v>
+        <v>854954</v>
       </c>
       <c r="R71" t="n">
-        <v>7477851</v>
+        <v>7478125</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7923,10 +7916,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855377</v>
+        <v>124855333</v>
       </c>
       <c r="B72" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7935,42 +7928,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>854672</v>
+        <v>854924</v>
       </c>
       <c r="R72" t="n">
-        <v>7477865</v>
+        <v>7478087</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7997,17 +7986,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>I utkanten av nytt hygge</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8016,7 +8000,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8035,7 +8018,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855424</v>
+        <v>124855420</v>
       </c>
       <c r="B73" t="n">
         <v>98101</v>
@@ -8075,10 +8058,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>854780</v>
+        <v>855071</v>
       </c>
       <c r="R73" t="n">
-        <v>7477939</v>
+        <v>7477912</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8137,7 +8120,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855468</v>
+        <v>124855424</v>
       </c>
       <c r="B74" t="n">
         <v>98101</v>
@@ -8177,10 +8160,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>855069</v>
+        <v>854780</v>
       </c>
       <c r="R74" t="n">
-        <v>7477999</v>
+        <v>7477939</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8239,10 +8222,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855500</v>
+        <v>124855366</v>
       </c>
       <c r="B75" t="n">
-        <v>79826</v>
+        <v>98101</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8251,38 +8234,42 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6457</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854850</v>
+        <v>854807</v>
       </c>
       <c r="R75" t="n">
-        <v>7477915</v>
+        <v>7477926</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8323,6 +8310,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8341,7 +8329,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855466</v>
+        <v>124855394</v>
       </c>
       <c r="B76" t="n">
         <v>98101</v>
@@ -8374,17 +8362,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>854921</v>
+        <v>854897</v>
       </c>
       <c r="R76" t="n">
-        <v>7478082</v>
+        <v>7477846</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8425,6 +8417,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8443,7 +8436,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124855380</v>
+        <v>124855421</v>
       </c>
       <c r="B77" t="n">
         <v>98101</v>
@@ -8483,10 +8476,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>854745</v>
+        <v>854951</v>
       </c>
       <c r="R77" t="n">
-        <v>7477946</v>
+        <v>7477899</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8527,7 +8520,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8546,10 +8538,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855483</v>
+        <v>124855417</v>
       </c>
       <c r="B78" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8558,25 +8550,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8586,10 +8578,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>855251</v>
+        <v>855202</v>
       </c>
       <c r="R78" t="n">
-        <v>7478036</v>
+        <v>7477976</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8648,10 +8640,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855333</v>
+        <v>124855277</v>
       </c>
       <c r="B79" t="n">
-        <v>79927</v>
+        <v>79920</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8664,21 +8656,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8688,10 +8680,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>854924</v>
+        <v>855068</v>
       </c>
       <c r="R79" t="n">
-        <v>7478087</v>
+        <v>7478046</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8750,10 +8742,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124855415</v>
+        <v>124855475</v>
       </c>
       <c r="B80" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8762,25 +8754,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8790,10 +8782,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>854928</v>
+        <v>854813</v>
       </c>
       <c r="R80" t="n">
-        <v>7478107</v>
+        <v>7477923</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8852,7 +8844,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855398</v>
+        <v>124855464</v>
       </c>
       <c r="B81" t="n">
         <v>98101</v>
@@ -8885,21 +8877,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>854737</v>
+        <v>854898</v>
       </c>
       <c r="R81" t="n">
-        <v>7477850</v>
+        <v>7478156</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8926,17 +8914,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8945,7 +8928,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8964,10 +8946,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124855250</v>
+        <v>124855423</v>
       </c>
       <c r="B82" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8976,25 +8958,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9004,10 +8986,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>854814</v>
+        <v>854915</v>
       </c>
       <c r="R82" t="n">
-        <v>7477852</v>
+        <v>7477851</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9066,10 +9048,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855313</v>
+        <v>124855390</v>
       </c>
       <c r="B83" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9078,38 +9060,42 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>854814</v>
+        <v>854899</v>
       </c>
       <c r="R83" t="n">
-        <v>7477852</v>
+        <v>7477831</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9150,6 +9136,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9168,10 +9155,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855231</v>
+        <v>124855275</v>
       </c>
       <c r="B84" t="n">
-        <v>105102</v>
+        <v>92321</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9180,38 +9167,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221725</v>
+        <v>5449</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>854954</v>
+        <v>854889</v>
       </c>
       <c r="R84" t="n">
-        <v>7478125</v>
+        <v>7477847</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9270,10 +9257,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855366</v>
+        <v>124855250</v>
       </c>
       <c r="B85" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9282,42 +9269,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>854807</v>
+        <v>854814</v>
       </c>
       <c r="R85" t="n">
-        <v>7477926</v>
+        <v>7477852</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9358,7 +9341,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9377,10 +9359,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855524</v>
+        <v>124855380</v>
       </c>
       <c r="B86" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9389,25 +9371,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9417,10 +9399,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>854793</v>
+        <v>854745</v>
       </c>
       <c r="R86" t="n">
-        <v>7477805</v>
+        <v>7477946</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9447,12 +9429,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9461,6 +9443,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9479,10 +9462,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855420</v>
+        <v>124855524</v>
       </c>
       <c r="B87" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9491,25 +9474,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9519,10 +9502,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>855071</v>
+        <v>854793</v>
       </c>
       <c r="R87" t="n">
-        <v>7477912</v>
+        <v>7477805</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9549,12 +9532,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9581,7 +9564,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855469</v>
+        <v>124855389</v>
       </c>
       <c r="B88" t="n">
         <v>98101</v>
@@ -9614,17 +9597,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>854979</v>
+        <v>854906</v>
       </c>
       <c r="R88" t="n">
-        <v>7477885</v>
+        <v>7477891</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9665,6 +9652,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9683,7 +9671,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855364</v>
+        <v>124855386</v>
       </c>
       <c r="B89" t="n">
         <v>98101</v>
@@ -9716,17 +9704,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>855120</v>
+        <v>854810</v>
       </c>
       <c r="R89" t="n">
-        <v>7477887</v>
+        <v>7477930</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9759,11 +9751,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9791,7 +9778,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124855404</v>
+        <v>124854790</v>
       </c>
       <c r="B90" t="n">
         <v>98101</v>
@@ -9826,19 +9813,19 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>854832</v>
+        <v>854766</v>
       </c>
       <c r="R90" t="n">
-        <v>7477880</v>
+        <v>7478012</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9898,10 +9885,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124855233</v>
+        <v>124855381</v>
       </c>
       <c r="B91" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9910,25 +9897,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9938,10 +9925,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>855073</v>
+        <v>854803</v>
       </c>
       <c r="R91" t="n">
-        <v>7477920</v>
+        <v>7477930</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9982,6 +9969,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -10000,7 +9988,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124855390</v>
+        <v>124855415</v>
       </c>
       <c r="B92" t="n">
         <v>98101</v>
@@ -10033,21 +10021,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>854899</v>
+        <v>854928</v>
       </c>
       <c r="R92" t="n">
-        <v>7477831</v>
+        <v>7478107</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10088,7 +10072,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10107,10 +10090,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124855318</v>
+        <v>124855358</v>
       </c>
       <c r="B93" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10119,38 +10102,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>854817</v>
+        <v>854772</v>
       </c>
       <c r="R93" t="n">
-        <v>7477931</v>
+        <v>7477881</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10185,12 +10168,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10209,10 +10198,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855275</v>
+        <v>124855512</v>
       </c>
       <c r="B94" t="n">
-        <v>92321</v>
+        <v>79926</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10221,38 +10210,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5449</v>
+        <v>6463</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>854889</v>
+        <v>854911</v>
       </c>
       <c r="R94" t="n">
-        <v>7477847</v>
+        <v>7478164</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10311,10 +10300,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124854790</v>
+        <v>124854791</v>
       </c>
       <c r="B95" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10323,42 +10312,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>854766</v>
+        <v>854840</v>
       </c>
       <c r="R95" t="n">
-        <v>7478012</v>
+        <v>7477716</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10385,12 +10370,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10399,7 +10384,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10418,7 +10402,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855371</v>
+        <v>124855416</v>
       </c>
       <c r="B96" t="n">
         <v>98101</v>
@@ -10451,21 +10435,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>854845</v>
+        <v>855002</v>
       </c>
       <c r="R96" t="n">
-        <v>7477869</v>
+        <v>7478149</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10506,7 +10486,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10525,10 +10504,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124855474</v>
+        <v>124855468</v>
       </c>
       <c r="B97" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10537,25 +10516,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10565,10 +10544,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>855065</v>
+        <v>855069</v>
       </c>
       <c r="R97" t="n">
-        <v>7478197</v>
+        <v>7477999</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10627,7 +10606,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124855386</v>
+        <v>124855359</v>
       </c>
       <c r="B98" t="n">
         <v>98101</v>
@@ -10660,21 +10639,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>854810</v>
+        <v>854838</v>
       </c>
       <c r="R98" t="n">
-        <v>7477930</v>
+        <v>7477840</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10707,6 +10682,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10734,10 +10714,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124855249</v>
+        <v>124855376</v>
       </c>
       <c r="B99" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10746,38 +10726,42 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>854811</v>
+        <v>854741</v>
       </c>
       <c r="R99" t="n">
-        <v>7477849</v>
+        <v>7477958</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10818,6 +10802,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10836,10 +10821,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124855381</v>
+        <v>124855318</v>
       </c>
       <c r="B100" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10848,25 +10833,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10876,10 +10861,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>854803</v>
+        <v>854817</v>
       </c>
       <c r="R100" t="n">
-        <v>7477930</v>
+        <v>7477931</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10920,7 +10905,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10939,10 +10923,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855316</v>
+        <v>124855377</v>
       </c>
       <c r="B101" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10951,38 +10935,42 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>855019</v>
+        <v>854672</v>
       </c>
       <c r="R101" t="n">
-        <v>7477888</v>
+        <v>7477865</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11009,12 +10997,17 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>I utkanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11023,6 +11016,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11041,7 +11035,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124855482</v>
+        <v>124855483</v>
       </c>
       <c r="B102" t="n">
         <v>78810</v>
@@ -11081,10 +11075,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>855134</v>
+        <v>855251</v>
       </c>
       <c r="R102" t="n">
-        <v>7477890</v>
+        <v>7478036</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11143,7 +11137,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855232</v>
+        <v>124855233</v>
       </c>
       <c r="B103" t="n">
         <v>105102</v>
@@ -11183,10 +11177,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>855094</v>
+        <v>855073</v>
       </c>
       <c r="R103" t="n">
-        <v>7477931</v>
+        <v>7477920</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11245,10 +11239,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855464</v>
+        <v>124855316</v>
       </c>
       <c r="B104" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11257,25 +11251,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11285,10 +11279,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>854898</v>
+        <v>855019</v>
       </c>
       <c r="R104" t="n">
-        <v>7478156</v>
+        <v>7477888</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11347,7 +11341,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855418</v>
+        <v>124855364</v>
       </c>
       <c r="B105" t="n">
         <v>98101</v>
@@ -11383,14 +11377,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>855131</v>
+        <v>855120</v>
       </c>
       <c r="R105" t="n">
-        <v>7477924</v>
+        <v>7477887</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11425,12 +11419,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11449,7 +11449,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855416</v>
+        <v>124855418</v>
       </c>
       <c r="B106" t="n">
         <v>98101</v>
@@ -11489,10 +11489,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>855002</v>
+        <v>855131</v>
       </c>
       <c r="R106" t="n">
-        <v>7478149</v>
+        <v>7477924</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11551,10 +11551,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855317</v>
+        <v>124855313</v>
       </c>
       <c r="B107" t="n">
-        <v>96985</v>
+        <v>91299</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11563,25 +11563,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221941</v>
+        <v>658</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11591,10 +11591,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>854783</v>
+        <v>854814</v>
       </c>
       <c r="R107" t="n">
-        <v>7477935</v>
+        <v>7477852</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11653,10 +11653,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855235</v>
+        <v>124855249</v>
       </c>
       <c r="B108" t="n">
-        <v>105102</v>
+        <v>91012</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11665,25 +11665,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221725</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11693,10 +11693,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>854686</v>
+        <v>854811</v>
       </c>
       <c r="R108" t="n">
-        <v>7477923</v>
+        <v>7477849</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11755,10 +11755,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855467</v>
+        <v>124855235</v>
       </c>
       <c r="B109" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11767,25 +11767,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11795,10 +11795,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>855062</v>
+        <v>854686</v>
       </c>
       <c r="R109" t="n">
-        <v>7478002</v>
+        <v>7477923</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427402</v>
+        <v>124427406</v>
       </c>
       <c r="B36" t="n">
-        <v>82597</v>
+        <v>91579</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4171,38 +4171,45 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>760</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>854960</v>
+        <v>855096</v>
       </c>
       <c r="R36" t="n">
-        <v>7478309</v>
+        <v>7478199</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4237,12 +4244,18 @@
           <t>2025-04-24</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4261,7 +4274,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427345</v>
+        <v>124427375</v>
       </c>
       <c r="B37" t="n">
         <v>79927</v>
@@ -4297,14 +4310,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>854967</v>
+        <v>854922</v>
       </c>
       <c r="R37" t="n">
-        <v>7478177</v>
+        <v>7478323</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4345,8 +4358,24 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4363,10 +4392,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427375</v>
+        <v>124427400</v>
       </c>
       <c r="B38" t="n">
-        <v>79927</v>
+        <v>82597</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4375,25 +4404,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4403,10 +4432,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>854922</v>
+        <v>855012</v>
       </c>
       <c r="R38" t="n">
-        <v>7478323</v>
+        <v>7478269</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4447,24 +4476,8 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4481,10 +4494,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427406</v>
+        <v>124427393</v>
       </c>
       <c r="B39" t="n">
-        <v>91579</v>
+        <v>56714</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4493,45 +4506,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>760</v>
+        <v>102612</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>855096</v>
+        <v>854990</v>
       </c>
       <c r="R39" t="n">
-        <v>7478199</v>
+        <v>7478363</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4566,18 +4572,12 @@
           <t>2025-04-24</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4596,10 +4596,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427365</v>
+        <v>124427351</v>
       </c>
       <c r="B40" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4608,38 +4608,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>854939</v>
+        <v>855056</v>
       </c>
       <c r="R40" t="n">
-        <v>7478324</v>
+        <v>7478165</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4680,6 +4684,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4698,10 +4703,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427388</v>
+        <v>124427399</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4710,42 +4715,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>855074</v>
+        <v>855007</v>
       </c>
       <c r="R41" t="n">
-        <v>7478164</v>
+        <v>7478357</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4786,7 +4787,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4907,10 +4907,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427391</v>
+        <v>124427398</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4919,42 +4919,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>855091</v>
+        <v>855100</v>
       </c>
       <c r="R43" t="n">
-        <v>7478207</v>
+        <v>7478058</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4995,7 +4991,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5014,10 +5009,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427399</v>
+        <v>124427356</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5026,20 +5021,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5050,14 +5045,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>855007</v>
+        <v>854977</v>
       </c>
       <c r="R44" t="n">
-        <v>7478357</v>
+        <v>7478167</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5116,10 +5111,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427346</v>
+        <v>124427369</v>
       </c>
       <c r="B45" t="n">
-        <v>79927</v>
+        <v>57666</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5128,38 +5123,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>855044</v>
+        <v>854943</v>
       </c>
       <c r="R45" t="n">
-        <v>7478074</v>
+        <v>7478362</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5218,10 +5213,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427401</v>
+        <v>124427352</v>
       </c>
       <c r="B46" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5230,38 +5225,42 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>855011</v>
+        <v>855059</v>
       </c>
       <c r="R46" t="n">
-        <v>7478352</v>
+        <v>7478173</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5302,6 +5301,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5320,7 +5320,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427386</v>
+        <v>124427391</v>
       </c>
       <c r="B47" t="n">
         <v>98101</v>
@@ -5355,7 +5355,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>855066</v>
+        <v>855091</v>
       </c>
       <c r="R47" t="n">
-        <v>7478180</v>
+        <v>7478207</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5427,10 +5427,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427356</v>
+        <v>124427345</v>
       </c>
       <c r="B48" t="n">
-        <v>79926</v>
+        <v>79927</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5443,21 +5443,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>854977</v>
+        <v>854967</v>
       </c>
       <c r="R48" t="n">
-        <v>7478167</v>
+        <v>7478177</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5529,10 +5529,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427369</v>
+        <v>124427365</v>
       </c>
       <c r="B49" t="n">
-        <v>57666</v>
+        <v>79428</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5545,21 +5545,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5569,10 +5569,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>854943</v>
+        <v>854939</v>
       </c>
       <c r="R49" t="n">
-        <v>7478362</v>
+        <v>7478324</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5631,7 +5631,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427351</v>
+        <v>124427388</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -5666,19 +5666,19 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>73</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>855056</v>
+        <v>855074</v>
       </c>
       <c r="R50" t="n">
-        <v>7478165</v>
+        <v>7478164</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5738,10 +5738,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427389</v>
+        <v>124427401</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>82597</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5750,42 +5750,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>855110</v>
+        <v>855011</v>
       </c>
       <c r="R51" t="n">
-        <v>7478072</v>
+        <v>7478352</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5826,7 +5822,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5845,10 +5840,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427393</v>
+        <v>124427354</v>
       </c>
       <c r="B52" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5861,34 +5856,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>854990</v>
+        <v>855018</v>
       </c>
       <c r="R52" t="n">
-        <v>7478363</v>
+        <v>7478119</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5947,7 +5942,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427387</v>
+        <v>124427389</v>
       </c>
       <c r="B53" t="n">
         <v>98101</v>
@@ -5982,7 +5977,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5991,10 +5986,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855102</v>
+        <v>855110</v>
       </c>
       <c r="R53" t="n">
-        <v>7478191</v>
+        <v>7478072</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6054,10 +6049,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427352</v>
+        <v>124427346</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6066,42 +6061,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>855059</v>
+        <v>855044</v>
       </c>
       <c r="R54" t="n">
-        <v>7478173</v>
+        <v>7478074</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6142,7 +6133,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6161,10 +6151,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427354</v>
+        <v>124427403</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>79826</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6173,38 +6163,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>855018</v>
+        <v>854946</v>
       </c>
       <c r="R55" t="n">
-        <v>7478119</v>
+        <v>7478367</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6245,6 +6235,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6263,10 +6254,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427398</v>
+        <v>124427387</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6275,38 +6266,42 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>855100</v>
+        <v>855102</v>
       </c>
       <c r="R56" t="n">
-        <v>7478058</v>
+        <v>7478191</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6347,6 +6342,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6365,10 +6361,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124427400</v>
+        <v>124427386</v>
       </c>
       <c r="B57" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6377,38 +6373,42 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>855012</v>
+        <v>855066</v>
       </c>
       <c r="R57" t="n">
-        <v>7478269</v>
+        <v>7478180</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6449,6 +6449,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6467,10 +6468,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124427403</v>
+        <v>124427402</v>
       </c>
       <c r="B58" t="n">
-        <v>79826</v>
+        <v>82597</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6479,25 +6480,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6457</v>
+        <v>1312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6507,10 +6508,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>854946</v>
+        <v>854960</v>
       </c>
       <c r="R58" t="n">
-        <v>7478367</v>
+        <v>7478309</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6551,7 +6552,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6570,10 +6570,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855469</v>
+        <v>124855249</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6582,25 +6582,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>854979</v>
+        <v>854811</v>
       </c>
       <c r="R59" t="n">
-        <v>7477885</v>
+        <v>7477849</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6672,7 +6672,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855466</v>
+        <v>124854790</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -6705,17 +6705,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>854921</v>
+        <v>854766</v>
       </c>
       <c r="R60" t="n">
-        <v>7478082</v>
+        <v>7478012</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6756,6 +6760,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6774,10 +6779,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124855404</v>
+        <v>124855232</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6786,42 +6791,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>854832</v>
+        <v>855094</v>
       </c>
       <c r="R61" t="n">
-        <v>7477880</v>
+        <v>7477931</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6862,7 +6863,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6881,10 +6881,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124855244</v>
+        <v>124855377</v>
       </c>
       <c r="B62" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6893,38 +6893,42 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>855187</v>
+        <v>854672</v>
       </c>
       <c r="R62" t="n">
-        <v>7478029</v>
+        <v>7477865</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6951,12 +6955,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>I utkanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6965,6 +6974,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6983,7 +6993,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124855371</v>
+        <v>124855418</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -7016,21 +7026,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>854845</v>
+        <v>855131</v>
       </c>
       <c r="R63" t="n">
-        <v>7477869</v>
+        <v>7477924</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7071,7 +7077,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7090,7 +7095,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124855467</v>
+        <v>124855420</v>
       </c>
       <c r="B64" t="n">
         <v>98101</v>
@@ -7130,10 +7135,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>855062</v>
+        <v>855071</v>
       </c>
       <c r="R64" t="n">
-        <v>7478002</v>
+        <v>7477912</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7192,10 +7197,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124855500</v>
+        <v>124855417</v>
       </c>
       <c r="B65" t="n">
-        <v>79826</v>
+        <v>98101</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7204,25 +7209,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6457</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7232,10 +7237,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>854850</v>
+        <v>855202</v>
       </c>
       <c r="R65" t="n">
-        <v>7477915</v>
+        <v>7477976</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7294,7 +7299,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855398</v>
+        <v>124855389</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -7329,19 +7334,19 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>854737</v>
+        <v>854906</v>
       </c>
       <c r="R66" t="n">
-        <v>7477850</v>
+        <v>7477891</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7368,17 +7373,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7406,10 +7406,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855317</v>
+        <v>124855313</v>
       </c>
       <c r="B67" t="n">
-        <v>96985</v>
+        <v>91299</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7418,25 +7418,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221941</v>
+        <v>658</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>854783</v>
+        <v>854814</v>
       </c>
       <c r="R67" t="n">
-        <v>7477935</v>
+        <v>7477852</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7508,7 +7508,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855232</v>
+        <v>124855231</v>
       </c>
       <c r="B68" t="n">
         <v>105102</v>
@@ -7548,10 +7548,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>855094</v>
+        <v>854954</v>
       </c>
       <c r="R68" t="n">
-        <v>7477931</v>
+        <v>7478125</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7610,10 +7610,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855482</v>
+        <v>124855398</v>
       </c>
       <c r="B69" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7622,38 +7622,42 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>855134</v>
+        <v>854737</v>
       </c>
       <c r="R69" t="n">
-        <v>7477890</v>
+        <v>7477850</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7680,12 +7684,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7694,6 +7703,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7712,10 +7722,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855474</v>
+        <v>124855380</v>
       </c>
       <c r="B70" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7724,25 +7734,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7752,10 +7762,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>855065</v>
+        <v>854745</v>
       </c>
       <c r="R70" t="n">
-        <v>7478197</v>
+        <v>7477946</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7796,6 +7806,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7814,10 +7825,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855231</v>
+        <v>124855275</v>
       </c>
       <c r="B71" t="n">
-        <v>105102</v>
+        <v>92321</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7826,38 +7837,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221725</v>
+        <v>5449</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>854954</v>
+        <v>854889</v>
       </c>
       <c r="R71" t="n">
-        <v>7478125</v>
+        <v>7477847</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7916,10 +7927,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855333</v>
+        <v>124855235</v>
       </c>
       <c r="B72" t="n">
-        <v>79927</v>
+        <v>105102</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7932,21 +7943,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6464</v>
+        <v>221725</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7956,10 +7967,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>854924</v>
+        <v>854686</v>
       </c>
       <c r="R72" t="n">
-        <v>7478087</v>
+        <v>7477923</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8018,10 +8029,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855420</v>
+        <v>124855316</v>
       </c>
       <c r="B73" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8030,25 +8041,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8058,10 +8069,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>855071</v>
+        <v>855019</v>
       </c>
       <c r="R73" t="n">
-        <v>7477912</v>
+        <v>7477888</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8120,10 +8131,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855424</v>
+        <v>124855500</v>
       </c>
       <c r="B74" t="n">
-        <v>98101</v>
+        <v>79826</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8132,25 +8143,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8160,10 +8171,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>854780</v>
+        <v>854850</v>
       </c>
       <c r="R74" t="n">
-        <v>7477939</v>
+        <v>7477915</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8222,10 +8233,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855366</v>
+        <v>124855524</v>
       </c>
       <c r="B75" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8234,42 +8245,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854807</v>
+        <v>854793</v>
       </c>
       <c r="R75" t="n">
-        <v>7477926</v>
+        <v>7477805</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8296,12 +8303,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8310,7 +8317,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8329,10 +8335,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855394</v>
+        <v>124855318</v>
       </c>
       <c r="B76" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8341,42 +8347,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>854897</v>
+        <v>854817</v>
       </c>
       <c r="R76" t="n">
-        <v>7477846</v>
+        <v>7477931</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8417,7 +8419,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8436,10 +8437,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124855421</v>
+        <v>124855482</v>
       </c>
       <c r="B77" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8448,25 +8449,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8476,10 +8477,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>854951</v>
+        <v>855134</v>
       </c>
       <c r="R77" t="n">
-        <v>7477899</v>
+        <v>7477890</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8538,7 +8539,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855417</v>
+        <v>124855371</v>
       </c>
       <c r="B78" t="n">
         <v>98101</v>
@@ -8571,17 +8572,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>855202</v>
+        <v>854845</v>
       </c>
       <c r="R78" t="n">
-        <v>7477976</v>
+        <v>7477869</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8622,6 +8627,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8640,10 +8646,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855277</v>
+        <v>124855466</v>
       </c>
       <c r="B79" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8652,25 +8658,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8680,10 +8686,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>855068</v>
+        <v>854921</v>
       </c>
       <c r="R79" t="n">
-        <v>7478046</v>
+        <v>7478082</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8742,10 +8748,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124855475</v>
+        <v>124855421</v>
       </c>
       <c r="B80" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8754,25 +8760,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8782,10 +8788,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>854813</v>
+        <v>854951</v>
       </c>
       <c r="R80" t="n">
-        <v>7477923</v>
+        <v>7477899</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8844,7 +8850,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855464</v>
+        <v>124855381</v>
       </c>
       <c r="B81" t="n">
         <v>98101</v>
@@ -8884,10 +8890,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>854898</v>
+        <v>854803</v>
       </c>
       <c r="R81" t="n">
-        <v>7478156</v>
+        <v>7477930</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8928,6 +8934,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8946,10 +8953,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124855423</v>
+        <v>124855277</v>
       </c>
       <c r="B82" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8958,25 +8965,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8986,10 +8993,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>854915</v>
+        <v>855068</v>
       </c>
       <c r="R82" t="n">
-        <v>7477851</v>
+        <v>7478046</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9048,10 +9055,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855390</v>
+        <v>124855475</v>
       </c>
       <c r="B83" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9060,42 +9067,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>854899</v>
+        <v>854813</v>
       </c>
       <c r="R83" t="n">
-        <v>7477831</v>
+        <v>7477923</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9136,7 +9139,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9155,10 +9157,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855275</v>
+        <v>124855366</v>
       </c>
       <c r="B84" t="n">
-        <v>92321</v>
+        <v>98101</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9167,38 +9169,42 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>854889</v>
+        <v>854807</v>
       </c>
       <c r="R84" t="n">
-        <v>7477847</v>
+        <v>7477926</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9239,6 +9245,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9257,10 +9264,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855250</v>
+        <v>124855483</v>
       </c>
       <c r="B85" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9273,21 +9280,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9297,10 +9304,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>854814</v>
+        <v>855251</v>
       </c>
       <c r="R85" t="n">
-        <v>7477852</v>
+        <v>7478036</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9359,7 +9366,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855380</v>
+        <v>124855390</v>
       </c>
       <c r="B86" t="n">
         <v>98101</v>
@@ -9392,17 +9399,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>854745</v>
+        <v>854899</v>
       </c>
       <c r="R86" t="n">
-        <v>7477946</v>
+        <v>7477831</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9462,10 +9473,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855524</v>
+        <v>124855394</v>
       </c>
       <c r="B87" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9474,38 +9485,42 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>854793</v>
+        <v>854897</v>
       </c>
       <c r="R87" t="n">
-        <v>7477805</v>
+        <v>7477846</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9532,12 +9547,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9546,6 +9561,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9564,10 +9580,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855389</v>
+        <v>124855244</v>
       </c>
       <c r="B88" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9576,42 +9592,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>854906</v>
+        <v>855187</v>
       </c>
       <c r="R88" t="n">
-        <v>7477891</v>
+        <v>7478029</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9652,7 +9664,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9671,10 +9682,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855386</v>
+        <v>124855233</v>
       </c>
       <c r="B89" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9683,42 +9694,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>854810</v>
+        <v>855073</v>
       </c>
       <c r="R89" t="n">
-        <v>7477930</v>
+        <v>7477920</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9759,7 +9766,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9778,10 +9784,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124854790</v>
+        <v>124855250</v>
       </c>
       <c r="B90" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9790,42 +9796,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>854766</v>
+        <v>854814</v>
       </c>
       <c r="R90" t="n">
-        <v>7478012</v>
+        <v>7477852</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9866,7 +9868,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9885,10 +9886,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124855381</v>
+        <v>124855333</v>
       </c>
       <c r="B91" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9897,25 +9898,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9925,10 +9926,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>854803</v>
+        <v>854924</v>
       </c>
       <c r="R91" t="n">
-        <v>7477930</v>
+        <v>7478087</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9969,7 +9970,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9988,10 +9988,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124855415</v>
+        <v>124855474</v>
       </c>
       <c r="B92" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10000,25 +10000,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>854928</v>
+        <v>855065</v>
       </c>
       <c r="R92" t="n">
-        <v>7478107</v>
+        <v>7478197</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10090,7 +10090,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124855358</v>
+        <v>124855423</v>
       </c>
       <c r="B93" t="n">
         <v>98101</v>
@@ -10126,14 +10126,14 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>854772</v>
+        <v>854915</v>
       </c>
       <c r="R93" t="n">
-        <v>7477881</v>
+        <v>7477851</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10168,18 +10168,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10198,10 +10192,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855512</v>
+        <v>124855404</v>
       </c>
       <c r="B94" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10210,38 +10204,42 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>854911</v>
+        <v>854832</v>
       </c>
       <c r="R94" t="n">
-        <v>7478164</v>
+        <v>7477880</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10282,6 +10280,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10300,10 +10299,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124854791</v>
+        <v>124855468</v>
       </c>
       <c r="B95" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10312,38 +10311,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>854840</v>
+        <v>855069</v>
       </c>
       <c r="R95" t="n">
-        <v>7477716</v>
+        <v>7477999</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10370,12 +10369,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10402,7 +10401,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855416</v>
+        <v>124855358</v>
       </c>
       <c r="B96" t="n">
         <v>98101</v>
@@ -10438,14 +10437,14 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>855002</v>
+        <v>854772</v>
       </c>
       <c r="R96" t="n">
-        <v>7478149</v>
+        <v>7477881</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10480,12 +10479,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10504,10 +10509,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124855468</v>
+        <v>124854791</v>
       </c>
       <c r="B97" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10516,38 +10521,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>855069</v>
+        <v>854840</v>
       </c>
       <c r="R97" t="n">
-        <v>7477999</v>
+        <v>7477716</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10574,12 +10579,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10606,7 +10611,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124855359</v>
+        <v>124855424</v>
       </c>
       <c r="B98" t="n">
         <v>98101</v>
@@ -10642,14 +10647,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>854838</v>
+        <v>854780</v>
       </c>
       <c r="R98" t="n">
-        <v>7477840</v>
+        <v>7477939</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10684,18 +10689,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10714,10 +10713,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124855376</v>
+        <v>124855317</v>
       </c>
       <c r="B99" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10726,42 +10725,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>854741</v>
+        <v>854783</v>
       </c>
       <c r="R99" t="n">
-        <v>7477958</v>
+        <v>7477935</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10802,7 +10797,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10821,10 +10815,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124855318</v>
+        <v>124855376</v>
       </c>
       <c r="B100" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10833,38 +10827,42 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>854817</v>
+        <v>854741</v>
       </c>
       <c r="R100" t="n">
-        <v>7477931</v>
+        <v>7477958</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10905,6 +10903,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10923,7 +10922,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855377</v>
+        <v>124855416</v>
       </c>
       <c r="B101" t="n">
         <v>98101</v>
@@ -10956,21 +10955,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>854672</v>
+        <v>855002</v>
       </c>
       <c r="R101" t="n">
-        <v>7477865</v>
+        <v>7478149</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10997,17 +10992,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>I utkanten av nytt hygge</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11016,7 +11006,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11035,10 +11024,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124855483</v>
+        <v>124855415</v>
       </c>
       <c r="B102" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11047,25 +11036,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11075,10 +11064,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>855251</v>
+        <v>854928</v>
       </c>
       <c r="R102" t="n">
-        <v>7478036</v>
+        <v>7478107</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11137,10 +11126,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855233</v>
+        <v>124855467</v>
       </c>
       <c r="B103" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11149,25 +11138,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11177,10 +11166,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>855073</v>
+        <v>855062</v>
       </c>
       <c r="R103" t="n">
-        <v>7477920</v>
+        <v>7478002</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11239,10 +11228,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855316</v>
+        <v>124855464</v>
       </c>
       <c r="B104" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11251,25 +11240,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11279,10 +11268,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>855019</v>
+        <v>854898</v>
       </c>
       <c r="R104" t="n">
-        <v>7477888</v>
+        <v>7478156</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11341,7 +11330,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855364</v>
+        <v>124855469</v>
       </c>
       <c r="B105" t="n">
         <v>98101</v>
@@ -11377,14 +11366,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>855120</v>
+        <v>854979</v>
       </c>
       <c r="R105" t="n">
-        <v>7477887</v>
+        <v>7477885</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11419,18 +11408,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11449,7 +11432,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855418</v>
+        <v>124855386</v>
       </c>
       <c r="B106" t="n">
         <v>98101</v>
@@ -11482,17 +11465,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>855131</v>
+        <v>854810</v>
       </c>
       <c r="R106" t="n">
-        <v>7477924</v>
+        <v>7477930</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11533,6 +11520,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11551,10 +11539,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855313</v>
+        <v>124855512</v>
       </c>
       <c r="B107" t="n">
-        <v>91299</v>
+        <v>79926</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11563,25 +11551,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11591,10 +11579,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>854814</v>
+        <v>854911</v>
       </c>
       <c r="R107" t="n">
-        <v>7477852</v>
+        <v>7478164</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11653,10 +11641,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855249</v>
+        <v>124855364</v>
       </c>
       <c r="B108" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11665,38 +11653,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>854811</v>
+        <v>855120</v>
       </c>
       <c r="R108" t="n">
-        <v>7477849</v>
+        <v>7477887</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11731,12 +11719,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11755,10 +11749,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855235</v>
+        <v>124855359</v>
       </c>
       <c r="B109" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11767,38 +11761,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>854686</v>
+        <v>854838</v>
       </c>
       <c r="R109" t="n">
-        <v>7477923</v>
+        <v>7477840</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11833,12 +11827,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -5111,10 +5111,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427369</v>
+        <v>124427352</v>
       </c>
       <c r="B45" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5123,38 +5123,42 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>854943</v>
+        <v>855059</v>
       </c>
       <c r="R45" t="n">
-        <v>7478362</v>
+        <v>7478173</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5195,6 +5199,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5213,7 +5218,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427352</v>
+        <v>124427391</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -5248,19 +5253,19 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>855059</v>
+        <v>855091</v>
       </c>
       <c r="R46" t="n">
-        <v>7478173</v>
+        <v>7478207</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5320,10 +5325,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427391</v>
+        <v>124427369</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5332,42 +5337,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>855091</v>
+        <v>854943</v>
       </c>
       <c r="R47" t="n">
-        <v>7478207</v>
+        <v>7478362</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5408,7 +5409,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5942,10 +5942,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427389</v>
+        <v>124427346</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5954,42 +5954,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855110</v>
+        <v>855044</v>
       </c>
       <c r="R53" t="n">
-        <v>7478072</v>
+        <v>7478074</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6030,7 +6026,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6049,10 +6044,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427346</v>
+        <v>124427403</v>
       </c>
       <c r="B54" t="n">
-        <v>79927</v>
+        <v>79826</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6065,34 +6060,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>6457</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>855044</v>
+        <v>854946</v>
       </c>
       <c r="R54" t="n">
-        <v>7478074</v>
+        <v>7478367</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6133,6 +6128,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6151,10 +6147,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427403</v>
+        <v>124427389</v>
       </c>
       <c r="B55" t="n">
-        <v>79826</v>
+        <v>98101</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6163,38 +6159,42 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6457</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>854946</v>
+        <v>855110</v>
       </c>
       <c r="R55" t="n">
-        <v>7478367</v>
+        <v>7478072</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7825,10 +7825,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855275</v>
+        <v>124855500</v>
       </c>
       <c r="B71" t="n">
-        <v>92321</v>
+        <v>79826</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7837,38 +7837,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5449</v>
+        <v>6457</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>854889</v>
+        <v>854850</v>
       </c>
       <c r="R71" t="n">
-        <v>7477847</v>
+        <v>7477915</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7927,10 +7927,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855235</v>
+        <v>124855316</v>
       </c>
       <c r="B72" t="n">
-        <v>105102</v>
+        <v>96985</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7943,21 +7943,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221725</v>
+        <v>221941</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>854686</v>
+        <v>855019</v>
       </c>
       <c r="R72" t="n">
-        <v>7477923</v>
+        <v>7477888</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8029,10 +8029,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855316</v>
+        <v>124855275</v>
       </c>
       <c r="B73" t="n">
-        <v>96985</v>
+        <v>92321</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8041,38 +8041,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221941</v>
+        <v>5449</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>855019</v>
+        <v>854889</v>
       </c>
       <c r="R73" t="n">
-        <v>7477888</v>
+        <v>7477847</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8131,10 +8131,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855500</v>
+        <v>124855235</v>
       </c>
       <c r="B74" t="n">
-        <v>79826</v>
+        <v>105102</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8147,21 +8147,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6457</v>
+        <v>221725</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8171,10 +8171,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>854850</v>
+        <v>854686</v>
       </c>
       <c r="R74" t="n">
-        <v>7477915</v>
+        <v>7477923</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8233,10 +8233,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855524</v>
+        <v>124855482</v>
       </c>
       <c r="B75" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8245,20 +8245,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8273,10 +8273,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854793</v>
+        <v>855134</v>
       </c>
       <c r="R75" t="n">
-        <v>7477805</v>
+        <v>7477890</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8303,12 +8303,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8437,10 +8437,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124855482</v>
+        <v>124855524</v>
       </c>
       <c r="B77" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8449,20 +8449,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -8477,10 +8477,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>855134</v>
+        <v>854793</v>
       </c>
       <c r="R77" t="n">
-        <v>7477890</v>
+        <v>7477805</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8507,12 +8507,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8539,7 +8539,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855371</v>
+        <v>124855466</v>
       </c>
       <c r="B78" t="n">
         <v>98101</v>
@@ -8572,21 +8572,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>854845</v>
+        <v>854921</v>
       </c>
       <c r="R78" t="n">
-        <v>7477869</v>
+        <v>7478082</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8627,7 +8623,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8646,7 +8641,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855466</v>
+        <v>124855371</v>
       </c>
       <c r="B79" t="n">
         <v>98101</v>
@@ -8679,17 +8674,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>854921</v>
+        <v>854845</v>
       </c>
       <c r="R79" t="n">
-        <v>7478082</v>
+        <v>7477869</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8730,6 +8729,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -10192,10 +10192,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855404</v>
+        <v>124854791</v>
       </c>
       <c r="B94" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10204,42 +10204,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>854832</v>
+        <v>854840</v>
       </c>
       <c r="R94" t="n">
-        <v>7477880</v>
+        <v>7477716</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10266,12 +10262,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10280,7 +10276,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10299,7 +10294,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855468</v>
+        <v>124855404</v>
       </c>
       <c r="B95" t="n">
         <v>98101</v>
@@ -10332,17 +10327,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>855069</v>
+        <v>854832</v>
       </c>
       <c r="R95" t="n">
-        <v>7477999</v>
+        <v>7477880</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10383,6 +10382,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10401,7 +10401,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855358</v>
+        <v>124855468</v>
       </c>
       <c r="B96" t="n">
         <v>98101</v>
@@ -10437,14 +10437,14 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>854772</v>
+        <v>855069</v>
       </c>
       <c r="R96" t="n">
-        <v>7477881</v>
+        <v>7477999</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10479,18 +10479,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10509,10 +10503,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124854791</v>
+        <v>124855358</v>
       </c>
       <c r="B97" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10521,25 +10515,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10549,10 +10543,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>854840</v>
+        <v>854772</v>
       </c>
       <c r="R97" t="n">
-        <v>7477716</v>
+        <v>7477881</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10579,12 +10573,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10593,6 +10592,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -5942,10 +5942,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427346</v>
+        <v>124427389</v>
       </c>
       <c r="B53" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5954,38 +5954,42 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855044</v>
+        <v>855110</v>
       </c>
       <c r="R53" t="n">
-        <v>7478074</v>
+        <v>7478072</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6026,6 +6030,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6044,10 +6049,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427403</v>
+        <v>124427346</v>
       </c>
       <c r="B54" t="n">
-        <v>79826</v>
+        <v>79927</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6060,34 +6065,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6457</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>854946</v>
+        <v>855044</v>
       </c>
       <c r="R54" t="n">
-        <v>7478367</v>
+        <v>7478074</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6128,7 +6133,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6147,10 +6151,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427389</v>
+        <v>124427403</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>79826</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6159,42 +6163,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>855110</v>
+        <v>854946</v>
       </c>
       <c r="R55" t="n">
-        <v>7478072</v>
+        <v>7478367</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7825,10 +7825,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855500</v>
+        <v>124855275</v>
       </c>
       <c r="B71" t="n">
-        <v>79826</v>
+        <v>92321</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7837,38 +7837,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6457</v>
+        <v>5449</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>854850</v>
+        <v>854889</v>
       </c>
       <c r="R71" t="n">
-        <v>7477915</v>
+        <v>7477847</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7927,10 +7927,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855316</v>
+        <v>124855235</v>
       </c>
       <c r="B72" t="n">
-        <v>96985</v>
+        <v>105102</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7943,21 +7943,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>855019</v>
+        <v>854686</v>
       </c>
       <c r="R72" t="n">
-        <v>7477888</v>
+        <v>7477923</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8029,10 +8029,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855275</v>
+        <v>124855316</v>
       </c>
       <c r="B73" t="n">
-        <v>92321</v>
+        <v>96985</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8041,38 +8041,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5449</v>
+        <v>221941</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>854889</v>
+        <v>855019</v>
       </c>
       <c r="R73" t="n">
-        <v>7477847</v>
+        <v>7477888</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8131,10 +8131,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855235</v>
+        <v>124855500</v>
       </c>
       <c r="B74" t="n">
-        <v>105102</v>
+        <v>79826</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8147,21 +8147,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221725</v>
+        <v>6457</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8171,10 +8171,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>854686</v>
+        <v>854850</v>
       </c>
       <c r="R74" t="n">
-        <v>7477923</v>
+        <v>7477915</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9264,10 +9264,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855483</v>
+        <v>124855244</v>
       </c>
       <c r="B85" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9280,21 +9280,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9304,10 +9304,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>855251</v>
+        <v>855187</v>
       </c>
       <c r="R85" t="n">
-        <v>7478036</v>
+        <v>7478029</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9366,10 +9366,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855390</v>
+        <v>124855483</v>
       </c>
       <c r="B86" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9378,42 +9378,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>854899</v>
+        <v>855251</v>
       </c>
       <c r="R86" t="n">
-        <v>7477831</v>
+        <v>7478036</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9454,7 +9450,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9580,10 +9575,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855244</v>
+        <v>124855233</v>
       </c>
       <c r="B88" t="n">
-        <v>91012</v>
+        <v>105102</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9592,25 +9587,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>221725</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9620,10 +9615,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>855187</v>
+        <v>855073</v>
       </c>
       <c r="R88" t="n">
-        <v>7478029</v>
+        <v>7477920</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9682,10 +9677,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855233</v>
+        <v>124855390</v>
       </c>
       <c r="B89" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9694,38 +9689,42 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>855073</v>
+        <v>854899</v>
       </c>
       <c r="R89" t="n">
-        <v>7477920</v>
+        <v>7477831</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9766,6 +9765,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10192,10 +10192,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124854791</v>
+        <v>124855404</v>
       </c>
       <c r="B94" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10204,38 +10204,42 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>854840</v>
+        <v>854832</v>
       </c>
       <c r="R94" t="n">
-        <v>7477716</v>
+        <v>7477880</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10262,12 +10266,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10276,6 +10280,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10294,7 +10299,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855404</v>
+        <v>124855468</v>
       </c>
       <c r="B95" t="n">
         <v>98101</v>
@@ -10327,21 +10332,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>854832</v>
+        <v>855069</v>
       </c>
       <c r="R95" t="n">
-        <v>7477880</v>
+        <v>7477999</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10382,7 +10383,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10401,7 +10401,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855468</v>
+        <v>124855358</v>
       </c>
       <c r="B96" t="n">
         <v>98101</v>
@@ -10437,14 +10437,14 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>855069</v>
+        <v>854772</v>
       </c>
       <c r="R96" t="n">
-        <v>7477999</v>
+        <v>7477881</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10479,12 +10479,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10503,10 +10509,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124855358</v>
+        <v>124854791</v>
       </c>
       <c r="B97" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10515,25 +10521,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10543,10 +10549,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>854772</v>
+        <v>854840</v>
       </c>
       <c r="R97" t="n">
-        <v>7477881</v>
+        <v>7477716</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10573,17 +10579,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10592,7 +10593,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -11641,7 +11641,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855364</v>
+        <v>124855359</v>
       </c>
       <c r="B108" t="n">
         <v>98101</v>
@@ -11681,10 +11681,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>855120</v>
+        <v>854838</v>
       </c>
       <c r="R108" t="n">
-        <v>7477887</v>
+        <v>7477840</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11749,7 +11749,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855359</v>
+        <v>124855364</v>
       </c>
       <c r="B109" t="n">
         <v>98101</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>854838</v>
+        <v>855120</v>
       </c>
       <c r="R109" t="n">
-        <v>7477840</v>
+        <v>7477887</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427406</v>
+        <v>124427401</v>
       </c>
       <c r="B36" t="n">
-        <v>91579</v>
+        <v>82597</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4171,45 +4171,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>760</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>855096</v>
+        <v>855011</v>
       </c>
       <c r="R36" t="n">
-        <v>7478199</v>
+        <v>7478352</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4244,18 +4237,12 @@
           <t>2025-04-24</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4274,10 +4261,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427375</v>
+        <v>124427387</v>
       </c>
       <c r="B37" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4286,38 +4273,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>854922</v>
+        <v>855102</v>
       </c>
       <c r="R37" t="n">
-        <v>7478323</v>
+        <v>7478191</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4361,21 +4352,6 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4392,10 +4368,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427400</v>
+        <v>124427389</v>
       </c>
       <c r="B38" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4404,38 +4380,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>855012</v>
+        <v>855110</v>
       </c>
       <c r="R38" t="n">
-        <v>7478269</v>
+        <v>7478072</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4476,6 +4456,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4494,10 +4475,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427393</v>
+        <v>124427365</v>
       </c>
       <c r="B39" t="n">
-        <v>56714</v>
+        <v>79428</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4510,21 +4491,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102612</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4534,10 +4515,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>854990</v>
+        <v>854939</v>
       </c>
       <c r="R39" t="n">
-        <v>7478363</v>
+        <v>7478324</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4596,10 +4577,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427351</v>
+        <v>124427393</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4608,42 +4589,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>855056</v>
+        <v>854990</v>
       </c>
       <c r="R40" t="n">
-        <v>7478165</v>
+        <v>7478363</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4684,7 +4661,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4703,10 +4679,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427399</v>
+        <v>124427400</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4719,21 +4695,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4743,10 +4719,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>855007</v>
+        <v>855012</v>
       </c>
       <c r="R41" t="n">
-        <v>7478357</v>
+        <v>7478269</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4805,10 +4781,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427347</v>
+        <v>124427352</v>
       </c>
       <c r="B42" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4817,38 +4793,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>855063</v>
+        <v>855059</v>
       </c>
       <c r="R42" t="n">
-        <v>7478044</v>
+        <v>7478173</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4889,6 +4869,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4907,10 +4888,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427398</v>
+        <v>124427369</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4923,21 +4904,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4947,10 +4928,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>855100</v>
+        <v>854943</v>
       </c>
       <c r="R43" t="n">
-        <v>7478058</v>
+        <v>7478362</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5009,10 +4990,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427356</v>
+        <v>124427386</v>
       </c>
       <c r="B44" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5021,38 +5002,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>854977</v>
+        <v>855066</v>
       </c>
       <c r="R44" t="n">
-        <v>7478167</v>
+        <v>7478180</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5093,6 +5078,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5111,10 +5097,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427352</v>
+        <v>124427403</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>79826</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5123,42 +5109,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>855059</v>
+        <v>854946</v>
       </c>
       <c r="R45" t="n">
-        <v>7478173</v>
+        <v>7478367</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5218,10 +5200,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427391</v>
+        <v>124427406</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>91579</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5234,38 +5216,41 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>855091</v>
+        <v>855096</v>
       </c>
       <c r="R46" t="n">
-        <v>7478207</v>
+        <v>7478199</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5298,6 +5283,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5325,10 +5315,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427369</v>
+        <v>124427399</v>
       </c>
       <c r="B47" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5341,21 +5331,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5365,10 +5355,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>854943</v>
+        <v>855007</v>
       </c>
       <c r="R47" t="n">
-        <v>7478362</v>
+        <v>7478357</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5427,7 +5417,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427345</v>
+        <v>124427347</v>
       </c>
       <c r="B48" t="n">
         <v>79927</v>
@@ -5467,10 +5457,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>854967</v>
+        <v>855063</v>
       </c>
       <c r="R48" t="n">
-        <v>7478177</v>
+        <v>7478044</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5529,10 +5519,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427365</v>
+        <v>124427398</v>
       </c>
       <c r="B49" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5545,21 +5535,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5569,10 +5559,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>854939</v>
+        <v>855100</v>
       </c>
       <c r="R49" t="n">
-        <v>7478324</v>
+        <v>7478058</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5631,10 +5621,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427388</v>
+        <v>124427354</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5643,42 +5633,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>855074</v>
+        <v>855018</v>
       </c>
       <c r="R50" t="n">
-        <v>7478164</v>
+        <v>7478119</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5719,7 +5705,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5738,10 +5723,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427401</v>
+        <v>124427346</v>
       </c>
       <c r="B51" t="n">
-        <v>82597</v>
+        <v>79927</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5750,38 +5735,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>855011</v>
+        <v>855044</v>
       </c>
       <c r="R51" t="n">
-        <v>7478352</v>
+        <v>7478074</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5840,10 +5825,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427354</v>
+        <v>124427388</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5852,38 +5837,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>855018</v>
+        <v>855074</v>
       </c>
       <c r="R52" t="n">
-        <v>7478119</v>
+        <v>7478164</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5924,6 +5913,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5942,7 +5932,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427389</v>
+        <v>124427391</v>
       </c>
       <c r="B53" t="n">
         <v>98101</v>
@@ -5977,7 +5967,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5986,10 +5976,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855110</v>
+        <v>855091</v>
       </c>
       <c r="R53" t="n">
-        <v>7478072</v>
+        <v>7478207</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6049,7 +6039,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427346</v>
+        <v>124427345</v>
       </c>
       <c r="B54" t="n">
         <v>79927</v>
@@ -6089,10 +6079,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>855044</v>
+        <v>854967</v>
       </c>
       <c r="R54" t="n">
-        <v>7478074</v>
+        <v>7478177</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6151,10 +6141,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427403</v>
+        <v>124427375</v>
       </c>
       <c r="B55" t="n">
-        <v>79826</v>
+        <v>79927</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6167,21 +6157,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6457</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6191,10 +6181,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>854946</v>
+        <v>854922</v>
       </c>
       <c r="R55" t="n">
-        <v>7478367</v>
+        <v>7478323</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6238,6 +6228,21 @@
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6254,10 +6259,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427387</v>
+        <v>124427402</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>82597</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6266,42 +6271,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>855102</v>
+        <v>854960</v>
       </c>
       <c r="R56" t="n">
-        <v>7478191</v>
+        <v>7478309</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6342,7 +6343,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6361,7 +6361,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124427386</v>
+        <v>124427351</v>
       </c>
       <c r="B57" t="n">
         <v>98101</v>
@@ -6396,19 +6396,19 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>137</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>855066</v>
+        <v>855056</v>
       </c>
       <c r="R57" t="n">
-        <v>7478180</v>
+        <v>7478165</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6468,10 +6468,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124427402</v>
+        <v>124427356</v>
       </c>
       <c r="B58" t="n">
-        <v>82597</v>
+        <v>79926</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6480,38 +6480,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>854960</v>
+        <v>854977</v>
       </c>
       <c r="R58" t="n">
-        <v>7478309</v>
+        <v>7478167</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6570,10 +6570,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855249</v>
+        <v>124855364</v>
       </c>
       <c r="B59" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6582,38 +6582,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>854811</v>
+        <v>855120</v>
       </c>
       <c r="R59" t="n">
-        <v>7477849</v>
+        <v>7477887</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6648,12 +6648,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6672,7 +6678,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124854790</v>
+        <v>124855467</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -6705,21 +6711,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>854766</v>
+        <v>855062</v>
       </c>
       <c r="R60" t="n">
-        <v>7478012</v>
+        <v>7478002</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6760,7 +6762,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6779,10 +6780,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124855232</v>
+        <v>124855275</v>
       </c>
       <c r="B61" t="n">
-        <v>105102</v>
+        <v>92321</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6791,38 +6792,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221725</v>
+        <v>5449</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>855094</v>
+        <v>854889</v>
       </c>
       <c r="R61" t="n">
-        <v>7477931</v>
+        <v>7477847</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6881,7 +6882,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124855377</v>
+        <v>124855380</v>
       </c>
       <c r="B62" t="n">
         <v>98101</v>
@@ -6914,21 +6915,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>854672</v>
+        <v>854745</v>
       </c>
       <c r="R62" t="n">
-        <v>7477865</v>
+        <v>7477946</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6955,17 +6952,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>I utkanten av nytt hygge</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6993,7 +6985,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124855418</v>
+        <v>124855415</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -7033,10 +7025,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>855131</v>
+        <v>854928</v>
       </c>
       <c r="R63" t="n">
-        <v>7477924</v>
+        <v>7478107</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7095,7 +7087,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124855420</v>
+        <v>124855377</v>
       </c>
       <c r="B64" t="n">
         <v>98101</v>
@@ -7128,17 +7120,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>855071</v>
+        <v>854672</v>
       </c>
       <c r="R64" t="n">
-        <v>7477912</v>
+        <v>7477865</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7165,12 +7161,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>I utkanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7179,6 +7180,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7197,7 +7199,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124855417</v>
+        <v>124855416</v>
       </c>
       <c r="B65" t="n">
         <v>98101</v>
@@ -7237,10 +7239,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>855202</v>
+        <v>855002</v>
       </c>
       <c r="R65" t="n">
-        <v>7477976</v>
+        <v>7478149</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7299,7 +7301,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855389</v>
+        <v>124855390</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -7334,7 +7336,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7343,10 +7345,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>854906</v>
+        <v>854899</v>
       </c>
       <c r="R66" t="n">
-        <v>7477891</v>
+        <v>7477831</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7406,10 +7408,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855313</v>
+        <v>124855250</v>
       </c>
       <c r="B67" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7422,21 +7424,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7508,10 +7510,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855231</v>
+        <v>124855404</v>
       </c>
       <c r="B68" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7520,38 +7522,42 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854954</v>
+        <v>854832</v>
       </c>
       <c r="R68" t="n">
-        <v>7478125</v>
+        <v>7477880</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7592,6 +7598,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7610,10 +7617,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855398</v>
+        <v>124855249</v>
       </c>
       <c r="B69" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7622,42 +7629,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>854737</v>
+        <v>854811</v>
       </c>
       <c r="R69" t="n">
-        <v>7477850</v>
+        <v>7477849</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7684,17 +7687,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7703,7 +7701,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7722,7 +7719,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855380</v>
+        <v>124855358</v>
       </c>
       <c r="B70" t="n">
         <v>98101</v>
@@ -7758,14 +7755,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>854745</v>
+        <v>854772</v>
       </c>
       <c r="R70" t="n">
-        <v>7477946</v>
+        <v>7477881</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7798,6 +7795,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7825,10 +7827,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855275</v>
+        <v>124855469</v>
       </c>
       <c r="B71" t="n">
-        <v>92321</v>
+        <v>98101</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7837,38 +7839,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>854889</v>
+        <v>854979</v>
       </c>
       <c r="R71" t="n">
-        <v>7477847</v>
+        <v>7477885</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7927,10 +7929,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855235</v>
+        <v>124855277</v>
       </c>
       <c r="B72" t="n">
-        <v>105102</v>
+        <v>79920</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7943,21 +7945,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7967,10 +7969,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>854686</v>
+        <v>855068</v>
       </c>
       <c r="R72" t="n">
-        <v>7477923</v>
+        <v>7478046</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8029,10 +8031,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855316</v>
+        <v>124855333</v>
       </c>
       <c r="B73" t="n">
-        <v>96985</v>
+        <v>79927</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8045,21 +8047,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221941</v>
+        <v>6464</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8069,10 +8071,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>855019</v>
+        <v>854924</v>
       </c>
       <c r="R73" t="n">
-        <v>7477888</v>
+        <v>7478087</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8131,10 +8133,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855500</v>
+        <v>124855475</v>
       </c>
       <c r="B74" t="n">
-        <v>79826</v>
+        <v>56714</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8143,25 +8145,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6457</v>
+        <v>102612</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8171,10 +8173,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>854850</v>
+        <v>854813</v>
       </c>
       <c r="R74" t="n">
-        <v>7477915</v>
+        <v>7477923</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8233,10 +8235,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855482</v>
+        <v>124854790</v>
       </c>
       <c r="B75" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8245,38 +8247,42 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>855134</v>
+        <v>854766</v>
       </c>
       <c r="R75" t="n">
-        <v>7477890</v>
+        <v>7478012</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8317,6 +8323,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8335,10 +8342,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855318</v>
+        <v>124855231</v>
       </c>
       <c r="B76" t="n">
-        <v>96985</v>
+        <v>105102</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8351,21 +8358,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8375,10 +8382,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>854817</v>
+        <v>854954</v>
       </c>
       <c r="R76" t="n">
-        <v>7477931</v>
+        <v>7478125</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8539,7 +8546,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855466</v>
+        <v>124855464</v>
       </c>
       <c r="B78" t="n">
         <v>98101</v>
@@ -8579,10 +8586,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>854921</v>
+        <v>854898</v>
       </c>
       <c r="R78" t="n">
-        <v>7478082</v>
+        <v>7478156</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8641,7 +8648,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855371</v>
+        <v>124855359</v>
       </c>
       <c r="B79" t="n">
         <v>98101</v>
@@ -8674,21 +8681,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>854845</v>
+        <v>854838</v>
       </c>
       <c r="R79" t="n">
-        <v>7477869</v>
+        <v>7477840</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8721,6 +8724,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8748,10 +8756,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124855421</v>
+        <v>124855233</v>
       </c>
       <c r="B80" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8760,25 +8768,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8788,10 +8796,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>854951</v>
+        <v>855073</v>
       </c>
       <c r="R80" t="n">
-        <v>7477899</v>
+        <v>7477920</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8850,7 +8858,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855381</v>
+        <v>124855376</v>
       </c>
       <c r="B81" t="n">
         <v>98101</v>
@@ -8883,17 +8891,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>854803</v>
+        <v>854741</v>
       </c>
       <c r="R81" t="n">
-        <v>7477930</v>
+        <v>7477958</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8953,10 +8965,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124855277</v>
+        <v>124855512</v>
       </c>
       <c r="B82" t="n">
-        <v>79920</v>
+        <v>79926</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8969,21 +8981,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8993,10 +9005,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>855068</v>
+        <v>854911</v>
       </c>
       <c r="R82" t="n">
-        <v>7478046</v>
+        <v>7478164</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9055,10 +9067,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855475</v>
+        <v>124855381</v>
       </c>
       <c r="B83" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9067,25 +9079,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9095,10 +9107,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>854813</v>
+        <v>854803</v>
       </c>
       <c r="R83" t="n">
-        <v>7477923</v>
+        <v>7477930</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9139,6 +9151,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9157,10 +9170,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855366</v>
+        <v>124855482</v>
       </c>
       <c r="B84" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9169,42 +9182,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>854807</v>
+        <v>855134</v>
       </c>
       <c r="R84" t="n">
-        <v>7477926</v>
+        <v>7477890</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9245,7 +9254,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9264,10 +9272,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855244</v>
+        <v>124855394</v>
       </c>
       <c r="B85" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9276,38 +9284,42 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>855187</v>
+        <v>854897</v>
       </c>
       <c r="R85" t="n">
-        <v>7478029</v>
+        <v>7477846</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9348,6 +9360,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9366,10 +9379,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855483</v>
+        <v>124855235</v>
       </c>
       <c r="B86" t="n">
-        <v>78810</v>
+        <v>105102</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9378,25 +9391,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9406,10 +9419,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>855251</v>
+        <v>854686</v>
       </c>
       <c r="R86" t="n">
-        <v>7478036</v>
+        <v>7477923</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9468,10 +9481,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855394</v>
+        <v>124855500</v>
       </c>
       <c r="B87" t="n">
-        <v>98101</v>
+        <v>79826</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9480,42 +9493,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>854897</v>
+        <v>854850</v>
       </c>
       <c r="R87" t="n">
-        <v>7477846</v>
+        <v>7477915</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9556,7 +9565,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9575,10 +9583,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855233</v>
+        <v>124855423</v>
       </c>
       <c r="B88" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9587,25 +9595,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9615,10 +9623,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>855073</v>
+        <v>854915</v>
       </c>
       <c r="R88" t="n">
-        <v>7477920</v>
+        <v>7477851</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9677,10 +9685,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855390</v>
+        <v>124855318</v>
       </c>
       <c r="B89" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9689,42 +9697,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>854899</v>
+        <v>854817</v>
       </c>
       <c r="R89" t="n">
-        <v>7477831</v>
+        <v>7477931</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9765,7 +9769,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9784,10 +9787,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124855250</v>
+        <v>124855417</v>
       </c>
       <c r="B90" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9796,25 +9799,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9824,10 +9827,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>854814</v>
+        <v>855202</v>
       </c>
       <c r="R90" t="n">
-        <v>7477852</v>
+        <v>7477976</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9886,10 +9889,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124855333</v>
+        <v>124855366</v>
       </c>
       <c r="B91" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9898,38 +9901,42 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>854924</v>
+        <v>854807</v>
       </c>
       <c r="R91" t="n">
-        <v>7478087</v>
+        <v>7477926</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9970,6 +9977,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -10090,7 +10098,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124855423</v>
+        <v>124855398</v>
       </c>
       <c r="B93" t="n">
         <v>98101</v>
@@ -10123,17 +10131,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>854915</v>
+        <v>854737</v>
       </c>
       <c r="R93" t="n">
-        <v>7477851</v>
+        <v>7477850</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10160,12 +10172,17 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10174,6 +10191,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10192,7 +10210,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855404</v>
+        <v>124855420</v>
       </c>
       <c r="B94" t="n">
         <v>98101</v>
@@ -10225,21 +10243,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>854832</v>
+        <v>855071</v>
       </c>
       <c r="R94" t="n">
-        <v>7477880</v>
+        <v>7477912</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10280,7 +10294,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10299,7 +10312,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855468</v>
+        <v>124855424</v>
       </c>
       <c r="B95" t="n">
         <v>98101</v>
@@ -10339,10 +10352,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>855069</v>
+        <v>854780</v>
       </c>
       <c r="R95" t="n">
-        <v>7477999</v>
+        <v>7477939</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10401,7 +10414,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855358</v>
+        <v>124855386</v>
       </c>
       <c r="B96" t="n">
         <v>98101</v>
@@ -10434,17 +10447,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>854772</v>
+        <v>854810</v>
       </c>
       <c r="R96" t="n">
-        <v>7477881</v>
+        <v>7477930</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10477,11 +10494,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10509,7 +10521,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124854791</v>
+        <v>124855483</v>
       </c>
       <c r="B97" t="n">
         <v>78810</v>
@@ -10545,14 +10557,14 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>854840</v>
+        <v>855251</v>
       </c>
       <c r="R97" t="n">
-        <v>7477716</v>
+        <v>7478036</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10579,12 +10591,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10611,10 +10623,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124855424</v>
+        <v>124854791</v>
       </c>
       <c r="B98" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10623,38 +10635,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>854780</v>
+        <v>854840</v>
       </c>
       <c r="R98" t="n">
-        <v>7477939</v>
+        <v>7477716</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10681,12 +10693,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10713,10 +10725,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124855317</v>
+        <v>124855418</v>
       </c>
       <c r="B99" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10725,25 +10737,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10753,10 +10765,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>854783</v>
+        <v>855131</v>
       </c>
       <c r="R99" t="n">
-        <v>7477935</v>
+        <v>7477924</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10815,10 +10827,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124855376</v>
+        <v>124855232</v>
       </c>
       <c r="B100" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10827,42 +10839,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>854741</v>
+        <v>855094</v>
       </c>
       <c r="R100" t="n">
-        <v>7477958</v>
+        <v>7477931</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10903,7 +10911,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10922,7 +10929,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855416</v>
+        <v>124855421</v>
       </c>
       <c r="B101" t="n">
         <v>98101</v>
@@ -10962,10 +10969,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>855002</v>
+        <v>854951</v>
       </c>
       <c r="R101" t="n">
-        <v>7478149</v>
+        <v>7477899</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11024,7 +11031,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124855415</v>
+        <v>124855466</v>
       </c>
       <c r="B102" t="n">
         <v>98101</v>
@@ -11064,10 +11071,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>854928</v>
+        <v>854921</v>
       </c>
       <c r="R102" t="n">
-        <v>7478107</v>
+        <v>7478082</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11126,7 +11133,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855467</v>
+        <v>124855389</v>
       </c>
       <c r="B103" t="n">
         <v>98101</v>
@@ -11159,17 +11166,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>855062</v>
+        <v>854906</v>
       </c>
       <c r="R103" t="n">
-        <v>7478002</v>
+        <v>7477891</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11210,6 +11221,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11228,10 +11240,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855464</v>
+        <v>124855317</v>
       </c>
       <c r="B104" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11240,25 +11252,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11268,10 +11280,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>854898</v>
+        <v>854783</v>
       </c>
       <c r="R104" t="n">
-        <v>7478156</v>
+        <v>7477935</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11330,10 +11342,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855469</v>
+        <v>124855316</v>
       </c>
       <c r="B105" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11342,25 +11354,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11370,10 +11382,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>854979</v>
+        <v>855019</v>
       </c>
       <c r="R105" t="n">
-        <v>7477885</v>
+        <v>7477888</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11432,7 +11444,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855386</v>
+        <v>124855468</v>
       </c>
       <c r="B106" t="n">
         <v>98101</v>
@@ -11465,21 +11477,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>854810</v>
+        <v>855069</v>
       </c>
       <c r="R106" t="n">
-        <v>7477930</v>
+        <v>7477999</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11520,7 +11528,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11539,10 +11546,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855512</v>
+        <v>124855371</v>
       </c>
       <c r="B107" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11551,38 +11558,42 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>854911</v>
+        <v>854845</v>
       </c>
       <c r="R107" t="n">
-        <v>7478164</v>
+        <v>7477869</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11623,6 +11634,7 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11641,10 +11653,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855359</v>
+        <v>124855244</v>
       </c>
       <c r="B108" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11653,38 +11665,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>854838</v>
+        <v>855187</v>
       </c>
       <c r="R108" t="n">
-        <v>7477840</v>
+        <v>7478029</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11719,18 +11731,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11749,10 +11755,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855364</v>
+        <v>124855313</v>
       </c>
       <c r="B109" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11761,38 +11767,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>855120</v>
+        <v>854814</v>
       </c>
       <c r="R109" t="n">
-        <v>7477887</v>
+        <v>7477852</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11827,18 +11833,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -4159,7 +4159,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427401</v>
+        <v>124427400</v>
       </c>
       <c r="B36" t="n">
         <v>82597</v>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>855011</v>
+        <v>855012</v>
       </c>
       <c r="R36" t="n">
-        <v>7478352</v>
+        <v>7478269</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4261,7 +4261,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427387</v>
+        <v>124427352</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4296,19 +4296,19 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>855102</v>
+        <v>855059</v>
       </c>
       <c r="R37" t="n">
-        <v>7478191</v>
+        <v>7478173</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4368,7 +4368,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427389</v>
+        <v>124427388</v>
       </c>
       <c r="B38" t="n">
         <v>98101</v>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>73</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4412,10 +4412,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>855110</v>
+        <v>855074</v>
       </c>
       <c r="R38" t="n">
-        <v>7478072</v>
+        <v>7478164</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4475,10 +4475,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427365</v>
+        <v>124427389</v>
       </c>
       <c r="B39" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4487,38 +4487,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>854939</v>
+        <v>855110</v>
       </c>
       <c r="R39" t="n">
-        <v>7478324</v>
+        <v>7478072</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4559,6 +4563,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4577,10 +4582,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427393</v>
+        <v>124427345</v>
       </c>
       <c r="B40" t="n">
-        <v>56714</v>
+        <v>79927</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4589,38 +4594,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>854990</v>
+        <v>854967</v>
       </c>
       <c r="R40" t="n">
-        <v>7478363</v>
+        <v>7478177</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4679,10 +4684,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427400</v>
+        <v>124427406</v>
       </c>
       <c r="B41" t="n">
-        <v>82597</v>
+        <v>91579</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4691,38 +4696,45 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>760</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>855012</v>
+        <v>855096</v>
       </c>
       <c r="R41" t="n">
-        <v>7478269</v>
+        <v>7478199</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4757,12 +4769,18 @@
           <t>2025-04-24</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4781,10 +4799,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427352</v>
+        <v>124427365</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>79428</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4793,42 +4811,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>855059</v>
+        <v>854939</v>
       </c>
       <c r="R42" t="n">
-        <v>7478173</v>
+        <v>7478324</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4869,7 +4883,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4888,10 +4901,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427369</v>
+        <v>124427354</v>
       </c>
       <c r="B43" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4904,34 +4917,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>854943</v>
+        <v>855018</v>
       </c>
       <c r="R43" t="n">
-        <v>7478362</v>
+        <v>7478119</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5097,10 +5110,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427403</v>
+        <v>124427356</v>
       </c>
       <c r="B45" t="n">
-        <v>79826</v>
+        <v>79926</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5113,34 +5126,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6457</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>854946</v>
+        <v>854977</v>
       </c>
       <c r="R45" t="n">
-        <v>7478367</v>
+        <v>7478167</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5181,7 +5194,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5200,10 +5212,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427406</v>
+        <v>124427402</v>
       </c>
       <c r="B46" t="n">
-        <v>91579</v>
+        <v>82597</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5212,45 +5224,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>760</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>855096</v>
+        <v>854960</v>
       </c>
       <c r="R46" t="n">
-        <v>7478199</v>
+        <v>7478309</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5285,18 +5290,12 @@
           <t>2025-04-24</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5315,10 +5314,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427399</v>
+        <v>124427347</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5327,38 +5326,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>855007</v>
+        <v>855063</v>
       </c>
       <c r="R47" t="n">
-        <v>7478357</v>
+        <v>7478044</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5417,7 +5416,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427347</v>
+        <v>124427375</v>
       </c>
       <c r="B48" t="n">
         <v>79927</v>
@@ -5453,14 +5452,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>855063</v>
+        <v>854922</v>
       </c>
       <c r="R48" t="n">
-        <v>7478044</v>
+        <v>7478323</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5501,8 +5500,24 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5519,10 +5534,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427398</v>
+        <v>124427401</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5535,21 +5550,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5559,10 +5574,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>855100</v>
+        <v>855011</v>
       </c>
       <c r="R49" t="n">
-        <v>7478058</v>
+        <v>7478352</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5621,10 +5636,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427354</v>
+        <v>124427403</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>79826</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5633,38 +5648,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>855018</v>
+        <v>854946</v>
       </c>
       <c r="R50" t="n">
-        <v>7478119</v>
+        <v>7478367</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5705,6 +5720,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5723,10 +5739,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427346</v>
+        <v>124427393</v>
       </c>
       <c r="B51" t="n">
-        <v>79927</v>
+        <v>56714</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5735,38 +5751,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>855044</v>
+        <v>854990</v>
       </c>
       <c r="R51" t="n">
-        <v>7478074</v>
+        <v>7478363</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5825,10 +5841,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427388</v>
+        <v>124427346</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5837,42 +5853,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>855074</v>
+        <v>855044</v>
       </c>
       <c r="R52" t="n">
-        <v>7478164</v>
+        <v>7478074</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5913,7 +5925,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5932,10 +5943,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427391</v>
+        <v>124427398</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5944,42 +5955,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855091</v>
+        <v>855100</v>
       </c>
       <c r="R53" t="n">
-        <v>7478207</v>
+        <v>7478058</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6020,7 +6027,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6039,10 +6045,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427345</v>
+        <v>124427391</v>
       </c>
       <c r="B54" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6051,38 +6057,42 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>854967</v>
+        <v>855091</v>
       </c>
       <c r="R54" t="n">
-        <v>7478177</v>
+        <v>7478207</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6123,6 +6133,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6141,10 +6152,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427375</v>
+        <v>124427399</v>
       </c>
       <c r="B55" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6153,25 +6164,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6181,10 +6192,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>854922</v>
+        <v>855007</v>
       </c>
       <c r="R55" t="n">
-        <v>7478323</v>
+        <v>7478357</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6225,24 +6236,8 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6259,10 +6254,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427402</v>
+        <v>124427369</v>
       </c>
       <c r="B56" t="n">
-        <v>82597</v>
+        <v>57666</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6275,21 +6270,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6299,10 +6294,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>854960</v>
+        <v>854943</v>
       </c>
       <c r="R56" t="n">
-        <v>7478309</v>
+        <v>7478362</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6468,10 +6463,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124427356</v>
+        <v>124427387</v>
       </c>
       <c r="B58" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6480,38 +6475,42 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>854977</v>
+        <v>855102</v>
       </c>
       <c r="R58" t="n">
-        <v>7478167</v>
+        <v>7478191</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6552,6 +6551,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6570,10 +6570,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855364</v>
+        <v>124855474</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6582,38 +6582,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>855120</v>
+        <v>855065</v>
       </c>
       <c r="R59" t="n">
-        <v>7477887</v>
+        <v>7478197</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6648,18 +6648,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6678,7 +6672,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855467</v>
+        <v>124855416</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -6718,10 +6712,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>855062</v>
+        <v>855002</v>
       </c>
       <c r="R60" t="n">
-        <v>7478002</v>
+        <v>7478149</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6780,10 +6774,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124855275</v>
+        <v>124855420</v>
       </c>
       <c r="B61" t="n">
-        <v>92321</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6792,38 +6786,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>854889</v>
+        <v>855071</v>
       </c>
       <c r="R61" t="n">
-        <v>7477847</v>
+        <v>7477912</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6882,10 +6876,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124855380</v>
+        <v>124855275</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
+        <v>92321</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6894,38 +6888,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>854745</v>
+        <v>854889</v>
       </c>
       <c r="R62" t="n">
-        <v>7477946</v>
+        <v>7477847</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6966,7 +6960,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6985,7 +6978,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124855415</v>
+        <v>124855468</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -7025,10 +7018,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>854928</v>
+        <v>855069</v>
       </c>
       <c r="R63" t="n">
-        <v>7478107</v>
+        <v>7477999</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7087,7 +7080,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124855377</v>
+        <v>124855464</v>
       </c>
       <c r="B64" t="n">
         <v>98101</v>
@@ -7120,21 +7113,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>854672</v>
+        <v>854898</v>
       </c>
       <c r="R64" t="n">
-        <v>7477865</v>
+        <v>7478156</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7161,17 +7150,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>I utkanten av nytt hygge</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7180,7 +7164,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7199,7 +7182,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124855416</v>
+        <v>124855423</v>
       </c>
       <c r="B65" t="n">
         <v>98101</v>
@@ -7239,10 +7222,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>855002</v>
+        <v>854915</v>
       </c>
       <c r="R65" t="n">
-        <v>7478149</v>
+        <v>7477851</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7301,7 +7284,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855390</v>
+        <v>124855424</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -7334,21 +7317,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>854899</v>
+        <v>854780</v>
       </c>
       <c r="R66" t="n">
-        <v>7477831</v>
+        <v>7477939</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7389,7 +7368,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7408,10 +7386,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855250</v>
+        <v>124855512</v>
       </c>
       <c r="B67" t="n">
-        <v>91012</v>
+        <v>79926</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7420,25 +7398,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7448,10 +7426,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>854814</v>
+        <v>854911</v>
       </c>
       <c r="R67" t="n">
-        <v>7477852</v>
+        <v>7478164</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7510,7 +7488,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855404</v>
+        <v>124855390</v>
       </c>
       <c r="B68" t="n">
         <v>98101</v>
@@ -7545,7 +7523,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>28</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7554,10 +7532,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854832</v>
+        <v>854899</v>
       </c>
       <c r="R68" t="n">
-        <v>7477880</v>
+        <v>7477831</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7617,7 +7595,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855249</v>
+        <v>124855244</v>
       </c>
       <c r="B69" t="n">
         <v>91012</v>
@@ -7657,10 +7635,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>854811</v>
+        <v>855187</v>
       </c>
       <c r="R69" t="n">
-        <v>7477849</v>
+        <v>7478029</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7719,10 +7697,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855358</v>
+        <v>124855317</v>
       </c>
       <c r="B70" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7731,38 +7709,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>854772</v>
+        <v>854783</v>
       </c>
       <c r="R70" t="n">
-        <v>7477881</v>
+        <v>7477935</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7797,18 +7775,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7827,10 +7799,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855469</v>
+        <v>124855233</v>
       </c>
       <c r="B71" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7839,25 +7811,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7867,10 +7839,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>854979</v>
+        <v>855073</v>
       </c>
       <c r="R71" t="n">
-        <v>7477885</v>
+        <v>7477920</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7929,10 +7901,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855277</v>
+        <v>124855249</v>
       </c>
       <c r="B72" t="n">
-        <v>79920</v>
+        <v>91012</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7941,25 +7913,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7969,10 +7941,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>855068</v>
+        <v>854811</v>
       </c>
       <c r="R72" t="n">
-        <v>7478046</v>
+        <v>7477849</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8031,10 +8003,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855333</v>
+        <v>124855466</v>
       </c>
       <c r="B73" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8043,25 +8015,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8071,10 +8043,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>854924</v>
+        <v>854921</v>
       </c>
       <c r="R73" t="n">
-        <v>7478087</v>
+        <v>7478082</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8133,10 +8105,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855475</v>
+        <v>124855366</v>
       </c>
       <c r="B74" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8145,38 +8117,42 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>854813</v>
+        <v>854807</v>
       </c>
       <c r="R74" t="n">
-        <v>7477923</v>
+        <v>7477926</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8217,6 +8193,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8235,10 +8212,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124854790</v>
+        <v>124855500</v>
       </c>
       <c r="B75" t="n">
-        <v>98101</v>
+        <v>79826</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8247,42 +8224,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854766</v>
+        <v>854850</v>
       </c>
       <c r="R75" t="n">
-        <v>7478012</v>
+        <v>7477915</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8323,7 +8296,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8342,7 +8314,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855231</v>
+        <v>124855232</v>
       </c>
       <c r="B76" t="n">
         <v>105102</v>
@@ -8382,10 +8354,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>854954</v>
+        <v>855094</v>
       </c>
       <c r="R76" t="n">
-        <v>7478125</v>
+        <v>7477931</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8546,10 +8518,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855464</v>
+        <v>124855333</v>
       </c>
       <c r="B78" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8558,25 +8530,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8586,10 +8558,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>854898</v>
+        <v>854924</v>
       </c>
       <c r="R78" t="n">
-        <v>7478156</v>
+        <v>7478087</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8648,7 +8620,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855359</v>
+        <v>124855418</v>
       </c>
       <c r="B79" t="n">
         <v>98101</v>
@@ -8684,14 +8656,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>854838</v>
+        <v>855131</v>
       </c>
       <c r="R79" t="n">
-        <v>7477840</v>
+        <v>7477924</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8726,18 +8698,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8756,10 +8722,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124855233</v>
+        <v>124855415</v>
       </c>
       <c r="B80" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8768,25 +8734,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8796,10 +8762,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>855073</v>
+        <v>854928</v>
       </c>
       <c r="R80" t="n">
-        <v>7477920</v>
+        <v>7478107</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8858,7 +8824,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855376</v>
+        <v>124855359</v>
       </c>
       <c r="B81" t="n">
         <v>98101</v>
@@ -8891,21 +8857,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>854741</v>
+        <v>854838</v>
       </c>
       <c r="R81" t="n">
-        <v>7477958</v>
+        <v>7477840</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8938,6 +8900,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8965,10 +8932,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124855512</v>
+        <v>124855386</v>
       </c>
       <c r="B82" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8977,38 +8944,42 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>854911</v>
+        <v>854810</v>
       </c>
       <c r="R82" t="n">
-        <v>7478164</v>
+        <v>7477930</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9049,6 +9020,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9067,7 +9039,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855381</v>
+        <v>124855377</v>
       </c>
       <c r="B83" t="n">
         <v>98101</v>
@@ -9100,17 +9072,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>854803</v>
+        <v>854672</v>
       </c>
       <c r="R83" t="n">
-        <v>7477930</v>
+        <v>7477865</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9137,12 +9113,17 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>I utkanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9272,10 +9253,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855394</v>
+        <v>124855277</v>
       </c>
       <c r="B85" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9284,42 +9265,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>854897</v>
+        <v>855068</v>
       </c>
       <c r="R85" t="n">
-        <v>7477846</v>
+        <v>7478046</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9360,7 +9337,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9379,10 +9355,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855235</v>
+        <v>124855469</v>
       </c>
       <c r="B86" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9391,25 +9367,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9419,10 +9395,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>854686</v>
+        <v>854979</v>
       </c>
       <c r="R86" t="n">
-        <v>7477923</v>
+        <v>7477885</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9481,10 +9457,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855500</v>
+        <v>124855417</v>
       </c>
       <c r="B87" t="n">
-        <v>79826</v>
+        <v>98101</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9493,25 +9469,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6457</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9521,10 +9497,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>854850</v>
+        <v>855202</v>
       </c>
       <c r="R87" t="n">
-        <v>7477915</v>
+        <v>7477976</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9583,10 +9559,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855423</v>
+        <v>124855231</v>
       </c>
       <c r="B88" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9595,25 +9571,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9623,10 +9599,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>854915</v>
+        <v>854954</v>
       </c>
       <c r="R88" t="n">
-        <v>7477851</v>
+        <v>7478125</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9685,10 +9661,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855318</v>
+        <v>124855250</v>
       </c>
       <c r="B89" t="n">
-        <v>96985</v>
+        <v>91012</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9697,25 +9673,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9725,10 +9701,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>854817</v>
+        <v>854814</v>
       </c>
       <c r="R89" t="n">
-        <v>7477931</v>
+        <v>7477852</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9787,10 +9763,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124855417</v>
+        <v>124855475</v>
       </c>
       <c r="B90" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9799,25 +9775,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9827,10 +9803,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>855202</v>
+        <v>854813</v>
       </c>
       <c r="R90" t="n">
-        <v>7477976</v>
+        <v>7477923</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9889,7 +9865,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124855366</v>
+        <v>124855398</v>
       </c>
       <c r="B91" t="n">
         <v>98101</v>
@@ -9924,19 +9900,19 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>854807</v>
+        <v>854737</v>
       </c>
       <c r="R91" t="n">
-        <v>7477926</v>
+        <v>7477850</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9963,12 +9939,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9996,10 +9977,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124855474</v>
+        <v>124855421</v>
       </c>
       <c r="B92" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10008,25 +9989,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10036,10 +10017,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>855065</v>
+        <v>854951</v>
       </c>
       <c r="R92" t="n">
-        <v>7478197</v>
+        <v>7477899</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10098,10 +10079,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124855398</v>
+        <v>124855318</v>
       </c>
       <c r="B93" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10110,42 +10091,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>854737</v>
+        <v>854817</v>
       </c>
       <c r="R93" t="n">
-        <v>7477850</v>
+        <v>7477931</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10172,17 +10149,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10191,7 +10163,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10210,10 +10181,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855420</v>
+        <v>124855316</v>
       </c>
       <c r="B94" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10222,25 +10193,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10250,10 +10221,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>855071</v>
+        <v>855019</v>
       </c>
       <c r="R94" t="n">
-        <v>7477912</v>
+        <v>7477888</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10312,10 +10283,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855424</v>
+        <v>124855313</v>
       </c>
       <c r="B95" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10324,25 +10295,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10352,10 +10323,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>854780</v>
+        <v>854814</v>
       </c>
       <c r="R95" t="n">
-        <v>7477939</v>
+        <v>7477852</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10414,7 +10385,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855386</v>
+        <v>124855380</v>
       </c>
       <c r="B96" t="n">
         <v>98101</v>
@@ -10447,21 +10418,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>854810</v>
+        <v>854745</v>
       </c>
       <c r="R96" t="n">
-        <v>7477930</v>
+        <v>7477946</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10521,10 +10488,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124855483</v>
+        <v>124855381</v>
       </c>
       <c r="B97" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10533,25 +10500,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10561,10 +10528,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>855251</v>
+        <v>854803</v>
       </c>
       <c r="R97" t="n">
-        <v>7478036</v>
+        <v>7477930</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10605,6 +10572,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10623,10 +10591,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124854791</v>
+        <v>124854790</v>
       </c>
       <c r="B98" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10635,38 +10603,42 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>854840</v>
+        <v>854766</v>
       </c>
       <c r="R98" t="n">
-        <v>7477716</v>
+        <v>7478012</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10693,12 +10665,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10707,6 +10679,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10725,7 +10698,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124855418</v>
+        <v>124855467</v>
       </c>
       <c r="B99" t="n">
         <v>98101</v>
@@ -10765,10 +10738,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>855131</v>
+        <v>855062</v>
       </c>
       <c r="R99" t="n">
-        <v>7477924</v>
+        <v>7478002</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10827,10 +10800,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124855232</v>
+        <v>124854791</v>
       </c>
       <c r="B100" t="n">
-        <v>105102</v>
+        <v>78810</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10839,38 +10812,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>855094</v>
+        <v>854840</v>
       </c>
       <c r="R100" t="n">
-        <v>7477931</v>
+        <v>7477716</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10897,12 +10870,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10929,10 +10902,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855421</v>
+        <v>124855483</v>
       </c>
       <c r="B101" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10941,25 +10914,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10969,10 +10942,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>854951</v>
+        <v>855251</v>
       </c>
       <c r="R101" t="n">
-        <v>7477899</v>
+        <v>7478036</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11031,7 +11004,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124855466</v>
+        <v>124855371</v>
       </c>
       <c r="B102" t="n">
         <v>98101</v>
@@ -11064,17 +11037,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>854921</v>
+        <v>854845</v>
       </c>
       <c r="R102" t="n">
-        <v>7478082</v>
+        <v>7477869</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11115,6 +11092,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11133,7 +11111,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855389</v>
+        <v>124855376</v>
       </c>
       <c r="B103" t="n">
         <v>98101</v>
@@ -11168,7 +11146,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>71</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11177,10 +11155,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>854906</v>
+        <v>854741</v>
       </c>
       <c r="R103" t="n">
-        <v>7477891</v>
+        <v>7477958</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11240,10 +11218,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855317</v>
+        <v>124855394</v>
       </c>
       <c r="B104" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11252,38 +11230,42 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>854783</v>
+        <v>854897</v>
       </c>
       <c r="R104" t="n">
-        <v>7477935</v>
+        <v>7477846</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11324,6 +11306,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11342,10 +11325,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855316</v>
+        <v>124855364</v>
       </c>
       <c r="B105" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11354,38 +11337,38 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>855019</v>
+        <v>855120</v>
       </c>
       <c r="R105" t="n">
-        <v>7477888</v>
+        <v>7477887</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11420,12 +11403,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11444,7 +11433,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855468</v>
+        <v>124855389</v>
       </c>
       <c r="B106" t="n">
         <v>98101</v>
@@ -11477,17 +11466,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>855069</v>
+        <v>854906</v>
       </c>
       <c r="R106" t="n">
-        <v>7477999</v>
+        <v>7477891</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11528,6 +11521,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11546,10 +11540,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855371</v>
+        <v>124855235</v>
       </c>
       <c r="B107" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11558,42 +11552,38 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>854845</v>
+        <v>854686</v>
       </c>
       <c r="R107" t="n">
-        <v>7477869</v>
+        <v>7477923</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11634,7 +11624,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11653,10 +11642,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855244</v>
+        <v>124855358</v>
       </c>
       <c r="B108" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11665,38 +11654,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>855187</v>
+        <v>854772</v>
       </c>
       <c r="R108" t="n">
-        <v>7478029</v>
+        <v>7477881</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11731,12 +11720,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11755,10 +11750,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855313</v>
+        <v>124855404</v>
       </c>
       <c r="B109" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11767,38 +11762,42 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>854814</v>
+        <v>854832</v>
       </c>
       <c r="R109" t="n">
-        <v>7477852</v>
+        <v>7477880</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11839,6 +11838,7 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -4159,7 +4159,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427400</v>
+        <v>124427401</v>
       </c>
       <c r="B36" t="n">
         <v>82597</v>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>855012</v>
+        <v>855011</v>
       </c>
       <c r="R36" t="n">
-        <v>7478269</v>
+        <v>7478352</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4261,10 +4261,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427352</v>
+        <v>124427356</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4273,42 +4273,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>855059</v>
+        <v>854977</v>
       </c>
       <c r="R37" t="n">
-        <v>7478173</v>
+        <v>7478167</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4349,7 +4345,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4368,10 +4363,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427388</v>
+        <v>124427347</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4380,42 +4375,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>855074</v>
+        <v>855063</v>
       </c>
       <c r="R38" t="n">
-        <v>7478164</v>
+        <v>7478044</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4456,7 +4447,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4475,7 +4465,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427389</v>
+        <v>124427352</v>
       </c>
       <c r="B39" t="n">
         <v>98101</v>
@@ -4510,19 +4500,19 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>855110</v>
+        <v>855059</v>
       </c>
       <c r="R39" t="n">
-        <v>7478072</v>
+        <v>7478173</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4582,10 +4572,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427345</v>
+        <v>124427354</v>
       </c>
       <c r="B40" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4594,25 +4584,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4622,10 +4612,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>854967</v>
+        <v>855018</v>
       </c>
       <c r="R40" t="n">
-        <v>7478177</v>
+        <v>7478119</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4684,10 +4674,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427406</v>
+        <v>124427393</v>
       </c>
       <c r="B41" t="n">
-        <v>91579</v>
+        <v>56714</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4696,45 +4686,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>760</v>
+        <v>102612</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>855096</v>
+        <v>854990</v>
       </c>
       <c r="R41" t="n">
-        <v>7478199</v>
+        <v>7478363</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4769,18 +4752,12 @@
           <t>2025-04-24</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4799,10 +4776,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427365</v>
+        <v>124427351</v>
       </c>
       <c r="B42" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4811,38 +4788,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>854939</v>
+        <v>855056</v>
       </c>
       <c r="R42" t="n">
-        <v>7478324</v>
+        <v>7478165</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4883,6 +4864,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4901,10 +4883,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427354</v>
+        <v>124427345</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4913,25 +4895,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4941,10 +4923,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>855018</v>
+        <v>854967</v>
       </c>
       <c r="R43" t="n">
-        <v>7478119</v>
+        <v>7478177</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5110,10 +5092,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427356</v>
+        <v>124427399</v>
       </c>
       <c r="B45" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5122,20 +5104,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5146,14 +5128,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>854977</v>
+        <v>855007</v>
       </c>
       <c r="R45" t="n">
-        <v>7478167</v>
+        <v>7478357</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5212,10 +5194,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427402</v>
+        <v>124427406</v>
       </c>
       <c r="B46" t="n">
-        <v>82597</v>
+        <v>91579</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5224,38 +5206,45 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>760</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>854960</v>
+        <v>855096</v>
       </c>
       <c r="R46" t="n">
-        <v>7478309</v>
+        <v>7478199</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5290,12 +5279,18 @@
           <t>2025-04-24</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5314,10 +5309,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427347</v>
+        <v>124427387</v>
       </c>
       <c r="B47" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5326,38 +5321,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>855063</v>
+        <v>855102</v>
       </c>
       <c r="R47" t="n">
-        <v>7478044</v>
+        <v>7478191</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5398,6 +5397,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5416,10 +5416,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427375</v>
+        <v>124427402</v>
       </c>
       <c r="B48" t="n">
-        <v>79927</v>
+        <v>82597</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5428,25 +5428,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5456,10 +5456,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>854922</v>
+        <v>854960</v>
       </c>
       <c r="R48" t="n">
-        <v>7478323</v>
+        <v>7478309</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5500,24 +5500,8 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5534,10 +5518,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427401</v>
+        <v>124427365</v>
       </c>
       <c r="B49" t="n">
-        <v>82597</v>
+        <v>79428</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5550,21 +5534,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5574,10 +5558,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>855011</v>
+        <v>854939</v>
       </c>
       <c r="R49" t="n">
-        <v>7478352</v>
+        <v>7478324</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5636,10 +5620,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427403</v>
+        <v>124427391</v>
       </c>
       <c r="B50" t="n">
-        <v>79826</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5648,38 +5632,42 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6457</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>854946</v>
+        <v>855091</v>
       </c>
       <c r="R50" t="n">
-        <v>7478367</v>
+        <v>7478207</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5739,10 +5727,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427393</v>
+        <v>124427400</v>
       </c>
       <c r="B51" t="n">
-        <v>56714</v>
+        <v>82597</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5755,21 +5743,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102612</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5779,10 +5767,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>854990</v>
+        <v>855012</v>
       </c>
       <c r="R51" t="n">
-        <v>7478363</v>
+        <v>7478269</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5841,10 +5829,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427346</v>
+        <v>124427389</v>
       </c>
       <c r="B52" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5853,38 +5841,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>855044</v>
+        <v>855110</v>
       </c>
       <c r="R52" t="n">
-        <v>7478074</v>
+        <v>7478072</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5925,6 +5917,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5943,10 +5936,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427398</v>
+        <v>124427388</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5955,38 +5948,42 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855100</v>
+        <v>855074</v>
       </c>
       <c r="R53" t="n">
-        <v>7478058</v>
+        <v>7478164</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6027,6 +6024,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6045,10 +6043,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427391</v>
+        <v>124427403</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>79826</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6057,42 +6055,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>855091</v>
+        <v>854946</v>
       </c>
       <c r="R54" t="n">
-        <v>7478207</v>
+        <v>7478367</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6152,10 +6146,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427399</v>
+        <v>124427369</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6168,21 +6162,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6192,10 +6186,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>855007</v>
+        <v>854943</v>
       </c>
       <c r="R55" t="n">
-        <v>7478357</v>
+        <v>7478362</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6254,10 +6248,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427369</v>
+        <v>124427375</v>
       </c>
       <c r="B56" t="n">
-        <v>57666</v>
+        <v>79927</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6266,25 +6260,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6294,10 +6288,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>854943</v>
+        <v>854922</v>
       </c>
       <c r="R56" t="n">
-        <v>7478362</v>
+        <v>7478323</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6338,8 +6332,24 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6356,10 +6366,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124427351</v>
+        <v>124427346</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6368,42 +6378,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>855056</v>
+        <v>855044</v>
       </c>
       <c r="R57" t="n">
-        <v>7478165</v>
+        <v>7478074</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6444,7 +6450,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6463,10 +6468,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124427387</v>
+        <v>124427398</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6475,42 +6480,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>855102</v>
+        <v>855100</v>
       </c>
       <c r="R58" t="n">
-        <v>7478191</v>
+        <v>7478058</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6551,7 +6552,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6570,10 +6570,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855474</v>
+        <v>124855359</v>
       </c>
       <c r="B59" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6582,38 +6582,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>855065</v>
+        <v>854838</v>
       </c>
       <c r="R59" t="n">
-        <v>7478197</v>
+        <v>7477840</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6648,12 +6648,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6672,10 +6678,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855416</v>
+        <v>124855313</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6684,25 +6690,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6712,10 +6718,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>855002</v>
+        <v>854814</v>
       </c>
       <c r="R60" t="n">
-        <v>7478149</v>
+        <v>7477852</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6774,10 +6780,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124855420</v>
+        <v>124855512</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6786,25 +6792,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6814,10 +6820,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>855071</v>
+        <v>854911</v>
       </c>
       <c r="R61" t="n">
-        <v>7477912</v>
+        <v>7478164</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6876,10 +6882,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124855275</v>
+        <v>124855474</v>
       </c>
       <c r="B62" t="n">
-        <v>92321</v>
+        <v>56714</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6892,34 +6898,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5449</v>
+        <v>102612</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>854889</v>
+        <v>855065</v>
       </c>
       <c r="R62" t="n">
-        <v>7477847</v>
+        <v>7478197</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6978,7 +6984,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124855468</v>
+        <v>124855394</v>
       </c>
       <c r="B63" t="n">
         <v>98101</v>
@@ -7011,17 +7017,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>855069</v>
+        <v>854897</v>
       </c>
       <c r="R63" t="n">
-        <v>7477999</v>
+        <v>7477846</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7062,6 +7072,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7080,7 +7091,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124855464</v>
+        <v>124855421</v>
       </c>
       <c r="B64" t="n">
         <v>98101</v>
@@ -7120,10 +7131,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>854898</v>
+        <v>854951</v>
       </c>
       <c r="R64" t="n">
-        <v>7478156</v>
+        <v>7477899</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7182,7 +7193,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124855423</v>
+        <v>124855464</v>
       </c>
       <c r="B65" t="n">
         <v>98101</v>
@@ -7222,10 +7233,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>854915</v>
+        <v>854898</v>
       </c>
       <c r="R65" t="n">
-        <v>7477851</v>
+        <v>7478156</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7284,10 +7295,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855424</v>
+        <v>124855316</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7296,25 +7307,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7324,10 +7335,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>854780</v>
+        <v>855019</v>
       </c>
       <c r="R66" t="n">
-        <v>7477939</v>
+        <v>7477888</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7386,10 +7397,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855512</v>
+        <v>124855381</v>
       </c>
       <c r="B67" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7398,25 +7409,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7426,10 +7437,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>854911</v>
+        <v>854803</v>
       </c>
       <c r="R67" t="n">
-        <v>7478164</v>
+        <v>7477930</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7470,6 +7481,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7488,7 +7500,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855390</v>
+        <v>124855469</v>
       </c>
       <c r="B68" t="n">
         <v>98101</v>
@@ -7521,21 +7533,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854899</v>
+        <v>854979</v>
       </c>
       <c r="R68" t="n">
-        <v>7477831</v>
+        <v>7477885</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7576,7 +7584,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7595,10 +7602,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855244</v>
+        <v>124855275</v>
       </c>
       <c r="B69" t="n">
-        <v>91012</v>
+        <v>92321</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7611,34 +7618,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>5449</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>855187</v>
+        <v>854889</v>
       </c>
       <c r="R69" t="n">
-        <v>7478029</v>
+        <v>7477847</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7697,10 +7704,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855317</v>
+        <v>124855277</v>
       </c>
       <c r="B70" t="n">
-        <v>96985</v>
+        <v>79920</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7713,21 +7720,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7737,10 +7744,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>854783</v>
+        <v>855068</v>
       </c>
       <c r="R70" t="n">
-        <v>7477935</v>
+        <v>7478046</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7799,10 +7806,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855233</v>
+        <v>124855418</v>
       </c>
       <c r="B71" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7811,25 +7818,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7839,10 +7846,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>855073</v>
+        <v>855131</v>
       </c>
       <c r="R71" t="n">
-        <v>7477920</v>
+        <v>7477924</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7901,10 +7908,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855249</v>
+        <v>124854790</v>
       </c>
       <c r="B72" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7913,38 +7920,42 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>854811</v>
+        <v>854766</v>
       </c>
       <c r="R72" t="n">
-        <v>7477849</v>
+        <v>7478012</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7985,6 +7996,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8003,10 +8015,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855466</v>
+        <v>124855483</v>
       </c>
       <c r="B73" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8015,25 +8027,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8043,10 +8055,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>854921</v>
+        <v>855251</v>
       </c>
       <c r="R73" t="n">
-        <v>7478082</v>
+        <v>7478036</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8105,10 +8117,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855366</v>
+        <v>124855249</v>
       </c>
       <c r="B74" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8117,42 +8129,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>854807</v>
+        <v>854811</v>
       </c>
       <c r="R74" t="n">
-        <v>7477926</v>
+        <v>7477849</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8193,7 +8201,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8212,10 +8219,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855500</v>
+        <v>124855358</v>
       </c>
       <c r="B75" t="n">
-        <v>79826</v>
+        <v>98101</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8224,38 +8231,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6457</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854850</v>
+        <v>854772</v>
       </c>
       <c r="R75" t="n">
-        <v>7477915</v>
+        <v>7477881</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8290,12 +8297,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8314,10 +8327,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855232</v>
+        <v>124855376</v>
       </c>
       <c r="B76" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8326,38 +8339,42 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>855094</v>
+        <v>854741</v>
       </c>
       <c r="R76" t="n">
-        <v>7477931</v>
+        <v>7477958</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8398,6 +8415,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8416,10 +8434,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124855524</v>
+        <v>124855250</v>
       </c>
       <c r="B77" t="n">
-        <v>79926</v>
+        <v>91012</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8428,25 +8446,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8456,10 +8474,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>854793</v>
+        <v>854814</v>
       </c>
       <c r="R77" t="n">
-        <v>7477805</v>
+        <v>7477852</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8486,12 +8504,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8518,10 +8536,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855333</v>
+        <v>124855377</v>
       </c>
       <c r="B78" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8530,38 +8548,42 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>854924</v>
+        <v>854672</v>
       </c>
       <c r="R78" t="n">
-        <v>7478087</v>
+        <v>7477865</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8588,12 +8610,17 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>I utkanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8602,6 +8629,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8620,10 +8648,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855418</v>
+        <v>124855235</v>
       </c>
       <c r="B79" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8632,25 +8660,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8660,10 +8688,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>855131</v>
+        <v>854686</v>
       </c>
       <c r="R79" t="n">
-        <v>7477924</v>
+        <v>7477923</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8722,7 +8750,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124855415</v>
+        <v>124855424</v>
       </c>
       <c r="B80" t="n">
         <v>98101</v>
@@ -8762,10 +8790,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>854928</v>
+        <v>854780</v>
       </c>
       <c r="R80" t="n">
-        <v>7478107</v>
+        <v>7477939</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8824,7 +8852,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855359</v>
+        <v>124855364</v>
       </c>
       <c r="B81" t="n">
         <v>98101</v>
@@ -8864,10 +8892,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>854838</v>
+        <v>855120</v>
       </c>
       <c r="R81" t="n">
-        <v>7477840</v>
+        <v>7477887</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8932,10 +8960,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124855386</v>
+        <v>124855500</v>
       </c>
       <c r="B82" t="n">
-        <v>98101</v>
+        <v>79826</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8944,42 +8972,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>854810</v>
+        <v>854850</v>
       </c>
       <c r="R82" t="n">
-        <v>7477930</v>
+        <v>7477915</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9020,7 +9044,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9039,10 +9062,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855377</v>
+        <v>124855244</v>
       </c>
       <c r="B83" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9051,42 +9074,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>854672</v>
+        <v>855187</v>
       </c>
       <c r="R83" t="n">
-        <v>7477865</v>
+        <v>7478029</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9113,17 +9132,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>I utkanten av nytt hygge</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9132,7 +9146,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9151,10 +9164,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855482</v>
+        <v>124855416</v>
       </c>
       <c r="B84" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9163,25 +9176,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9191,10 +9204,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>855134</v>
+        <v>855002</v>
       </c>
       <c r="R84" t="n">
-        <v>7477890</v>
+        <v>7478149</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9253,10 +9266,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855277</v>
+        <v>124855380</v>
       </c>
       <c r="B85" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9265,25 +9278,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9293,10 +9306,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>855068</v>
+        <v>854745</v>
       </c>
       <c r="R85" t="n">
-        <v>7478046</v>
+        <v>7477946</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9337,6 +9350,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9355,10 +9369,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855469</v>
+        <v>124855318</v>
       </c>
       <c r="B86" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9367,25 +9381,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9395,10 +9409,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>854979</v>
+        <v>854817</v>
       </c>
       <c r="R86" t="n">
-        <v>7477885</v>
+        <v>7477931</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9457,7 +9471,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855417</v>
+        <v>124855467</v>
       </c>
       <c r="B87" t="n">
         <v>98101</v>
@@ -9497,10 +9511,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>855202</v>
+        <v>855062</v>
       </c>
       <c r="R87" t="n">
-        <v>7477976</v>
+        <v>7478002</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9559,10 +9573,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855231</v>
+        <v>124855404</v>
       </c>
       <c r="B88" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9571,38 +9585,42 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>854954</v>
+        <v>854832</v>
       </c>
       <c r="R88" t="n">
-        <v>7478125</v>
+        <v>7477880</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9643,6 +9661,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9661,10 +9680,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855250</v>
+        <v>124855233</v>
       </c>
       <c r="B89" t="n">
-        <v>91012</v>
+        <v>105102</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9673,25 +9692,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>221725</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9701,10 +9720,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>854814</v>
+        <v>855073</v>
       </c>
       <c r="R89" t="n">
-        <v>7477852</v>
+        <v>7477920</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9763,10 +9782,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124855475</v>
+        <v>124855232</v>
       </c>
       <c r="B90" t="n">
-        <v>56714</v>
+        <v>105102</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9775,25 +9794,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>102612</v>
+        <v>221725</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9803,10 +9822,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>854813</v>
+        <v>855094</v>
       </c>
       <c r="R90" t="n">
-        <v>7477923</v>
+        <v>7477931</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9865,10 +9884,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124855398</v>
+        <v>124855475</v>
       </c>
       <c r="B91" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9877,42 +9896,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>854737</v>
+        <v>854813</v>
       </c>
       <c r="R91" t="n">
-        <v>7477850</v>
+        <v>7477923</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9939,17 +9954,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9958,7 +9968,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9977,10 +9986,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124855421</v>
+        <v>124855482</v>
       </c>
       <c r="B92" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9989,25 +9998,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10017,10 +10026,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>854951</v>
+        <v>855134</v>
       </c>
       <c r="R92" t="n">
-        <v>7477899</v>
+        <v>7477890</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10079,10 +10088,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124855318</v>
+        <v>124855390</v>
       </c>
       <c r="B93" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10091,38 +10100,42 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>854817</v>
+        <v>854899</v>
       </c>
       <c r="R93" t="n">
-        <v>7477931</v>
+        <v>7477831</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10163,6 +10176,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10181,10 +10195,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855316</v>
+        <v>124855231</v>
       </c>
       <c r="B94" t="n">
-        <v>96985</v>
+        <v>105102</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10197,21 +10211,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10221,10 +10235,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>855019</v>
+        <v>854954</v>
       </c>
       <c r="R94" t="n">
-        <v>7477888</v>
+        <v>7478125</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10283,10 +10297,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855313</v>
+        <v>124855386</v>
       </c>
       <c r="B95" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10295,38 +10309,42 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>854814</v>
+        <v>854810</v>
       </c>
       <c r="R95" t="n">
-        <v>7477852</v>
+        <v>7477930</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10367,6 +10385,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10385,10 +10404,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855380</v>
+        <v>124855524</v>
       </c>
       <c r="B96" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10397,25 +10416,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10425,10 +10444,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>854745</v>
+        <v>854793</v>
       </c>
       <c r="R96" t="n">
-        <v>7477946</v>
+        <v>7477805</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10455,12 +10474,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10469,7 +10488,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10488,7 +10506,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124855381</v>
+        <v>124855398</v>
       </c>
       <c r="B97" t="n">
         <v>98101</v>
@@ -10521,17 +10539,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>854803</v>
+        <v>854737</v>
       </c>
       <c r="R97" t="n">
-        <v>7477930</v>
+        <v>7477850</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10558,12 +10580,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10591,7 +10618,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124854790</v>
+        <v>124855371</v>
       </c>
       <c r="B98" t="n">
         <v>98101</v>
@@ -10626,19 +10653,19 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>112</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>854766</v>
+        <v>854845</v>
       </c>
       <c r="R98" t="n">
-        <v>7478012</v>
+        <v>7477869</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10698,7 +10725,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124855467</v>
+        <v>124855423</v>
       </c>
       <c r="B99" t="n">
         <v>98101</v>
@@ -10738,10 +10765,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>855062</v>
+        <v>854915</v>
       </c>
       <c r="R99" t="n">
-        <v>7478002</v>
+        <v>7477851</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10800,10 +10827,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124854791</v>
+        <v>124855389</v>
       </c>
       <c r="B100" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10812,38 +10839,42 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>854840</v>
+        <v>854906</v>
       </c>
       <c r="R100" t="n">
-        <v>7477716</v>
+        <v>7477891</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10870,12 +10901,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10884,6 +10915,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10902,10 +10934,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855483</v>
+        <v>124855366</v>
       </c>
       <c r="B101" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10914,38 +10946,42 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>855251</v>
+        <v>854807</v>
       </c>
       <c r="R101" t="n">
-        <v>7478036</v>
+        <v>7477926</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10986,6 +11022,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11004,10 +11041,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124855371</v>
+        <v>124854791</v>
       </c>
       <c r="B102" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11016,42 +11053,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>854845</v>
+        <v>854840</v>
       </c>
       <c r="R102" t="n">
-        <v>7477869</v>
+        <v>7477716</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11078,12 +11111,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11092,7 +11125,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11111,10 +11143,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855376</v>
+        <v>124855333</v>
       </c>
       <c r="B103" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11123,42 +11155,38 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>854741</v>
+        <v>854924</v>
       </c>
       <c r="R103" t="n">
-        <v>7477958</v>
+        <v>7478087</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11199,7 +11227,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11218,7 +11245,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855394</v>
+        <v>124855415</v>
       </c>
       <c r="B104" t="n">
         <v>98101</v>
@@ -11251,21 +11278,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>854897</v>
+        <v>854928</v>
       </c>
       <c r="R104" t="n">
-        <v>7477846</v>
+        <v>7478107</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11306,7 +11329,6 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11325,7 +11347,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855364</v>
+        <v>124855420</v>
       </c>
       <c r="B105" t="n">
         <v>98101</v>
@@ -11361,14 +11383,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>855120</v>
+        <v>855071</v>
       </c>
       <c r="R105" t="n">
-        <v>7477887</v>
+        <v>7477912</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11403,18 +11425,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11433,7 +11449,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855389</v>
+        <v>124855417</v>
       </c>
       <c r="B106" t="n">
         <v>98101</v>
@@ -11466,21 +11482,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>854906</v>
+        <v>855202</v>
       </c>
       <c r="R106" t="n">
-        <v>7477891</v>
+        <v>7477976</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11521,7 +11533,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11540,10 +11551,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855235</v>
+        <v>124855317</v>
       </c>
       <c r="B107" t="n">
-        <v>105102</v>
+        <v>96985</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11556,21 +11567,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221725</v>
+        <v>221941</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11580,10 +11591,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>854686</v>
+        <v>854783</v>
       </c>
       <c r="R107" t="n">
-        <v>7477923</v>
+        <v>7477935</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11642,7 +11653,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855358</v>
+        <v>124855466</v>
       </c>
       <c r="B108" t="n">
         <v>98101</v>
@@ -11678,14 +11689,14 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>854772</v>
+        <v>854921</v>
       </c>
       <c r="R108" t="n">
-        <v>7477881</v>
+        <v>7478082</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11720,18 +11731,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11750,7 +11755,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855404</v>
+        <v>124855468</v>
       </c>
       <c r="B109" t="n">
         <v>98101</v>
@@ -11783,21 +11788,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>854832</v>
+        <v>855069</v>
       </c>
       <c r="R109" t="n">
-        <v>7477880</v>
+        <v>7477999</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11838,7 +11839,6 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -6570,10 +6570,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855359</v>
+        <v>124855313</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6582,38 +6582,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>854838</v>
+        <v>854814</v>
       </c>
       <c r="R59" t="n">
-        <v>7477840</v>
+        <v>7477852</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6648,18 +6648,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6678,10 +6672,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855313</v>
+        <v>124855359</v>
       </c>
       <c r="B60" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6690,38 +6684,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>854814</v>
+        <v>854838</v>
       </c>
       <c r="R60" t="n">
-        <v>7477852</v>
+        <v>7477840</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6756,12 +6750,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -8015,10 +8015,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855483</v>
+        <v>124855358</v>
       </c>
       <c r="B73" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8027,38 +8027,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>855251</v>
+        <v>854772</v>
       </c>
       <c r="R73" t="n">
-        <v>7478036</v>
+        <v>7477881</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8093,12 +8093,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8117,10 +8123,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855249</v>
+        <v>124855376</v>
       </c>
       <c r="B74" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8129,38 +8135,42 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>854811</v>
+        <v>854741</v>
       </c>
       <c r="R74" t="n">
-        <v>7477849</v>
+        <v>7477958</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8201,6 +8211,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8219,10 +8230,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855358</v>
+        <v>124855249</v>
       </c>
       <c r="B75" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8231,38 +8242,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854772</v>
+        <v>854811</v>
       </c>
       <c r="R75" t="n">
-        <v>7477881</v>
+        <v>7477849</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8297,18 +8308,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8327,10 +8332,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855376</v>
+        <v>124855483</v>
       </c>
       <c r="B76" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8339,42 +8344,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>854741</v>
+        <v>855251</v>
       </c>
       <c r="R76" t="n">
-        <v>7477958</v>
+        <v>7478036</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8415,7 +8416,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427401</v>
+        <v>124427352</v>
       </c>
       <c r="B36" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4171,38 +4171,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>855011</v>
+        <v>855059</v>
       </c>
       <c r="R36" t="n">
-        <v>7478352</v>
+        <v>7478173</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4243,6 +4247,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4261,10 +4266,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427356</v>
+        <v>124427406</v>
       </c>
       <c r="B37" t="n">
-        <v>79926</v>
+        <v>91579</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4273,38 +4278,45 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>760</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>854977</v>
+        <v>855096</v>
       </c>
       <c r="R37" t="n">
-        <v>7478167</v>
+        <v>7478199</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4339,12 +4351,18 @@
           <t>2025-04-24</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4363,10 +4381,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427347</v>
+        <v>124427401</v>
       </c>
       <c r="B38" t="n">
-        <v>79927</v>
+        <v>82597</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4375,38 +4393,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>855063</v>
+        <v>855011</v>
       </c>
       <c r="R38" t="n">
-        <v>7478044</v>
+        <v>7478352</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4465,10 +4483,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427352</v>
+        <v>124427346</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4477,42 +4495,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>855059</v>
+        <v>855044</v>
       </c>
       <c r="R39" t="n">
-        <v>7478173</v>
+        <v>7478074</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4553,7 +4567,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4572,10 +4585,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427354</v>
+        <v>124427356</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4584,20 +4597,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4612,10 +4625,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>855018</v>
+        <v>854977</v>
       </c>
       <c r="R40" t="n">
-        <v>7478119</v>
+        <v>7478167</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4674,10 +4687,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427393</v>
+        <v>124427375</v>
       </c>
       <c r="B41" t="n">
-        <v>56714</v>
+        <v>79927</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4686,25 +4699,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4714,10 +4727,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>854990</v>
+        <v>854922</v>
       </c>
       <c r="R41" t="n">
-        <v>7478363</v>
+        <v>7478323</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4758,8 +4771,24 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4776,7 +4805,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427351</v>
+        <v>124427389</v>
       </c>
       <c r="B42" t="n">
         <v>98101</v>
@@ -4811,19 +4840,19 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>855056</v>
+        <v>855110</v>
       </c>
       <c r="R42" t="n">
-        <v>7478165</v>
+        <v>7478072</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4883,10 +4912,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427345</v>
+        <v>124427400</v>
       </c>
       <c r="B43" t="n">
-        <v>79927</v>
+        <v>82597</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4895,38 +4924,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>854967</v>
+        <v>855012</v>
       </c>
       <c r="R43" t="n">
-        <v>7478177</v>
+        <v>7478269</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4985,10 +5014,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427386</v>
+        <v>124427399</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4997,42 +5026,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>855066</v>
+        <v>855007</v>
       </c>
       <c r="R44" t="n">
-        <v>7478180</v>
+        <v>7478357</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5073,7 +5098,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5092,10 +5116,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427399</v>
+        <v>124427347</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5104,38 +5128,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>855007</v>
+        <v>855063</v>
       </c>
       <c r="R45" t="n">
-        <v>7478357</v>
+        <v>7478044</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5194,10 +5218,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427406</v>
+        <v>124427398</v>
       </c>
       <c r="B46" t="n">
-        <v>91579</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5206,45 +5230,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>855096</v>
+        <v>855100</v>
       </c>
       <c r="R46" t="n">
-        <v>7478199</v>
+        <v>7478058</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5279,18 +5296,12 @@
           <t>2025-04-24</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5416,10 +5427,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427402</v>
+        <v>124427388</v>
       </c>
       <c r="B48" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5428,38 +5439,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>854960</v>
+        <v>855074</v>
       </c>
       <c r="R48" t="n">
-        <v>7478309</v>
+        <v>7478164</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5500,6 +5515,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5620,10 +5636,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427391</v>
+        <v>124427354</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5632,42 +5648,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>855091</v>
+        <v>855018</v>
       </c>
       <c r="R50" t="n">
-        <v>7478207</v>
+        <v>7478119</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5708,7 +5720,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5727,10 +5738,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427400</v>
+        <v>124427369</v>
       </c>
       <c r="B51" t="n">
-        <v>82597</v>
+        <v>57666</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5743,21 +5754,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5767,10 +5778,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>855012</v>
+        <v>854943</v>
       </c>
       <c r="R51" t="n">
-        <v>7478269</v>
+        <v>7478362</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5829,7 +5840,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427389</v>
+        <v>124427386</v>
       </c>
       <c r="B52" t="n">
         <v>98101</v>
@@ -5864,7 +5875,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>117</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5873,10 +5884,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>855110</v>
+        <v>855066</v>
       </c>
       <c r="R52" t="n">
-        <v>7478072</v>
+        <v>7478180</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5936,10 +5947,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427388</v>
+        <v>124427345</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5948,42 +5959,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855074</v>
+        <v>854967</v>
       </c>
       <c r="R53" t="n">
-        <v>7478164</v>
+        <v>7478177</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6024,7 +6031,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6146,10 +6152,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427369</v>
+        <v>124427402</v>
       </c>
       <c r="B55" t="n">
-        <v>57666</v>
+        <v>82597</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6162,21 +6168,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6186,10 +6192,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>854943</v>
+        <v>854960</v>
       </c>
       <c r="R55" t="n">
-        <v>7478362</v>
+        <v>7478309</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6248,10 +6254,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427375</v>
+        <v>124427391</v>
       </c>
       <c r="B56" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6260,38 +6266,42 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>854922</v>
+        <v>855091</v>
       </c>
       <c r="R56" t="n">
-        <v>7478323</v>
+        <v>7478207</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6335,21 +6345,6 @@
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6366,10 +6361,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124427346</v>
+        <v>124427393</v>
       </c>
       <c r="B57" t="n">
-        <v>79927</v>
+        <v>56714</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6378,38 +6373,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>855044</v>
+        <v>854990</v>
       </c>
       <c r="R57" t="n">
-        <v>7478074</v>
+        <v>7478363</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6468,10 +6463,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124427398</v>
+        <v>124427351</v>
       </c>
       <c r="B58" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6480,38 +6475,42 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>855100</v>
+        <v>855056</v>
       </c>
       <c r="R58" t="n">
-        <v>7478058</v>
+        <v>7478165</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6552,6 +6551,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6570,10 +6570,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855313</v>
+        <v>124855398</v>
       </c>
       <c r="B59" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6582,38 +6582,42 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>854814</v>
+        <v>854737</v>
       </c>
       <c r="R59" t="n">
-        <v>7477852</v>
+        <v>7477850</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6640,12 +6644,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6654,6 +6663,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6672,7 +6682,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855359</v>
+        <v>124855371</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -6705,17 +6715,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>854838</v>
+        <v>854845</v>
       </c>
       <c r="R60" t="n">
-        <v>7477840</v>
+        <v>7477869</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6748,11 +6762,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6780,10 +6789,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124855512</v>
+        <v>124855468</v>
       </c>
       <c r="B61" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6792,25 +6801,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6820,10 +6829,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>854911</v>
+        <v>855069</v>
       </c>
       <c r="R61" t="n">
-        <v>7478164</v>
+        <v>7477999</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6882,10 +6891,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124855474</v>
+        <v>124855313</v>
       </c>
       <c r="B62" t="n">
-        <v>56714</v>
+        <v>91299</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6898,21 +6907,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>102612</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6922,10 +6931,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>855065</v>
+        <v>854814</v>
       </c>
       <c r="R62" t="n">
-        <v>7478197</v>
+        <v>7477852</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6984,10 +6993,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124855394</v>
+        <v>124855475</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6996,42 +7005,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>854897</v>
+        <v>854813</v>
       </c>
       <c r="R63" t="n">
-        <v>7477846</v>
+        <v>7477923</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7072,7 +7077,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7091,10 +7095,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124855421</v>
+        <v>124855474</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7103,25 +7107,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7131,10 +7135,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>854951</v>
+        <v>855065</v>
       </c>
       <c r="R64" t="n">
-        <v>7477899</v>
+        <v>7478197</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7193,10 +7197,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124855464</v>
+        <v>124855275</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
+        <v>92321</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7205,38 +7209,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>854898</v>
+        <v>854889</v>
       </c>
       <c r="R65" t="n">
-        <v>7478156</v>
+        <v>7477847</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7295,10 +7299,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855316</v>
+        <v>124855390</v>
       </c>
       <c r="B66" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7307,38 +7311,42 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>855019</v>
+        <v>854899</v>
       </c>
       <c r="R66" t="n">
-        <v>7477888</v>
+        <v>7477831</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7379,6 +7387,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7397,7 +7406,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855381</v>
+        <v>124855416</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -7437,10 +7446,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>854803</v>
+        <v>855002</v>
       </c>
       <c r="R67" t="n">
-        <v>7477930</v>
+        <v>7478149</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7481,7 +7490,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7500,7 +7508,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855469</v>
+        <v>124855404</v>
       </c>
       <c r="B68" t="n">
         <v>98101</v>
@@ -7533,17 +7541,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854979</v>
+        <v>854832</v>
       </c>
       <c r="R68" t="n">
-        <v>7477885</v>
+        <v>7477880</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7584,6 +7596,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7602,10 +7615,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855275</v>
+        <v>124855366</v>
       </c>
       <c r="B69" t="n">
-        <v>92321</v>
+        <v>98101</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7614,38 +7627,42 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>854889</v>
+        <v>854807</v>
       </c>
       <c r="R69" t="n">
-        <v>7477847</v>
+        <v>7477926</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7686,6 +7703,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7704,10 +7722,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855277</v>
+        <v>124855317</v>
       </c>
       <c r="B70" t="n">
-        <v>79920</v>
+        <v>96985</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7720,21 +7738,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7744,10 +7762,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>855068</v>
+        <v>854783</v>
       </c>
       <c r="R70" t="n">
-        <v>7478046</v>
+        <v>7477935</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7806,10 +7824,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855418</v>
+        <v>124855250</v>
       </c>
       <c r="B71" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7818,25 +7836,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7846,10 +7864,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>855131</v>
+        <v>854814</v>
       </c>
       <c r="R71" t="n">
-        <v>7477924</v>
+        <v>7477852</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7908,7 +7926,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124854790</v>
+        <v>124855394</v>
       </c>
       <c r="B72" t="n">
         <v>98101</v>
@@ -7943,19 +7961,19 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>854766</v>
+        <v>854897</v>
       </c>
       <c r="R72" t="n">
-        <v>7478012</v>
+        <v>7477846</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8015,7 +8033,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855358</v>
+        <v>124855389</v>
       </c>
       <c r="B73" t="n">
         <v>98101</v>
@@ -8048,17 +8066,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>854772</v>
+        <v>854906</v>
       </c>
       <c r="R73" t="n">
-        <v>7477881</v>
+        <v>7477891</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8091,11 +8113,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8123,7 +8140,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855376</v>
+        <v>124855420</v>
       </c>
       <c r="B74" t="n">
         <v>98101</v>
@@ -8156,21 +8173,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>854741</v>
+        <v>855071</v>
       </c>
       <c r="R74" t="n">
-        <v>7477958</v>
+        <v>7477912</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8211,7 +8224,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8230,10 +8242,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855249</v>
+        <v>124855235</v>
       </c>
       <c r="B75" t="n">
-        <v>91012</v>
+        <v>105102</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8242,25 +8254,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>221725</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8270,10 +8282,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854811</v>
+        <v>854686</v>
       </c>
       <c r="R75" t="n">
-        <v>7477849</v>
+        <v>7477923</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8332,10 +8344,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855483</v>
+        <v>124855464</v>
       </c>
       <c r="B76" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8344,25 +8356,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8372,10 +8384,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>855251</v>
+        <v>854898</v>
       </c>
       <c r="R76" t="n">
-        <v>7478036</v>
+        <v>7478156</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8434,10 +8446,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124855250</v>
+        <v>124854790</v>
       </c>
       <c r="B77" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8446,38 +8458,42 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>854814</v>
+        <v>854766</v>
       </c>
       <c r="R77" t="n">
-        <v>7477852</v>
+        <v>7478012</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8518,6 +8534,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8536,7 +8553,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855377</v>
+        <v>124855364</v>
       </c>
       <c r="B78" t="n">
         <v>98101</v>
@@ -8569,21 +8586,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>854672</v>
+        <v>855120</v>
       </c>
       <c r="R78" t="n">
-        <v>7477865</v>
+        <v>7477887</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8610,17 +8623,17 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>I utkanten av nytt hygge</t>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8648,10 +8661,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855235</v>
+        <v>124855424</v>
       </c>
       <c r="B79" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8660,25 +8673,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8688,10 +8701,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>854686</v>
+        <v>854780</v>
       </c>
       <c r="R79" t="n">
-        <v>7477923</v>
+        <v>7477939</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8750,10 +8763,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124855424</v>
+        <v>124855333</v>
       </c>
       <c r="B80" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8762,25 +8775,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8790,10 +8803,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>854780</v>
+        <v>854924</v>
       </c>
       <c r="R80" t="n">
-        <v>7477939</v>
+        <v>7478087</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8852,7 +8865,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855364</v>
+        <v>124855376</v>
       </c>
       <c r="B81" t="n">
         <v>98101</v>
@@ -8885,17 +8898,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>855120</v>
+        <v>854741</v>
       </c>
       <c r="R81" t="n">
-        <v>7477887</v>
+        <v>7477958</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8928,11 +8945,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8960,10 +8972,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124855500</v>
+        <v>124855249</v>
       </c>
       <c r="B82" t="n">
-        <v>79826</v>
+        <v>91012</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8972,25 +8984,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6457</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9000,10 +9012,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>854850</v>
+        <v>854811</v>
       </c>
       <c r="R82" t="n">
-        <v>7477915</v>
+        <v>7477849</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9062,10 +9074,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855244</v>
+        <v>124855469</v>
       </c>
       <c r="B83" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9074,25 +9086,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9102,10 +9114,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>855187</v>
+        <v>854979</v>
       </c>
       <c r="R83" t="n">
-        <v>7478029</v>
+        <v>7477885</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9164,7 +9176,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855416</v>
+        <v>124855380</v>
       </c>
       <c r="B84" t="n">
         <v>98101</v>
@@ -9204,10 +9216,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>855002</v>
+        <v>854745</v>
       </c>
       <c r="R84" t="n">
-        <v>7478149</v>
+        <v>7477946</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9248,6 +9260,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9266,7 +9279,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855380</v>
+        <v>124855423</v>
       </c>
       <c r="B85" t="n">
         <v>98101</v>
@@ -9306,10 +9319,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>854745</v>
+        <v>854915</v>
       </c>
       <c r="R85" t="n">
-        <v>7477946</v>
+        <v>7477851</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9350,7 +9363,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9369,10 +9381,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855318</v>
+        <v>124855232</v>
       </c>
       <c r="B86" t="n">
-        <v>96985</v>
+        <v>105102</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9385,21 +9397,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9409,7 +9421,7 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>854817</v>
+        <v>855094</v>
       </c>
       <c r="R86" t="n">
         <v>7477931</v>
@@ -9573,10 +9585,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855404</v>
+        <v>124855244</v>
       </c>
       <c r="B88" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9585,42 +9597,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>854832</v>
+        <v>855187</v>
       </c>
       <c r="R88" t="n">
-        <v>7477880</v>
+        <v>7478029</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9661,7 +9669,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9680,10 +9687,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855233</v>
+        <v>124855417</v>
       </c>
       <c r="B89" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9692,25 +9699,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9720,10 +9727,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>855073</v>
+        <v>855202</v>
       </c>
       <c r="R89" t="n">
-        <v>7477920</v>
+        <v>7477976</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9782,10 +9789,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124855232</v>
+        <v>124855377</v>
       </c>
       <c r="B90" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9794,38 +9801,42 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>855094</v>
+        <v>854672</v>
       </c>
       <c r="R90" t="n">
-        <v>7477931</v>
+        <v>7477865</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9852,12 +9863,17 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>I utkanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9866,6 +9882,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9884,10 +9901,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124855475</v>
+        <v>124855483</v>
       </c>
       <c r="B91" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9900,21 +9917,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9924,10 +9941,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>854813</v>
+        <v>855251</v>
       </c>
       <c r="R91" t="n">
-        <v>7477923</v>
+        <v>7478036</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9986,10 +10003,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124855482</v>
+        <v>124855233</v>
       </c>
       <c r="B92" t="n">
-        <v>78810</v>
+        <v>105102</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9998,25 +10015,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10026,10 +10043,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>855134</v>
+        <v>855073</v>
       </c>
       <c r="R92" t="n">
-        <v>7477890</v>
+        <v>7477920</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10088,10 +10105,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124855390</v>
+        <v>124855524</v>
       </c>
       <c r="B93" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10100,42 +10117,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>854899</v>
+        <v>854793</v>
       </c>
       <c r="R93" t="n">
-        <v>7477831</v>
+        <v>7477805</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10162,12 +10175,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10176,7 +10189,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10195,10 +10207,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855231</v>
+        <v>124855482</v>
       </c>
       <c r="B94" t="n">
-        <v>105102</v>
+        <v>78810</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10207,25 +10219,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10235,10 +10247,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>854954</v>
+        <v>855134</v>
       </c>
       <c r="R94" t="n">
-        <v>7478125</v>
+        <v>7477890</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10297,10 +10309,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855386</v>
+        <v>124854791</v>
       </c>
       <c r="B95" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10309,42 +10321,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>854810</v>
+        <v>854840</v>
       </c>
       <c r="R95" t="n">
-        <v>7477930</v>
+        <v>7477716</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10371,12 +10379,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10385,7 +10393,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10404,10 +10411,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855524</v>
+        <v>124855418</v>
       </c>
       <c r="B96" t="n">
-        <v>79926</v>
+        <v>98101</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10416,25 +10423,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10444,10 +10451,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>854793</v>
+        <v>855131</v>
       </c>
       <c r="R96" t="n">
-        <v>7477805</v>
+        <v>7477924</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10474,12 +10481,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10506,7 +10513,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124855398</v>
+        <v>124855381</v>
       </c>
       <c r="B97" t="n">
         <v>98101</v>
@@ -10539,21 +10546,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>854737</v>
+        <v>854803</v>
       </c>
       <c r="R97" t="n">
-        <v>7477850</v>
+        <v>7477930</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10580,17 +10583,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10618,10 +10616,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124855371</v>
+        <v>124855500</v>
       </c>
       <c r="B98" t="n">
-        <v>98101</v>
+        <v>79826</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10630,42 +10628,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>854845</v>
+        <v>854850</v>
       </c>
       <c r="R98" t="n">
-        <v>7477869</v>
+        <v>7477915</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10706,7 +10700,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10725,10 +10718,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124855423</v>
+        <v>124855512</v>
       </c>
       <c r="B99" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10737,25 +10730,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10765,10 +10758,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>854915</v>
+        <v>854911</v>
       </c>
       <c r="R99" t="n">
-        <v>7477851</v>
+        <v>7478164</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10827,7 +10820,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124855389</v>
+        <v>124855421</v>
       </c>
       <c r="B100" t="n">
         <v>98101</v>
@@ -10860,21 +10853,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>854906</v>
+        <v>854951</v>
       </c>
       <c r="R100" t="n">
-        <v>7477891</v>
+        <v>7477899</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10915,7 +10904,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10934,7 +10922,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855366</v>
+        <v>124855358</v>
       </c>
       <c r="B101" t="n">
         <v>98101</v>
@@ -10967,21 +10955,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>854807</v>
+        <v>854772</v>
       </c>
       <c r="R101" t="n">
-        <v>7477926</v>
+        <v>7477881</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11014,6 +10998,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11041,10 +11030,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124854791</v>
+        <v>124855386</v>
       </c>
       <c r="B102" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11053,38 +11042,42 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>854840</v>
+        <v>854810</v>
       </c>
       <c r="R102" t="n">
-        <v>7477716</v>
+        <v>7477930</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11111,12 +11104,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11125,6 +11118,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11143,10 +11137,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855333</v>
+        <v>124855466</v>
       </c>
       <c r="B103" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11155,25 +11149,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11183,10 +11177,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>854924</v>
+        <v>854921</v>
       </c>
       <c r="R103" t="n">
-        <v>7478087</v>
+        <v>7478082</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11347,10 +11341,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855420</v>
+        <v>124855316</v>
       </c>
       <c r="B105" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11359,25 +11353,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11387,10 +11381,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>855071</v>
+        <v>855019</v>
       </c>
       <c r="R105" t="n">
-        <v>7477912</v>
+        <v>7477888</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11449,10 +11443,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855417</v>
+        <v>124855318</v>
       </c>
       <c r="B106" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11461,25 +11455,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11489,10 +11483,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>855202</v>
+        <v>854817</v>
       </c>
       <c r="R106" t="n">
-        <v>7477976</v>
+        <v>7477931</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11551,10 +11545,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855317</v>
+        <v>124855277</v>
       </c>
       <c r="B107" t="n">
-        <v>96985</v>
+        <v>79920</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11567,21 +11561,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11591,10 +11585,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>854783</v>
+        <v>855068</v>
       </c>
       <c r="R107" t="n">
-        <v>7477935</v>
+        <v>7478046</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11653,10 +11647,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855466</v>
+        <v>124855231</v>
       </c>
       <c r="B108" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11665,25 +11659,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11693,10 +11687,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>854921</v>
+        <v>854954</v>
       </c>
       <c r="R108" t="n">
-        <v>7478082</v>
+        <v>7478125</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11755,7 +11749,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855468</v>
+        <v>124855359</v>
       </c>
       <c r="B109" t="n">
         <v>98101</v>
@@ -11791,14 +11785,14 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>855069</v>
+        <v>854838</v>
       </c>
       <c r="R109" t="n">
-        <v>7477999</v>
+        <v>7477840</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11833,12 +11827,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -6152,10 +6152,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427402</v>
+        <v>124427393</v>
       </c>
       <c r="B55" t="n">
-        <v>82597</v>
+        <v>56714</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6168,21 +6168,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6192,10 +6192,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>854960</v>
+        <v>854990</v>
       </c>
       <c r="R55" t="n">
-        <v>7478309</v>
+        <v>7478363</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6361,10 +6361,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124427393</v>
+        <v>124427402</v>
       </c>
       <c r="B57" t="n">
-        <v>56714</v>
+        <v>82597</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6377,21 +6377,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>102612</v>
+        <v>1312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6401,10 +6401,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>854990</v>
+        <v>854960</v>
       </c>
       <c r="R57" t="n">
-        <v>7478363</v>
+        <v>7478309</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7299,10 +7299,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855390</v>
+        <v>124855250</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7311,42 +7311,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>854899</v>
+        <v>854814</v>
       </c>
       <c r="R66" t="n">
-        <v>7477831</v>
+        <v>7477852</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7387,7 +7383,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7406,7 +7401,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855416</v>
+        <v>124855390</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -7439,17 +7434,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>855002</v>
+        <v>854899</v>
       </c>
       <c r="R67" t="n">
-        <v>7478149</v>
+        <v>7477831</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7490,6 +7489,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7508,7 +7508,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855404</v>
+        <v>124855416</v>
       </c>
       <c r="B68" t="n">
         <v>98101</v>
@@ -7541,21 +7541,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854832</v>
+        <v>855002</v>
       </c>
       <c r="R68" t="n">
-        <v>7477880</v>
+        <v>7478149</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7596,7 +7592,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7615,7 +7610,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855366</v>
+        <v>124855404</v>
       </c>
       <c r="B69" t="n">
         <v>98101</v>
@@ -7650,7 +7645,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -7659,10 +7654,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>854807</v>
+        <v>854832</v>
       </c>
       <c r="R69" t="n">
-        <v>7477926</v>
+        <v>7477880</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7722,10 +7717,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855317</v>
+        <v>124855366</v>
       </c>
       <c r="B70" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7734,38 +7729,42 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>854783</v>
+        <v>854807</v>
       </c>
       <c r="R70" t="n">
-        <v>7477935</v>
+        <v>7477926</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7806,6 +7805,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7824,10 +7824,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855250</v>
+        <v>124855317</v>
       </c>
       <c r="B71" t="n">
-        <v>91012</v>
+        <v>96985</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7836,25 +7836,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7864,10 +7864,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>854814</v>
+        <v>854783</v>
       </c>
       <c r="R71" t="n">
-        <v>7477852</v>
+        <v>7477935</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7926,10 +7926,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855394</v>
+        <v>124855235</v>
       </c>
       <c r="B72" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7938,42 +7938,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>854897</v>
+        <v>854686</v>
       </c>
       <c r="R72" t="n">
-        <v>7477846</v>
+        <v>7477923</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8014,7 +8010,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8033,7 +8028,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855389</v>
+        <v>124855394</v>
       </c>
       <c r="B73" t="n">
         <v>98101</v>
@@ -8068,7 +8063,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8077,10 +8072,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>854906</v>
+        <v>854897</v>
       </c>
       <c r="R73" t="n">
-        <v>7477891</v>
+        <v>7477846</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8140,7 +8135,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855420</v>
+        <v>124855389</v>
       </c>
       <c r="B74" t="n">
         <v>98101</v>
@@ -8173,17 +8168,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>855071</v>
+        <v>854906</v>
       </c>
       <c r="R74" t="n">
-        <v>7477912</v>
+        <v>7477891</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8224,6 +8223,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8242,10 +8242,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855235</v>
+        <v>124855420</v>
       </c>
       <c r="B75" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8254,25 +8254,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8282,10 +8282,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854686</v>
+        <v>855071</v>
       </c>
       <c r="R75" t="n">
-        <v>7477923</v>
+        <v>7477912</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8553,10 +8553,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855364</v>
+        <v>124855333</v>
       </c>
       <c r="B78" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8565,38 +8565,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>855120</v>
+        <v>854924</v>
       </c>
       <c r="R78" t="n">
-        <v>7477887</v>
+        <v>7478087</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8631,18 +8631,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8661,7 +8655,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855424</v>
+        <v>124855364</v>
       </c>
       <c r="B79" t="n">
         <v>98101</v>
@@ -8697,14 +8691,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>854780</v>
+        <v>855120</v>
       </c>
       <c r="R79" t="n">
-        <v>7477939</v>
+        <v>7477887</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8739,12 +8733,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8763,10 +8763,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124855333</v>
+        <v>124855424</v>
       </c>
       <c r="B80" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8775,25 +8775,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8803,10 +8803,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>854924</v>
+        <v>854780</v>
       </c>
       <c r="R80" t="n">
-        <v>7478087</v>
+        <v>7477939</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9074,7 +9074,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855469</v>
+        <v>124855423</v>
       </c>
       <c r="B83" t="n">
         <v>98101</v>
@@ -9114,10 +9114,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>854979</v>
+        <v>854915</v>
       </c>
       <c r="R83" t="n">
-        <v>7477885</v>
+        <v>7477851</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9176,7 +9176,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855380</v>
+        <v>124855469</v>
       </c>
       <c r="B84" t="n">
         <v>98101</v>
@@ -9216,10 +9216,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>854745</v>
+        <v>854979</v>
       </c>
       <c r="R84" t="n">
-        <v>7477946</v>
+        <v>7477885</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9260,7 +9260,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9279,7 +9278,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855423</v>
+        <v>124855380</v>
       </c>
       <c r="B85" t="n">
         <v>98101</v>
@@ -9319,10 +9318,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>854915</v>
+        <v>854745</v>
       </c>
       <c r="R85" t="n">
-        <v>7477851</v>
+        <v>7477946</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9363,6 +9362,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -10820,7 +10820,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124855421</v>
+        <v>124855358</v>
       </c>
       <c r="B100" t="n">
         <v>98101</v>
@@ -10856,14 +10856,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>854951</v>
+        <v>854772</v>
       </c>
       <c r="R100" t="n">
-        <v>7477899</v>
+        <v>7477881</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10898,12 +10898,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10922,7 +10928,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855358</v>
+        <v>124855421</v>
       </c>
       <c r="B101" t="n">
         <v>98101</v>
@@ -10958,14 +10964,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>854772</v>
+        <v>854951</v>
       </c>
       <c r="R101" t="n">
-        <v>7477881</v>
+        <v>7477899</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11000,18 +11006,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11341,7 +11341,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855316</v>
+        <v>124855318</v>
       </c>
       <c r="B105" t="n">
         <v>96985</v>
@@ -11381,10 +11381,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>855019</v>
+        <v>854817</v>
       </c>
       <c r="R105" t="n">
-        <v>7477888</v>
+        <v>7477931</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11443,7 +11443,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855318</v>
+        <v>124855316</v>
       </c>
       <c r="B106" t="n">
         <v>96985</v>
@@ -11483,10 +11483,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>854817</v>
+        <v>855019</v>
       </c>
       <c r="R106" t="n">
-        <v>7477931</v>
+        <v>7477888</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11647,10 +11647,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855231</v>
+        <v>124855359</v>
       </c>
       <c r="B108" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11659,38 +11659,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>854954</v>
+        <v>854838</v>
       </c>
       <c r="R108" t="n">
-        <v>7478125</v>
+        <v>7477840</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11725,12 +11725,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11749,10 +11755,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855359</v>
+        <v>124855231</v>
       </c>
       <c r="B109" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11761,38 +11767,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>854838</v>
+        <v>854954</v>
       </c>
       <c r="R109" t="n">
-        <v>7477840</v>
+        <v>7478125</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11827,18 +11833,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427352</v>
+        <v>124427401</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>82597</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4171,42 +4171,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>855059</v>
+        <v>855011</v>
       </c>
       <c r="R36" t="n">
-        <v>7478173</v>
+        <v>7478352</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4247,7 +4243,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4266,10 +4261,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427406</v>
+        <v>124427400</v>
       </c>
       <c r="B37" t="n">
-        <v>91579</v>
+        <v>82597</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4278,45 +4273,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>760</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>855096</v>
+        <v>855012</v>
       </c>
       <c r="R37" t="n">
-        <v>7478199</v>
+        <v>7478269</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4351,18 +4339,12 @@
           <t>2025-04-24</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4381,10 +4363,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427401</v>
+        <v>124427354</v>
       </c>
       <c r="B38" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4397,34 +4379,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>855011</v>
+        <v>855018</v>
       </c>
       <c r="R38" t="n">
-        <v>7478352</v>
+        <v>7478119</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4483,7 +4465,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427346</v>
+        <v>124427375</v>
       </c>
       <c r="B39" t="n">
         <v>79927</v>
@@ -4519,14 +4501,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>855044</v>
+        <v>854922</v>
       </c>
       <c r="R39" t="n">
-        <v>7478074</v>
+        <v>7478323</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4567,8 +4549,24 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4585,10 +4583,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427356</v>
+        <v>124427399</v>
       </c>
       <c r="B40" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4597,20 +4595,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4621,14 +4619,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>854977</v>
+        <v>855007</v>
       </c>
       <c r="R40" t="n">
-        <v>7478167</v>
+        <v>7478357</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4687,10 +4685,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427375</v>
+        <v>124427393</v>
       </c>
       <c r="B41" t="n">
-        <v>79927</v>
+        <v>56714</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4699,25 +4697,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4727,10 +4725,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>854922</v>
+        <v>854990</v>
       </c>
       <c r="R41" t="n">
-        <v>7478323</v>
+        <v>7478363</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4771,24 +4769,8 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4805,10 +4787,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427389</v>
+        <v>124427345</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4817,42 +4799,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>855110</v>
+        <v>854967</v>
       </c>
       <c r="R42" t="n">
-        <v>7478072</v>
+        <v>7478177</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4893,7 +4871,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4912,10 +4889,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427400</v>
+        <v>124427398</v>
       </c>
       <c r="B43" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4928,21 +4905,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4952,10 +4929,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>855012</v>
+        <v>855100</v>
       </c>
       <c r="R43" t="n">
-        <v>7478269</v>
+        <v>7478058</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5014,10 +4991,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427399</v>
+        <v>124427406</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>91579</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5026,38 +5003,45 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>855007</v>
+        <v>855096</v>
       </c>
       <c r="R44" t="n">
-        <v>7478357</v>
+        <v>7478199</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5092,12 +5076,18 @@
           <t>2025-04-24</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5116,10 +5106,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427347</v>
+        <v>124427402</v>
       </c>
       <c r="B45" t="n">
-        <v>79927</v>
+        <v>82597</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5128,38 +5118,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>855063</v>
+        <v>854960</v>
       </c>
       <c r="R45" t="n">
-        <v>7478044</v>
+        <v>7478309</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5218,10 +5208,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427398</v>
+        <v>124427403</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>79826</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5230,25 +5220,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5258,10 +5248,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>855100</v>
+        <v>854946</v>
       </c>
       <c r="R46" t="n">
-        <v>7478058</v>
+        <v>7478367</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5302,6 +5292,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5320,10 +5311,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427387</v>
+        <v>124427365</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>79428</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5332,42 +5323,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>855102</v>
+        <v>854939</v>
       </c>
       <c r="R47" t="n">
-        <v>7478191</v>
+        <v>7478324</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5408,7 +5395,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5427,7 +5413,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427388</v>
+        <v>124427391</v>
       </c>
       <c r="B48" t="n">
         <v>98101</v>
@@ -5462,7 +5448,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5471,10 +5457,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>855074</v>
+        <v>855091</v>
       </c>
       <c r="R48" t="n">
-        <v>7478164</v>
+        <v>7478207</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5534,10 +5520,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427365</v>
+        <v>124427388</v>
       </c>
       <c r="B49" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5546,38 +5532,42 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>854939</v>
+        <v>855074</v>
       </c>
       <c r="R49" t="n">
-        <v>7478324</v>
+        <v>7478164</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5618,6 +5608,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5636,10 +5627,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427354</v>
+        <v>124427386</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5648,38 +5639,42 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>855018</v>
+        <v>855066</v>
       </c>
       <c r="R50" t="n">
-        <v>7478119</v>
+        <v>7478180</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5720,6 +5715,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5738,10 +5734,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427369</v>
+        <v>124427389</v>
       </c>
       <c r="B51" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5750,38 +5746,42 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>854943</v>
+        <v>855110</v>
       </c>
       <c r="R51" t="n">
-        <v>7478362</v>
+        <v>7478072</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5822,6 +5822,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5840,10 +5841,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427386</v>
+        <v>124427369</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5852,42 +5853,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>855066</v>
+        <v>854943</v>
       </c>
       <c r="R52" t="n">
-        <v>7478180</v>
+        <v>7478362</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5928,7 +5925,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5947,7 +5943,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427345</v>
+        <v>124427347</v>
       </c>
       <c r="B53" t="n">
         <v>79927</v>
@@ -5987,10 +5983,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>854967</v>
+        <v>855063</v>
       </c>
       <c r="R53" t="n">
-        <v>7478177</v>
+        <v>7478044</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6049,10 +6045,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427403</v>
+        <v>124427346</v>
       </c>
       <c r="B54" t="n">
-        <v>79826</v>
+        <v>79927</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6065,34 +6061,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6457</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>854946</v>
+        <v>855044</v>
       </c>
       <c r="R54" t="n">
-        <v>7478367</v>
+        <v>7478074</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6133,7 +6129,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6152,10 +6147,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427393</v>
+        <v>124427352</v>
       </c>
       <c r="B55" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6164,38 +6159,42 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>854990</v>
+        <v>855059</v>
       </c>
       <c r="R55" t="n">
-        <v>7478363</v>
+        <v>7478173</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6236,6 +6235,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6254,10 +6254,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427391</v>
+        <v>124427356</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6266,42 +6266,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>855091</v>
+        <v>854977</v>
       </c>
       <c r="R56" t="n">
-        <v>7478207</v>
+        <v>7478167</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6342,7 +6338,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6361,10 +6356,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124427402</v>
+        <v>124427351</v>
       </c>
       <c r="B57" t="n">
-        <v>82597</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6373,38 +6368,42 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>854960</v>
+        <v>855056</v>
       </c>
       <c r="R57" t="n">
-        <v>7478309</v>
+        <v>7478165</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6445,6 +6444,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6463,7 +6463,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124427351</v>
+        <v>124427387</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -6498,19 +6498,19 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>855056</v>
+        <v>855102</v>
       </c>
       <c r="R58" t="n">
-        <v>7478165</v>
+        <v>7478191</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6570,10 +6570,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855398</v>
+        <v>124855318</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6582,42 +6582,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>854737</v>
+        <v>854817</v>
       </c>
       <c r="R59" t="n">
-        <v>7477850</v>
+        <v>7477931</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6644,17 +6640,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6663,7 +6654,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6682,10 +6672,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855371</v>
+        <v>124854791</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6694,42 +6684,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>854845</v>
+        <v>854840</v>
       </c>
       <c r="R60" t="n">
-        <v>7477869</v>
+        <v>7477716</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6756,12 +6742,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6770,7 +6756,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6789,10 +6774,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124855468</v>
+        <v>124855482</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6801,25 +6786,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6829,10 +6814,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>855069</v>
+        <v>855134</v>
       </c>
       <c r="R61" t="n">
-        <v>7477999</v>
+        <v>7477890</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6891,10 +6876,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124855313</v>
+        <v>124855420</v>
       </c>
       <c r="B62" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6903,25 +6888,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6931,10 +6916,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>854814</v>
+        <v>855071</v>
       </c>
       <c r="R62" t="n">
-        <v>7477852</v>
+        <v>7477912</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6993,10 +6978,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124855475</v>
+        <v>124855415</v>
       </c>
       <c r="B63" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7005,25 +6990,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7033,10 +7018,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>854813</v>
+        <v>854928</v>
       </c>
       <c r="R63" t="n">
-        <v>7477923</v>
+        <v>7478107</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7095,10 +7080,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124855474</v>
+        <v>124855358</v>
       </c>
       <c r="B64" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7107,38 +7092,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>855065</v>
+        <v>854772</v>
       </c>
       <c r="R64" t="n">
-        <v>7478197</v>
+        <v>7477881</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7173,12 +7158,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7197,10 +7188,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124855275</v>
+        <v>124855316</v>
       </c>
       <c r="B65" t="n">
-        <v>92321</v>
+        <v>96985</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7209,38 +7200,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5449</v>
+        <v>221941</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>854889</v>
+        <v>855019</v>
       </c>
       <c r="R65" t="n">
-        <v>7477847</v>
+        <v>7477888</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7299,10 +7290,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855250</v>
+        <v>124855416</v>
       </c>
       <c r="B66" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7311,25 +7302,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7339,10 +7330,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>854814</v>
+        <v>855002</v>
       </c>
       <c r="R66" t="n">
-        <v>7477852</v>
+        <v>7478149</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7401,7 +7392,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855390</v>
+        <v>124855381</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -7434,21 +7425,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>854899</v>
+        <v>854803</v>
       </c>
       <c r="R67" t="n">
-        <v>7477831</v>
+        <v>7477930</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7508,7 +7495,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855416</v>
+        <v>124855389</v>
       </c>
       <c r="B68" t="n">
         <v>98101</v>
@@ -7541,17 +7528,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>855002</v>
+        <v>854906</v>
       </c>
       <c r="R68" t="n">
-        <v>7478149</v>
+        <v>7477891</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7592,6 +7583,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7610,7 +7602,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855404</v>
+        <v>124855376</v>
       </c>
       <c r="B69" t="n">
         <v>98101</v>
@@ -7645,7 +7637,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>71</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -7654,10 +7646,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>854832</v>
+        <v>854741</v>
       </c>
       <c r="R69" t="n">
-        <v>7477880</v>
+        <v>7477958</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7717,7 +7709,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855366</v>
+        <v>124855359</v>
       </c>
       <c r="B70" t="n">
         <v>98101</v>
@@ -7750,21 +7742,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>854807</v>
+        <v>854838</v>
       </c>
       <c r="R70" t="n">
-        <v>7477926</v>
+        <v>7477840</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7797,6 +7785,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7824,10 +7817,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855317</v>
+        <v>124855244</v>
       </c>
       <c r="B71" t="n">
-        <v>96985</v>
+        <v>91012</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7836,25 +7829,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7864,10 +7857,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>854783</v>
+        <v>855187</v>
       </c>
       <c r="R71" t="n">
-        <v>7477935</v>
+        <v>7478029</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7926,10 +7919,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855235</v>
+        <v>124855394</v>
       </c>
       <c r="B72" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7938,38 +7931,42 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>854686</v>
+        <v>854897</v>
       </c>
       <c r="R72" t="n">
-        <v>7477923</v>
+        <v>7477846</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8010,6 +8007,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8028,7 +8026,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855394</v>
+        <v>124855380</v>
       </c>
       <c r="B73" t="n">
         <v>98101</v>
@@ -8061,21 +8059,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>854897</v>
+        <v>854745</v>
       </c>
       <c r="R73" t="n">
-        <v>7477846</v>
+        <v>7477946</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8135,7 +8129,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855389</v>
+        <v>124855464</v>
       </c>
       <c r="B74" t="n">
         <v>98101</v>
@@ -8168,21 +8162,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>854906</v>
+        <v>854898</v>
       </c>
       <c r="R74" t="n">
-        <v>7477891</v>
+        <v>7478156</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8223,7 +8213,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8242,7 +8231,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855420</v>
+        <v>124855386</v>
       </c>
       <c r="B75" t="n">
         <v>98101</v>
@@ -8275,17 +8264,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>855071</v>
+        <v>854810</v>
       </c>
       <c r="R75" t="n">
-        <v>7477912</v>
+        <v>7477930</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8326,6 +8319,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8344,10 +8338,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855464</v>
+        <v>124855232</v>
       </c>
       <c r="B76" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8356,25 +8350,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8384,10 +8378,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>854898</v>
+        <v>855094</v>
       </c>
       <c r="R76" t="n">
-        <v>7478156</v>
+        <v>7477931</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8446,10 +8440,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124854790</v>
+        <v>124855483</v>
       </c>
       <c r="B77" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8458,42 +8452,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>854766</v>
+        <v>855251</v>
       </c>
       <c r="R77" t="n">
-        <v>7478012</v>
+        <v>7478036</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8534,7 +8524,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8553,10 +8542,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855333</v>
+        <v>124855390</v>
       </c>
       <c r="B78" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8565,38 +8554,42 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>854924</v>
+        <v>854899</v>
       </c>
       <c r="R78" t="n">
-        <v>7478087</v>
+        <v>7477831</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8637,6 +8630,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8655,7 +8649,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855364</v>
+        <v>124855468</v>
       </c>
       <c r="B79" t="n">
         <v>98101</v>
@@ -8691,14 +8685,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>855120</v>
+        <v>855069</v>
       </c>
       <c r="R79" t="n">
-        <v>7477887</v>
+        <v>7477999</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8733,18 +8727,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8763,10 +8751,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124855424</v>
+        <v>124855277</v>
       </c>
       <c r="B80" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8775,25 +8763,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8803,10 +8791,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>854780</v>
+        <v>855068</v>
       </c>
       <c r="R80" t="n">
-        <v>7477939</v>
+        <v>7478046</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8865,10 +8853,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855376</v>
+        <v>124855231</v>
       </c>
       <c r="B81" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8877,42 +8865,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>854741</v>
+        <v>854954</v>
       </c>
       <c r="R81" t="n">
-        <v>7477958</v>
+        <v>7478125</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8953,7 +8937,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8972,10 +8955,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124855249</v>
+        <v>124855398</v>
       </c>
       <c r="B82" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8984,38 +8967,42 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>854811</v>
+        <v>854737</v>
       </c>
       <c r="R82" t="n">
-        <v>7477849</v>
+        <v>7477850</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9042,12 +9029,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9056,6 +9048,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9074,7 +9067,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855423</v>
+        <v>124854790</v>
       </c>
       <c r="B83" t="n">
         <v>98101</v>
@@ -9107,17 +9100,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>854915</v>
+        <v>854766</v>
       </c>
       <c r="R83" t="n">
-        <v>7477851</v>
+        <v>7478012</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9158,6 +9155,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9278,7 +9276,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855380</v>
+        <v>124855466</v>
       </c>
       <c r="B85" t="n">
         <v>98101</v>
@@ -9318,10 +9316,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>854745</v>
+        <v>854921</v>
       </c>
       <c r="R85" t="n">
-        <v>7477946</v>
+        <v>7478082</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9362,7 +9360,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9381,10 +9378,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855232</v>
+        <v>124855404</v>
       </c>
       <c r="B86" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9393,38 +9390,42 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>855094</v>
+        <v>854832</v>
       </c>
       <c r="R86" t="n">
-        <v>7477931</v>
+        <v>7477880</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9465,6 +9466,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9483,7 +9485,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855467</v>
+        <v>124855366</v>
       </c>
       <c r="B87" t="n">
         <v>98101</v>
@@ -9516,17 +9518,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>855062</v>
+        <v>854807</v>
       </c>
       <c r="R87" t="n">
-        <v>7478002</v>
+        <v>7477926</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9567,6 +9573,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9585,10 +9592,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855244</v>
+        <v>124855377</v>
       </c>
       <c r="B88" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9597,38 +9604,42 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>855187</v>
+        <v>854672</v>
       </c>
       <c r="R88" t="n">
-        <v>7478029</v>
+        <v>7477865</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9655,12 +9666,17 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>I utkanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9669,6 +9685,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9687,10 +9704,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855417</v>
+        <v>124855250</v>
       </c>
       <c r="B89" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9699,25 +9716,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9727,10 +9744,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>855202</v>
+        <v>854814</v>
       </c>
       <c r="R89" t="n">
-        <v>7477976</v>
+        <v>7477852</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9789,10 +9806,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124855377</v>
+        <v>124855475</v>
       </c>
       <c r="B90" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9801,42 +9818,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>854672</v>
+        <v>854813</v>
       </c>
       <c r="R90" t="n">
-        <v>7477865</v>
+        <v>7477923</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9863,17 +9876,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>I utkanten av nytt hygge</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9882,7 +9890,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9901,10 +9908,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124855483</v>
+        <v>124855333</v>
       </c>
       <c r="B91" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9913,25 +9920,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9941,10 +9948,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>855251</v>
+        <v>854924</v>
       </c>
       <c r="R91" t="n">
-        <v>7478036</v>
+        <v>7478087</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10003,10 +10010,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124855233</v>
+        <v>124855418</v>
       </c>
       <c r="B92" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10015,25 +10022,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10043,10 +10050,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>855073</v>
+        <v>855131</v>
       </c>
       <c r="R92" t="n">
-        <v>7477920</v>
+        <v>7477924</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10105,10 +10112,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124855524</v>
+        <v>124855275</v>
       </c>
       <c r="B93" t="n">
-        <v>79926</v>
+        <v>92321</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10117,38 +10124,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6463</v>
+        <v>5449</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>854793</v>
+        <v>854889</v>
       </c>
       <c r="R93" t="n">
-        <v>7477805</v>
+        <v>7477847</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10175,12 +10182,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10207,10 +10214,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855482</v>
+        <v>124855317</v>
       </c>
       <c r="B94" t="n">
-        <v>78810</v>
+        <v>96985</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10219,25 +10226,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10247,10 +10254,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>855134</v>
+        <v>854783</v>
       </c>
       <c r="R94" t="n">
-        <v>7477890</v>
+        <v>7477935</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10309,10 +10316,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124854791</v>
+        <v>124855421</v>
       </c>
       <c r="B95" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10321,38 +10328,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>854840</v>
+        <v>854951</v>
       </c>
       <c r="R95" t="n">
-        <v>7477716</v>
+        <v>7477899</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10379,12 +10386,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10411,7 +10418,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855418</v>
+        <v>124855364</v>
       </c>
       <c r="B96" t="n">
         <v>98101</v>
@@ -10447,14 +10454,14 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>855131</v>
+        <v>855120</v>
       </c>
       <c r="R96" t="n">
-        <v>7477924</v>
+        <v>7477887</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10489,12 +10496,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10513,10 +10526,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124855381</v>
+        <v>124855512</v>
       </c>
       <c r="B97" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10525,25 +10538,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10553,10 +10566,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>854803</v>
+        <v>854911</v>
       </c>
       <c r="R97" t="n">
-        <v>7477930</v>
+        <v>7478164</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10597,7 +10610,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10616,10 +10628,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124855500</v>
+        <v>124855371</v>
       </c>
       <c r="B98" t="n">
-        <v>79826</v>
+        <v>98101</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10628,38 +10640,42 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6457</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>854850</v>
+        <v>854845</v>
       </c>
       <c r="R98" t="n">
-        <v>7477915</v>
+        <v>7477869</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10700,6 +10716,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10718,10 +10735,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124855512</v>
+        <v>124855249</v>
       </c>
       <c r="B99" t="n">
-        <v>79926</v>
+        <v>91012</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10730,25 +10747,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10758,10 +10775,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>854911</v>
+        <v>854811</v>
       </c>
       <c r="R99" t="n">
-        <v>7478164</v>
+        <v>7477849</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10820,10 +10837,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124855358</v>
+        <v>124855474</v>
       </c>
       <c r="B100" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10832,38 +10849,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>854772</v>
+        <v>855065</v>
       </c>
       <c r="R100" t="n">
-        <v>7477881</v>
+        <v>7478197</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10898,18 +10915,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10928,7 +10939,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855421</v>
+        <v>124855467</v>
       </c>
       <c r="B101" t="n">
         <v>98101</v>
@@ -10968,10 +10979,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>854951</v>
+        <v>855062</v>
       </c>
       <c r="R101" t="n">
-        <v>7477899</v>
+        <v>7478002</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11030,7 +11041,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124855386</v>
+        <v>124855424</v>
       </c>
       <c r="B102" t="n">
         <v>98101</v>
@@ -11063,21 +11074,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>854810</v>
+        <v>854780</v>
       </c>
       <c r="R102" t="n">
-        <v>7477930</v>
+        <v>7477939</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11118,7 +11125,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11137,7 +11143,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855466</v>
+        <v>124855423</v>
       </c>
       <c r="B103" t="n">
         <v>98101</v>
@@ -11177,10 +11183,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>854921</v>
+        <v>854915</v>
       </c>
       <c r="R103" t="n">
-        <v>7478082</v>
+        <v>7477851</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11239,10 +11245,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855415</v>
+        <v>124855235</v>
       </c>
       <c r="B104" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11251,25 +11257,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11279,10 +11285,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>854928</v>
+        <v>854686</v>
       </c>
       <c r="R104" t="n">
-        <v>7478107</v>
+        <v>7477923</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11341,10 +11347,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855318</v>
+        <v>124855233</v>
       </c>
       <c r="B105" t="n">
-        <v>96985</v>
+        <v>105102</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11357,21 +11363,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11381,10 +11387,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>854817</v>
+        <v>855073</v>
       </c>
       <c r="R105" t="n">
-        <v>7477931</v>
+        <v>7477920</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11443,10 +11449,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855316</v>
+        <v>124855313</v>
       </c>
       <c r="B106" t="n">
-        <v>96985</v>
+        <v>91299</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11455,25 +11461,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221941</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11483,10 +11489,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>855019</v>
+        <v>854814</v>
       </c>
       <c r="R106" t="n">
-        <v>7477888</v>
+        <v>7477852</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11545,10 +11551,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855277</v>
+        <v>124855500</v>
       </c>
       <c r="B107" t="n">
-        <v>79920</v>
+        <v>79826</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11561,21 +11567,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6462</v>
+        <v>6457</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11585,10 +11591,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>855068</v>
+        <v>854850</v>
       </c>
       <c r="R107" t="n">
-        <v>7478046</v>
+        <v>7477915</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11647,10 +11653,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855359</v>
+        <v>124855524</v>
       </c>
       <c r="B108" t="n">
-        <v>98101</v>
+        <v>79926</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11659,38 +11665,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>854838</v>
+        <v>854793</v>
       </c>
       <c r="R108" t="n">
-        <v>7477840</v>
+        <v>7477805</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11717,17 +11723,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11736,7 +11737,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11755,10 +11755,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855231</v>
+        <v>124855417</v>
       </c>
       <c r="B109" t="n">
-        <v>105102</v>
+        <v>98101</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11767,25 +11767,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11795,10 +11795,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>854954</v>
+        <v>855202</v>
       </c>
       <c r="R109" t="n">
-        <v>7478125</v>
+        <v>7477976</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427401</v>
+        <v>124427369</v>
       </c>
       <c r="B36" t="n">
-        <v>82597</v>
+        <v>57793</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4175,21 +4175,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>855011</v>
+        <v>854943</v>
       </c>
       <c r="R36" t="n">
-        <v>7478352</v>
+        <v>7478362</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4261,10 +4261,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427400</v>
+        <v>124427393</v>
       </c>
       <c r="B37" t="n">
-        <v>82597</v>
+        <v>56828</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4277,21 +4277,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4301,10 +4301,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>855012</v>
+        <v>854990</v>
       </c>
       <c r="R37" t="n">
-        <v>7478269</v>
+        <v>7478363</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4363,10 +4363,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427354</v>
+        <v>124427386</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4375,38 +4375,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>855018</v>
+        <v>855066</v>
       </c>
       <c r="R38" t="n">
-        <v>7478119</v>
+        <v>7478180</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4447,6 +4451,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4465,10 +4470,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427375</v>
+        <v>124427401</v>
       </c>
       <c r="B39" t="n">
-        <v>79927</v>
+        <v>82737</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4477,25 +4482,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4505,10 +4510,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>854922</v>
+        <v>855011</v>
       </c>
       <c r="R39" t="n">
-        <v>7478323</v>
+        <v>7478352</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4549,24 +4554,8 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4583,10 +4572,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427399</v>
+        <v>124427346</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>80064</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4595,38 +4584,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>855007</v>
+        <v>855044</v>
       </c>
       <c r="R40" t="n">
-        <v>7478357</v>
+        <v>7478074</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4685,10 +4674,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427393</v>
+        <v>124427400</v>
       </c>
       <c r="B41" t="n">
-        <v>56714</v>
+        <v>82737</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4701,21 +4690,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102612</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4725,10 +4714,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>854990</v>
+        <v>855012</v>
       </c>
       <c r="R41" t="n">
-        <v>7478363</v>
+        <v>7478269</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4787,10 +4776,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427345</v>
+        <v>124427347</v>
       </c>
       <c r="B42" t="n">
-        <v>79927</v>
+        <v>80064</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4827,10 +4816,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>854967</v>
+        <v>855063</v>
       </c>
       <c r="R42" t="n">
-        <v>7478177</v>
+        <v>7478044</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4889,10 +4878,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427398</v>
+        <v>124427387</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4901,38 +4890,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>855100</v>
+        <v>855102</v>
       </c>
       <c r="R43" t="n">
-        <v>7478058</v>
+        <v>7478191</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4973,6 +4966,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4994,7 +4988,7 @@
         <v>124427406</v>
       </c>
       <c r="B44" t="n">
-        <v>91579</v>
+        <v>91737</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5106,10 +5100,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427402</v>
+        <v>124427398</v>
       </c>
       <c r="B45" t="n">
-        <v>82597</v>
+        <v>78947</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5122,21 +5116,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5146,10 +5140,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>854960</v>
+        <v>855100</v>
       </c>
       <c r="R45" t="n">
-        <v>7478309</v>
+        <v>7478058</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5208,10 +5202,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427403</v>
+        <v>124427356</v>
       </c>
       <c r="B46" t="n">
-        <v>79826</v>
+        <v>80063</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5224,34 +5218,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6457</v>
+        <v>6463</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>854946</v>
+        <v>854977</v>
       </c>
       <c r="R46" t="n">
-        <v>7478367</v>
+        <v>7478167</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5292,7 +5286,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5314,7 +5307,7 @@
         <v>124427365</v>
       </c>
       <c r="B47" t="n">
-        <v>79428</v>
+        <v>79565</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5413,10 +5406,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427391</v>
+        <v>124427388</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5448,7 +5441,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>73</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5457,10 +5450,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>855091</v>
+        <v>855074</v>
       </c>
       <c r="R48" t="n">
-        <v>7478207</v>
+        <v>7478164</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5520,10 +5513,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427388</v>
+        <v>124427389</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5555,7 +5548,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5564,10 +5557,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>855074</v>
+        <v>855110</v>
       </c>
       <c r="R49" t="n">
-        <v>7478164</v>
+        <v>7478072</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5627,10 +5620,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427386</v>
+        <v>124427354</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5639,42 +5632,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>855066</v>
+        <v>855018</v>
       </c>
       <c r="R50" t="n">
-        <v>7478180</v>
+        <v>7478119</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5715,7 +5704,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5734,10 +5722,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427389</v>
+        <v>124427352</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5769,19 +5757,19 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>855110</v>
+        <v>855059</v>
       </c>
       <c r="R51" t="n">
-        <v>7478072</v>
+        <v>7478173</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5841,10 +5829,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427369</v>
+        <v>124427402</v>
       </c>
       <c r="B52" t="n">
-        <v>57666</v>
+        <v>82737</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5857,21 +5845,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5881,10 +5869,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>854943</v>
+        <v>854960</v>
       </c>
       <c r="R52" t="n">
-        <v>7478362</v>
+        <v>7478309</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5943,10 +5931,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427347</v>
+        <v>124427391</v>
       </c>
       <c r="B53" t="n">
-        <v>79927</v>
+        <v>98269</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5955,38 +5943,42 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855063</v>
+        <v>855091</v>
       </c>
       <c r="R53" t="n">
-        <v>7478044</v>
+        <v>7478207</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6027,6 +6019,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6045,10 +6038,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427346</v>
+        <v>124427375</v>
       </c>
       <c r="B54" t="n">
-        <v>79927</v>
+        <v>80064</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6081,14 +6074,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>855044</v>
+        <v>854922</v>
       </c>
       <c r="R54" t="n">
-        <v>7478074</v>
+        <v>7478323</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6129,8 +6122,24 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6147,10 +6156,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427352</v>
+        <v>124427351</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6182,7 +6191,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>137</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6191,10 +6200,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>855059</v>
+        <v>855056</v>
       </c>
       <c r="R55" t="n">
-        <v>7478173</v>
+        <v>7478165</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6254,10 +6263,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427356</v>
+        <v>124427399</v>
       </c>
       <c r="B56" t="n">
-        <v>79926</v>
+        <v>78947</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6266,20 +6275,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6290,14 +6299,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>854977</v>
+        <v>855007</v>
       </c>
       <c r="R56" t="n">
-        <v>7478167</v>
+        <v>7478357</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6356,10 +6365,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124427351</v>
+        <v>124427345</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>80064</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6368,42 +6377,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>855056</v>
+        <v>854967</v>
       </c>
       <c r="R57" t="n">
-        <v>7478165</v>
+        <v>7478177</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6444,7 +6449,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6463,10 +6467,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124427387</v>
+        <v>124427403</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>79963</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6475,42 +6479,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>855102</v>
+        <v>854946</v>
       </c>
       <c r="R58" t="n">
-        <v>7478191</v>
+        <v>7478367</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6570,10 +6570,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855318</v>
+        <v>124855475</v>
       </c>
       <c r="B59" t="n">
-        <v>96985</v>
+        <v>56828</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6582,25 +6582,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221941</v>
+        <v>102612</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>854817</v>
+        <v>854813</v>
       </c>
       <c r="R59" t="n">
-        <v>7477931</v>
+        <v>7477923</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6672,10 +6672,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124854791</v>
+        <v>124855423</v>
       </c>
       <c r="B60" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6684,38 +6684,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>854840</v>
+        <v>854915</v>
       </c>
       <c r="R60" t="n">
-        <v>7477716</v>
+        <v>7477851</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6742,12 +6742,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6774,10 +6774,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124855482</v>
+        <v>124854791</v>
       </c>
       <c r="B61" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6810,14 +6810,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>855134</v>
+        <v>854840</v>
       </c>
       <c r="R61" t="n">
-        <v>7477890</v>
+        <v>7477716</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6844,12 +6844,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6879,7 +6879,7 @@
         <v>124855420</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6978,10 +6978,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124855415</v>
+        <v>124855235</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>105278</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6990,25 +6990,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>854928</v>
+        <v>854686</v>
       </c>
       <c r="R63" t="n">
-        <v>7478107</v>
+        <v>7477923</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7080,10 +7080,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124855358</v>
+        <v>124855233</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>105278</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7092,38 +7092,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>854772</v>
+        <v>855073</v>
       </c>
       <c r="R64" t="n">
-        <v>7477881</v>
+        <v>7477920</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7158,18 +7158,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7191,7 +7185,7 @@
         <v>124855316</v>
       </c>
       <c r="B65" t="n">
-        <v>96985</v>
+        <v>97153</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7290,10 +7284,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855416</v>
+        <v>124855483</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7302,25 +7296,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7330,10 +7324,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>855002</v>
+        <v>855251</v>
       </c>
       <c r="R66" t="n">
-        <v>7478149</v>
+        <v>7478036</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7392,10 +7386,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855381</v>
+        <v>124855232</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
+        <v>105278</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7404,25 +7398,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7432,10 +7426,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>854803</v>
+        <v>855094</v>
       </c>
       <c r="R67" t="n">
-        <v>7477930</v>
+        <v>7477931</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7476,7 +7470,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7495,10 +7488,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855389</v>
+        <v>124855386</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7530,7 +7523,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7539,10 +7532,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854906</v>
+        <v>854810</v>
       </c>
       <c r="R68" t="n">
-        <v>7477891</v>
+        <v>7477930</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7602,10 +7595,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855376</v>
+        <v>124855466</v>
       </c>
       <c r="B69" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7635,21 +7628,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>854741</v>
+        <v>854921</v>
       </c>
       <c r="R69" t="n">
-        <v>7477958</v>
+        <v>7478082</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7690,7 +7679,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7709,10 +7697,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855359</v>
+        <v>124855464</v>
       </c>
       <c r="B70" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7745,14 +7733,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>854838</v>
+        <v>854898</v>
       </c>
       <c r="R70" t="n">
-        <v>7477840</v>
+        <v>7478156</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7787,18 +7775,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7817,10 +7799,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855244</v>
+        <v>124855390</v>
       </c>
       <c r="B71" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7829,38 +7811,42 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>855187</v>
+        <v>854899</v>
       </c>
       <c r="R71" t="n">
-        <v>7478029</v>
+        <v>7477831</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7901,6 +7887,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7919,10 +7906,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855394</v>
+        <v>124855512</v>
       </c>
       <c r="B72" t="n">
-        <v>98101</v>
+        <v>80063</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7931,42 +7918,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>854897</v>
+        <v>854911</v>
       </c>
       <c r="R72" t="n">
-        <v>7477846</v>
+        <v>7478164</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8007,7 +7990,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8026,10 +8008,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124855380</v>
+        <v>124855424</v>
       </c>
       <c r="B73" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8066,10 +8048,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>854745</v>
+        <v>854780</v>
       </c>
       <c r="R73" t="n">
-        <v>7477946</v>
+        <v>7477939</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8110,7 +8092,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8129,10 +8110,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855464</v>
+        <v>124855381</v>
       </c>
       <c r="B74" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8169,10 +8150,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>854898</v>
+        <v>854803</v>
       </c>
       <c r="R74" t="n">
-        <v>7478156</v>
+        <v>7477930</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8213,6 +8194,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8231,10 +8213,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855386</v>
+        <v>124855358</v>
       </c>
       <c r="B75" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8264,21 +8246,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854810</v>
+        <v>854772</v>
       </c>
       <c r="R75" t="n">
-        <v>7477930</v>
+        <v>7477881</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8311,6 +8289,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8338,10 +8321,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855232</v>
+        <v>124855524</v>
       </c>
       <c r="B76" t="n">
-        <v>105102</v>
+        <v>80063</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8354,21 +8337,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221725</v>
+        <v>6463</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8378,10 +8361,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>855094</v>
+        <v>854793</v>
       </c>
       <c r="R76" t="n">
-        <v>7477931</v>
+        <v>7477805</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8408,12 +8391,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8440,10 +8423,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124855483</v>
+        <v>124855359</v>
       </c>
       <c r="B77" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8452,38 +8435,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>855251</v>
+        <v>854838</v>
       </c>
       <c r="R77" t="n">
-        <v>7478036</v>
+        <v>7477840</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8518,12 +8501,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8542,10 +8531,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855390</v>
+        <v>124855418</v>
       </c>
       <c r="B78" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8575,21 +8564,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>854899</v>
+        <v>855131</v>
       </c>
       <c r="R78" t="n">
-        <v>7477831</v>
+        <v>7477924</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8630,7 +8615,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8649,10 +8633,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855468</v>
+        <v>124855249</v>
       </c>
       <c r="B79" t="n">
-        <v>98101</v>
+        <v>91166</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8661,25 +8645,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8689,10 +8673,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>855069</v>
+        <v>854811</v>
       </c>
       <c r="R79" t="n">
-        <v>7477999</v>
+        <v>7477849</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8751,10 +8735,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124855277</v>
+        <v>124855417</v>
       </c>
       <c r="B80" t="n">
-        <v>79920</v>
+        <v>98269</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8763,25 +8747,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8791,10 +8775,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>855068</v>
+        <v>855202</v>
       </c>
       <c r="R80" t="n">
-        <v>7478046</v>
+        <v>7477976</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8853,10 +8837,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855231</v>
+        <v>124855244</v>
       </c>
       <c r="B81" t="n">
-        <v>105102</v>
+        <v>91166</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8865,25 +8849,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221725</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8893,10 +8877,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>854954</v>
+        <v>855187</v>
       </c>
       <c r="R81" t="n">
-        <v>7478125</v>
+        <v>7478029</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8955,10 +8939,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124855398</v>
+        <v>124855275</v>
       </c>
       <c r="B82" t="n">
-        <v>98101</v>
+        <v>92476</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8967,42 +8951,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>854737</v>
+        <v>854889</v>
       </c>
       <c r="R82" t="n">
-        <v>7477850</v>
+        <v>7477847</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9029,17 +9009,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9048,7 +9023,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9067,10 +9041,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124854790</v>
+        <v>124855317</v>
       </c>
       <c r="B83" t="n">
-        <v>98101</v>
+        <v>97153</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9079,42 +9053,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>854766</v>
+        <v>854783</v>
       </c>
       <c r="R83" t="n">
-        <v>7478012</v>
+        <v>7477935</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9155,7 +9125,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9174,10 +9143,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855469</v>
+        <v>124855364</v>
       </c>
       <c r="B84" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9210,14 +9179,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>854979</v>
+        <v>855120</v>
       </c>
       <c r="R84" t="n">
-        <v>7477885</v>
+        <v>7477887</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9252,12 +9221,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9276,10 +9251,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855466</v>
+        <v>124855404</v>
       </c>
       <c r="B85" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9309,17 +9284,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>854921</v>
+        <v>854832</v>
       </c>
       <c r="R85" t="n">
-        <v>7478082</v>
+        <v>7477880</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9360,6 +9339,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9378,10 +9358,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855404</v>
+        <v>124855366</v>
       </c>
       <c r="B86" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9413,7 +9393,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>167</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9422,10 +9402,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>854832</v>
+        <v>854807</v>
       </c>
       <c r="R86" t="n">
-        <v>7477880</v>
+        <v>7477926</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9485,10 +9465,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855366</v>
+        <v>124855250</v>
       </c>
       <c r="B87" t="n">
-        <v>98101</v>
+        <v>91166</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9497,42 +9477,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>854807</v>
+        <v>854814</v>
       </c>
       <c r="R87" t="n">
-        <v>7477926</v>
+        <v>7477852</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9573,7 +9549,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9592,10 +9567,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855377</v>
+        <v>124855482</v>
       </c>
       <c r="B88" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9604,42 +9579,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>854672</v>
+        <v>855134</v>
       </c>
       <c r="R88" t="n">
-        <v>7477865</v>
+        <v>7477890</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9666,17 +9637,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>I utkanten av nytt hygge</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9685,7 +9651,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9704,10 +9669,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855250</v>
+        <v>124855416</v>
       </c>
       <c r="B89" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9716,25 +9681,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9744,10 +9709,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>854814</v>
+        <v>855002</v>
       </c>
       <c r="R89" t="n">
-        <v>7477852</v>
+        <v>7478149</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9806,10 +9771,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124855475</v>
+        <v>124854790</v>
       </c>
       <c r="B90" t="n">
-        <v>56714</v>
+        <v>98269</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9818,38 +9783,42 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>854813</v>
+        <v>854766</v>
       </c>
       <c r="R90" t="n">
-        <v>7477923</v>
+        <v>7478012</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9890,6 +9859,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9908,10 +9878,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124855333</v>
+        <v>124855389</v>
       </c>
       <c r="B91" t="n">
-        <v>79927</v>
+        <v>98269</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9920,38 +9890,42 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>854924</v>
+        <v>854906</v>
       </c>
       <c r="R91" t="n">
-        <v>7478087</v>
+        <v>7477891</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9992,6 +9966,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -10010,10 +9985,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124855418</v>
+        <v>124855318</v>
       </c>
       <c r="B92" t="n">
-        <v>98101</v>
+        <v>97153</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10022,25 +9997,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10050,10 +10025,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>855131</v>
+        <v>854817</v>
       </c>
       <c r="R92" t="n">
-        <v>7477924</v>
+        <v>7477931</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10112,10 +10087,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124855275</v>
+        <v>124855380</v>
       </c>
       <c r="B93" t="n">
-        <v>92321</v>
+        <v>98269</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10124,38 +10099,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>854889</v>
+        <v>854745</v>
       </c>
       <c r="R93" t="n">
-        <v>7477847</v>
+        <v>7477946</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10196,6 +10171,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10214,10 +10190,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855317</v>
+        <v>124855376</v>
       </c>
       <c r="B94" t="n">
-        <v>96985</v>
+        <v>98269</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10226,38 +10202,42 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>854783</v>
+        <v>854741</v>
       </c>
       <c r="R94" t="n">
-        <v>7477935</v>
+        <v>7477958</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10298,6 +10278,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10316,10 +10297,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855421</v>
+        <v>124855313</v>
       </c>
       <c r="B95" t="n">
-        <v>98101</v>
+        <v>91459</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10328,25 +10309,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10356,10 +10337,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>854951</v>
+        <v>854814</v>
       </c>
       <c r="R95" t="n">
-        <v>7477899</v>
+        <v>7477852</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10418,10 +10399,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855364</v>
+        <v>124855377</v>
       </c>
       <c r="B96" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10451,17 +10432,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>855120</v>
+        <v>854672</v>
       </c>
       <c r="R96" t="n">
-        <v>7477887</v>
+        <v>7477865</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10488,17 +10473,17 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>I kanten av nytt hygge.</t>
+          <t>I utkanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10526,10 +10511,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124855512</v>
+        <v>124855415</v>
       </c>
       <c r="B97" t="n">
-        <v>79926</v>
+        <v>98269</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10538,25 +10523,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10566,10 +10551,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>854911</v>
+        <v>854928</v>
       </c>
       <c r="R97" t="n">
-        <v>7478164</v>
+        <v>7478107</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10628,10 +10613,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124855371</v>
+        <v>124855277</v>
       </c>
       <c r="B98" t="n">
-        <v>98101</v>
+        <v>80057</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10640,42 +10625,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>854845</v>
+        <v>855068</v>
       </c>
       <c r="R98" t="n">
-        <v>7477869</v>
+        <v>7478046</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10716,7 +10697,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10735,10 +10715,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124855249</v>
+        <v>124855371</v>
       </c>
       <c r="B99" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10747,38 +10727,42 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>854811</v>
+        <v>854845</v>
       </c>
       <c r="R99" t="n">
-        <v>7477849</v>
+        <v>7477869</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10819,6 +10803,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10837,10 +10822,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124855474</v>
+        <v>124855421</v>
       </c>
       <c r="B100" t="n">
-        <v>56714</v>
+        <v>98269</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10849,25 +10834,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10877,10 +10862,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>855065</v>
+        <v>854951</v>
       </c>
       <c r="R100" t="n">
-        <v>7478197</v>
+        <v>7477899</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10939,10 +10924,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855467</v>
+        <v>124855398</v>
       </c>
       <c r="B101" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10972,17 +10957,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>855062</v>
+        <v>854737</v>
       </c>
       <c r="R101" t="n">
-        <v>7478002</v>
+        <v>7477850</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11009,12 +10998,17 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11023,6 +11017,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11041,10 +11036,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124855424</v>
+        <v>124855394</v>
       </c>
       <c r="B102" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11074,17 +11069,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>854780</v>
+        <v>854897</v>
       </c>
       <c r="R102" t="n">
-        <v>7477939</v>
+        <v>7477846</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11125,6 +11124,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11143,10 +11143,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855423</v>
+        <v>124855467</v>
       </c>
       <c r="B103" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11183,10 +11183,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>854915</v>
+        <v>855062</v>
       </c>
       <c r="R103" t="n">
-        <v>7477851</v>
+        <v>7478002</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11245,10 +11245,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855235</v>
+        <v>124855333</v>
       </c>
       <c r="B104" t="n">
-        <v>105102</v>
+        <v>80064</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11261,21 +11261,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221725</v>
+        <v>6464</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11285,10 +11285,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>854686</v>
+        <v>854924</v>
       </c>
       <c r="R104" t="n">
-        <v>7477923</v>
+        <v>7478087</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11347,10 +11347,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855233</v>
+        <v>124855474</v>
       </c>
       <c r="B105" t="n">
-        <v>105102</v>
+        <v>56828</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11359,25 +11359,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221725</v>
+        <v>102612</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11387,10 +11387,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>855073</v>
+        <v>855065</v>
       </c>
       <c r="R105" t="n">
-        <v>7477920</v>
+        <v>7478197</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11449,10 +11449,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855313</v>
+        <v>124855500</v>
       </c>
       <c r="B106" t="n">
-        <v>91299</v>
+        <v>79963</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11461,25 +11461,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>6457</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11489,10 +11489,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>854814</v>
+        <v>854850</v>
       </c>
       <c r="R106" t="n">
-        <v>7477852</v>
+        <v>7477915</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11551,10 +11551,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855500</v>
+        <v>124855231</v>
       </c>
       <c r="B107" t="n">
-        <v>79826</v>
+        <v>105278</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11567,21 +11567,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6457</v>
+        <v>221725</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11591,10 +11591,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>854850</v>
+        <v>854954</v>
       </c>
       <c r="R107" t="n">
-        <v>7477915</v>
+        <v>7478125</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11653,10 +11653,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855524</v>
+        <v>124855469</v>
       </c>
       <c r="B108" t="n">
-        <v>79926</v>
+        <v>98269</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11665,25 +11665,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11693,10 +11693,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>854793</v>
+        <v>854979</v>
       </c>
       <c r="R108" t="n">
-        <v>7477805</v>
+        <v>7477885</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11723,12 +11723,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11755,10 +11755,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855417</v>
+        <v>124855468</v>
       </c>
       <c r="B109" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11795,10 +11795,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>855202</v>
+        <v>855069</v>
       </c>
       <c r="R109" t="n">
-        <v>7477976</v>
+        <v>7477999</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -4470,10 +4470,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427401</v>
+        <v>124427346</v>
       </c>
       <c r="B39" t="n">
-        <v>82737</v>
+        <v>80064</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4482,38 +4482,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>855011</v>
+        <v>855044</v>
       </c>
       <c r="R39" t="n">
-        <v>7478352</v>
+        <v>7478074</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4572,10 +4572,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427346</v>
+        <v>124427401</v>
       </c>
       <c r="B40" t="n">
-        <v>80064</v>
+        <v>82737</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4584,38 +4584,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>855044</v>
+        <v>855011</v>
       </c>
       <c r="R40" t="n">
-        <v>7478074</v>
+        <v>7478352</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -8837,10 +8837,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855244</v>
+        <v>124855275</v>
       </c>
       <c r="B81" t="n">
-        <v>91166</v>
+        <v>92476</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8853,34 +8853,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>5449</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>855187</v>
+        <v>854889</v>
       </c>
       <c r="R81" t="n">
-        <v>7478029</v>
+        <v>7477847</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8939,10 +8939,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124855275</v>
+        <v>124855364</v>
       </c>
       <c r="B82" t="n">
-        <v>92476</v>
+        <v>98269</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8951,25 +8951,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8979,10 +8979,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>854889</v>
+        <v>855120</v>
       </c>
       <c r="R82" t="n">
-        <v>7477847</v>
+        <v>7477887</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9017,12 +9017,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9041,10 +9047,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855317</v>
+        <v>124855404</v>
       </c>
       <c r="B83" t="n">
-        <v>97153</v>
+        <v>98269</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9053,38 +9059,42 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>854783</v>
+        <v>854832</v>
       </c>
       <c r="R83" t="n">
-        <v>7477935</v>
+        <v>7477880</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9125,6 +9135,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9143,7 +9154,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855364</v>
+        <v>124855366</v>
       </c>
       <c r="B84" t="n">
         <v>98269</v>
@@ -9176,17 +9187,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>855120</v>
+        <v>854807</v>
       </c>
       <c r="R84" t="n">
-        <v>7477887</v>
+        <v>7477926</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9219,11 +9234,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9251,10 +9261,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855404</v>
+        <v>124855244</v>
       </c>
       <c r="B85" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9263,42 +9273,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>854832</v>
+        <v>855187</v>
       </c>
       <c r="R85" t="n">
-        <v>7477880</v>
+        <v>7478029</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9339,7 +9345,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9358,10 +9363,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855366</v>
+        <v>124855317</v>
       </c>
       <c r="B86" t="n">
-        <v>98269</v>
+        <v>97153</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9370,42 +9375,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>854807</v>
+        <v>854783</v>
       </c>
       <c r="R86" t="n">
-        <v>7477926</v>
+        <v>7477935</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9446,7 +9447,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9465,10 +9465,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855250</v>
+        <v>124855482</v>
       </c>
       <c r="B87" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9481,21 +9481,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9505,10 +9505,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>854814</v>
+        <v>855134</v>
       </c>
       <c r="R87" t="n">
-        <v>7477852</v>
+        <v>7477890</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9567,10 +9567,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855482</v>
+        <v>124855416</v>
       </c>
       <c r="B88" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9579,25 +9579,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9607,10 +9607,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>855134</v>
+        <v>855002</v>
       </c>
       <c r="R88" t="n">
-        <v>7477890</v>
+        <v>7478149</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9669,7 +9669,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855416</v>
+        <v>124854790</v>
       </c>
       <c r="B89" t="n">
         <v>98269</v>
@@ -9702,17 +9702,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>855002</v>
+        <v>854766</v>
       </c>
       <c r="R89" t="n">
-        <v>7478149</v>
+        <v>7478012</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9753,6 +9757,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9771,7 +9776,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124854790</v>
+        <v>124855389</v>
       </c>
       <c r="B90" t="n">
         <v>98269</v>
@@ -9806,19 +9811,19 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>854766</v>
+        <v>854906</v>
       </c>
       <c r="R90" t="n">
-        <v>7478012</v>
+        <v>7477891</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9878,10 +9883,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124855389</v>
+        <v>124855250</v>
       </c>
       <c r="B91" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9890,42 +9895,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>854906</v>
+        <v>854814</v>
       </c>
       <c r="R91" t="n">
-        <v>7477891</v>
+        <v>7477852</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9966,7 +9967,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -11143,10 +11143,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855467</v>
+        <v>124855333</v>
       </c>
       <c r="B103" t="n">
-        <v>98269</v>
+        <v>80064</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11155,25 +11155,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11183,10 +11183,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>855062</v>
+        <v>854924</v>
       </c>
       <c r="R103" t="n">
-        <v>7478002</v>
+        <v>7478087</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11245,10 +11245,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855333</v>
+        <v>124855474</v>
       </c>
       <c r="B104" t="n">
-        <v>80064</v>
+        <v>56828</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11257,25 +11257,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11285,10 +11285,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>854924</v>
+        <v>855065</v>
       </c>
       <c r="R104" t="n">
-        <v>7478087</v>
+        <v>7478197</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11347,10 +11347,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855474</v>
+        <v>124855467</v>
       </c>
       <c r="B105" t="n">
-        <v>56828</v>
+        <v>98269</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11359,25 +11359,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11387,10 +11387,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>855065</v>
+        <v>855062</v>
       </c>
       <c r="R105" t="n">
-        <v>7478197</v>
+        <v>7478002</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427369</v>
+        <v>124427351</v>
       </c>
       <c r="B36" t="n">
-        <v>57793</v>
+        <v>98269</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4171,38 +4171,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>854943</v>
+        <v>855056</v>
       </c>
       <c r="R36" t="n">
-        <v>7478362</v>
+        <v>7478165</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4243,6 +4247,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4261,10 +4266,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427393</v>
+        <v>124427354</v>
       </c>
       <c r="B37" t="n">
-        <v>56828</v>
+        <v>78947</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4277,34 +4282,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>854990</v>
+        <v>855018</v>
       </c>
       <c r="R37" t="n">
-        <v>7478363</v>
+        <v>7478119</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4363,7 +4368,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124427386</v>
+        <v>124427389</v>
       </c>
       <c r="B38" t="n">
         <v>98269</v>
@@ -4398,7 +4403,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4407,10 +4412,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>855066</v>
+        <v>855110</v>
       </c>
       <c r="R38" t="n">
-        <v>7478180</v>
+        <v>7478072</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4470,10 +4475,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124427346</v>
+        <v>124427369</v>
       </c>
       <c r="B39" t="n">
-        <v>80064</v>
+        <v>57793</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4482,38 +4487,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>855044</v>
+        <v>854943</v>
       </c>
       <c r="R39" t="n">
-        <v>7478074</v>
+        <v>7478362</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4572,10 +4577,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124427401</v>
+        <v>124427346</v>
       </c>
       <c r="B40" t="n">
-        <v>82737</v>
+        <v>80064</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4584,38 +4589,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>855011</v>
+        <v>855044</v>
       </c>
       <c r="R40" t="n">
-        <v>7478352</v>
+        <v>7478074</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4674,7 +4679,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124427400</v>
+        <v>124427402</v>
       </c>
       <c r="B41" t="n">
         <v>82737</v>
@@ -4714,10 +4719,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>855012</v>
+        <v>854960</v>
       </c>
       <c r="R41" t="n">
-        <v>7478269</v>
+        <v>7478309</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4776,7 +4781,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124427347</v>
+        <v>124427375</v>
       </c>
       <c r="B42" t="n">
         <v>80064</v>
@@ -4812,14 +4817,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>855063</v>
+        <v>854922</v>
       </c>
       <c r="R42" t="n">
-        <v>7478044</v>
+        <v>7478323</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4860,8 +4865,24 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -4878,10 +4899,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427387</v>
+        <v>124427356</v>
       </c>
       <c r="B43" t="n">
-        <v>98269</v>
+        <v>80063</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4890,42 +4911,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>855102</v>
+        <v>854977</v>
       </c>
       <c r="R43" t="n">
-        <v>7478191</v>
+        <v>7478167</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4966,7 +4983,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4985,10 +5001,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427406</v>
+        <v>124427391</v>
       </c>
       <c r="B44" t="n">
-        <v>91737</v>
+        <v>98269</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5001,41 +5017,38 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>855096</v>
+        <v>855091</v>
       </c>
       <c r="R44" t="n">
-        <v>7478199</v>
+        <v>7478207</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5068,11 +5081,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-24</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På gamal klen sälg.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5100,10 +5108,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427398</v>
+        <v>124427388</v>
       </c>
       <c r="B45" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5112,38 +5120,42 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>855100</v>
+        <v>855074</v>
       </c>
       <c r="R45" t="n">
-        <v>7478058</v>
+        <v>7478164</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5184,6 +5196,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5202,10 +5215,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124427356</v>
+        <v>124427401</v>
       </c>
       <c r="B46" t="n">
-        <v>80063</v>
+        <v>82737</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5214,38 +5227,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>854977</v>
+        <v>855011</v>
       </c>
       <c r="R46" t="n">
-        <v>7478167</v>
+        <v>7478352</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5304,10 +5317,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427365</v>
+        <v>124427393</v>
       </c>
       <c r="B47" t="n">
-        <v>79565</v>
+        <v>56828</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5320,21 +5333,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>102612</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5344,10 +5357,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>854939</v>
+        <v>854990</v>
       </c>
       <c r="R47" t="n">
-        <v>7478324</v>
+        <v>7478363</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5406,10 +5419,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427388</v>
+        <v>124427403</v>
       </c>
       <c r="B48" t="n">
-        <v>98269</v>
+        <v>79963</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5418,42 +5431,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>855074</v>
+        <v>854946</v>
       </c>
       <c r="R48" t="n">
-        <v>7478164</v>
+        <v>7478367</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5513,7 +5522,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124427389</v>
+        <v>124427352</v>
       </c>
       <c r="B49" t="n">
         <v>98269</v>
@@ -5548,19 +5557,19 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>855110</v>
+        <v>855059</v>
       </c>
       <c r="R49" t="n">
-        <v>7478072</v>
+        <v>7478173</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5620,10 +5629,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124427354</v>
+        <v>124427347</v>
       </c>
       <c r="B50" t="n">
-        <v>78947</v>
+        <v>80064</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5632,25 +5641,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5660,10 +5669,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>855018</v>
+        <v>855063</v>
       </c>
       <c r="R50" t="n">
-        <v>7478119</v>
+        <v>7478044</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5722,10 +5731,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124427352</v>
+        <v>124427365</v>
       </c>
       <c r="B51" t="n">
-        <v>98269</v>
+        <v>79565</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5734,42 +5743,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>855059</v>
+        <v>854939</v>
       </c>
       <c r="R51" t="n">
-        <v>7478173</v>
+        <v>7478324</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5810,7 +5815,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5829,10 +5833,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124427402</v>
+        <v>124427386</v>
       </c>
       <c r="B52" t="n">
-        <v>82737</v>
+        <v>98269</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5841,38 +5845,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>854960</v>
+        <v>855066</v>
       </c>
       <c r="R52" t="n">
-        <v>7478309</v>
+        <v>7478180</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5913,6 +5921,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5931,10 +5940,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124427391</v>
+        <v>124427400</v>
       </c>
       <c r="B53" t="n">
-        <v>98269</v>
+        <v>82737</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5943,42 +5952,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855091</v>
+        <v>855012</v>
       </c>
       <c r="R53" t="n">
-        <v>7478207</v>
+        <v>7478269</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6019,7 +6024,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6038,10 +6042,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427375</v>
+        <v>124427399</v>
       </c>
       <c r="B54" t="n">
-        <v>80064</v>
+        <v>78947</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6050,25 +6054,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6078,10 +6082,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>854922</v>
+        <v>855007</v>
       </c>
       <c r="R54" t="n">
-        <v>7478323</v>
+        <v>7478357</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6122,24 +6126,8 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6156,10 +6144,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124427351</v>
+        <v>124427398</v>
       </c>
       <c r="B55" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6168,42 +6156,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>855056</v>
+        <v>855100</v>
       </c>
       <c r="R55" t="n">
-        <v>7478165</v>
+        <v>7478058</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6244,7 +6228,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6263,10 +6246,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124427399</v>
+        <v>124427387</v>
       </c>
       <c r="B56" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6275,38 +6258,42 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>855007</v>
+        <v>855102</v>
       </c>
       <c r="R56" t="n">
-        <v>7478357</v>
+        <v>7478191</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6347,6 +6334,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6365,10 +6353,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124427345</v>
+        <v>124427406</v>
       </c>
       <c r="B57" t="n">
-        <v>80064</v>
+        <v>91737</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6377,38 +6365,45 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6464</v>
+        <v>760</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>854967</v>
+        <v>855096</v>
       </c>
       <c r="R57" t="n">
-        <v>7478177</v>
+        <v>7478199</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6443,12 +6438,18 @@
           <t>2025-04-24</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På gamal klen sälg.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6467,10 +6468,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124427403</v>
+        <v>124427345</v>
       </c>
       <c r="B58" t="n">
-        <v>79963</v>
+        <v>80064</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6483,34 +6484,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6457</v>
+        <v>6464</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>854946</v>
+        <v>854967</v>
       </c>
       <c r="R58" t="n">
-        <v>7478367</v>
+        <v>7478177</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6551,7 +6552,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6570,10 +6570,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855475</v>
+        <v>124855464</v>
       </c>
       <c r="B59" t="n">
-        <v>56828</v>
+        <v>98269</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6582,25 +6582,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>854813</v>
+        <v>854898</v>
       </c>
       <c r="R59" t="n">
-        <v>7477923</v>
+        <v>7478156</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6672,10 +6672,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855423</v>
+        <v>124855277</v>
       </c>
       <c r="B60" t="n">
-        <v>98269</v>
+        <v>80057</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6684,25 +6684,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6712,10 +6712,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>854915</v>
+        <v>855068</v>
       </c>
       <c r="R60" t="n">
-        <v>7477851</v>
+        <v>7478046</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6774,10 +6774,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124854791</v>
+        <v>124855358</v>
       </c>
       <c r="B61" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6786,25 +6786,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>854840</v>
+        <v>854772</v>
       </c>
       <c r="R61" t="n">
-        <v>7477716</v>
+        <v>7477881</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6844,12 +6844,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6858,6 +6863,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6876,10 +6882,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124855420</v>
+        <v>124854791</v>
       </c>
       <c r="B62" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6888,38 +6894,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>855071</v>
+        <v>854840</v>
       </c>
       <c r="R62" t="n">
-        <v>7477912</v>
+        <v>7477716</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6946,12 +6952,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6978,10 +6984,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124855235</v>
+        <v>124855376</v>
       </c>
       <c r="B63" t="n">
-        <v>105278</v>
+        <v>98269</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6990,38 +6996,42 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>854686</v>
+        <v>854741</v>
       </c>
       <c r="R63" t="n">
-        <v>7477923</v>
+        <v>7477958</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7062,6 +7072,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7080,10 +7091,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124855233</v>
+        <v>124855415</v>
       </c>
       <c r="B64" t="n">
-        <v>105278</v>
+        <v>98269</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7092,25 +7103,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7120,10 +7131,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>855073</v>
+        <v>854928</v>
       </c>
       <c r="R64" t="n">
-        <v>7477920</v>
+        <v>7478107</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7182,10 +7193,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124855316</v>
+        <v>124855377</v>
       </c>
       <c r="B65" t="n">
-        <v>97153</v>
+        <v>98269</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7194,38 +7205,42 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>855019</v>
+        <v>854672</v>
       </c>
       <c r="R65" t="n">
-        <v>7477888</v>
+        <v>7477865</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7252,12 +7267,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>I utkanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7266,6 +7286,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7284,10 +7305,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124855483</v>
+        <v>124855231</v>
       </c>
       <c r="B66" t="n">
-        <v>78947</v>
+        <v>105278</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7296,25 +7317,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7324,10 +7345,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>855251</v>
+        <v>854954</v>
       </c>
       <c r="R66" t="n">
-        <v>7478036</v>
+        <v>7478125</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7386,7 +7407,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124855232</v>
+        <v>124855233</v>
       </c>
       <c r="B67" t="n">
         <v>105278</v>
@@ -7426,10 +7447,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>855094</v>
+        <v>855073</v>
       </c>
       <c r="R67" t="n">
-        <v>7477931</v>
+        <v>7477920</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7488,7 +7509,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124855386</v>
+        <v>124855469</v>
       </c>
       <c r="B68" t="n">
         <v>98269</v>
@@ -7521,21 +7542,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854810</v>
+        <v>854979</v>
       </c>
       <c r="R68" t="n">
-        <v>7477930</v>
+        <v>7477885</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7576,7 +7593,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7595,10 +7611,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855466</v>
+        <v>124855244</v>
       </c>
       <c r="B69" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7607,25 +7623,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7635,10 +7651,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>854921</v>
+        <v>855187</v>
       </c>
       <c r="R69" t="n">
-        <v>7478082</v>
+        <v>7478029</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7697,7 +7713,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855464</v>
+        <v>124855467</v>
       </c>
       <c r="B70" t="n">
         <v>98269</v>
@@ -7737,10 +7753,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>854898</v>
+        <v>855062</v>
       </c>
       <c r="R70" t="n">
-        <v>7478156</v>
+        <v>7478002</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7799,7 +7815,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855390</v>
+        <v>124855394</v>
       </c>
       <c r="B71" t="n">
         <v>98269</v>
@@ -7834,7 +7850,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -7843,10 +7859,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>854899</v>
+        <v>854897</v>
       </c>
       <c r="R71" t="n">
-        <v>7477831</v>
+        <v>7477846</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7906,10 +7922,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855512</v>
+        <v>124855398</v>
       </c>
       <c r="B72" t="n">
-        <v>80063</v>
+        <v>98269</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7918,38 +7934,42 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>854911</v>
+        <v>854737</v>
       </c>
       <c r="R72" t="n">
-        <v>7478164</v>
+        <v>7477850</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7976,12 +7996,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7990,6 +8015,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8110,7 +8136,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124855381</v>
+        <v>124855423</v>
       </c>
       <c r="B74" t="n">
         <v>98269</v>
@@ -8150,10 +8176,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>854803</v>
+        <v>854915</v>
       </c>
       <c r="R74" t="n">
-        <v>7477930</v>
+        <v>7477851</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8194,7 +8220,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8213,7 +8238,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124855358</v>
+        <v>124855386</v>
       </c>
       <c r="B75" t="n">
         <v>98269</v>
@@ -8246,17 +8271,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>854772</v>
+        <v>854810</v>
       </c>
       <c r="R75" t="n">
-        <v>7477881</v>
+        <v>7477930</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8289,11 +8318,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8321,10 +8345,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124855524</v>
+        <v>124855275</v>
       </c>
       <c r="B76" t="n">
-        <v>80063</v>
+        <v>92476</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8333,38 +8357,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6463</v>
+        <v>5449</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>854793</v>
+        <v>854889</v>
       </c>
       <c r="R76" t="n">
-        <v>7477805</v>
+        <v>7477847</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8391,12 +8415,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8423,10 +8447,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124855359</v>
+        <v>124855318</v>
       </c>
       <c r="B77" t="n">
-        <v>98269</v>
+        <v>97153</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8435,38 +8459,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>854838</v>
+        <v>854817</v>
       </c>
       <c r="R77" t="n">
-        <v>7477840</v>
+        <v>7477931</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8501,18 +8525,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8531,10 +8549,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124855418</v>
+        <v>124855232</v>
       </c>
       <c r="B78" t="n">
-        <v>98269</v>
+        <v>105278</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8543,25 +8561,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8571,10 +8589,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>855131</v>
+        <v>855094</v>
       </c>
       <c r="R78" t="n">
-        <v>7477924</v>
+        <v>7477931</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8633,10 +8651,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124855249</v>
+        <v>124855421</v>
       </c>
       <c r="B79" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8645,25 +8663,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8673,10 +8691,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>854811</v>
+        <v>854951</v>
       </c>
       <c r="R79" t="n">
-        <v>7477849</v>
+        <v>7477899</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8735,7 +8753,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124855417</v>
+        <v>124855466</v>
       </c>
       <c r="B80" t="n">
         <v>98269</v>
@@ -8775,10 +8793,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>855202</v>
+        <v>854921</v>
       </c>
       <c r="R80" t="n">
-        <v>7477976</v>
+        <v>7478082</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8837,10 +8855,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124855275</v>
+        <v>124855404</v>
       </c>
       <c r="B81" t="n">
-        <v>92476</v>
+        <v>98269</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8849,38 +8867,42 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>854889</v>
+        <v>854832</v>
       </c>
       <c r="R81" t="n">
-        <v>7477847</v>
+        <v>7477880</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8921,6 +8943,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8939,10 +8962,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124855364</v>
+        <v>124855482</v>
       </c>
       <c r="B82" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8951,38 +8974,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>855120</v>
+        <v>855134</v>
       </c>
       <c r="R82" t="n">
-        <v>7477887</v>
+        <v>7477890</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9017,18 +9040,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9047,10 +9064,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855404</v>
+        <v>124855249</v>
       </c>
       <c r="B83" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9059,42 +9076,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>854832</v>
+        <v>854811</v>
       </c>
       <c r="R83" t="n">
-        <v>7477880</v>
+        <v>7477849</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9135,7 +9148,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9154,10 +9166,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855366</v>
+        <v>124855313</v>
       </c>
       <c r="B84" t="n">
-        <v>98269</v>
+        <v>91459</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9166,42 +9178,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>854807</v>
+        <v>854814</v>
       </c>
       <c r="R84" t="n">
-        <v>7477926</v>
+        <v>7477852</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9242,7 +9250,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9261,10 +9268,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124855244</v>
+        <v>124855389</v>
       </c>
       <c r="B85" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9273,38 +9280,42 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>855187</v>
+        <v>854906</v>
       </c>
       <c r="R85" t="n">
-        <v>7478029</v>
+        <v>7477891</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9345,6 +9356,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9363,10 +9375,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855317</v>
+        <v>124855371</v>
       </c>
       <c r="B86" t="n">
-        <v>97153</v>
+        <v>98269</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9375,38 +9387,42 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>854783</v>
+        <v>854845</v>
       </c>
       <c r="R86" t="n">
-        <v>7477935</v>
+        <v>7477869</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9447,6 +9463,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9465,10 +9482,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855482</v>
+        <v>124855500</v>
       </c>
       <c r="B87" t="n">
-        <v>78947</v>
+        <v>79963</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9477,25 +9494,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9505,10 +9522,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>855134</v>
+        <v>854850</v>
       </c>
       <c r="R87" t="n">
-        <v>7477890</v>
+        <v>7477915</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9567,10 +9584,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855416</v>
+        <v>124855524</v>
       </c>
       <c r="B88" t="n">
-        <v>98269</v>
+        <v>80063</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9579,25 +9596,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9607,10 +9624,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>855002</v>
+        <v>854793</v>
       </c>
       <c r="R88" t="n">
-        <v>7478149</v>
+        <v>7477805</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9637,12 +9654,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9669,10 +9686,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124854790</v>
+        <v>124855333</v>
       </c>
       <c r="B89" t="n">
-        <v>98269</v>
+        <v>80064</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9681,42 +9698,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>854766</v>
+        <v>854924</v>
       </c>
       <c r="R89" t="n">
-        <v>7478012</v>
+        <v>7478087</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9757,7 +9770,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9776,7 +9788,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124855389</v>
+        <v>124855417</v>
       </c>
       <c r="B90" t="n">
         <v>98269</v>
@@ -9809,21 +9821,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>854906</v>
+        <v>855202</v>
       </c>
       <c r="R90" t="n">
-        <v>7477891</v>
+        <v>7477976</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9864,7 +9872,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9883,10 +9890,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124855250</v>
+        <v>124855512</v>
       </c>
       <c r="B91" t="n">
-        <v>91166</v>
+        <v>80063</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9895,25 +9902,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9923,10 +9930,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>854814</v>
+        <v>854911</v>
       </c>
       <c r="R91" t="n">
-        <v>7477852</v>
+        <v>7478164</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9985,10 +9992,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124855318</v>
+        <v>124855364</v>
       </c>
       <c r="B92" t="n">
-        <v>97153</v>
+        <v>98269</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9997,38 +10004,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>854817</v>
+        <v>855120</v>
       </c>
       <c r="R92" t="n">
-        <v>7477931</v>
+        <v>7477887</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10063,12 +10070,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10087,7 +10100,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124855380</v>
+        <v>124855420</v>
       </c>
       <c r="B93" t="n">
         <v>98269</v>
@@ -10127,10 +10140,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>854745</v>
+        <v>855071</v>
       </c>
       <c r="R93" t="n">
-        <v>7477946</v>
+        <v>7477912</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10171,7 +10184,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10190,7 +10202,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855376</v>
+        <v>124855468</v>
       </c>
       <c r="B94" t="n">
         <v>98269</v>
@@ -10223,21 +10235,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>854741</v>
+        <v>855069</v>
       </c>
       <c r="R94" t="n">
-        <v>7477958</v>
+        <v>7477999</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10278,7 +10286,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10297,10 +10304,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855313</v>
+        <v>124855475</v>
       </c>
       <c r="B95" t="n">
-        <v>91459</v>
+        <v>56828</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10313,21 +10320,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10337,10 +10344,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>854814</v>
+        <v>854813</v>
       </c>
       <c r="R95" t="n">
-        <v>7477852</v>
+        <v>7477923</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10399,10 +10406,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855377</v>
+        <v>124855483</v>
       </c>
       <c r="B96" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10411,42 +10418,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>854672</v>
+        <v>855251</v>
       </c>
       <c r="R96" t="n">
-        <v>7477865</v>
+        <v>7478036</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10473,17 +10476,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>I utkanten av nytt hygge</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10492,7 +10490,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10511,7 +10508,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124855415</v>
+        <v>124855359</v>
       </c>
       <c r="B97" t="n">
         <v>98269</v>
@@ -10547,14 +10544,14 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>854928</v>
+        <v>854838</v>
       </c>
       <c r="R97" t="n">
-        <v>7478107</v>
+        <v>7477840</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10589,12 +10586,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10613,10 +10616,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124855277</v>
+        <v>124855390</v>
       </c>
       <c r="B98" t="n">
-        <v>80057</v>
+        <v>98269</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10625,38 +10628,42 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>855068</v>
+        <v>854899</v>
       </c>
       <c r="R98" t="n">
-        <v>7478046</v>
+        <v>7477831</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10697,6 +10704,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10715,7 +10723,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124855371</v>
+        <v>124855381</v>
       </c>
       <c r="B99" t="n">
         <v>98269</v>
@@ -10748,21 +10756,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>854845</v>
+        <v>854803</v>
       </c>
       <c r="R99" t="n">
-        <v>7477869</v>
+        <v>7477930</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10822,10 +10826,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124855421</v>
+        <v>124855316</v>
       </c>
       <c r="B100" t="n">
-        <v>98269</v>
+        <v>97153</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10834,25 +10838,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10862,10 +10866,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>854951</v>
+        <v>855019</v>
       </c>
       <c r="R100" t="n">
-        <v>7477899</v>
+        <v>7477888</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10924,7 +10928,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855398</v>
+        <v>124855416</v>
       </c>
       <c r="B101" t="n">
         <v>98269</v>
@@ -10957,21 +10961,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>854737</v>
+        <v>855002</v>
       </c>
       <c r="R101" t="n">
-        <v>7477850</v>
+        <v>7478149</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10998,17 +10998,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11017,7 +11012,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11036,7 +11030,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124855394</v>
+        <v>124855366</v>
       </c>
       <c r="B102" t="n">
         <v>98269</v>
@@ -11071,7 +11065,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>167</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -11080,10 +11074,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>854897</v>
+        <v>854807</v>
       </c>
       <c r="R102" t="n">
-        <v>7477846</v>
+        <v>7477926</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11143,10 +11137,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855333</v>
+        <v>124855317</v>
       </c>
       <c r="B103" t="n">
-        <v>80064</v>
+        <v>97153</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11159,21 +11153,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6464</v>
+        <v>221941</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11183,10 +11177,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>854924</v>
+        <v>854783</v>
       </c>
       <c r="R103" t="n">
-        <v>7478087</v>
+        <v>7477935</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11245,10 +11239,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855474</v>
+        <v>124855418</v>
       </c>
       <c r="B104" t="n">
-        <v>56828</v>
+        <v>98269</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11257,25 +11251,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11285,10 +11279,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>855065</v>
+        <v>855131</v>
       </c>
       <c r="R104" t="n">
-        <v>7478197</v>
+        <v>7477924</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11347,7 +11341,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855467</v>
+        <v>124854790</v>
       </c>
       <c r="B105" t="n">
         <v>98269</v>
@@ -11380,17 +11374,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>855062</v>
+        <v>854766</v>
       </c>
       <c r="R105" t="n">
-        <v>7478002</v>
+        <v>7478012</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11431,6 +11429,7 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11449,10 +11448,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855500</v>
+        <v>124855250</v>
       </c>
       <c r="B106" t="n">
-        <v>79963</v>
+        <v>91166</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11461,25 +11460,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6457</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11489,10 +11488,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>854850</v>
+        <v>854814</v>
       </c>
       <c r="R106" t="n">
-        <v>7477915</v>
+        <v>7477852</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11551,10 +11550,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855231</v>
+        <v>124855380</v>
       </c>
       <c r="B107" t="n">
-        <v>105278</v>
+        <v>98269</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11563,25 +11562,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11591,10 +11590,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>854954</v>
+        <v>854745</v>
       </c>
       <c r="R107" t="n">
-        <v>7478125</v>
+        <v>7477946</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11635,6 +11634,7 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11653,10 +11653,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855469</v>
+        <v>124855474</v>
       </c>
       <c r="B108" t="n">
-        <v>98269</v>
+        <v>56828</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11665,25 +11665,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11693,10 +11693,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>854979</v>
+        <v>855065</v>
       </c>
       <c r="R108" t="n">
-        <v>7477885</v>
+        <v>7478197</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11755,10 +11755,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855468</v>
+        <v>124855235</v>
       </c>
       <c r="B109" t="n">
-        <v>98269</v>
+        <v>105278</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11767,25 +11767,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11795,10 +11795,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>855069</v>
+        <v>854686</v>
       </c>
       <c r="R109" t="n">
-        <v>7477999</v>
+        <v>7477923</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124427351</v>
+        <v>124427354</v>
       </c>
       <c r="B36" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4171,42 +4171,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>855056</v>
+        <v>855018</v>
       </c>
       <c r="R36" t="n">
-        <v>7478165</v>
+        <v>7478119</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4247,7 +4243,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4266,10 +4261,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124427354</v>
+        <v>124427351</v>
       </c>
       <c r="B37" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4278,38 +4273,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>855018</v>
+        <v>855056</v>
       </c>
       <c r="R37" t="n">
-        <v>7478119</v>
+        <v>7478165</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4350,6 +4349,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124427356</v>
+        <v>124427391</v>
       </c>
       <c r="B43" t="n">
-        <v>80063</v>
+        <v>98269</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4911,38 +4911,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>854977</v>
+        <v>855091</v>
       </c>
       <c r="R43" t="n">
-        <v>7478167</v>
+        <v>7478207</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4983,6 +4987,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5001,7 +5006,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124427391</v>
+        <v>124427388</v>
       </c>
       <c r="B44" t="n">
         <v>98269</v>
@@ -5036,7 +5041,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>73</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5045,10 +5050,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>855091</v>
+        <v>855074</v>
       </c>
       <c r="R44" t="n">
-        <v>7478207</v>
+        <v>7478164</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5108,10 +5113,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124427388</v>
+        <v>124427356</v>
       </c>
       <c r="B45" t="n">
-        <v>98269</v>
+        <v>80063</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5120,42 +5125,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>855074</v>
+        <v>854977</v>
       </c>
       <c r="R45" t="n">
-        <v>7478164</v>
+        <v>7478167</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5196,7 +5197,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5317,10 +5317,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427393</v>
+        <v>124427403</v>
       </c>
       <c r="B47" t="n">
-        <v>56828</v>
+        <v>79963</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5329,25 +5329,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102612</v>
+        <v>6457</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>854990</v>
+        <v>854946</v>
       </c>
       <c r="R47" t="n">
-        <v>7478363</v>
+        <v>7478367</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5401,6 +5401,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5419,10 +5420,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124427403</v>
+        <v>124427393</v>
       </c>
       <c r="B48" t="n">
-        <v>79963</v>
+        <v>56828</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5431,25 +5432,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6457</v>
+        <v>102612</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5459,10 +5460,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>854946</v>
+        <v>854990</v>
       </c>
       <c r="R48" t="n">
-        <v>7478367</v>
+        <v>7478363</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5503,7 +5504,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -8962,10 +8962,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124855482</v>
+        <v>124855249</v>
       </c>
       <c r="B82" t="n">
-        <v>78947</v>
+        <v>91166</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8978,21 +8978,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9002,10 +9002,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>855134</v>
+        <v>854811</v>
       </c>
       <c r="R82" t="n">
-        <v>7477890</v>
+        <v>7477849</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9064,10 +9064,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124855249</v>
+        <v>124855313</v>
       </c>
       <c r="B83" t="n">
-        <v>91166</v>
+        <v>91459</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9080,21 +9080,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9104,10 +9104,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>854811</v>
+        <v>854814</v>
       </c>
       <c r="R83" t="n">
-        <v>7477849</v>
+        <v>7477852</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9166,10 +9166,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124855313</v>
+        <v>124855482</v>
       </c>
       <c r="B84" t="n">
-        <v>91459</v>
+        <v>78947</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9182,21 +9182,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9206,10 +9206,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>854814</v>
+        <v>855134</v>
       </c>
       <c r="R84" t="n">
-        <v>7477852</v>
+        <v>7477890</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11137,10 +11137,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855317</v>
+        <v>124855418</v>
       </c>
       <c r="B103" t="n">
-        <v>97153</v>
+        <v>98269</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11149,25 +11149,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11177,10 +11177,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>854783</v>
+        <v>855131</v>
       </c>
       <c r="R103" t="n">
-        <v>7477935</v>
+        <v>7477924</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11239,7 +11239,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855418</v>
+        <v>124854790</v>
       </c>
       <c r="B104" t="n">
         <v>98269</v>
@@ -11272,17 +11272,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>855131</v>
+        <v>854766</v>
       </c>
       <c r="R104" t="n">
-        <v>7477924</v>
+        <v>7478012</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11323,6 +11327,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11341,10 +11346,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124854790</v>
+        <v>124855317</v>
       </c>
       <c r="B105" t="n">
-        <v>98269</v>
+        <v>97153</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11353,42 +11358,38 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>854766</v>
+        <v>854783</v>
       </c>
       <c r="R105" t="n">
-        <v>7478012</v>
+        <v>7477935</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11429,7 +11430,6 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9402-2025 artfynd.xlsx
+++ b/artfynd/A 9402-2025 artfynd.xlsx
@@ -6672,10 +6672,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855277</v>
+        <v>124855358</v>
       </c>
       <c r="B60" t="n">
-        <v>80057</v>
+        <v>98269</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6684,38 +6684,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>855068</v>
+        <v>854772</v>
       </c>
       <c r="R60" t="n">
-        <v>7478046</v>
+        <v>7477881</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6750,12 +6750,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6774,10 +6780,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124855358</v>
+        <v>124855277</v>
       </c>
       <c r="B61" t="n">
-        <v>98269</v>
+        <v>80057</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6786,38 +6792,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>854772</v>
+        <v>855068</v>
       </c>
       <c r="R61" t="n">
-        <v>7477881</v>
+        <v>7478046</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6852,18 +6858,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
